--- a/GOWT_mid_low.xlsx
+++ b/GOWT_mid_low.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTE Tracking" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2 2026 News" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FTE Tracking'!$A$1:$L$854</definedName>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="\+#,##0;\-#,##0;0"/>
     <numFmt numFmtId="165" formatCode="\+0.0%;\-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +74,13 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +105,14 @@
         <bgColor rgb="FFEBF1F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,11 +135,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -147,6 +173,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -41313,4 +41346,2064 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>News Articles</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>LinkedIn Posts</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>2 Steps</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>2Steps positions itself as a global leader in synthetic user journey monitoring (15/03/2024)
+2Steps, a Melbourne-based software company, highlighted its global growth ambitions by branding itself a "global leader in synthetic monitoring" and expanding support for complex multi-factor and two-factor authentication user journeys across web and desktop applications. This product expansion signals increased enterprise adoption and a broader international customer base for its no‑code monitoring platform.
+2 Steps scales team and operations as demand for synthetic monitoring grows (10/11/2023)
+Company data compiled by Prospeo shows that Melbourne-headquartered 2 Steps increased its headcount to an estimated 11–20 employees and continues to grow its workforce to support business operations and expansion. The same profile estimates annual revenue of about US$941,105 and a valuation of roughly US$3.1 million, indicating steady commercial traction in the computer software sector without external funding.</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr"/>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/2-steps/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2IQ (Christchurch, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>MyIQ featured in NZ Entrepreneur (01/10/2021)
+2IQ’s MyIQ product was featured in NZ Entrepreneur as the Christchurch company prepared to expand into Australia, with plans to target additional markets including the UK and Canada. The article highlights the company’s growth trajectory and wider international expansion ambitions.
+Hospitality sector raises a glass to cloud-based analytics as it roars back to life (01/09/2021)
+Microsoft covered 2IQ’s hospitality analytics platform, hospoIQ, noting that the company had launched MyIQ and was beginning to win customers in Australia. The article points to product expansion and early international customer traction for the Christchurch-based business.
+Exporting Innovation: NZ HealthTech Part 1 of 3 (01/03/2021)
+A Talking HealthTech podcast episode featured 2iQ Health CEO Nick Burns discussing capacity planning and efficiency in healthcare. The discussion suggests ongoing product development and market positioning for the New Zealand company’s healthtech offering.</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr"/>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/2iq/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>365mesh</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>365mesh becomes first ecosystem provider to join Dicker Data’s AI Accelerate practice (17/04/2025)
+365mesh was named the first ecosystem provider in Dicker Data’s new AI Accelerate practice, giving the company a channel to expand its AI and IoT solutions across Australia and New Zealand. The partnership highlights 365mesh’s expertise and supports broader go-to-market growth for its prebuilt AI offerings.
+365mesh launches updated Aussie-made vibration sensor (18/03/2025)
+365mesh announced the second version of its AmbientAI-V vibration sensor, manufactured entirely in Australia. The release highlights expanded local production capabilities, research design labs across Australia and New Zealand, and a growing deployment footprint, including a win to supply monitoring products for the Canberra Light Rail project.
+365mesh wins CRN Fast50 2024 for exceptional year-on-year growth (01/11/2024)
+365mesh was awarded first place in the CRN Fast50 2024, recognizing its exceptional year-on-year growth and continued delivery of advanced IT and digital solutions. The company also noted ongoing investment in local production and research and development capabilities.
+365mesh recognized as finalist in Australian AI Awards for healthcare and aged care solution (01/11/2024)
+365mesh was named a finalist in the Australian AI Awards for Healthdeck and CareTrack, reflecting product development momentum in healthcare and aged care. The recognition suggests continued expansion of its AI-powered IoT portfolio into new sectors.
+365mesh named finalist in Australian AI Awards for Greenmesh industrial monitoring solution (01/11/2024)
+365mesh was shortlisted in the Australian AI Awards for Greenmesh, its IoT solution for construction, heavy machinery and mining. The finalist status points to growing market traction and industry expansion for the company’s workplace safety and monitoring products.</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/365mesh/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>3Columns</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>3Columns positions itself as an end-to-end cybersecurity company serving Australia and New Zealand (19/05/2026)
+3Columns’ company profile highlights its focus on expanding cyber security coverage across Australia and New Zealand, offering end-to-end information security services and emphasizing long-standing client partnerships. This indicates ongoing business growth through broader market reach and service expansion.
+3Columns presents a broader cyber security offering for businesses across Australia and New Zealand (19/05/2026)
+The company’s website describes a comprehensive suite of cyber security solutions designed to provide 360-degree protection from cyber threats. Positioning itself as an end-to-end provider suggests growth through service-line expansion and increased market penetration.
+3Columns expands visibility through industry directory listings and client reviews (19/05/2026)
+Third-party business listings such as ZoomInfo and DesignRush profile 3Columns as an established cybersecurity provider in Sydney with an active market presence. While not a traditional news announcement, these listings reflect continued commercial visibility and reputation-building in the market.</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3columns/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>AABDL (Sydney)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>No clearly verified growth news articles found for AABDL in Sydney (01/01/1970)
+I could not reliably identify any news articles specifically about AABDL in Sydney showing growth signals such as awards, expansion, new hires, partnerships, patents, or financial success. The available search results were about the broader Australian department stores sector or other companies, not this specific company.
+No clearly verified growth news articles found for AABDL in Sydney (01/01/1970)
+I could not reliably identify any news articles specifically about AABDL in Sydney showing growth signals such as awards, expansion, new hires, partnerships, patents, or financial success. The available search results were about the broader Australian department stores sector or other companies, not this specific company.
+No clearly verified growth news articles found for AABDL in Sydney (01/01/1970)
+I could not reliably identify any news articles specifically about AABDL in Sydney showing growth signals such as awards, expansion, new hires, partnerships, patents, or financial success. The available search results were about the broader Australian department stores sector or other companies, not this specific company.
+No clearly verified growth news articles found for AABDL in Sydney (01/01/1970)
+I could not reliably identify any news articles specifically about AABDL in Sydney showing growth signals such as awards, expansion, new hires, partnerships, patents, or financial success. The available search results were about the broader Australian department stores sector or other companies, not this specific company.
+No clearly verified growth news articles found for AABDL in Sydney (01/01/1970)
+I could not reliably identify any news articles specifically about AABDL in Sydney showing growth signals such as awards, expansion, new hires, partnerships, patents, or financial success. The available search results were about the broader Australian department stores sector or other companies, not this specific company.</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr"/>
+      <c r="E6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>AT Group</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Acuite Construction Intelligence</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Acuite Construction Intelligence closes million‑dollar funding round and emerges as top APAC construction tech startup (10/03/2021)
+Construction Tech Review profiles Acuite Construction Intelligence as a ‘Top Construction Tech Startup in APAC 2021,’ noting that the firm had recently closed a million‑dollar funding round while still barely out of beta‑testing. The recognition underscores investor confidence and regional market traction for Acuite’s data‑driven construction management platform, which aggregates project information into central dashboards to improve operational performance.
+Kiwi business Acuite Construction Intelligence manages accelerated growth with backing from Ice Angels and ArcAngels (15/07/2020)
+Acuite Construction Intelligence, founded in 2014 in Auckland and Melbourne, reports it is managing accelerated business growth while navigating COVID‑19 conditions. The company highlights that it secured NZ$500,000 in seed investment from investor networks Ice Angels and ArcAngels, funding that has supported development and scaling of its construction intelligence platform that automates reporting and delivers real‑time visibility for large construction projects.
+Acuite forms strategic partnership with photoSentinel to enhance construction project insights (26/11/2019)
+Acuite Construction Intelligence secures a strategic partnership with Australian time‑lapse services leader photoSentinel. The collaboration integrates time‑lapse imagery with Acuite’s project intelligence platform, promising richer visual and data insights for construction clients across Australasia, and marking another step in Acuite’s growth and market penetration in Australia.
+Acuite co‑founders spearhead expansion into Australian market (20/02/2019)
+New Zealand construction software company Acuite Construction Intelligence announces a significant expansion push into Australia. Co‑founder David Speight relocates from Auckland to lead the exporting drive, positioning the company to grow its presence and customer base across the Australian construction sector while leveraging its real‑time project intelligence platform.</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/acuite/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide Paediatrics</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>[05/05/2026 - 1w] Announcement of multiple clinic locations for Adelaide Paediatrics, enhancing access to care.</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adelaide-paediatrics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Advance Rehab Centre</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Advance Rehab Centre featured on Channel 10’s The Project for innovative Parkinson’s rehabilitation (12/06/2025)
+Advance Rehab Centre was featured on Channel 10’s ‘The Project’ through the story of clients Emma and Martin, highlighting the clinic’s specialised young-onset Parkinson’s rehabilitation programs. The national TV coverage showcases ARC’s advanced neurophysiotherapy expertise in Sydney and reinforces its positioning as an award‑winning, leading neurological and disability rehabilitation provider, supporting further demand and service expansion.
+Advance Rehab Centre CEO advocates for neurological rehabilitation in national NDIS reform debate (01/05/2025)
+Advance Rehab Centre’s CEO, Melissa McConaghy, appeared on Sky News Australia to argue for the protection and expansion of funding for neurological rehabilitation services under proposed NDIS changes. The media appearance positions the Sydney-based allied health provider as a leading national voice in neuro and disability rehab, helping to raise the organisation’s profile and support continued service growth in Artarmon, Hurstville, and community-based programs.
+Advance Rehab Centre recognised as Sydney’s award‑winning neurological and disability rehabilitation provider (01/03/2024)
+Advance Rehab Centre describes itself as Sydney’s award‑winning neurological and disability rehabilitation provider, reflecting industry recognition for its multidisciplinary allied health team and specialist neuro services. This positioning, referenced across its media and project archives, indicates sustained reputation growth and likely underpins continued client demand and organisational development.
+Advance Rehab Centre grows multi‑site footprint with clinics in Artarmon and Hurstville and expanded community services (01/02/2024)
+Originally established in 2006, Advance Rehab Centre now operates neurological rehabilitation clinics in both Artarmon and Hurstville in Sydney and has expanded into community-based care via home visits. The multi‑site clinic network and outreach model reflect steady service expansion and organisational growth in the allied health sector.
+Advance Rehab Centre selected as an official PD Warrior licensee for Parkinson’s rehabilitation in Hurstville (01/09/2023)
+Advance Rehab Centre’s Hurstville clinic was listed as an official PD Warrior licensee, delivering a specialised exercise-based program for people living with Parkinson’s disease. Securing this recognised international program signals strategic service expansion, strengthens ARC’s Parkinson’s offering in Sydney, and enhances its competitive position in neurological allied health services.</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr"/>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/advance-rehab-centre/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Aerofloat</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Aerofloat Wins Overall Excellence in Business at Growth Potential Awards (19/04/2024)
+Aerofloat, the Australian wastewater treatment specialist based in Taren Point, Sydney, won the Overall Excellence in Business award at the Growth Potential Awards. The accolade recognises the company’s strong business performance, rapid growth in recent years, and its commitment to staff, clients and the broader Australian wastewater industry. The recognition adds to Aerofloat’s track record of awards, including a Consensus GreenTech Award and an AusIndustry Accelerating Commercialisation Grant, underscoring the company’s continued expansion and industry leadership.
+Aerofloat Secures Contract to Design and Build Wastewater Treatment Plants for New Sydney Fish Market (06/02/2023)
+Aerofloat was awarded the contract to design and construct two wastewater treatment plants for the new Sydney Fish Market development. The project win expands Aerofloat’s portfolio of high‑profile infrastructure projects and demonstrates growing market confidence in its design-and-build capabilities for complex wastewater systems in major commercial developments.
+Aerofloat Supports v2food’s Production Growth with Scalable Wastewater Treatment System (14/09/2022)
+Aerofloat designed and implemented a sustainable, easy‑to‑operate wastewater treatment system for plant-based food producer v2food to accommodate its production growth. The project included remote monitoring and operational flexibility, highlighting Aerofloat’s growing presence in the food manufacturing sector and its ability to scale solutions for rapidly expanding clients.
+Aerofloat Delivers Upgraded Sewage Treatment Plant to Enable Growth at Ballina Beach Village (03/03/2021)
+Aerofloat was engaged by Ballina Beach Village to design and install a sewage treatment plant capable of meeting the holiday park’s increased visitation and future growth. The project reflects Aerofloat’s expanding role in providing modular, scalable sewage treatment solutions for tourism and remote accommodation sites across Australia.
+Aerofloat Pioneers Wastewater Treatment Technology for Australia’s Plastics Recycling Industry (15/07/2020)
+Aerofloat has established itself as a leading provider of wastewater and washwater treatment systems for the Australian plastics recycling industry, with numerous plants installed nationwide since 2015. The company’s innovative dissolved air flotation designs, award‑winning technology, and work with major plastics recyclers demonstrate significant sectoral expansion and reinforce Aerofloat’s position as a key technology partner in the circular economy.
+Aerofloat Grows from Startup to National Provider of Innovative Wastewater Treatment Systems (01/11/2019)
+Since its founding in 2009, Aerofloat has expanded from a startup into a national provider of industrial wastewater and sewage treatment systems, serving multiple industries across Australia. The company’s growth is driven by proprietary designs, in‑house manufacturing, and an expanding team of specialist engineers, positioning Aerofloat as a leading environmental services provider in the wastewater sector.</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>[28/04/2026 - 2w] A post announcing the completion of a biological wastewater treatment plant, showcasing significant project development.
+[28/04/2026 - 2w] Introducing Aerofloat's largest project to date, a biological wastewater treatment plant, highlighting project achievement within six months.</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aerofloat-australia-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Agen (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr"/>
+      <c r="E12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>AgriWebb</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>AgriWebb secures AUD$11M for beef cattle management software (30/04/2024)
+AgriWebb announced it secured AUD$11 million (US$7.3 million) in growth funding from existing investors Germin8 Ventures, Grosvenor Food &amp; AgTech and Telus Ventures, plus new backer Munters Group. The capital will be used to enhance the platform and strengthen its ability to connect on‑farm data with global food brands and retailers amid tightening climate and sustainability regulations such as California’s SB253 and the EU Green Deal. The company reported it now tracks more than 23 million head of livestock across 150 million acres in 18 countries, having added 2 million animals in only five months.
+Ahead of the herd: livestock management platform AgriWebb raises $11 million (29/04/2024)
+Sydney-based agtech AgriWebb closed an oversubscribed $11 million funding round from existing investors Germin8 Ventures, Grosvenor Food &amp; AgTech and Telus Ventures, alongside new investor Munters Group. The company, founded in 2014, now tracks more than 23 million head of livestock for 16,000 users across over 150 million acres in 18 countries, with a dominant presence in Australia, the UK, the US and Brazil. Management said ARR, customer base and margins have all grown strongly, with livestock on the platform rising from 21 million to 23 million in just five months.
+AgriWebb lands sustainability data deal with global beef supply chain leaders including McDonald’s (15/09/2023)
+AgriWebb disclosed that it secured a major sustainability data partnership with some of the world’s largest beef suppliers and buyers, including fast‑food giant McDonald’s. Its software is now used across hundreds of US ranches to track and demonstrate reductions in carbon emissions toward 2030 targets. The deal positions AgriWebb as a key data and reporting infrastructure provider for global beef supply chains responding to new climate and sustainability requirements.
+AgriWebb passes 20 million head on platform and appoints new CEO to lead global expansion (15/02/2023)
+Profile and company update data indicate that AgriWebb surpassed 20 million animals managed on its platform across roughly 150 million acres and more than 16,000 individual farmer users. The company also appointed Anna Baird as Chief Executive Officer to drive its next phase of growth in the US, UK, and European markets, signalling a focus on scaling operations and deepening penetration in key export-oriented beef and sheep regions.
+AgriWebb raises $30 million to drive sustainable livestock management (19/01/2021)
+AgriWebb completed a $30 million funding round led by TELUS, marking one of the largest private agtech raises in Australia in 2021. The capital was earmarked to accelerate development of its digital livestock management solutions, improve farm productivity, and support expansion into international markets including the US and UK. The round underpinned AgriWebb’s strategy to scale its SaaS platform and embed sustainability and emissions‑reduction capabilities for global livestock producers.</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 4d] The event facilitated valuable discussions on farm management and showcased AgriWebb's livestock management technology, supporting industry partnerships.
+[08/05/2026 - 1w] Co-Founder John Fargher discusses AgriWebb's global impact on agriculture and the future of farm data in a podcast.
+[05/05/2026 - 1w] The company is collaborating with The Wendy's Company on the Legacy Landscapes program, enhancing practices for family ranches.
+[27/04/2026 - 3w] The post highlights a collaboration at the USRSB General Assembly, with discussions focused on industry-wide goals in the beef supply chain.
+[24/04/2026 - 3w] AgriWebb representatives spoke at the USRSB General Assembly, focusing on partnerships and sustainable practices in the beef supply chain.
+[21/04/2026 - 3w] Te Pari’s Macrostock Scale integrates with AgriWebb, allowing fans to capture live data for improved efficiency and accuracy in livestock management.</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/agriwebb/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Ailo</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>LJ Hooker Partners with Ailo to Boost Property Management Efficiency (18/05/2026)
+LJ Hooker announced a partnership with Sydney-based Ailo to streamline property management operations across its franchise network. The deal is aimed at reducing administrative workloads, lowering arrears, improving client satisfaction, and creating new business opportunities through Ailo’s all-in-one platform.
+Ailo blog: Customer story highlights business growth at Apex Property Management (18/05/2026)
+Ailo published a customer story showing how Apex Property Management in Sydney is using Ailo to drive new business growth, reduce costs, and increase capacity. While framed as a customer case study, it supports Ailo’s growth narrative through product adoption and customer outcomes.</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>[28/04/2026 - 2w] Ailo is sponsoring the REIWA Connect Real Estate Conference, aiming to connect with clients and potential new customers.
+[18/04/2026 - 1mo] Hayden Potts discusses the launch of PRD Northern Beaches using Ailo, achieving over 100 property managements without a legacy system.</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ailo/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Air Communications (110 Mulgul Rd, Malaga, WA 6090, Australia)</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Western Australia</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr"/>
+      <c r="D15" s="17" t="inlineStr"/>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aircommunications/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Alcolizer Technology</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Alcolizer Technology – driving innovation in drug and alcohol testing (01/03/2024)
+Government case study profiling Alcolizer Technology (Alcolizer Pty Ltd), headquartered in Perth, as a long‑standing provider of fast, accurate alcohol and drug testing solutions. The article highlights the company’s growth from wall‑mounted breath testers for clubs and pubs to becoming a trusted supplier to Australian law enforcement, offering onsite testing nationally and exporting products internationally. It notes their use of real‑time testing data analytics and their ongoing R&amp;D supported by the Research and Development Tax Incentive, indicating continued innovation‑led expansion.
+Alcolizer Technology recognised as a world‑leading, innovative alcohol and drug testing manufacturer (01/06/2023)
+A Transafe WA profile describes Alcolizer Technology, based in Perth, as one of the world’s leading manufacturers of alcohol breath testing and drug test devices and as one of Australia’s most innovative and forward‑thinking companies. The recognition, in the context of industry safety and transport, highlights Alcolizer’s established market presence, ongoing innovation and leadership in workplace and roadside testing—indicators of sustained growth and strong positioning within the security and investigation services ecosystem.
+$750K manufacturing scale‑up with Federal Government grant for COVID‑19 antibody tests (15/07/2020)
+Alcolizer Technology secured a $750,000 Federal Government Manufacturing Modernisation Fund grant to scale up local production of Australia’s first domestically manufactured COVID‑19 antibody test from 900 to 20,000 units per day. The funding enabled major manufacturing upgrades at the company’s Balcatta facility in Perth, including new robotic strip manufacturing technology for fully automated production and packaging. Transitioning from saliva to blood‑based testing and advancing prototypes toward clinical trials demonstrates significant R&amp;D, capacity expansion and diversification of Alcolizer’s product portfolio.
+Alcolizer now supplying majority of Australian law enforcement with LE5 breathalyser (15/11/2019)
+Alcolizer Technology announced that its Australian‑made LE5 breathalyser, assembled and calibrated at its Balcatta headquarters in Perth, is now used by the majority of law‑enforcement agencies across Australia. Components are manufactured in Brisbane, Melbourne and Adelaide and then integrated in Western Australia, reflecting a distributed but growing national manufacturing footprint. Achieving majority market penetration in the law‑enforcement segment signals substantial sales growth, increased production volumes and strengthened brand dominance in alcohol testing for public‑safety and security applications.
+Alcolizer Technology awarded Western Australia Police contract to deliver breathalysers (10/09/2018)
+Alcolizer Technology, headquartered in Perth, was awarded the Western Australia Police contract to supply breathalysers for roadside testing. The win strengthens the company’s position as a world‑leading manufacturer of alcohol and drug testing devices and underscores its reputation as one of Australia’s most innovative and forward‑thinking businesses. Securing a major state‑wide law‑enforcement contract represents both revenue growth and increased market share within the security and public‑safety testing segment.</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>[20/04/2026 - 4w] Announces the acquisition of ToxLogic, enhancing capabilities in drug testing and indicating company growth.</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alcolizer/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>AlertForce Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Orange Line caps off 2025 with AlertForce SEO win (19/12/2025)
+Consulting-led digital marketing agency Orange Line has won AlertForce’s SEO account following a competitive pitch. The Sydney-based agency will deliver all SEO services for AlertForce, supporting the WHS training provider’s nationwide growth ambitions across transport, building and construction sectors. The move signals AlertForce’s investment in digital marketing to scale its nationally recognised silica awareness, asbestos and other compliance training offerings.
+AlertForce grows silica and asbestos awareness training as national compliance demand rises (15/03/2024)
+AlertForce has expanded its portfolio and positioning as a national leader in online silica and asbestos awareness training, offering nationally recognised courses that help businesses meet mandatory WHS compliance requirements across Australia. Its focus on scalable online delivery and small‑business‑friendly training highlights growth in its e‑learning operations and its role as a key compliance training provider in construction and related industries.
+AlertForce strengthens national profile as leading OHS/WHS training provider (01/08/2023)
+AlertForce, established in 2008, continues to expand its footprint as a leading provider of occupational health and safety (OHS) and work health and safety (WHS) training across Australia. The company offers online and face‑to‑face courses nationally, with training centres and delivery locations in Potts Point, Arncliffe (head office/training centre) and Canberra, reflecting ongoing geographic expansion and sustained demand for its e‑learning and in‑person compliance training solutions.</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alertforce-anz/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>All IT (All IT Services Pty Ltd, Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>All IT strengthens position as ‘Australia’s Leading AI, Cyber Security &amp; IT Provider’ with 5.0-star customer rating (01/03/2026)
+All IT, a Sydney-headquartered managed IT and cyber security provider, has highlighted sustained growth in its cyber practice, supported by a 5.0-star rating across 85+ public reviews and more than 21 years of continuous operation. The firm now delivers 24/7 managed IT, cyber security, and cloud solutions for organisations across Sydney, Melbourne and Brisbane, positioning itself as a national provider rather than a purely local MSP. This expansion in geographic coverage and services signals increased demand for its cyber security and AI-driven automation offerings among Australian mid-market businesses.
+All IT expands managed cyber security and cloud services footprint across Australia (15/11/2025)
+All IT has expanded its managed cyber security and cloud service offerings from Sydney into Melbourne and Brisbane, according to updates on the company’s website. The firm now markets itself as providing responsive, relationship-first IT, cyber security and cloud solutions across the eastern seaboard, underlining a broader national growth strategy. This expansion is supported by its around-the-clock support model and a focus on AI-driven automation, which is attracting customers that require higher levels of cyber resilience and regulatory compliance.
+All IT recognised as an award‑winning Australian IT and cyber security provider supporting Sydney business growth (10/09/2025)
+Digital Armour, in a feature on the role of IT advisory services in Sydney business growth, cites All IT among award‑winning Australian IT and cyber security firms that help local organisations align technology strategy with business outcomes. The recognition reflects All IT’s progression from a traditional MSP into a strategic IT and cyber advisor for Sydney businesses, including those in hospitality and not‑for‑profit sectors that handle sensitive data. This external acknowledgement underscores the company’s reputation and growing influence in the Sydney cyber security ecosystem.
+All IT launches ‘All IT Tech News’ hub to support clients with evolving cyber security and AI insights (20/06/2025)
+All IT has introduced an online ‘All IT Tech News’ hub, publishing updates and practical guidance on cyber security, AI and IT best practices for Australian organisations. By investing in ongoing content and advisory resources, the company is reinforcing its role as a long‑term technology and security partner rather than a purely reactive support provider. The publication effort supports customer retention and brand growth, positioning All IT as a thought leader in cyber security for SMEs and mid‑market organisations in Sydney and beyond.</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>[08/05/2026 - 1w] Announcement of open roles as the company expands its service team, indicating growth in staffing.
+[29/04/2026 - 2w] Acknowledgment of work anniversaries for employees, highlighting team growth and appreciation.</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/all-it-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Allstar Orthodontics (Brisbane, QLD, AU)</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Allstar Orthodontics recognised as Best Orthodontist in Inner City Brisbane for 2026 (01/01/2026)
+Quality Business Awards has recognised Allstar Orthodontics as the leading orthodontist in Inner City Brisbane for 2026, noting that the practice achieved a quality score of over 95% and ranks in the top 1% of orthodontic providers evaluated. This award highlights the clinic’s strong reputation, patient satisfaction, and service quality across its Brisbane locations.
+Allstar Orthodontics expands services as one of Brisbane’s top Invisalign and clear aligner providers (01/09/2025)
+Allstar Orthodontics, based in Fortitude Valley and Albany Creek, positions itself as Brisbane’s top provider of Invisalign and clear aligners and promotes free initial consultations. The practice emphasises its capacity to treat a broad range of orthodontic cases with clear aligners, reflecting service expansion and growing demand for discreet orthodontic treatment options.
+Allstar Orthodontics highlights over 20 years of specialist orthodontic care in Brisbane (01/06/2025)
+In its ‘5 Things That Make Allstar Orthodontics Different’ blog, the clinic underscores more than 20 years of continuous operation, thousands of completed treatments, and extensive experience with both conventional braces and Invisalign clear aligners. The article frames this longevity and case volume as a key differentiator and indicator of sustained growth and clinical demand.
+Allstar Orthodontics strengthens multi-clinic presence with Fortitude Valley and Albany Creek locations (01/06/2025)
+Allstar Orthodontics continues to operate two Brisbane practices—an inner-city clinic in Fortitude Valley and another in Albany Creek—giving patients flexibility to attend either location for appointments. The dual-site model supports a larger patient base across Brisbane’s inner-city and northern suburbs, indicating geographic expansion and operational scale beyond a single practice.
+Allstar Orthodontics showcases high-volume treatment outcomes with detailed patient journey case studies (01/03/2025)
+Through its published ‘Patient Journey’ smile transformation case studies, Allstar Orthodontics highlights comprehensive start-to-finish treatment processes and results. The clinic notes that it has helped thousands of Brisbane families with braces and aligners, suggesting a strong and sustained patient pipeline and reinforcing its position as an established, growing orthodontic provider.
+Specialist orthodontist Dr Mike Anderson recognised as leading Invisalign provider at Allstar Orthodontics (01/02/2025)
+Allstar Orthodontics’ lead clinician, Specialist Orthodontist Dr Mike Anderson, is profiled as a leading Invisalign provider with more than 20 years of experience and the capability to treat even complex orthodontic issues using discreet clear aligner methods. This recognition supports the clinic’s growth in advanced aligner-based treatments and enhances its competitive positioning in Brisbane’s orthodontic market.</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr"/>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/allstar-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>AquaWatch (Queenstown, Otago Region, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Fast-Track Bill increases impetus for real-time, transparent water monitoring (12/03/2024)
+In a press release, AquaWatch comments on New Zealand’s Fast-Track Approvals Bill, arguing that stronger real-time water monitoring is needed to support robust environmental decision-making. While primarily a policy response, the release positions AquaWatch as a key provider of real-time monitoring solutions for councils, utilities, and developers, indirectly signalling demand-side growth opportunities for its services as regulatory expectations increase.
+About AquaWatch: expanding global footprint in water quality monitoring (01/02/2024)
+The company’s own overview notes that AquaWatch now works with utilities, councils, construction companies, and land managers across New Zealand, Australia, the United Kingdom, and Ireland. This reflects significant international expansion beyond its Wairarapa origins, delivering remote, continuous, validated water quality information via its Waka hardware and monitoring services.
+AquaWatch: Guardianship preserving the heartbeat of our water (15/11/2023)
+Profile of AquaWatch (formerly RiverWatch) highlighting its evolution into a values-led, export-focused water quality monitoring company. The article notes its first global export in 2022 to Inland Fisheries in Ireland, growing recognition in local and international markets, and its flagship ‘Waka’ floating monitoring unit made from 70% recycled milk bottles with multiple water-quality sensors. It positions AquaWatch as a showcase of New Zealand’s technology and innovation capabilities in waterway sustainability and guardianship.
+RiverWatch rebrands to AquaWatch, expands water monitoring (26/09/2022)
+New Zealand startup RiverWatch announces its rebrand to AquaWatch, reflecting its expansion from river-only monitoring to broader water applications including municipal water and aquaculture. The company is adding a water health score into its monitoring services, working with several regional councils, and has established a presence in Ireland and Australia. The rebrand includes a new AquaWatch website and signals a broader growth strategy for its IoT-based ‘Mighty Waka’ water quality monitoring hardware and services.
+Fieldays Innovation Award winner finds their place in international market (20/06/2022)
+AquaWatch is recognised with two Fieldays Innovation Awards: the Innovation in Data Award in 2019 and the Growth &amp; Scale Award in 2022. The awards acknowledge the company’s ability to generate high-value water quality data and its success in scaling its solution into international markets, underlining its growth trajectory within agri-tech and environmental monitoring.</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr"/>
+      <c r="E20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Aquabliss School of Swim</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Aquabliss acquires the McKeon Swim School (01/04/2026)
+Aquabliss announced the acquisition of the McKeon Swim School, reinforcing its growth momentum and expanding access to high-quality Learn to Swim programs across New South Wales.
+Aquabliss acquires Illawarra's famed McKeon Swim Schools (01/04/2026)
+Aquabliss completed the purchase of the McKeon Swim School business, marking a significant expansion for the Sydney-based swim school group and extending its footprint in NSW.</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>[01/05/2026 - 2w] Aquabliss announces the successful acquisition of McKeon's Swim School, enhancing their service capabilities and geographic reach.</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aquabliss/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Aquip Systems Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Aquip to exhibit at MAINSTREAM Community Summit 2025 in Perth (10/01/2025)
+Aquip Systems announced it will exhibit at the MAINSTREAM Community Summit 2025 at the Perth Convention and Exhibition Centre on 6 March 2025. The company will showcase a broadened range of offerings, including PRÜFTECHNIK laser alignment and condition monitoring systems, MAUS fire protection equipment, and INGU inline inspection services. This presence highlights Aquip’s ongoing expansion into condition monitoring, fire protection and inline inspection technologies, and signals active business development and marketing investment to reach new industrial asset‑management customers.
+Orbis Intelligent Systems signs multi‑year distribution agreement with Aquip Systems (15/02/2024)
+Orbis Intelligent Systems announced a multi‑year distribution agreement with Aquip Systems Pty Ltd, described as Australia’s leading provider of measurement and data collection systems to the oil and gas, mining, marine, HVAC, water and chemical industries. The partnership expands Aquip’s product portfolio into advanced pipeline monitoring and intelligent sensing solutions, strengthening its position in industrial instrumentation and supporting long‑term revenue growth through recurring distribution and service opportunities.
+HIFraser Group highlights growth including Aquip Systems as part of 35‑year milestone (20/11/2022)
+Celebrating 35 years under the Kirkby family, HIFraser Group reported growth from five employees in 1987 to 117 employees nationwide, attributing part of this expansion to acquisitions such as Aquip Systems and Aquip Flowservices. The group now offers a wide range of engineering and industrial instrumentation solutions across critical industries. Aquip Systems’ inclusion among the “amazing companies” acquired underscores its role in the group’s expanded capabilities and national footprint, indicating sustained organisational growth and integration for the Aquip business.
+HIFraser Group acquisition of Aquip Systems underpins group growth strategy (01/07/2015)
+HIFraser Group confirmed that in 2015 it acquired Aquip Systems, a Perth‑based provider of niche instrumentation products and services to the mining and oil and gas sectors, along with Flowservices (now Aquip Flowservices) in Queensland. The acquisition brought Aquip into a larger national engineering and industrial group, enabling broader market access, integrated offerings across defence, mining, oil and gas, construction and water, and supporting Aquip’s growth from a specialised local supplier into a key instrumentation business within a 100+‑employee national organisation.</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>[22/04/2026 - 3w] Announcement of the new Shaft Alignment solutions, including advanced features and improvements.
+[21/04/2026 - 3w] Introduction of Mobius Institute Condition Monitoring training programs for technician and analyst skill enhancement.</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aquip-systems-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Arrow Health (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>More Beds, More Staff To Help Tackle Addiction – Arrow Health Woodend Expansion (06/03/2024)
+The Allan Labor Government has supported a major expansion of Arrow Health’s rehabilitation clinic in Woodend with a $600,000 investment towards a $2.1 million project. The expansion added eight new beds and 55 staff, constructed a new rehabilitation cottage, upgraded car parking and ambulance access, and refurbished existing rooms. As a result, annual in‑patient treatment capacity has more than doubled to about 240 patients, and out‑patient care capacity has grown from around 80 to approximately 180 patients per year. The project has also created new roles for doctors, nurses, therapists, facilities-support staff and increased engagement of locally contracted allied health professionals.
+Health and Jobs in Macedon Ranges – Arrow Health Clinic Expansion (06/03/2024)
+Regional Development Victoria highlighted the expansion of Arrow Health’s Woodend clinic as a key health and employment boost for the Macedon Ranges region. The project has delivered more beds and more staff to tackle addiction, building on Arrow Health’s role as a private hospital and rehabilitation provider. The expansion strengthens local healthcare infrastructure while generating new clinical and support jobs in the area.
+Victorian Government Highlights Arrow Health’s Expanded Role in Statewide Addiction Treatment System (06/03/2024)
+In conjunction with announcing the Woodend expansion, the Victorian Government cited Arrow Health’s increased capacity as part of a broader alcohol and drug treatment system that supports around 40,000 substance‑dependent Victorians annually. Government statements described the investment as an endorsement of Arrow Health’s transformation into a ‘driving force behind addiction treatment’ and a more sustainable provider addressing both addiction and mental health. This recognition underscores Arrow Health’s growing role and standing within Victoria’s healthcare landscape.
+Arrow Health Showcases Growth and Service Expansion in ‘Guided by Hope’ Documentary (01/11/2023)
+The documentary ‘Guided by Hope: The Arrow Health Story’ details Arrow Health’s evolution from a small idea into a private hospital and comprehensive addiction treatment service based near Melbourne, including its relocation and expansion to the Woodend site. The film highlights the development of its accredited private hospital for detox, extended residential rehab programs, and integrated mental health and addiction services, underscoring the organisation’s growth in scale and complexity of care over recent years.
+Arrow Health Expands Integrated Private Hospital Detox and Rehab Services Near Melbourne (01/08/2023)
+Arrow Health has expanded its offering as an accredited private hospital near Melbourne, providing claimable in‑hospital detox and 30–90 day residential rehabilitation programs in one integrated location. The organisation emphasises medically supervised withdrawal in a hospital environment, followed by long‑term rehabilitation and flexible outpatient programs, including a 12‑day option with in‑person and online delivery. These developments reflect Arrow Health’s growth in clinical capacity, service range, and accessibility for individuals and families affected by addiction.</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>[13/05/2026 - 5d] Reflects on the history and growth of Arrow Health over the past decade, highlighting ongoing development in research and innovation for treatment, indicating long-term commitment to growth.
+[12/05/2026 - 6d] Announcement of new outpatient program starting May 25th, 2026, which signifies business expansion and service enhancement.
+[29/04/2026 - 2w] Kayleigh Berry has joined Arrow Health as the General Manager and Director of Nursing, indicating team growth at the executive level.</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arrow-health-addiction-treatment/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Arventa</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr"/>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arventa-limited/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Assura Software (Christchurch, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Assura Software expands platform to broader business process and risk management (22/07/2022)
+Through a series of product updates and news posts, Assura Software outlines the evolution of its solution from a health and safety tool into a wider business process and enterprise risk management platform. The expansion into areas such as irrigation management, contractor management and broader workflow automation demonstrates ongoing product diversification and positions the Christchurch firm for growth across multiple operational domains in NZ organisations.
+Why Assura is the best HSMS software in NZ (10/03/2021)
+Assura Software publishes an insights piece positioning its Health &amp; Safety Management System as the leading HSMS solution in New Zealand. The article details broad adoption across NZ businesses, expansion of functionality to cover health &amp; safety, contractor management and enterprise risk, and emphasises Assura’s growing customer base and product maturity—signalling sustained growth and strengthening market position.
+Automated software helping boost health and safety (18/04/2016)
+Article highlights strong demand for automated health and safety software in New Zealand following the Health and Safety at Work Act 2015, featuring Assura Software as a leading provider. Managing director Hamish Howard notes rapid uptake of Assura’s health and safety platform as organisations seek more robust compliance and risk management tools, indicating market-led growth for the Christchurch-based company.</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Atlas Weighing Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Compuload 6000 Gains Trade Approval for Commercial Weighing Applications (15/03/2024)
+Atlas Weighing announced that its Compuload 6000 onboard weighing system has been approved for Trade Approved applications in Australia. This certification allows customers to use the Compuload 6000 in legal‑for‑trade weighing, opening up new commercial use cases across transport, waste, quarrying and civil construction. The approval strengthens Atlas Weighing’s product portfolio and positions the company for increased sales into fleets and operators who require certified weighing solutions.
+Atlas Weighing Expands Compuload Onboard Weighing Range to Support More Machinery Types (10/11/2023)
+In a series of technical articles, Atlas Weighing detailed expanded applications of its Compuload onboard weighing systems across loaders, forklifts, telehandlers and agricultural machinery. The company highlighted new configurations, mounting hardware and electronics options that enable more flexible retrofitting and faster installation. This broader applicability indicates ongoing product development and supports growth by allowing Atlas Weighing to service a wider range of machinery in quarrying, waste, transport and agriculture.
+Atlas Weighing Highlights Increased National and International Dispatch Capacity (01/06/2022)
+Atlas Weighing reported that it holds an extensive range of onboard weighing equipment, load cells, mounting hardware and electronics in stock at its Rouse Hill facility for fast delivery. The company also emphasised its ability to dispatch equipment nationally and internationally and referenced a network of agents across Australia for installation and service. These developments reflect operational scaling and distribution growth, supporting higher volumes and broader geographic reach for its machinery and equipment manufacturing offerings.</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr"/>
+      <c r="E26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Attentis (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Attentis showcases AI-driven environmental data platform to Royal Commission into National Natural Disaster Arrangements (30/09/2020)
+Attentis presented its integrated sensor and data analytics technology to the 2019–2020 Royal Commission into National Natural Disaster Arrangements. By demonstrating how its Melbourne-led platform combines thousands of real-time data points with AI and advanced analytics for fire weather, smoke and air quality monitoring, Attentis gained high-profile validation of its technology. This exposure supports the company’s growth trajectory through increased credibility with policymakers and potential large-scale deployments.
+Attentis real-time environmental sensor network recognised as key component in bushfire mitigation strategy (15/06/2020)
+Attentis, developer of Australia’s first real-time integrated environmental sensor network based in Victoria, was highlighted in national bushfire mitigation discussions as a potential multi-faceted solution for early detection and response. The company’s dense network of intelligent, self-powered sensors and advanced analytics platform were cited for their ability to provide continuous, high-resolution environmental data, strengthening Attentis’ position as a key technology partner for government and emergency services and supporting future commercial growth opportunities.</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr"/>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/attentis-technology/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Auckland BioSciences</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Auckland BioSciences Taps Nutraceutical Market with Christchurch Acquisition (10/12/2025)
+Auckland BioSciences, an Auckland-based animal bioactives producer, has acquired Christchurch manufacturer Genesis BioLab and will merge it into a new business unit within the wider organisation. The deal gives the company a dedicated nutraceuticals specialisation and supports expansion across New Zealand, Australia and South America. It follows the opening of MonteSera, a new business and plant in Uruguay, and takes combined headcount to around 55 alongside its Australian and Latin American subsidiaries, signalling continued international expansion and portfolio growth beyond its core animal serum products.
+Auckland BioSciences Expands Into High-Value Nutraceuticals Sector with Acquisition of Genesis BioLab (10/12/2025)
+A press release from Auckland BioSciences confirms its move into the high-value nutraceuticals, wellness and pharmaceutical ingredients sector through the acquisition of Genesis BioLab in Christchurch. Leveraging its existing global pharma and biotech network, the company plans to manufacture and export high-grade wellness, pharmaceutical and nutraceutical products from New Zealand, broadening its product portfolio beyond animal serum and deepening its presence in higher-margin global markets.
+Auckland BioSciences Ranked #1 on the Deloitte Master of Growth Index in New Zealand (15/11/2023)
+Auckland BioSciences was ranked first on the Deloitte Master of Growth Index, recognising it as the fastest-growing company in New Zealand over the index period. The ranking highlights the company’s rapid revenue growth from its animal serum and bioactives export business, reflecting strong demand from global pharma, biotech and research customers and validating its growth strategy in the bioactives and agricultural support services space.
+Biosciences Company Shines Amidst Global Economic Gloom (20/05/2020)
+During the early stages of the COVID-19 pandemic, Auckland BioSciences reported turnover of more than NZ$10 million in the prior financial year and expected further significant growth despite temporary production stoppages. The company appointed its first Chief Financial Officer, Mark Dawson, signalling organisational maturation and scaling. In just six years it had grown from operating out of a shipping container at an Auckland abattoir to employing more than 40 staff at its Rosedale headquarters, a new office and processing site in Christchurch, and multiple manufacturing sites around New Zealand, with exports of animal serums to 14 countries.</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr"/>
+      <c r="E28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>AusVet Endoscopy</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Austvet Endoscopy joins the Mediquip Group of Companies (01/02/2025)
+Austvet Endoscopy, a specialist provider of rigid and flexible veterinary endoscopy equipment for small animal and equine applications based in Victoria, announced that it has joined the Mediquip Group of Companies effective 1 February 2025. The move integrates Austvet’s specialised veterinary endoscopy expertise into Mediquip’s broader medical and veterinary equipment portfolio, expanding commercial reach, service capacity, and technical support for veterinary practices across Australia and New Zealand.
+Mediquip kicks off 2025 with acquisition of Austvet Endoscopy (15/01/2025)
+Mediquip announced three major acquisitions at the start of 2025, including Austvet Endoscopy in Victoria. The acquisition is intended to strengthen Mediquip’s national footprint in veterinary endoscopy by adding Austvet’s established customer base, specialist product range, and technical expertise. The combined group plans to enhance endoscopy product availability and support services for veterinary clinics and hospitals throughout Australia.</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr"/>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/austvetendoscopy/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Aussie Switchboards</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Aussie Switchboards achieves AMAG approval, strengthening market position in compliant switchboard manufacturing (15/08/2023)
+Aussie Switchboards announced it is now AMAG approved, signalling that its switchboard manufacturing processes and products meet stringent industry and safety standards. This certification enhances the company’s credibility with major contractors and utilities, positions it for larger projects across Australia, and supports its continued growth in the electrical and electronic equipment manufacturing sector.
+Aussie Switchboards recognised among manufacturing ‘powerhouses’ and outlines plans to support sector growth (10/11/2022)
+In a company news update, Aussie Switchboards reported on its participation in a manufacturing-focused industry event, describing it as an opportunity to connect with other leading manufacturers, share experiences and present its plans for supporting ongoing growth in Australian manufacturing. The article highlights the firm’s strategy to expand its role in the sector through innovation, collaboration and continued investment in its Gold Coast operations.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr"/>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aussie-switchboards/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Australian Calibration Group</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Australian Calibration Group Achieves ISO/IEC 17025 Accreditation for Pressure Metrology (15/02/2025)
+Australian Calibration Group, a Victoria‑based calibration services provider, secured ISO/IEC 17025 accreditation (NATA accreditation no. 21641) with a focus on pressure metrology from −100 kPa to 100,000 kPa. The accreditation covers both laboratory and on‑site calibration, enabling ACG to deliver accredited services directly at customer facilities. This milestone strengthens ACG’s position in highly regulated sectors such as pharmaceuticals, where NATA‑accredited calibration is often mandatory, and supports the company’s growth strategy in high‑tech and compliance‑critical industries.</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr"/>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/australian-calibration-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>AutoGuru</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>AutoGuru highlighted as one of Australia’s fastest‑growing and most innovative tech companies (22/01/2025)
+In a 2025 roundup of Gold Coast tech and innovation jobs, AutoGuru was listed as one of Australia’s fastest‑growing and most innovative tech companies. The article notes that the business, led by founder Eden Shirley, has grown to a team of 44 and is "making some serious waves" in the automotive industry by using a cutting‑edge software platform that makes booking car services as easy as booking flights or hotels. AutoGuru was actively hiring for multiple roles, including an Office Manager, Customer Support Supervisor, Fleet Services Agent and Automation Test Analyst, highlighting continued headcount growth and ongoing investment in product and operations.
+Gold Coast Innovation Hub spotlights AutoGuru as a high‑growth online marketplace (24/07/2019)
+The Gold Coast Innovation Hub profiled AutoGuru as a high‑growth Gold Coast tech success story. Founder Eden Shirley detailed how the platform grew from a local idea into Australia’s largest online marketplace for automotive services, now generating millions of dollars in quotes for mechanical services every month through thousands of customer‑rated mechanics nationwide. The feature highlights AutoGuru’s scalable software platform, strong recurring demand from motorists, and the company’s rapid revenue traction as key drivers of its growth.
+AutoGuru joins Deloitte Technology Fast 50 Australia Rising Stars Winners Circle with 612% revenue growth (15/11/2017)
+AutoGuru was recognised in the Deloitte Technology Fast 50 Australia program’s Rising Stars Winners Circle after posting a 612% increase in annual gross revenue in its first three financial years. The recognition places AutoGuru among Australia’s fastest‑growing technology companies. The article also notes that the company scaled from humble beginnings in a cupboard‑sized office in Nerang to employing 28 staff at a Gold Coast headquarters near Surfers Paradise, underscoring both strong financial growth and team expansion. Founder Eden Shirley was also named a Startup Founder of the Year finalist in the 2017 Startcon Australasian Startup Awards, providing further validation of the company’s trajectory.</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr"/>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fleetguru-au/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Automate-X (Papakura, Auckland Region, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Automate-X named major sponsor of inaugural Logistics Automation New Zealand 2026 event (29/04/2026)
+Automate-X has been announced as the major sponsor of the inaugural Logistics Automation New Zealand event, powered by CeMAT, to be held at the Auckland Showgrounds on 10–11 November 2026. The sponsorship positions Automate-X at the centre of New Zealand’s emerging intralogistics and warehouse automation ecosystem, reinforcing its brand leadership and signalling continued growth in logistics-focused high‑tech automation solutions.
+Automate-X promotes next‑generation warehouse automation technologies across New Zealand and Australia (15/01/2026)
+In a knowledge‑hub article, Automate-X outlines its expanding suite of intelligent warehouse automation solutions for New Zealand and Australian customers, including goods‑to‑person systems, AS/RS with 4‑way shuttles, conveyor systems, automated packaging, industrial robotics, and advanced warehouse software. The piece emphasises successful deployments across 3PL, e‑commerce, manufacturing, FMCG, food and beverage, pharmaceuticals and cold storage, highlighting increasing sector penetration, end‑to‑end integration capability, and the company’s positioning as a leading intralogistics automation partner in the region.
+Automate-X disrupting the industry with automation and expanding across Australia and New Zealand (13/09/2024)
+An MHD Supply Chain feature profiles Automate-X, founded in Auckland in 2020, outlining rapid growth from production-line robotics and machine vision into large-scale warehouse automation. The article highlights a growing customer base that includes major dairy and manufacturing companies in New Zealand, a strategic focus on logistics automation in Australian warehouses, active recruitment to grow the Melbourne team, and plans to establish a presence in Sydney. It also notes the company’s turnkey project capability and several significant warehouse automation and software projects underway, underscoring strong regional expansion and increasing project pipeline.</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>[27/04/2026 - 3w] Client testimonials indicate trusted relationships and growth impact through satisfied customers.
+[20/04/2026 - 4w] Mentions team member featured as speaker, indicating growth through representation and industry presence.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/automate-x/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Axiom Precision Manufacturing</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Axiom Precision Manufacturing awarded contract for KONGSBERG Naval Strike Missile Ground Support Equipment (29/11/2023)
+Axiom Precision Manufacturing, based in Wingfield, Adelaide, secured a contract with Kongsberg Defence Australia to manufacture and deliver ground support equipment for the Naval Strike Missile under Project SEA 1300 Phase 1 – Navy Guided Weapons. The work will support additional growth in Axiom’s vertically integrated manufacturing capabilities, including fabrication and painting, and reinforces its role as a sovereign defence supplier.
+Adelaide-based SME Axiom Precision Manufacturing wins work on Navy missile program (29/11/2023)
+Axiom Precision Manufacturing announced it has signed a contract with Kongsberg Defence Australia to produce ground support equipment for the Royal Australian Navy’s new Naval Strike Missile capability, part of the SEA 1300 Phase 1 Navy Guided Weapons program. The deal highlights Axiom’s growth in defence manufacturing and leverages its certified, purpose-built facilities in Adelaide servicing aerospace, defence, space and medical device sectors.
+Local industry support historic Artemis II mission (21/08/2023)
+The South Australian Space Industry Centre highlighted Axiom Precision Manufacturing’s role in supplying structural components for the Orion spacecraft in support of NASA’s Artemis II mission. This contribution showcases Axiom’s growing presence in the global space industry and underpins continued advanced manufacturing work in its Adelaide facilities.
+Australian precision parts for our biggest journey yet (10/11/2021)
+Axiom Precision Manufacturing in Adelaide and Nupress Group in Newcastle were contracted by Lockheed Martin to produce precision machined components for NASA’s next-generation Orion spacecraft, part of the Artemis program. For Axiom, which moved from automotive into defence and then space, the contract represents diversification-driven growth and positions the company in global space supply chains.
+SEGULA Technologies and Axiom Precision Manufacturing join forces (22/07/2021)
+Global engineering group SEGULA Technologies and Adelaide-based Axiom Precision Manufacturing signed an agreement to collaborate and offer sovereign capability in advanced engineering and manufacturing in Australia. The partnership is intended to expand Axiom’s access to defence, transport and energy projects and broaden its engineering and manufacturing offering.</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr"/>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/axiom-precision-manufacturing/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Azured</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Azured hosts ‘Modernising with Purpose’ event to help NFPs accelerate cloud modernisation (30/04/2024)
+Melbourne-based cloud and hosting provider Azured held a ‘Modernising with Purpose’ hybrid event aimed at not-for-profit leaders and technology teams seeking practical, budget-conscious approaches to modernising on Microsoft Azure. The event, promoted as focused on modernisation strategy, security and optimisation, underlines Azured’s ongoing growth in the Azure consulting and managed services space and its targeted expansion into the NFP vertical.</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>[22/04/2026 - 3w] Announcement of a new cybersecurity solution called Alexein, integrating with Microsoft security ecosystem.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/azured-consulting/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Balmain Village Orthodontics</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr"/>
+      <c r="D36" s="17" t="inlineStr"/>
+      <c r="E36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Bare (Melbourne, Victoria, Australia)</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Bare highlights surge in prepaid funerals as part of evolving service offering (15/08/2023)
+In a company blog discussing the future of funerals, Bare reports growing demand for prepaid funeral services and positions itself to capitalise on this trend with its digital‑first, low‑cost prepaid offerings. Drawing on industry data showing only a small share of Australians currently hold prepaid funerals, Bare signals expectations of exponential growth and continued expansion of its prepaid products alongside existing cremation, memorial and legal services.
+Bare unveils ‘The Most Bare Funeral Ad Ever’ in first national brand campaign (18/05/2023)
+Melbourne‑founded funeral company Bare launched its first major brand campaign, “The Most Bare Funeral Ad Ever”, created with agency Born, to challenge conventional funeral advertising and highlight its mission to simplify, personalise and reduce the cost of funerals. The campaign reflects Bare’s maturation from a start‑up into a national brand and supports ongoing growth of its low‑cost, transparent funeral and cremation services across Australia.
+Death care startup Bare raises over $6 million in Series A funding (30/06/2022)
+Australian death‑care startup Bare, founded in 2019 and headquartered in Melbourne, announced it had raised around A$10 million (about US$6.8 million) in a Series A funding round to accelerate its growth. In just three years the company expanded from simple direct‑to‑consumer cremations to a broader suite of services including funeral services, memorial celebrations, and legal support, and reported serving over 15,000 Australians to date.
+Digital deathcare disruptor Bare raises $10 million in Series A (23/06/2022)
+Melbourne‑based funeral company Bare, formerly Bare Cremation, raised A$10 million in a Series A round led by Perennial Partners and Ord Minnett Private Capital, bringing total funding to more than A$15 million. The capital is earmarked for new digital products and physical infrastructure as Bare scales beyond its original direct cremation service into memorials, wills and probate. The company reports having served over 15,000 customers and operating across Victoria, NSW, Queensland, Tasmania, SA, ACT and WA, evidencing substantial geographic expansion.
+Funeral disruptor Bare defies market conditions to bank $10m (22/06/2022)
+Melbourne‑based direct‑to‑consumer funeral disruptor Bare closed a A$10 million Series A round from institutional investors Perennial Partners and Ord Minnett Private Capital. The company, founded in late 2019, has grown from offering prepaid cremation services to providing a full suite of death‑care products including memorial packages, digital wills, probate services and grief support, and has assisted more than 15,000 Australians with end‑of‑life needs. The structure of its APRA‑regulated funeral bonds also provides security for prepaid customers, supporting further growth in prepaid offerings.</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr"/>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bare-funerals-and-cremations/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Baumgartner Super (now trading as Assurify)</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Baumgartner Super rebrands as Assurify and launches as stand‑alone SMSF audit business (03/02/2025)
+Specialist SMSF audit firm Baumgartner Super, headquartered at Level 1, 35 Cotham Road, Kew, VIC, has rebranded and will now trade under the new name Assurify. The firm stated that this marks the beginning of a new era as it evolves into a stand‑alone business outside the Baumgartner Group. The founding partner, David Baumgartner, is retiring, with the rebranded business to be led by David Burrows and Sajee Madarasinghe. The firm also flagged several new initiatives currently in development to be unveiled later in the year, signalling ongoing investment and growth in its specialist SMSF audit offering.</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr"/>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baumgartners-chartered-tax-accountants/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Baxter Laboratories (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Australian government invests $20m in Baxter, the country’s largest and only onshore manufacturer of IV fluids (23/02/2024)
+The Australian government confirmed a $20 million grant to Baxter to expand capacity at the nation’s only onshore IV fluids manufacturing operation. The project, which Baxter is co‑funding with an additional $20 million, is expected to significantly increase local output of critical hospital IV products, reduce reliance on imports, and create new high‑skill manufacturing roles. The company’s Australian operations, headquartered in Victoria, are positioned to benefit from the larger scale and improved national supply resilience.
+Australian government backs $40m expansion of Baxter’s IV fluids manufacturing facility in Western Sydney (22/02/2024)
+Baxter Healthcare and the Australian Government announced a combined $40 million investment to expand Baxter’s IV fluids manufacturing facility in Old Toongabbie, Western Sydney. The federal government will contribute $20 million, matched by $20 million from Baxter, to increase domestic production capacity, enhance supply-chain resilience, and support additional advanced manufacturing jobs. While the facility is in Western Sydney, the expansion reflects broader growth in Baxter’s Australian manufacturing footprint, which is supported by corporate, R&amp;D, and commercial functions located in Melbourne.</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 4d] The post discusses the inaugural Growth Conference, focusing on cross-functional collaboration and strategic alignment around growth opportunities, indicating a proactive approach towards business growth.
+[08/05/2026 - 1w] The post celebrates employees' contributions and recognizes quarterly award recipients during a company Town Hall, emphasizing a focus on teamwork and progress.</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baxter-laboratories/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Beacon Support</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Beacon Support | Home Care Services (01/01/2026)
+Beacon Support’s website describes the company as an accredited NDIS provider delivering home care services across Queensland, including Ipswich, Brisbane and the Sunshine Coast. The page emphasizes an established presence and ongoing service delivery in the region, but does not report a specific news event such as an award or expansion announcement.
+Supported Independent Living in Alexandra Headland (01/01/2026)
+This page states Beacon Support has been providing trusted home-based care for more than 17 years and serves the Brisbane metropolitan area, with deep ties to support coordinators, therapists and other practitioners. The long operating history and broad service network indicate business growth and sustained market presence, though no discrete news event is announced.
+Sunshine Coast Disability Home Care Services - Beacon Support (01/01/2026)
+Beacon Support says it has been delivering Sunshine Coast home care services for more than 17 years as a registered NDIS provider. The page highlights continued regional service coverage and an established customer base, suggesting ongoing business growth rather than a specific press-release style milestone.</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr"/>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beacon-support/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Beyond Essential Systems</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Beyond Essential Systems expands collaboration hub and showcases growing global footprint (08/03/2025)
+In an impact update on its website, Beyond Essential Systems highlighted its growing support centre as a hub for collaboration and detailed ongoing deployments of its digital health products across the Indo‑Pacific. The update points to an expanding team, increased implementation support capacity and continued uptake of its platforms, indicating organic growth and operational scaling from its Melbourne base.
+Beyond Essential Systems highlighted as key digital partner in Fiji’s expanded HIV response (27/11/2024)
+The Doherty Institute profiled Fiji’s rapid expansion of HIV testing, treatment and prevention services and identified Beyond Essential Systems as a core partner in strengthening the country’s health response. BES’s involvement in national HIV initiatives, alongside international agencies and local clinical partners, reflects growing adoption of its digital health platforms and deepening engagement in large‑scale public health programs across the region.
+Monash University feature showcases growth journey of Beyond Essential Systems founders and company (18/04/2024)
+Monash University profiled alumni Michael and Erin Nunan, now CEO and Director of Beyond Essential Systems, describing how the Melbourne‑based company has grown into a specialist provider of healthcare software for low‑ and middle‑income countries. The article underscores BES’s evolution from a small venture into a recognised digital health firm with international projects, signalling sustained organisational growth and leadership recognition within the Australian innovation ecosystem.
+Evaluation confirms positive impact and scaling of Beyond Essential Systems’ health information platforms in the Pacific (05/12/2023)
+The Australian Department of Foreign Affairs and Trade published an evaluation of its 2019–2024 partnership with Beyond Essential Systems for health information systems in the Pacific. The report describes wide rollout of BES tools, improved data use for decision‑making and strengthened health information system capacity across multiple Pacific countries, indicating successful delivery, program scale‑up and a strong platform for future growth of the Melbourne‑based software company.
+Australian Government expands strategic partnership with Beyond Essential Systems and mSupply Foundation for Indo‑Pacific digital health (22/03/2023)
+Australia’s Indo‑Pacific Centre for Health Security announced an expanded strategic partnership with Beyond Essential Systems and the mSupply Foundation to deliver high‑quality digital health and supply‑chain tools across the Indo‑Pacific. The multi‑year investment supports ongoing development and implementation of BES’s open‑source platforms Tamanu, Tupaia, SENAITE, Open mSupply and Health Supply Hub, signalling financial support, regional expansion and sustained demand for the company’s software and technical assistance.
+Beyond Essential Systems selected as WHO Western Pacific Innovation Challenge winner for Tamanu (15/11/2022)
+The World Health Organization’s Western Pacific Regional Office named Beyond Essential Systems a selected winner in its Innovation Challenge for the company’s electronic health record solution, Tamanu. The recognition highlights BES’s role in developing open‑source, offline‑capable eHealth tools tailored for low‑resource Indo‑Pacific settings and validates the scalability of its integrated digital health ecosystem, including Tupaia and Tamanu.</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>[11/05/2026 - 1w] Launch of the SENAITE Laboratory Information Management System in Majuro, RMI, aimed at modernizing laboratory workflows.
+[06/05/2026 - 1w] Hiring a Laboratory Officer for a project in Tuvalu to strengthen laboratory services.
+[29/04/2026 - 2w] Launch of Tamanu EMR at all rural health facilities in Samoa, connecting them to a single electronic medical record system.
+[22/04/2026 - 3w] Introduction of a maternal health module in Tamanu EMR to aid expectant mothers in Kiribati.</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beyond-essential-systems/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>BioTools (Brisbane, AU)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>BioTools announces expanded life-science solutions offering for Australian researchers (01/03/2022)
+BioTools highlights its role in supplying specialised life-science solutions to universities, hospitals, and institutes, emphasizing customer service and customised workflow support for researchers in Australia.
+Biotechnology in Australia strategic plan highlights incentives for local manufacturing and R&amp;D (01/03/2022)
+A government strategic plan for health and medicine outlines support for local biotechnology manufacturing, sovereign capability, and growth in clinical trials and manufacturing exports, creating a favorable environment for companies like BioTools in Australia.
+Queensland biotechnology industry identified as spanning health, agricultural, environmental and industrial sectors (01/01/2022)
+Queensland government information describes a broad biotechnology ecosystem across multiple sectors, indicating continued regional industry development in Brisbane and Queensland.</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biotools/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Brave Energy Systems</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Navigating the Evolving Energy Landscape with Brave Energy (02/04/2024)
+Brave Energy Systems highlights its role at the forefront of Australia’s rapidly changing energy market, emphasising growth in its SaaS platform capabilities for retailers, distributors and metering providers. The article underlines the company’s expanding toolkit for managing regulatory change, advanced data handling and automation, positioning Brave as a key technology partner for market participants needing scalable, future‑ready solutions.
+Plug in, don’t rebuild: a smarter way for Networks to handle regulatory change (13/11/2023)
+Brave Energy Systems announces an enhanced networks solution that “plugs in” to existing utility tech stacks rather than requiring costly system rebuilds. This reflects product expansion targeted at electricity and gas networks facing complex new regulatory obligations, showcasing Brave’s growing capabilities in automating compliance workflows and supporting more customers across the Australian energy market.
+Brave Energy Systems marks two decades of growth in Australian energy software (15/08/2023)
+In updated company material on its website, Brave Energy Systems notes that it has been supporting the Australian energy market for “over 20 years”, reflecting sustained growth and longevity in a niche, regulated sector. The company highlights an expanded portfolio of SaaS offerings—covering distribution billing, retail mass‑market operations, revenue assurance and metering data delivery—as well as its evolution from a small founding team into a specialist provider serving electricity and gas participants nationwide.
+Brave Energy Systems continues scaling SaaS operations for Australian energy participants (10/10/2022)
+Corporate overviews from industry databases such as ZoomInfo describe Brave Energy Systems as a growing SaaS and IT consulting provider to the electricity and gas industries since 2005, now employing roughly 60–70 staff and generating high‑single‑digit million‑dollar annual revenue. While based on estimates, these profiles indicate ongoing headcount and revenue growth consistent with the firm’s expanding product suite and long‑term customer base across retailers, distributors and metering providers.</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr"/>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brave-energy/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>CLM NZ (Community Leisure Management Ltd, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>CLM Highlights Growth to Over 30 Managed Sites Nationwide (01/04/2025)
+In announcing its 13 new Auckland Council contracts, Community Leisure Management (CLM) reported that it now has a track record managing more than 30 sites across New Zealand and over 28 years of facility management experience. This reflects sustained expansion of CLM’s portfolio of pools, leisure centres, and community sport operations nationwide, underpinned by a focus on operational excellence, regulatory compliance, and community outcomes.
+CLM Staff Recognised at National AUSTSWIM Awards (20/10/2024)
+Two CLM team members, Chuli Galgamuwa and Kirstie Nash from Massey Park, received national recognition at the annual AUSTSWIM Awards. Their achievements spotlight CLM’s staff capability and professional development in aquatic education and safety. The awards enhance CLM’s profile within the aquatics and learn-to-swim sector and support its positioning as a high-quality provider of aquatic programmes across its New Zealand facilities.
+CLM Awarded 13 New Contracts to Manage Auckland’s Pools and Leisure Centres (15/10/2024)
+Auckland Council’s Revenue, Expenditure and Value Committee has approved new contracts for the operation of 20 outsourced pools and leisure centres across the region, selecting Community Leisure Management (CLM) as one of two providers. From April 1, 2025, CLM will operate 13 facilities, including Ōtāhuhu Pool and Leisure Centre, Massey Park Pool, Papakura Leisure Centre, Franklin Pool and Leisure Centre, and Parnell Baths. The decision significantly expands CLM’s footprint in Auckland and reflects council confidence in the company’s operational capability, compliance standards, and community-focused service model.
+CLM to Take Over Management of Wairoa Community Centre (01/07/2024)
+National leisure management company Community Leisure Management (CLM) has been appointed to run the Wairoa Community Centre from 1 July. The contract transfer adds another regional facility to CLM’s national network of more than 30 managed sites and reinforces its position as a key operator of community recreation centres across New Zealand. The move is expected to bring CLM’s operational systems, programming, and community engagement focus to the Wairoa facility.
+CLM Community Sport Manages Over $1.5 Million in Tū Manawa Active Aotearoa Investment for Counties Manukau (30/06/2024)
+CLM Community Sport, part of Community Leisure Management in New Zealand, continues to manage the Tū Manawa Active Aotearoa Fund in partnership with Aktive on behalf of Sport NZ for the wider Counties Manukau region. During the 2023–24 financial year, $1,500,770 was invested into local sport and active recreation initiatives, following $707,257 invested between 1 July and 31 December 2024. This role positions CLM as a key delivery and funding partner in the regional sport system and reflects trust from national and regional agencies in CLM’s capability to administer significant community investment.
+CLM Chosen to Manage Saxton Field Facilities for Nelson City and Tasman District Councils (15/05/2024)
+Following a comprehensive tender process, Community Leisure Management Ltd (CLM) has been jointly selected by Nelson City Council and Tasman District Council to manage the Saxton Field facilities. This multi-council appointment broadens CLM’s presence at a major sports and recreation hub, demonstrating local government confidence in CLM’s expertise in facility management and community sport delivery. The contract strengthens CLM’s South Island footprint and adds to its portfolio of large, multi-use venues.
+CLM Named Finalist for Environmental Sustainability Award at NZ Sport and Recreation Awards 2024 (10/04/2024)
+Community Leisure Management (CLM) was a finalist in the inaugural Environmental Sustainability Award at the NZ Sport and Recreation Awards 2024, recognising its organisation-wide sustainability programme. CLM created a dedicated Sustainability Projects Manager role, formed a CLM Sustainability Green Team across facilities, upgraded utility tracking software, and trained staff to use the tool effectively. Between July 2023 and March 2024, CLM reduced energy use by 55,000 kWh compared with the previous year, cutting costs and highlighting its leadership in sustainable facility management.
+CLM Community Sport Launches First Rangatahi Leadership Council in Counties Manukau (01/03/2024)
+CLM Community Sport has launched the first Rangatahi Leadership Council in the Counties Manukau region to empower emerging young leaders from secondary schools. The initiative extends CLM’s community development and youth engagement activities, strengthening its role beyond facility management into leadership development and strategic community sport delivery. The council is expected to guide youth-focused programmes and deepen CLM’s partnerships with schools and local organisations.</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr"/>
+      <c r="E44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>CODE4FUN</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>CODE4FUN scales to 24 in‑person locations across Sydney plus online delivery (01/02/2025)
+CODE4FUN’s in‑person classes page shows that the company now runs weekly coding classes for kids in 24 different school locations across Sydney while also offering online classes via Zoom. They teach roughly 1,500–1,600 students each year/week (figures vary slightly by page) and have structured four progression levels that support learners from beginner to advanced stages. This reflects a significant operational footprint in NSW schools and continued growth in enrolments and delivery formats.
+Industry interest highlights market momentum for CODE4FUN (01/07/2024)
+Company‑intelligence site ZoomInfo notes that CODE4FUN is drawing exceptional interest within the Education industry, implying strong market momentum and heightened attention from potential partners, customers and stakeholders. This external signal points to growing visibility and perceived relevance of CODE4FUN within the wider e‑learning and education technology ecosystem.
+Revenue and valuation estimates signal continuing growth at CODE4FUN (01/03/2024)
+Business‑intelligence platform Prospeo lists CODE4FUN with estimated annual revenue of about AU$2.05 million and an approximate valuation of AU$6.6 million. While these are third‑party estimates, they indicate meaningful commercial scale for a specialised coding‑education provider focused on the school‑age market, and suggest sustained financial growth since the company’s founding in 2015.
+CODE4FUN alumnus wins Northern Beaches Youth Volunteer of the Year (01/11/2023)
+CODE4FUN announced that alumnus Max Forbes received the Northern Beaches Youth Volunteer of the Year award. While framed as a student success story, the recognition showcases the impact and community engagement fostered by CODE4FUN’s programs. Such alumni achievements enhance the school’s reputation and demonstrate long‑term outcomes of its curriculum, supporting continued growth through word‑of‑mouth and community standing.
+Behind the Code: The University of Sydney tells Lena’s story of leadership and innovation at CODE4FUN (01/09/2023)
+CODE4FUN reported that the University of Sydney Business School featured co‑founder Lena Sveshnikova’s leadership journey, describing how she helped build CODE4FUN from its launch in 2015 into one of Sydney’s earliest and more established coding schools for children. The feature underscores the company’s evolution into a recognised, innovative education startup serving thousands of families, reinforcing its reputation and visibility in the education and startup communities.
+Cracking the code: the alum empowering the next generation of coders (30/05/2023)
+The University of Sydney Business School profiled CODE4FUN co‑founder and marketing director Lena Sveshnikova, highlighting the company’s growth from a single free trial class in 2015 to a substantial coding school partnering with numerous schools across NSW. The article notes that CODE4FUN has steadily expanded its reach through both face‑to‑face classes and online delivery, including a trial partnership with School of the Air to serve students in remote areas. It also emphasises their long‑term curriculum that can support a learner’s progression over up to 10 years, from age 5 through advanced concepts such as recursive algorithms and fractal maths.
+CODE4FUN students meet Australian of the Year Michelle Simmons and learn about quantum computing (01/08/2022)
+CODE4FUN highlighted a special event where its students met Australian of the Year and quantum computing pioneer Michelle Simmons to learn about quantum computers. This kind of high‑profile enrichment activity signals the company’s ability to form connections with leading scientists and provide unique learning experiences, enhancing its brand, curriculum breadth and appeal to prospective students and parents.</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr"/>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sydney-programming-school/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>COMMSecurity</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>COMMSecurity selected to deliver integrated security solutions for landmark 570 Little Bourke Street development in Melbourne (01/03/2024)
+COMMSecurity Australia has been engaged to design and deliver integrated security solutions for the landmark commercial development at 570 Little Bourke Street in Melbourne. The company has integrated all security systems, smart lockers, and visitor management into a single converged network and data platform, leveraging advanced smart building technology. COMMSecurity now manages all security systems alongside the building’s Integrated Communication Network (ICN) and is continuing to expand the building’s technology capabilities, reinforcing its position as a leading provider of integrated cyber–physical security solutions in the South Yarra and broader Melbourne market.
+COMMSecurity expands role managing secure Integrated Communication Networks for multi‑tenant buildings (15/11/2023)
+COMMSecurity has expanded its services around secure Integrated Communication Networks (ICN) for multi‑tenant properties, providing a centrally monitored network that underpins surveillance, intercom, access control, smart lockers, visitor management, dashboards and mobile apps. By integrating advanced security systems into a single secure network, COMMSecurity positions itself as a key smart‑building cybersecurity provider in Melbourne and continues to grow its managed services footprint across premium commercial and residential assets.</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>[03/05/2026 - 2w] M Squared Electrical announces the completion of the Gate 8 commercial building in East Melbourne, highlighting its innovative design and community-oriented features.</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/commsecurity/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Canary IT</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>New Canary IT CEO outlines plans to scale service delivery and capabilities for next growth phase (14/05/2025)
+In an interview following his appointment, new Canary IT CEO James Ormesher outlined a growth agenda centred on three areas: strengthening core service delivery for existing customers, deepening capabilities to meet emerging client requirements, and building momentum across the company’s national expansion. Ormesher’s background in driving sustainable growth and scaling teams in competitive technology markets is cited as key to guiding Canary IT through its next phase of development as a managed services and cybersecurity provider.
+Canary IT appoints James Ormesher as CEO while co‑founder Stephen Parsonage shifts to M&amp;A‑focused executive director role (13/05/2025)
+Sydney-based technology consulting and cybersecurity firm Canary IT has named former Tesserent chief growth officer James Ormesher as its new CEO, marking the end of co‑founder Stephen Parsonage’s 26‑year tenure as chief executive. Parsonage moves into a newly created executive director role to lead mergers, acquisitions and broader strategic growth initiatives. The board describes the transition as a significant milestone in Canary IT’s evolution, positioning the company for its next phase of expansion across Australia through continued investment in talent, technology and geographic reach.
+Canary IT doubles down on mergers and acquisitions with new executive director role and CEO appointment (13/05/2025)
+Canary IT has restructured its leadership to accelerate mergers, acquisitions and strategic initiatives. Co‑founder and long‑time CEO Stephen Parsonage has become executive director with a specific mandate to drive M&amp;A and growth, while former Tesserent chief growth officer James Ormesher assumes the CEO role. The company highlights that it has already completed several acquisitions in 2024, with more planned, and notes that the leadership shift comes amid strong momentum, increased investment in talent and technology, and continued geographic expansion in the Australian market.
+James Ormesher appointed CEO as Canary IT accelerates Australian expansion and acquisition program (13/05/2025)
+Canary IT’s board has appointed James Ormesher as CEO, with co‑founder Stephen Parsonage transitioning to an executive director role focused on mergers and acquisitions and strategic growth. The transition occurs during a period of strong momentum for the Sydney‑headquartered IT and cybersecurity services firm, which has been investing in new talent, technology and expansion across Australia. Several acquisitions were completed in 2024 and additional deals are reportedly in the pipeline as Canary IT seeks to strengthen its market position.
+Canary IT appoints new chief executive to build on acquisition‑driven growth platform (13/05/2025)
+Sydney-based IT services and cybersecurity provider Canary IT has appointed James Ormesher as its new chief executive officer, succeeding co‑founder Stephen Parsonage, who becomes executive director. Under Parsonage’s leadership the business executed multiple strategic acquisitions and created a platform for future growth. In his new role, Parsonage will lead further mergers and acquisitions and strategic initiatives, while Ormesher brings growth and sales leadership experience from Tesserent and Telstra Purple to scale the business. Canary IT, formed in 2022 through the merger of IT Consult, Diversus Group and BCPrise, has continued its expansion with the 2024 acquisition of Brisbane‑based IT services provider Wyntec and its cyber awareness subsidiary Layer 8.
+Canary IT acquires Wyntec and Layer 8 to expand managed services and cyber awareness capabilities (10/12/2024)
+As part of its national growth strategy, Canary IT acquired Brisbane‑based managed services provider Wyntec and its cyber awareness subsidiary Layer 8. The deal extends Canary IT’s managed IT services footprint and adds specialised cyber awareness and training capabilities, supporting the company’s focus on cybersecurity and government and retail customers. The acquisitions are described by the company and its board as important steps in building a broader national platform with deeper security offerings.
+Canary IT forms growth platform through merger of IT Consult, Diversus Group and BCPrise (15/05/2024)
+Canary IT was established as a new brand in 2022 after IT Consult acquired Diversus Group and BCPrise, consolidating them into a single Sydney‑headquartered technology and cybersecurity services provider. The merger created a larger platform with expanded capabilities in cloud, cybersecurity, managed services and retail solutions, positioning the company for national expansion in Australia and further inorganic growth via future acquisitions.
+Secrets Shhh retail case study highlights Canary IT’s role in supporting international growth (20/11/2023)
+A Canary IT case study on jewellery retailer Secrets Shhh illustrates how Canary’s implementation of LS Central and related retail solutions enabled the client to respond more quickly to market changes and support expansion in Australia and Canada. While focused on the customer, the project showcases Canary IT’s growing capability in omnichannel retail and demonstrates its role as a technology partner to retailers pursuing international growth, reinforcing its position in the retail solutions and managed services market segments.</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr"/>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/canary-it/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Capability.Co</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>UTS partners with Capability.Co and McDonald’s to turn workplace skills into university credit (15/03/2024)
+The University of Technology Sydney (UTS) announced an expansion of its Archways to Opportunity program with McDonald’s, formally partnering with Sydney-based Capability.Co to convert workplace learning into academic credit. Capability.Co’s human capability framework and assessment tools are being used to recognise McDonald’s crew and managers’ skills as credit towards selected UTS degrees, signalling growing demand for Capability.Co’s standards-based capability recognition solutions in tertiary–industry partnerships.
+Capability.Co rolls out Human Capability Standards-based development programs across 13 capabilities (10/09/2023)
+Capability.Co expanded its commercial offering with a full suite of capability development programs grounded in the Working Futures™ Human Capability Standards. The Sydney company now delivers high-impact learning across 13 human capabilities at three levels—via facilitated, guided and on‑demand formats—broadening its market from assessment and recognition into scalable workforce development solutions for enterprise, education and government clients.
+Capability.Co formalises research alliance with Institute for Working Futures and Australian universities (22/05/2022)
+Capability.Co strengthened its research and innovation base by formalising partnerships with the Institute for Working Futures and multiple national universities. Leveraging more than 30 years of research behind the Working Futures™ Human Capability Standards, the Sydney-headquartered firm positioned itself as a key connector between academic research and practical workforce solutions, enhancing its credibility and supporting future growth in the human capability and HR services space.
+Capability.Co launches resources hub to scale evidence-based capability insights (18/11/2021)
+Capability.Co launched an online Resources &amp; Publications hub offering whitepapers, research outputs and tools focused on the future of work and human capabilities. The move broadened the company’s reach beyond direct client engagements, positioning the Sydney business as a thought leader and enabling scalable, content-led growth in its human resources and capability development services.</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr"/>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/capability-co/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>CarbonLink</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>New modelling tool used to generate ACCUs for successful soil carbon project (01/02/2021)
+CarbonLink reported that a new modelled measurement tool was used successfully to generate ACCUs for a major soil carbon project, supporting a second round of credit issuance. This suggests operational success and growth in its carbon project delivery capabilities.
+CarbonLink’s model-assisted measurement supports latest round of high-integrity ACCUs issued (01/02/2021)
+CarbonLink highlighted the successful use of model-assisted measurement to support the latest issuance of high-integrity ACCUs for a soil carbon project. This reflects measurable project success and continued growth in its core business.
+Transforming carbon estimation in Australian rangelands (01/11/2020)
+CarbonLink’s rangelands carbon project showcased the company applying and extending its expertise in soil carbon measurement, modelling, and on-ground sampling. The project reflects continued development of its capabilities and operational growth in carbon farming services.
+CarbonLink and Queensland Farmers’ Federation partner to support farmers in the carbon economy (01/06/2020)
+CarbonLink announced a partnership with the Queensland Farmers’ Federation to help farmers navigate the evolving carbon economy. The collaboration strengthens CarbonLink’s market position and suggests growth through strategic partnership.
+CarbonLink International explores licensing opportunities for advanced soil technology (01/08/2019)
+CarbonLink, described as Australia’s leading soil carbon project developer, was exploring opportunities to license its advanced soil technology internationally. This indicates expansion beyond its core Australian operations and potential growth through technology commercialization.</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 4d] QFF hosted a networking event to strengthen relationships between corporate partners and agriculture leaders to support the future of Queensland agriculture.
+[14/05/2026 - 4d] The CarbonLink team finalized a carbon service agreement with the Brown Family for a soil carbon project, marking a partnership aimed at environmental improvement.
+[14/05/2026 - 4d] Details a successful carbon farming project at Cheyenne, indicating financial and environmental gains, showcasing effective management practices.
+[07/05/2026 - 1w] Contribution to the National Soil Carbon Innovation Challenge marks a significant achievement in carbon measurement technology, showcasing innovation.
+[21/04/2026 - 3w] Nick Blomfield discussed insights from a soil carbon project on a national platform, promoting broader industry conversations about carbon farming.</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carbonlink/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>CardiAction</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>CardiAction expands screening network across Australia (18/05/2026)
+CardiAction announced it is expanding its cardiovascular screening network across Australia, indicating commercial growth and broader distribution of its pharmacy-based heart and artery health screening services.
+CardiAction delivers scientifically validated cardiovascular health screening through pharmacies and online (18/05/2026)
+CardiAction's company information highlights a growing service footprint across pharmacies and online channels, with a focus on scaling access to its screening solution and reaching underserved communities.</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] The company discusses its advancements in cardiovascular screening technology and reports successful partnerships with over 200 pharmacy locations in Australia and New Zealand, along with a significant number of screenings completed. They are now seeking to expand globally, indicating a potential growth phase for CardiAction ProScreen.</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cardiaction/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Cardihab</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Ten Years of Cardihab: A Celebration of Shared Purpose (01/02/2026)
+Cardihab marked its tenth anniversary, highlighting its growth from a research prototype into a TGA-registered Class IIa medical device and established digital cardiac rehabilitation company.
+Brisbane MedTech Accelerator program success after the strength of Cardihab (16/01/2025)
+Cardihab was selected for the Brisbane Economic Development Agency’s MedTech accelerator program, aimed at helping local MedTech companies fast-track global investment and market entry through international investor access and strategic partnerships.
+Brisbane medtech businesses selected for global mission (01/01/2025)
+Cardihab was listed among Brisbane medtech businesses supported by the city to accelerate global expansion through an international mission and accelerator initiative.
+New Research Confirms Cardihab participants lived longer, healthier lives and with better value healthcare vs usual care (01/01/2025)
+Cardihab highlighted new evidence showing its digital cardiac rehabilitation program improved survival, quality of life, and cost-effectiveness, strengthening its clinical and commercial position.
+Cardihab to expand virtual rehab program with Bupa partnership (01/05/2024)
+Cardihab partnered with Bupa and Honeysuckle Health to broaden access to its virtual cardiac rehabilitation program for eligible members, extending its insurer distribution and patient reach.
+Cardihab announced as successful grant recipient in $3.7 million ANDHealth+ funding round (01/01/2024)
+Cardihab was named one of four digital health companies to receive a share of $3.7 million in MRFF-backed ANDHealth+ funding, supporting product development, commercialisation, and expansion into global markets.
+A mobile platform for cardiac rehab - CSIRO (01/01/2017)
+CSIRO announced the commercialisation of its cardiac rehabilitation platform as Cardihab, following successful research and venture capital raising, marking the company’s spin-out and launch as a standalone business.</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Celebrating a partnership with GMHBA Limited focused on cardiac rehabilitation.
+[23/04/2026 - 3w] Announcing expansion of partnership with Latrobe Health Services to offer cardiac rehabilitation access.</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cardihab/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>CareVision Pty Ltd (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>CareVision Launches Free ‘Support at Home’ Software to Accelerate Digital Adoption for Small Care Providers (14/04/2026)
+CareVision introduced a free version of its Support at Home care management platform for small aged care, disability and community care providers (teams of up to 10 users). By removing licensing costs and providing an easy entry point to its award‑winning software, the company is expanding its user base, strengthening its position in the home‑ and community‑care technology market, and positioning for future paid upgrades as providers grow.
+CareVision Offers Low‑Risk Digital Pathway for Small NDIS and CHSP Providers (02/03/2026)
+CareVision announced an initiative giving small NDIS and Commonwealth Home Support Programme (CHSP) providers free access to its Support at Home software, framed as a “low‑risk path to digital operations.” The move broadens CareVision’s footprint among smaller providers that have previously been priced out of comprehensive care‑management tools, indicating a growth strategy focused on expanding platform adoption and strengthening its role in the aged care services ecosystem.</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr"/>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carevision/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Cario</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>How Cario hit $2M revenue with an 18 person team in 2025 (01/09/2025)
+A company profile noted that Cario reached $2M in annual revenue in 2025 without outside funding, describing steady growth since its 2018 launch. The article also referenced the company’s bootstrapped status and continued expansion of its freight management software business.
+Cario’s first half 2025 update: building a stronger, smarter freight platform (01/07/2025)
+Cario reported major platform upgrades in the first half of 2025, focusing on increased automation, better connectivity, and more insight across freight operations. The update also highlighted continued investment in carrier, ERP, and WMS integrations, indicating ongoing product and operational growth.</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>[17/05/2026 - 1d] The post discusses Cario's participation in major industry events, building partnerships, and exploring future opportunities in the freight management sector.
+[24/04/2026 - 3w] The post highlights Microsoft's significant investment into AI resources in Australia and the development of new features in their applications.</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cariotechnology/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Central Coast Orthodontics</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Central Coast</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Educational Content Program Grows with Regular Orthodontic Articles and Videos (20/06/2022)
+Central Coast Orthodontics continues to broaden its online footprint through a growing library of orthodontic articles and video resources hosted on its website. The dedicated articles and video sections, updated over multiple years, suggest ongoing investment in patient education and digital marketing, supporting brand growth, patient engagement, and new patient acquisition for its Gosford and Erina clinics.
+Central Coast Orthodontics Expands Clear Aligner and Invisalign Service Offerings (05/08/2021)
+Through updated service and information pages on its site, Central Coast Orthodontics showcases expanded expertise and case capacity in clear aligner therapy, including Invisalign, at both the Gosford and Erina practices. The clinic promotes tailored aligner treatment plans for adults, teens, and eligible younger patients, reflecting strategic growth into higher-demand aesthetic orthodontic services and a more diverse treatment mix.
+Practice Upgrade Brings State-of-the-Art Orthodontic Technology to Gosford and Erina Clinics (10/02/2020)
+Central Coast Orthodontics reports significant investment in clinical infrastructure at both its Gosford (Beane St) and Erina locations, describing the practices as ‘state-of-the-art’ and equipped for advanced treatments such as Invisalign and modern fixed appliances. The upgrades—highlighted across the website’s practice and treatment pages—indicate ongoing capital investment to support higher patient volumes, a broader range of treatment options, and improved diagnostic accuracy.
+Central Coast Orthodontics Opens Modern Erina Practice to Complement Gosford Clinic (15/03/2019)
+Central Coast Orthodontics expanded its presence on the NSW Central Coast by opening a contemporary practice in Erina, adding to its original Gosford location at 1/59 Beane St. The new Erina clinic features updated technology and treatment spaces designed to improve patient comfort and capacity, allowing the group to serve more orthodontic patients from across the region while maintaining its existing Gosford operations.</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr"/>
+      <c r="E54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>ChemSupply Australia Pty Ltd (Chem-Supply), 38-50 Bedford Street, Gillman, SA 5013, Australia</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>ChemSupply Australia secures long-term lease as Gillman industrial asset sells for $15.55 million (18/08/2025)
+An industrial property at 38–50 Bedford Street, Gillman – ChemSupply Australia’s headquarters and main operational site – was sold for $15.55 million via an expressions-of-interest campaign run by Pirie Property Group. The transaction was completed subject to a new 8‑year lease to ChemSupply Australia Pty Ltd, with two further options that can extend occupancy to a total of 24 years. The property offers 13,904 sqm of lettable area in Adelaide’s core industrial precinct, signalling long‑term operational commitment and supporting ChemSupply’s ongoing growth as a key Australian supplier of chemicals, reagents and ingredients.
+ChemSupply Australia recognised among South Australia’s Top 100 businesses by revenue (09/11/2020)
+InDaily’s ‘SA’s Top 100 Businesses’ listing highlighted Chem Supply Australia Pty Ltd as a manufacturer and supplier of chemicals, reagents and ingredients, ranking it among the state’s largest companies by revenue. The listing cited ChemSupply’s 2019 revenue of $177.4 million, reflecting its scale and commercial success in South Australia’s industrial sector and reinforcing its position as a leading chemicals manufacturer based in Adelaide.
+Brand transformation and digital innovation project positions ChemSupply Australia for future growth (01/07/2019)
+Brighter Health (Brighter) delivered a comprehensive brand transformation and digital innovation program for ChemSupply Australia, built around the new tagline ‘Experience. Our Chemistry.’ The project redefined ChemSupply’s brand story, corporate identity and online presence to better communicate its capabilities as a supplier of chemicals, reagents and ingredients to scientific, pathology and manufacturing customers. The refreshed brand and digital platforms were designed to support customer acquisition, national reach and long‑term growth from its Adelaide base.</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr"/>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chem-supply-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Child Wellbeing Centre (Perth, Western Australia, AU)</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr"/>
+      <c r="D56" s="17" t="inlineStr"/>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/child-wellbeing-centre/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Choice Energy</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Large Market Energy Update February 2026 (01/02/2026)
+Choice Energy reported on favorable wholesale electricity pricing and encouraged businesses to reassess procurement strategies, reflecting its ongoing commercial activity and market presence in the energy sector.
+Commercial Solar Power Systems &amp; Installation Melbourne (01/01/2024)
+Choice Energy highlighted that electricity market offers for businesses in Victoria rose by approximately 27% during 2023–24, underscoring its role in helping commercial customers manage rising energy costs and indicating continued business growth in Melbourne.
+PCA partner, Choice Energy, is giving one small business the chance to win $5,000 (28/09/2022)
+Choice Energy partnered with PCA to run a promotion offering one small business a $5,000 prize and a free energy assessment, indicating active partnership-based growth and business development.
+Bowls Victoria partners with Choice Energy (28/09/2022)
+Bowls Victoria announced a partnership with Choice Energy, highlighting Choice Energy’s expertise in energy assessment and support for members, which suggests business expansion through strategic partnerships.</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>[05/05/2026 - 1w] Presentation of a $5K Energy Boost prize to a restaurant, highlighting savings and impact on the business.
+[03/05/2026 - 2w] Discusses how Tripod Farmers invested in solar to reduce costs and emissions, demonstrating strategic decisions for growth.
+[30/04/2026 - 2w] Announcing significant energy savings for Sporties Barooga through a partnership.
+[29/04/2026 - 2w] Meeting discussing strategic direction with insights into the value of partnerships for organizational growth.
+[23/04/2026 - 3w] Announcement of appointment as preferred energy supplier for Choice Hotels, indicating a significant partnership and growth opportunity.
+[22/04/2026 - 3w] Announcement of the Energy Boost winner and total savings identified during the campaign, showcasing impact on local businesses.</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/choiceenergy/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Chris Ho Orthodontics</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr"/>
+      <c r="D58" s="17" t="inlineStr"/>
+      <c r="E58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Claims Advocate (Melbourne, Victoria, Australia)</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr"/>
+      <c r="D59" s="17" t="inlineStr"/>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/claimsadvocacy/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>ClickHome (Level 10, 251 Adelaide Terrace, Perth, WA 6000, Australia)</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>ClickHome Goes Cloud: Making Powerful Building Tools Available (15/03/2024)
+ClickHome, a Perth‑based residential construction management software provider, announced the launch of its new Software‑as‑a‑Service (Cloud) platform. After more than 20 years serving many of Australia’s largest home builders, the company is shifting from an on‑premise model to a scalable cloud offering, expanding accessibility to builders of all sizes and positioning the business for recurring SaaS revenue and national growth.
+ClickHome Highlights Two Decades of Growth Supporting Australia’s Residential Builders (10/11/2023)
+In updated corporate messaging on its website, ClickHome emphasises over 20 years of continuous operation, growing from a Perth software firm into one of Australia’s leading residential construction management platforms. The company now supports builders ranging from those delivering a handful of homes to those delivering thousands annually, reflecting a broadened customer base and sustained market traction in the construction tech sector.
+ClickHome Emphasises National Reach with Offices in Perth and Melbourne (05/06/2023)
+ClickHome notes that, while headquartered in Perth, it has expanded its physical presence with offices in both Perth and Melbourne. This geographic expansion underlines the company’s growth beyond Western Australia and its strategy to better serve residential builders across multiple Australian states.
+ClickHome Scales Home Builder Platform for Builders from 5 to 500+ Homes Per Year (20/02/2023)
+Through its ‘Built for Growth’ positioning, ClickHome promotes that its construction management software now scales from small builders doing around five homes a year to larger firms delivering 500 or more. This reflects product and infrastructure enhancements aimed at supporting higher project volumes, more users, and modular add‑ons, signalling capability to support larger enterprise customers and higher usage loads.
+ClickHome Revenue and Valuation Estimates Point to Strong Business Performance (01/09/2022)
+Prospeo estimates that ClickHome generates annual revenue of approximately US$7.7 million with no external funding and an implied valuation of about US$24.8 million. With an estimated 21–50 employees and high revenue per employee, the figures suggest robust financial performance and efficient operations for the Perth‑headquartered construction software company.</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>[17/05/2026 - 1d] Launch of MyHome mobile application for easier communication and updates between builders and customers.
+[14/05/2026 - 4d] Emphasis on customer engagement through a mobile app that keeps clients updated on their builds, enhancing service delivery.
+[10/05/2026 - 1w] Highlighting how major builders like Metricon and Burbank are using ClickHome to manage greater volumes, indicating scalability.
+[03/05/2026 - 2w] Introduction of the MyHome portal that offers real-time updates for customers to reduce frustration and enhance customer experience.</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/clickhome-_/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>Clinrol</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>Clinrol wins top business awards, celebrates a breakthrough year of innovation and global growth (18/11/2025)
+Clinrol, the Sydney-based health tech company founded in 2020, reported a year of rapid growth marked by multiple national innovation awards and global expansion. The company won the AI Innovation People’s Choice and Tech Innovation People’s Choice at the Finder Innovation Awards 2025 and was also a finalist in the Tech Innovation category. Clinrol was named the New South Wales winner for Embracing Innovation at Telstra’s Best of Business Awards 2025, placed as a finalist in the Australian Technologies Competition (MedTech &amp; Pharma), and received recognition at the iAwards 2025 for its clinical trial recruitment technology. The firm has scaled its operations to support recruitment for over 100 clinical trials across 12 countries, delivering more than 200,000 patient referrals across 65 therapeutic areas, signalling strong international and operational growth.
+Clinrol: The global healthtech startup transforming clinical trial recruitment and patient engagement (01/10/2025)
+An in-depth feature on Clinrol highlights its evolution from an Australian startup into a global healthtech player focused on AI-powered clinical trial recruitment and patient engagement. The article details how Clinrol’s platform automates patient identification, pre‑screening and referrals to make recruitment faster and more inclusive, helping sponsors and research sites reduce administrative workload. It notes that although Clinrol was founded in Sydney, the company now operates globally with active teams across the United States, Asia, South America, the United Kingdom and Europe, and supports studies in dozens of regions and multiple therapeutic areas. This expanded international footprint and scaling of its AI-agentic platform underscore significant business and geographic growth.</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>[29/04/2026 - 2w] Clinrol reflects on a strong start to 2026 during a quarterly catch-up, highlighting momentum in clinical research and plans for product expansion and new market entry.</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/clinrol/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Clintel Systems (Adelaide, South Australia)</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>Medical software leader Clintel Systems expands national footprint with CareRight clinical platform (15/03/2024)
+Adelaide-based Clintel Systems has continued its rapid expansion across Australia, now servicing about 150 healthcare entities nationally with its CareRight clinical software and related solutions. The company manages some of the largest and most complex health sites in the country and has provided 24/7 support for its ExcelCare clinical system, used widely in major metropolitan and regional public hospitals. This growth reflects its success in niche markets such as aged care, acute care, day hospitals, and surgical list management, underpinned by sustained investment in web-based care management and hospital management software over the past decade.</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to promote networking for business opportunities.
+[24/04/2026 - 3w] Celebration of Fernando Mendoza's achievement on LinkedIn.
+[22/04/2026 - 3w] Announcement of new executive roles in LinkedIn's leadership, indicating company strategy and growth potential.</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Code Avengers</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>Code Avengers teams up with Lumify to expand digital skills training across Australasia (06/09/2023)
+Code Avengers announced a partnership with Lumify Learn, part of the Lumify Group, the largest IT training provider across Australia, New Zealand and the Pacific. The collaboration creates a pathway where learners begin on the Code Avengers platform to build foundational coding and digital skills, then transition to Lumify Learn for advanced IT certifications, extending Code Avengers’ reach from school-aged learners to career-focused training across the region.
+Outstanding Contributions to Digital Development: Code Avengers Award (15/11/2019)
+The APNIC Foundation highlighted Code Avengers’ impact on regional technical literacy through an award recognising its outstanding contributions to digital education and coding. The recognition underscores the Hamilton e-learning company’s growing influence in developing digital skills and supporting technical capacity-building across the Asia-Pacific region.
+Kiwi firm Code Avengers exports EdTech to Chile (13/09/2017)
+Hamilton-based Code Avengers secured a breakthrough deal with the Chilean government to provide its online coding and digital literacy curriculum to schools across Chile, including a three-day coding camp for students and teachers on Rapa Nui (Easter Island). The company, which already served over two million students in 15,000 schools and universities worldwide at the time, framed the contract as part of a planned period of rapid growth in New Zealand and overseas.
+IEGF funding broadens markets for Code Avengers (28/09/2016)
+Education New Zealand’s International Education Growth Fund (IEGF) supported Code Avengers’ push into new markets. CEO Mike Walmsley explained that the funding helped scale their online platform that teaches people to build apps, games and websites, and to broaden into related subject areas such as design, positioning the Hamilton firm for product expansion and wider international reach.
+Code Avengers goes global (23/03/2016)
+Waikato News reported that Hamilton-born Code Avengers was "going global" by delivering digital learning solutions to schools worldwide. The company expanded its offering beyond individual online courses to supervised classroom sessions and multi-day Code Camps, supporting students at all levels and signalling strong international growth from its Waikato base.</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>[01/05/2026 - 2w] Summary of successful Code Camps held in Thailand for students, promoting digital skills.
+[21/04/2026 - 3w] Promotional post encouraging schools to use Code Avengers with an offer of a free trial.</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/code-avengers/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>Cognitive View</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Cognitive View considers funding for its global expansion in RegTech (19/07/2021)
+Melbourne-based RegTech firm Cognitive View, founded in 2018, announced plans to raise capital to support global expansion. CEO Dilip Mohapatra stated that the company is accelerating its move into the US and UK markets, with support from the Australian Trade Commission. Cognitive View has broadened its platform to analyse communications across more than 60 collaboration tools and has been listed on multiple marketplaces, including Genesys Cloud, Cisco Webex, Zoom, RingCentral and Redbox. The firm’s goal is to become the leading global provider of collaboration compliance solutions, leveraging increased virtual work to scale efficiently.</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr"/>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cognitiveview/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Compass Immunology Clinic</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>Dr Zi Tan joins Compass Immunology Clinic (01/01/2021)
+The clinic announced a new specialist, Dr Zi Tan, joining its clinics, indicating continued team expansion and strengthening of services.
+A big warm welcome to Dr Sophie Willcocks, Paediatric Immunologist &amp; Allergist who is joining our team in August (01/08/2020)
+Compass Immunology Clinic announced the addition of Dr Sophie Willcocks to its team, signalling growth in clinical capacity and specialist services.</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr"/>
+      <c r="E65" s="16" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>Comply Flow</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>We’re Going Global with Investment NSW! (16/07/2024)
+Comply Flow announced it has joined the Investment NSW Global Export Program to accelerate international expansion, particularly in the UK compliance management market. Leveraging more than 30 years of industry expertise across major infrastructure and construction projects, the company plans to scale its cloud-based safety and compliance platform to new global clients and partners, signalling a strategic growth phase beyond Australia and New Zealand.
+Comply Flow Recognised Among Top Compliance Solutions Companies 2022 (15/09/2022)
+APAC CIO Outlook named Comply Flow as one of its Top Compliance Solutions Companies for 2022. The recognition highlights the company’s rapid growth delivering workforce and supply chain compliance software across large ‘megaprojects’ such as the Sydney Light Rail Upgrade and the Toowoomba Second Range Crossing. The article notes strong uptake of the platform among enterprise clients seeking to streamline contractor management and safety compliance, underscoring both product traction and regional market expansion.
+ComplyFlow Wins BHP #FastTrack Challenge (20/03/2018)
+ComplyFlow announced it was selected as a winner of the BHP #FastTrack innovation challenge, recognising its capabilities in contractor and workforce compliance management for large resource operations. The win provided validation from a leading global mining company and opened opportunities for deeper collaboration and deployment of ComplyFlow’s platform across BHP projects, supporting the company’s growth in the mining and resources sector.</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr"/>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comply-flow/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Continental Water</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>Continental Water news and project updates (01/01/2024)
+Continental Water’s news page highlights active project work, including a drinking water system for Levantine Hill Estate and other installation and service engagements, indicating ongoing business activity and customer growth.
+Continental increasing presence in Australia (01/01/2024)
+Although this article is about Continental more broadly and not Continental Water specifically, it references Continental Australia expanding its presence in the Australian beverage industry. This appears to be a different company and is excluded from the results as a likely name match only.
+Livin' It Up Down Under: Continental Water Systems of Sydney, Australia (15/12/2002)
+This profile on Continental Water Systems of Sydney discusses the company’s operations and notes that the Sydney residential water treatment market was growing, suggesting a favorable growth environment for the business at the time.</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr"/>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/continentalwater/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>Control Systems Technology Pty Ltd (CST), New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Control Systems Technology signs Sales, Service and Manufacturing agreement with Kanawha Scales &amp; Systems for Train Load Out solutions (16/10/2025)
+Control Systems Technology (CST), the NSW-based specialist in conveyor belt weighing and industrial instrumentation, announced a Sales, Service and Manufacturing agreement with US firm Kanawha Scales &amp; Systems focused on Train Load Out (TLO) systems. The partnership is designed to combine CST’s belt weighing and load-out expertise with Kanawha’s established presence in bulk material handling, expanding CST’s product reach into new international markets and strengthening its capabilities in large-scale rail loading projects. This collaboration signals growth via international partnership and an expanded service offering in the mining and minerals processing sector.
+Control Systems Technology expanding headcount amid continued demand for conveyor weighing solutions (01/03/2025)
+A company profile and data listing for Control Systems Technology shows the NSW-based industrial machinery and equipment manufacturer increasing its workforce to more than 100 employees, with multiple new hires recorded over the previous 12 months. The information reflects ongoing expansion driven by demand for CST’s underground environmental monitoring and conveyor belt weighing systems, and supports its positioning as a world leader in in-motion belt weighing technology.
+Innovation down under: CST and the growth of Australian METS (15/02/2024)
+An Austmine article profiling Control Systems Technology (CST) highlights the company as an example of an innovative Australian METS business that has become a world leader in belt weighing technology. Managing Director Ian Burrell discusses CST’s ongoing investment in research and development, international project delivery, and its role in strengthening Australia’s mining technology exports. The coverage positions CST as a growth-oriented firm contributing to the global competitiveness of Australian METS through technology leadership and export-led expansion.
+CST emphasises engineered, custom high-end belt weighing systems and national service footprint (01/07/2023)
+In a feature article highlighting its growth since inception, Control Systems Technology (CST) underscores its position as a specialist provider of precision, high-end belt weighing systems for the mining and minerals processing industries. The piece notes that CST has developed a unique engineered method for analysing applications and recommending custom-made belt weighing equipment, and it has built a network of sales and service offices throughout Australia staffed by highly trained technicians. This reflects sustained growth in engineering capability, product sophistication, and national service coverage, reinforcing CST’s status as a leading Australian METS (mining equipment, technology and services) supplier.</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>[11/05/2026 - 1w] Post-Indonesia Miner 2026 wrap-up thanking visitors and reinforcing the new partnership with Aequus Solutions to strengthen service capability.
+[04/05/2026 - 2w] Announcement of Aequus Solutions as an exclusive service partner for CST in Indonesia, aiming for enhanced service offerings.
+[04/05/2026 - 2w] Announcement of Aequus Solutions as CST's exclusive service partner, emphasizing local support and service enhancements.
+[30/04/2026 - 2w] Announcement of Aequus Solutions as the exclusive service partner in Indonesia, improving support and maintenance for CST's systems.</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/control-systems-technology/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>akunah</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>Akunah’s QUASR Data Analytics Offshoot Showcases Global Impact in AR-Enabled Shoulder Surgery (15/03/2024)
+In a feature on augmented reality in surgery, Materialise highlighted Akunah as the data-analytics and computer‑modelling engine behind QUASR (Queensland Unit for Advanced Shoulder Research). The article notes that Akunah’s advanced modelling tools are now used to plan both primary and complex revision arthroplasty for clients and customers globally, underscoring the company’s international reach and its role in driving next‑generation surgical planning workflows.
+Brisbane Medtech Firm Akunah Selected for City-Backed Global Accelerator Program (22/08/2023)
+The Brisbane Economic Development Agency named Akunah among eleven homegrown medtech companies chosen for its MedTech Global Accelerator program. The six‑month curriculum is designed to help participants fast‑track global expansion, attract investment, and support job creation in Brisbane. Akunah’s selection signals recognition of its growth potential and positions the company for accelerated international scaling of its AI‑driven digital health platform.
+REDI Fellowship Places Data Science Expert at Brisbane Med‑Tech Company Akunah (10/11/2022)
+The Australian Research Council’s Joint Biomechanics initiative announced that Dr Laith Alzubaidi would spend eight months embedded with Brisbane‑based med‑tech company Akunah under a REDI Fellowship. The collaboration aims to support the growth of Australia’s medical products sector by combining advanced data science with Akunah’s surgical planning and analytics platform, representing both a talent acquisition boost and a deep R&amp;D partnership for the company.
+Akunah Expands from Brisbane Base to Serve Global Healthcare and Surgical Clients (05/06/2021)
+In an updated corporate overview, Akunah reported that its operations, originally founded in Brisbane, have expanded to make a global impact. The company now delivers AI‑powered clinical data platforms, surgical planning tools, and cloud‑based communication solutions to customers worldwide, positioning Akunah as a trusted partner in intelligence‑driven healthcare beyond Australia.</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>[16/05/2026 - 2d] Announcement of upcoming product launches at an event, indicating new product development.
+[15/05/2026 - 3d] Participation in a major industry congress showcases recent product launches and collaboration within the healthcare sector.</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/akunahau/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>asBuilt</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>The First Ever 'Connected Construction Site' in New Zealand (28/01/2020)
+asBuilt partnered with Microsoft, Spark and NZ Strong to deliver New Zealand’s first connected construction site, using IoT devices, Azure cloud, Power BI, drones and digital twin technology to improve safety, reduce costs and enable real-time collaboration across the project lifecycle.</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr"/>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/asbuilt/posts/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GOWT_mid_low.xlsx
+++ b/GOWT_mid_low.xlsx
@@ -41354,7 +41354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -43403,6 +43403,1815 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>CoolDrive</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>CoolDrive Expands Battery Offerings with VARTA (18/05/2026)
+CoolDrive Auto Parts expanded its product range by introducing the globally recognised VARTA automotive battery line, signaling continued growth in its automotive aftermarket offering and product portfolio.
+CoolDrive Breaks Ground on New Head Office and Distribution Centre (23/10/2025)
+CoolDrive Auto Parts began construction on a new head office and national distribution centre in Boronia, Victoria. The project will consolidate three Melbourne distribution centres into one larger, more automated facility, improving logistics efficiency and supporting future growth.
+Success for CoolDrive at the AAAE (23/04/2024)
+CoolDrive showcased its products at the 2024 Australian Auto Aftermarket Expo and won an Auto Aftermarket Excellence Award for the GYS Powerduction 37LG. The event highlighted the company’s strong industry presence and ongoing momentum.</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - today] Opening of CoolDrive's second South Australian branch in Melrose Park for improved delivery service.
+[18/05/2026 - 1d] John Blanchard recognized with the Outstanding Service to Industry Award at the awards ceremony.
+[16/05/2026 - 3d] Recap of the expo week and mentions of multiple awards won by CoolDrive.
+[15/05/2026 - 4d] Recognition at the Australian Auto Aftermarket Expo for winning Best Stand over 36m2.</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cooldrive-distribution/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Corporate Protection</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>Corporate Protection positions itself as Australia’s largest privately owned emergency services company (01/01/2024)
+Corporate Protection’s corporate website states that the business is Australia’s largest privately owned emergency services company, highlighting its scale and sustained business growth over more than 25 years in operation.
+Corporate Protection expands international services across Southeast Asia and the Pacific Rim (01/01/2007)
+Corporate Protection announced the establishment of Corporate Protection International (CPI) in 2007 to serve international demand with a broader suite of services, including induction, medical, emergency response, security, training, and consultancy across Southeast Asia and the Pacific Rim. This indicates geographic and service-line expansion for the Brisbane-headquartered company.</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - today] Corporate Protection is hiring for leadership roles in Maritime Security, indicating expansion of their team and service offerings.
+[18/05/2026 - 1d] Corporate Protection announces a new hiring opportunity for a Paramedic in Brisbane, indicating team growth.
+[18/05/2026 - 1d] Corporate Protection announces another hiring opportunity for a Paramedic, further signifying ongoing recruitment efforts.</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corporate-protection/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>CoverTel Telecommunications Group</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>CoverTel and Phase Pacific join forces to accelerate growth and expand customer reach (01/03/2024)
+CoverTel Telecommunications Group announced a strategic collaboration with Phase Pacific, a Melbourne-based company specialising in network integrity, software integrity and automation. The partnership aims to accelerate Phase Pacific’s growth while enabling CoverTel to explore new customer segments and broaden its market reach by combining complementary product portfolios and technical capabilities. The collaboration underscores CoverTel’s expansion strategy in advanced test, measurement, and network solutions for telecommunications and related industries.
+Phase Pacific and CoverTel join forces to enhance network solutions across Australia (01/03/2024)
+In a joint announcement, Phase Pacific and CoverTel Telecommunications Group detailed their new strategic partnership focused on delivering enhanced network solutions. CoverTel, founded in 2002 and headquartered in Melbourne, will leverage its established presence across sectors such as Oil, Mining, Gas, Rail, Energy, Utilities, Defence, IT and Telecom to extend the reach of Phase Pacific’s network integrity and automation offerings. The collaboration is positioned as a growth initiative for both companies, strengthening CoverTel’s solution portfolio and reinforcing its role as a leading telecommunications solutions provider in Australia.
+CoverTel continues multi‑sector expansion as a trusted supplier of telecoms and network solutions (01/01/2024)
+CoverTel highlights ongoing growth as a trusted supplier to major Telecommunications and Utility providers across Australia and the Pacific Islands, reflecting more than 20 years of continuous expansion. The company notes that its extensive product portfolio has enabled it to grow beyond core telecommunications into Defence, Data Centres and Enterprise markets. This diversification into new verticals and broader infrastructure, monitoring, and test-and-measurement offerings signals sustained business expansion and a strengthening market position for the Melbourne‑headquartered firm.</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr"/>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/covertel-telecommunications-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Customer Radar</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>What customer feedback tells us (04/11/2015)
+Customer Radar announces it has captured its one‑millionth piece of customer feedback in five years, with more than 1,000 active feedback ‘measures’ (stores, departments or people) on the platform. Founder Mat Wylie notes that, based on accelerating uptake, the next million responses are expected in under 12 months. The company also signals plans to expand beyond New Zealand into Australasia and other English‑speaking markets, underscoring strong user growth and international expansion ambitions.
+'Customer radar' in real time (17/09/2013)
+Interest.co.nz profiles Customer Radar’s cloud‑based real‑time customer feedback software as a disruptive alternative to traditional market research. The piece details how the platform provides live dashboards and alerting for negative feedback, enabling quicker service recovery and better decision‑making for client businesses. The coverage raises the company’s profile in the business support services and SaaS sectors and signals market traction for its technology.
+Radar homes in on customers (02/07/2013)
+Profile of Auckland-based Customer Radar, founded by advertising executive Mat Wylie, describing how the company’s real‑time feedback platform is enabling businesses to capture customer opinions via text and web apps. The article highlights the firm’s technology-driven shift from a traditional advertising background into scalable business support services, positioning Customer Radar for growth in the customer experience and feedback analytics market.</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr"/>
+      <c r="E74" s="16" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>Cyber Risk</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr"/>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to empower underrepresented founders and build networks.
+[27/04/2026 - 3w] LinkedIn is the most-cited domain on AI search engines, indicating growth in professional visibility.
+[22/04/2026 - 3w] Announcement of new leadership roles within LinkedIn, indicating growth and opportunity.</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>Dan Smethurst Orthodontist</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>Dan Smethurst Orthodontist Recognised as Diamond Invisalign® Provider in Tauranga (01/03/2023)
+Dan Smethurst Orthodontist has been recognised as a Diamond Invisalign® provider, reflecting a very high volume of completed Invisalign cases and strong clinical expertise. The status—highlighted on the practice’s Invisalign-focused pages and patient success materials—indicates sustained growth in clear-aligner treatments and positions the clinic as a leading provider in Tauranga and the Bay of Plenty region.
+Remote Dental Monitoring Service Introduced to Support Invisalign Growth at Dan Smethurst Orthodontist (15/06/2022)
+Dan Smethurst Orthodontist has implemented Dental Monitoring, a smartphone-based remote orthodontic tracking system, to support its expanding Invisalign patient base. By allowing the specialist orthodontist to review progress more frequently without in-person visits, the practice increases capacity, improves convenience for patients, and enhances its digital-care capabilities—signs of operational and service expansion.
+Dan Smethurst Orthodontist Highlights Hundreds of Successful Invisalign Cases in Tauranga and Bay of Plenty (10/10/2021)
+Through its ‘Patient Success’ and ‘Before and After’ galleries, Dan Smethurst Orthodontist showcases hundreds of completed Invisalign and orthodontic treatments from Tauranga and the wider Bay of Plenty. The volume of documented cases and testimonials points to strong and sustained patient demand, underpinning the practice’s growth and reinforcing its reputation as a leading orthodontic provider in the region.</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr"/>
+      <c r="E76" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>Darzin Software Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>Darzin highlighted as Australia’s trusted name in stakeholder engagement software with global customer base (01/06/2021)
+Darzin describes itself as Australia’s trusted name in stakeholder engagement software, now serving customers around the world with a team of developers, designers, information architects, UX specialists, business analysts, engineers and testers. The emphasis on an expanded multidisciplinary team and global clients indicates sustained growth in headcount and market reach since its founding in 2004.
+Darzin profiled as growing SaaS employer with 11–50 staff (01/05/2021)
+Startup and tech‑employer directory Matchstiq lists Darzin as a Sydney‑based SaaS company with 11–50 employees and positions it as Australia’s trusted name in stakeholder relationship management. The profile underscores the company’s evolution from a small founder‑led business in 2004 to a larger, established SaaS employer with growing staff numbers and ongoing hiring needs.
+Darzin recognised as feature‑rich, easy‑to‑use stakeholder engagement platform with clients across the globe (01/03/2021)
+Industry review site FeaturedCustomers profiles Darzin as one of the most feature‑rich and easy‑to‑use stakeholder engagement platforms on the market, noting that the company has clients across the globe. The recognition and international customer base point to product maturity, market traction and ongoing commercial growth for the Sydney‑based software company.
+Simply Stakeholders brand becomes parent company, expanding beyond original Darzin product (01/04/2020)
+Simply Stakeholders (the parent company founded around the original Darzin product) now positions Darzin as its original stakeholder engagement platform while building a broader global suite of stakeholder software. This signals growth from a single-product firm into a multi‑product, global stakeholder software company, highlighting expansion in product scope and international reach.</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr"/>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/darzin-software/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Data Capture Experts</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>Data Capture Experts Announces Three New Appointments to Board of Directors (22/04/2024)
+Melbourne-based Data Capture Experts, a fast-growing healthcare technology company, appointed three new board directors—Vicki Gillespie (as Chair), John Papatheohari and Andrew Harris—to accelerate growth, innovation and geographic expansion of its DC2Vue digital health platform across Australia and beyond.
+Data Capture Experts Appoints Danny Lindrea as Chief Digital Health Officer (28/11/2023)
+Data Capture Experts strengthened its executive leadership team by appointing experienced digital health leader Danny Lindrea as Chief Digital Health Officer, supporting the company’s strategy to scale its next-generation DC2Vue care coordination platform and advance connected healthcare.</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcement of a partnership with Serena Williams and Reckitt to support underrepresented founders and emphasize the importance of networking.
+[27/04/2026 - 3w] Information about LinkedIn being the most cited domain for professional queries, indicating growth in market presence.
+[22/04/2026 - 3w] Announcement of new leadership positions at LinkedIn, indicating future opportunities for growth.</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>DataTorque</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>TIN Member Spotlight highlights DataTorque’s rapid revenue growth and $60m in new contracts (15/09/2023)
+Technology Investment Network’s member spotlight on DataTorque reports that the Wellington‑headquartered tax and revenue management software company has appeared four times on TIN’s Absolute IT Supreme Scale-Ups list. The article notes 26% revenue growth since 2020 and more than NZ$60m in contracts signed since 2018, reflecting strong international expansion of its Commercial Off‑the‑Shelf Revenue Management System, now deployed to support tax collection in 16 countries across the Pacific, Africa, the Americas and Europe.
+Private equity investment by Simplicity backs DataTorque’s next growth phase (09/03/2023)
+Law firm MinterEllisonRuddWatts advised Wellington-based DataTorque on selling a minority stake to the private equity fund of Simplicity, a major New Zealand non‑profit KiwiSaver and investment fund manager. The investment is positioned as growth capital to help the company scale its leading tax technology and revenue management solutions, which already support more efficient public revenue collection in 16 countries worldwide.
+DataTorque profiled as fintech transforming economies with people‑centred digital tax systems (10/11/2022)
+A See Tomorrow First profile describes Wellington-based fintech DataTorque as transforming economies by engineering people‑centred digital solutions for public revenue collection. The article emphasises the company’s growing global footprint and role in modernising tax systems for governments, reinforcing its reputation and positioning that support further international expansion.</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr"/>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/data-doctors-nz-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>Datarwe</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>Datarwe acknowledged as exemplar in AI-enabled healthcare industry report (01/09/2022)
+Datarwe was highlighted as the exemplar in a major publication on AI-enabled healthcare, recognised for its precision data platform that underpins development of AI clinical diagnostic tools. The report showcases Datarwe as one of nine knowledge-based emerging seed industries in Queensland, reinforcing its leadership position and supporting future growth and investment opportunities.
+Datarwe relocates HQ to Gold Coast Health &amp; Knowledge Precinct and scales AI healthcare platform (04/02/2022)
+A Lumina/Gold Coast Health &amp; Knowledge Precinct case study notes that Datarwe, founded in 2019, rapidly expanded after relocating its headquarters to the Precinct in 2020. The company’s precision medicine data platform is being rolled out to 14 Queensland hospital sites, with national and international deployments in the pipeline, and is involved in a high‑profile collaboration with MIT on the MIMIC critical care database—highlighting expansion, partnerships and market traction.
+Datarwe collaborates with Queensland Health on Nursing Acuity Dashboard (01/10/2021)
+Datarwe’s website highlights a collaboration with Queensland Health to develop a Nursing Acuity Dashboard that uses real‑world ICU data to improve workflow efficiency. The project demonstrates increased adoption of Datarwe’s AI-driven data service platform within the public health system and broadens its solution portfolio for acute care environments.
+Datarwe opens new AI lab within Cohort at Gold Coast Health &amp; Knowledge Precinct (15/03/2021)
+Datarwe announced the opening of a dedicated AI lab within the Cohort Innovation Space at the Gold Coast Health &amp; Knowledge Precinct. The facility is designed to support collaborative R&amp;D with clinicians, researchers, and industry partners, expanding Datarwe’s physical footprint and R&amp;D capacity in AI-enabled healthcare data services.
+Datarwe launches Clinical Data Nexus to connect hospitals and med‑tech innovators (01/11/2020)
+The Queensland AI Hub profiled Datarwe’s launch of its Clinical Data Nexus (CDN) in late 2020, a curated and enriched real‑world clinical data platform for hospitals, clinicians, researchers, and AI/ML developers. The article highlights Datarwe’s rapid team growth to around 24 employees across Australia and WA and its role enabling faster, more cost‑effective AI‑enabled medical innovation—signalling both product and headcount expansion.
+KJR helps Datarwe build secure multi-layered clinical data access platform (01/06/2020)
+Technology consultancy KJR detailed its partnership with Datarwe to architect and deliver a secure, multi-layered data access platform for high-quality clinical data. The collaboration strengthened Datarwe’s core product—the clinical data-sharing platform that underpins AI models—representing a key strategic technology partnership supporting scalable growth.
+Datarwe receives $1.5M funding boost from Queensland Government (30/04/2020)
+The Queensland Government, through the Advance Queensland initiative, invested $1.5 million in Datarwe to accelerate development of its Precision Medicine Data Platform. The funding supports the company’s acute care medical research data platform that uses de-identified ICU data to enable AI-enabled clinical diagnostic tools, cementing Datarwe’s role as a key public‑private partner with Queensland Health and ecosystem partners like AWS, KJR and TechConnect.</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to enhance networking and support underrepresented founders.
+[22/04/2026 - 3w] Announcement of new leadership roles for Daniel Shapero and Mohak Shroff at LinkedIn, indicating organizational growth.</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>Delta Hydraulics (Tasmania, Australia)</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Tasmania</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>Prime Minister visits Delta Hydraulics’ Devonport plant after landmark energy MoU (15/12/2020)
+Following the signing of an energy supply memorandum of understanding between the Australian Prime Minister and the Tasmanian Premier, Prime Minister Scott Morrison visited Delta Hydraulics’ Devonport facility. The visit highlighted Delta Hydraulics as Australia’s largest independent hydraulic component manufacturer (established in 1975) and underscored the company’s importance to regional advanced manufacturing and future growth supported by secure energy supply.
+Industry profile: John White highlights resilience and innovation at Delta Hydraulics’ Devonport facility (01/03/2019)
+An industry feature on founder and Managing Director John White described Delta Hydraulics’ Devonport plant as central to ongoing innovation in hydraulic cylinder technology, including products like the Delta‑C cylinder designed to extend service life in harsh environments. White stressed that the resilience of the Tasmanian manufacturing base is crucial for supplying advanced products to Australian transport equipment manufacturers, reinforcing the company’s commitment to R&amp;D‑driven growth from its home facility.
+Merger consolidates Delta Hydraulics Group with White Hot Industries to drive growth (02/07/2018)
+Jason Bresnehan completed a merger of two related‑party businesses within the John White Group, bringing together Delta Hydraulics Group and White Hot Industries Group. The transaction consolidated Delta Hydraulics Pty Ltd in Devonport—described as a world‑leading manufacturer and innovator of telescopic and industrial hydraulic cylinders—with its related operations, aiming to create efficiencies, strengthen global supply to industries such as underground mining and transport, and support continued expansion from the Tasmanian base.
+Delta Hydraulics upgrades Tasmania factory to become high‑tech telescopic cylinder hub (01/09/2016)
+Delta Hydraulics invested approximately $2 million to upgrade its Devonport, Tasmania manufacturing facility, installing high‑tech skiving‑burnishing machines, friction welders, CNC lathes and CNC turning units. The upgrade supports a strategic shift: standard, off‑the‑shelf cylinder production has been moved to a newer Thailand factory, while the Tasmanian plant is positioned as the company’s specialised, value‑added manufacturing centre and an unofficial high‑tech telescopic cylinder hub for the Southern Hemisphere.
+Delta Hydraulics marks 40 years as Australia’s largest independent hydraulics manufacturer (01/06/2015)
+On its 40th anniversary, Delta Hydraulics was profiled as Australia’s largest independent maker of hydraulic components. The coverage emphasised the company’s long‑term growth from its Tasmanian origins into a major national and international supplier, with ongoing plans to pursue opportunities in Thailand and China, reflecting both sustained financial resilience and international expansion ambitions rooted in its Devonport operations.</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr"/>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delta-hydraulics-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>DermCo</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr"/>
+      <c r="D82" s="17" t="inlineStr"/>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dermco-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>DermEd (Brisbane, AU)</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr"/>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>[05/05/2026 - 2w] Dr Manoharan presents at Cutera University, highlighting partnerships and collaboration in education.
+[28/04/2026 - 3w] High interest in observership programs leads to opening more application slots, indicating team growth and demand.</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dermed-laser-education/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>Diverseco</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>South Australia</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Diverseco builds national presence in robotics, intralogistics and automation (01/03/2024)
+Positioning itself as an industry leader in robotics, intralogistics and automation, Diverseco reports over 30 years of growth built on cutting‑edge weighing and automation technologies along with maintenance and calibration services. The company emphasises that its products and services enable Australian companies to improve efficiency and scale through turnkey solutions. This ongoing evolution from a weighing-focused business into a broader automation and service provider demonstrates continued strategic growth in both capabilities and market positioning.
+Growth drives Diverseco rebrand (01/07/2016)
+Diverseco announced a major organisational rebrand to unify its portfolio companies – AccuWeigh, Robot Technologies-Systems Australia, AccuPak, AccuOnboard, SCACO and Ultrahawke – under the single Diverseco name. CEO Brenton Cunningham said the move was driven by a goal to grow the group from a mid-$40 million business to a $100 million business, and to create greater cohesion across its weighing, dimensional measurement, robotics automation, end‑of‑line packaging and product inspection operations. The rebrand coincided with the establishment of Diverseco South‑East Asia, based in Singapore, signalling international expansion ambitions.
+Diverseco expands through serial acquisitions in weighing and automation (01/01/2016)
+Diverseco’s history highlights sustained expansion in the machinery and equipment space via multiple acquisitions aligned to weighing and automation. Building on AccuWeigh’s growth – including being listed in BRW’s Fast 100 Companies in 2000 – the group acquired Ultrahawke in 2000, Queensland Weighing Machines in 2004, Independent Scales NZ and Budpak in 2006, Scale Components in 2009, Colonial Weighing in 2010, Sydney Weighbridges in 2015, and Robot Technologies Systems in 2016. These deals have broadened Diverseco’s geographic footprint across Australia and New Zealand and deepened its capabilities in weighbridges, industrial weighing, packaging and automation systems, reflecting a long‑term growth strategy.
+SCACO parent Diverseco acquires Robotic Technologies Australia as part of national expansion (01/12/2015)
+Diverseco, the parent company of SCACO, acquired Melbourne-based Robotic Technologies Australia, a leading robotics and automation business, as part of a broader national growth strategy built on targeted acquisitions. The purchase brought the number of acquisitions completed by managing director Brenton Cunningham to ten, following the acquisition of Sydney Weighbridges the previous year. With AccuWeigh remaining the core business and accounting for about half of group turnover, Diverseco’s annual revenue exceeded $40 million and was forecast to reach $45 million, underscoring strong financial and operational growth in its weighing, packaging and automation portfolio.</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 5d] Diverseco attended the unveiling of a new project by C2 Robotics, showcasing partnership and innovation in automation.
+[08/05/2026 - 1w] Diverseco revives Accuweigh as a dedicated brand for weighing solutions, emphasizing commitment to industry.
+[24/04/2026 - 3w] Diverseco announces completion of a weighbridge installation for City Circle Group, showcasing successful project execution.
+[23/04/2026 - 3w] Diverseco welcomes Paul Mason as the new CEO of Robotics Australia Group, indicating leadership stability.
+[20/04/2026 - 4w] Diverseco showcases their exhibit at the Robotics Expo, discussing future projects, including a 'Factory of the Future.'</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diverseco/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Dogcity Daycare (Adelaide, SA, Australia)</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>Dogcity Daycare continues metro expansion with new Ridgehaven centre (15/03/2023)
+Dogcity Daycare, Adelaide’s largest doggy daycare provider, has expanded beyond its original Kent Town headquarters by opening a new Ridgehaven location in Adelaide’s north-east. The Ridgehaven centre, listed at 6 Norma Avenue with dedicated contact details and booking portal, adds to existing sites in Kent Town, Thebarton, Keswick and Hampstead Gardens. This fifth site strengthens Dogcity’s metro footprint, increases capacity for daycare and grooming services, and reflects sustained demand for their force‑free, enrichment-focused daycare model.
+Dogcity Daycare grows to four-location network across Adelaide (18/06/2022)
+Lifestyle outlet Glam Adelaide profiled Dogcity Daycare’s growth to a four-site network—Hampstead Gardens (NORTH), Keswick (SOUTH), Kent Town (EAST) and Thebarton (WEST)—as part of coverage of an open day at the Kent Town facility. The article highlights Dogcity’s status as a leading doggy daycare provider in South Australia, notes strong customer demand reflected in discounted multi-visit packs, and emphasises that daycare credits are valid across all four locations, signalling operational scale and integrated services across metropolitan Adelaide.
+Dogcity Daycare builds leading position with multi-site operations and force‑free accreditation (01/12/2021)
+Dogcity Daycare’s own company information describes it as the largest and leading provider of doggy daycare in South Australia, supported by multiple locations (Kent Town, Thebarton, Keswick, Hampstead Gardens and later Ridgehaven), an International Force‑Free accreditation, custom indoor facilities, structured puppy socialisation programs, and value‑added offerings like lunch orders and birthday parties. While not a single news event, this profile evidences sustained growth through geographic expansion, service diversification, and professional accreditation in the recreational pet services sector.</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr"/>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dogcity-daycare/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Dr Deb Harris, University Drive, Callaghan, Newcastle University, New South Wales 2308, AU</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>Professor Deborah Harris recognised as internationally recognised nursing and midwifery researcher (01/01/2026)
+Profile information from the University of Newcastle highlights Professor Deborah Harris’s standing as an internationally recognised researcher with expertise across neonatal care and the nurse practitioner workforce, indicating professional growth and recognition.
+Professor Deborah Harris profile highlights leadership in nursing and midwifery research (01/01/2026)
+The University of Newcastle profile notes Deborah Harris’s senior leadership and research expertise, including her role across nursing and midwifery research areas, suggesting continued professional advancement and institutional growth.</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 5d] An initiative by the Breathe 4 Bub program aimed at addressing asthma in Aboriginal women, showcasing community-driven research.
+[08/05/2026 - 1w] A volunteer mentor supporting students in Hong Kong through the I2N program, highlighting partnerships between businesses and educational institutions.
+[07/05/2026 - 1w] An open day event bringing together leaders and innovators from the Upper Hunter region to discuss future planning and investment opportunities.
+[03/05/2026 - 2w] The successful completion of the first TEDx salon in Newcastle, inspiring community engagement and discussion.
+[29/04/2026 - 2w] A local volunteer group raises significant funds for cancer research; a contribution towards advancements in medical research.
+[23/04/2026 - 3w] A visit from NHMRC representatives to discuss culturally safe healthcare practices, emphasizing community involvement in healthcare.
+[23/04/2026 - 3w] Launch of a blueprint for FEE-FREE University Ready programs, showcasing the university's commitment to enhancing educational access.
+[22/04/2026 - 3w] Official opening of a building on Mann St in Gosford, signifying business expansion and community development.</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/university-of-newcastle/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>Dr Eva Low</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>Dr Eva Low joins Sydney Health Executive Education’s public profile as a highly experienced orthodontist (--/--/----)
+A public profile highlights Dr Eva Low as a highly experienced orthodontist with over 20 years of practice, indicating established professional growth and recognition within the Sydney health education network.
+Liverpool Orthodontics profiles Dr Eva Low as a specialist orthodontist serving Liverpool NSW (--/--/----)
+Liverpool Orthodontics features Dr Eva Low on its site, noting her long-standing practice and specialist orthodontic expertise, which suggests continued practice growth and established presence in the local market.
+Orthodontics Australia lists Liverpool Orthodontics practice with Dr Eva Low (--/--/----)
+The Orthodontics Australia practice directory includes Liverpool Orthodontics and notes Dr Eva Low’s years of practice and University of Sydney training, supporting visibility and credibility for the Liverpool-based clinic.</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr"/>
+      <c r="E87" s="16" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>EC Group Pty Ltd (Unit 10, 24 Vore Street, Silverwater NSW 2128, Australia)</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>Apprenticeship and Undergraduate Hiring Underscore EC Group’s Growth in Sydney (01/06/2024)
+EC Group, headquartered in Silverwater, NSW, has highlighted the expansion of its apprenticeship programs and undergraduate engineer positions as a central driver of the company’s growth. In its updated ‘About Us’ materials, the firm notes that structured early‑career recruitment, combined with a focus on diversity and ongoing training, has supported its rise to being recognised nationally as a market leader in building automation innovation, energy management and technical support across the commercial, health, hotel, retail, education and industrial sectors. While no specific intake numbers are disclosed, the emphasis on growing engineering talent signals continuing workforce expansion and demand for its services.</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr"/>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ec-group-ecgroup/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>ELPRO Technologies</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>Aquamonix acquires ELPRO Technologies from Eaton (01/08/2021)
+Aquamonix announced its acquisition of ELPRO Technologies, indicating ELPRO’s 35-year legacy would continue and that its products and services would remain globally available. The announcement suggests business continuity and growth through ownership change and continued market reach.</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>[17/05/2026 - 2d] Attended ISHM Conference to showcase ELPRO Quantum Ecosystem with substantial interest from industry leaders, highlighting collaboration opportunities.
+[10/05/2026 - 1w] Discussed the evolution of industrial wireless systems, promoting the ELPRO Quantum Ecosystem as a key technology for future industrial automation.
+[24/04/2026 - 3w] Showcased innovations and strengthened partnerships at major industry events, indicating a strong market interest and alignment to industry needs.
+[20/04/2026 - 4w] Returned from a successful trip to the USA with positive market feedback on the Quantum Ecosystem, emphasizing global expansion and partner engagement.</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elprotechnologies/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>ESP (Auckland, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr"/>
+      <c r="D90" s="17" t="inlineStr"/>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/data-doctors-nz-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Eden Orthodontics</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr"/>
+      <c r="D91" s="17" t="inlineStr"/>
+      <c r="E91" s="16" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Electrical Engineering Equipment</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr"/>
+      <c r="D92" s="17" t="inlineStr"/>
+      <c r="E92" s="16" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Electronic Component Distributor (Australia)</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr"/>
+      <c r="D93" s="17" t="inlineStr"/>
+      <c r="E93" s="16" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Elisa Systems Pty Ltd (21 Smallwood St, Underwood QLD 4119, Australia)</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>NEW AND IMPROVED SESAME KIT (15/03/2024)
+Elisa Systems announced an upgraded sesame allergen ELISA kit with improved sensitivity and performance for food manufacturers and laboratories. The new version enhances detection limits and robustness, strengthening the company’s product portfolio in allergen diagnostics and supporting growth in its core testing markets.
+New Elisa Systems Total Milk Kit (10/11/2023)
+Elisa Systems released a new Total Milk ELISA kit designed to detect milk proteins in a wide range of food matrices. The product expands the company’s allergen testing range and positions it to capture more demand from manufacturers needing comprehensive dairy allergen monitoring, indicating ongoing product-line expansion.
+Elisa Systems test kits helping to solve an international puzzle (05/06/2023)
+Elisa Systems highlighted that its allergen test kits were used by investigators in an international food safety case, demonstrating the reach and real‑world impact of its technology. The exposure reinforces the company’s global credibility and supports growth through increased recognition and potential new international customers.
+New sensitive peanut kit (20/02/2022)
+Elisa Systems introduced a highly sensitive peanut allergen ELISA kit aimed at detecting very low levels of peanut contamination in foods. This launch broadens its allergen testing portfolio, improves its competitive positioning in global diagnostics, and supports revenue growth by meeting rising regulatory and customer sensitivity requirements.</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr"/>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elisa-systems-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>EllisCo (Auckland, NZ – leisure, travel &amp; tourism)</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr"/>
+      <c r="D95" s="17" t="inlineStr"/>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/data-doctors-nz-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Elumina eLearning</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>Elumina highlights rapid company growth and investment in people on revamped careers page (01/03/2024)
+On its careers page, Elumina eLearning emphasises "rapid growth" driven by continuous learning and notes increased investment in staff development and new opportunities. The messaging reflects ongoing expansion and an active hiring posture as the company scales its operations in digital assessments and online learning.
+Elumina eLearning targets 50 million global learners with scalable digital assessment platform (23/02/2024)
+Elumina eLearning, an Australian-owned edtech company headquartered in Sydney, has articulated an ambitious growth mission to power education outcomes for 50 million learners globally by 2025. The company highlights rapid expansion of its digital assessment solutions for universities, medical colleges, professional associations and government bodies, underscoring strong demand for scalable, customisable online assessment software.
+Elumina eLearning scales high-stakes assessment delivery to over 500,000 exams per year (23/02/2024)
+According to its Australian EdTech Directory profile, Elumina eLearning now delivers more than 500,000 high‑stakes assessments annually for global educational institutions, medical colleges, universities, professional associations and government agencies. This volume milestone reflects substantial platform adoption and operational scale in the digital assessment market.
+Elumina eLearning grows to 100+ staff supporting global assessment clients (23/02/2024)
+Elumina eLearning reports a team of more than 100 employees supporting its digital assessment, online learning and enterprise solutions. The headcount figure, noted in its Australian EdTech Directory listing, indicates sustained hiring and organisational growth to meet increasing demand from education and government clients.
+Elumina launches AI-powered Assess App to streamline digital assessment lifecycle (15/01/2024)
+Elumina eLearning has introduced its AI-powered Assess App, positioned as a way for institutions and organisations to manage the entire assessment process—including development, delivery and marking—within a single platform. The product launch signals continued product innovation and an expansion of Elumina’s capabilities in automating and scaling assessments.</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr"/>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eluminaelearning/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Embrace Orthodontists (Canberra, ACT, Australia)</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>Embrace Orthodontists recognised among Canberra’s best orthodontic practices (15/04/2025)
+Local Canberra lifestyle outlets Region Media and Canberra Daily both named Embrace Orthodontists as one of the best orthodontic practices in Canberra, highlighting its award‑winning status, leading role in Invisalign and braces treatments, and strong patient experience. This recognition reinforces the practice’s market position and brand strength in the Canberra region.
+Embrace Orthodontists expands to three practices across Canberra (10/03/2024)
+Embrace Orthodontists has grown its physical footprint to three clinics in Canberra—Belconnen, Manuka and Gungahlin—providing increased access to specialist orthodontic care across North and South Canberra and the Gungahlin growth corridor. The expansion reflects sustained demand for orthodontic and Invisalign services and indicates operational growth beyond its original base in Manuka.
+Embrace Orthodontists promoted as a leading Invisalign provider in Canberra (01/09/2023)
+Embrace Orthodontists is promoted on its corporate site as Canberra’s leading Invisalign provider and a Black Diamond Invisalign Provider, a designation typically awarded to practices with high case volumes. This status suggests strong patient throughput, deep clinical experience with clear aligner therapy, and a solid revenue base from Invisalign-related services.
+Embrace Orthodontists scales operations with multi‑site service model (20/02/2023)
+Through its Manuka headquarters and additional Belconnen and Gungahlin practices, Embrace Orthodontists has implemented a multi‑site service model with extended weekday opening hours. This structure supports higher patient capacity, improved accessibility for different regions of Canberra, and operational scalability for the allied health business.</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr"/>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/embrace-orthodontists/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Emergent Group</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>Emergent Group Leans Into The Future (01/01/2024)
+Emergent Group completed a three-month recruitment campaign called The Network Effect, signaling a push to evolve the business and strengthen its workforce. The article highlights the company’s strategy to leverage network theory and adapt for future growth.
+Emergent Group launches campaign to attract workforce talent (01/06/2023)
+Emergent Group launched The Network Effect recruitment campaign to attract talent across engineering, science, and leadership roles. The initiative included referral rewards, aimed to fill vacancies, and explicitly encouraged nominations of women candidates to help address gender imbalance in the team.</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>[20/04/2026 - 4w] Highlighting the significant work of the product development team at Novecom, focusing on their new 'SureWaste' technology that addresses waste in the health sector.</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emergentgroup/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>EncompaaS</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>Atturra expands AI offerings through partnership with EncompaaS (11/11/2025)
+Technology services provider Atturra entered a strategic partnership with EncompaaS to expand its artificial intelligence offerings and support successful enterprise adoption of agentic AI. Under the partnership, Atturra will combine its consulting and delivery expertise with EncompaaS’s intelligent data-preparation and information management platform, helping clients build AI-ready, governed data foundations across sectors such as defence, government, education and manufacturing.
+Atturra and EncompaaS partner to ensure successful agentic AI adoption by enterprises (11/11/2025)
+Atturra and EncompaaS jointly announced an Australia-based strategic partnership focused on enabling enterprises to re-engineer business processes and confidently adopt agentic AI. The collaboration leverages EncompaaS’s AI-powered platform for data discovery, classification and governance along with Atturra’s technology deployment capabilities, positioning EncompaaS more deeply within large enterprise and regulated industries pursuing advanced AI initiatives.
+EncompaaS named finalist in InnovationAus 2024 Awards for Excellence (10/09/2024)
+NSW-based EncompaaS was named a finalist in the InnovationAus 2024 Awards for Excellence, recognising its AI-powered information management platform that discovers, enriches and organises structured and unstructured enterprise data. The recognition validates the company’s strategy of using AI and machine learning, including integrations with Microsoft Azure OpenAI and other AI services, to help organisations extract value from data sprawl while maintaining compliance and security.
+EncompaaS launches focused ‘Get AI Ready’ data-preparation offering (15/04/2024)
+EncompaaS introduced a refined market proposition under the banner “Get AI Ready with Beautifully Prepared Data,” emphasising automated preparation of unstructured data for AI use. The offering underscores the company’s growth strategy around AI data readiness, enabling enterprises to normalise and govern content across repositories and make it suitable for advanced AI services, reinforcing EncompaaS’s positioning in the emerging AI infrastructure and data-preparation space.
+EncompaaS positions platform as foundation for AI-ready enterprise data (01/03/2024)
+Through updates highlighted on its corporate site, EncompaaS is positioning its intelligent information management platform as a way for regulated enterprises to transform fragmented, high-risk content into a secure, AI-ready foundation. The Sydney-based company emphasises new AI-powered capabilities for discovering and organising structured and unstructured data across cloud, on‑premises and hybrid environments, supporting enterprise adoption of tools such as Microsoft Copilot and Azure OpenAI while maintaining compliance and governance.
+NSW Department of Planning and Environment adopts EncompaaS cloud platform (16/08/2022)
+The NSW Department of Planning and Environment implemented the EncompaaS cloud platform to improve compliance and records management in its Microsoft 365 environment. This government deployment follows Bendigo and Adelaide Bank’s selection of EncompaaS to automate electronic document compliance, highlighting growing traction for the company’s cloud-based governance and compliance solution in both public sector and financial services.
+EncompaaS in $14m capital raise, targets global growth (08/10/2021)
+Enterprise compliance SaaS provider EncompaaS completed a AU$14 million capital raise led by CVC Emerging Companies, Future Now Capital and Marshall Investments to accelerate its scale‑up strategy. The funding is earmarked to expand international sales, further develop its cloud-based information governance platform, and support global market entry. The company has recently secured major contracts with one of Australia’s top five banks and a large NSW government department, and has established offices in the UK and US, adding a major European bank to its client list.</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to support underrepresented founders.
+[27/04/2026 - 3w] LinkedIn's recognition as the most-cited domain for professional inquiries, showcasing success.
+[22/04/2026 - 3w] Announcement of new executive appointments at LinkedIn indicating leadership growth.</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Endotherapeutics (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>Endotherapeutics Awarded EcoVadis Bronze Medal for Sustainability (18/09/2025)
+Endotherapeutics, the Sydney-based medical technology distributor, was awarded a Bronze Medal by EcoVadis for its sustainability performance. The recognition reflects the company’s progress in areas such as environmental practices, ethics, and responsible procurement, and positions Endotherapeutics more competitively with hospitals and health systems that increasingly factor ESG credentials into supplier selection. The medal supports the company’s brand reputation and can help underpin future commercial growth and partnership opportunities.</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Announcement of exclusive partnership with Bien-Air Surgery for distribution of power tools in Australia.
+[11/05/2026 - 1w] Celebration of International Nurses Day while encouraging hiring and career exploration.
+[23/04/2026 - 3w] Announcement of exclusive partnership as the sole distributor for VARIXIO in Australia and New Zealand.</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/endotherapeutics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Energetica (152 Elizabeth St, Melbourne, VIC 3000, Australia)</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>No verified growth-related news articles found for Energetica at 152 Elizabeth St, Melbourne (01/01/1900)
+A search of public web sources and industry news (renewable energy in Victoria and Australia more broadly) did not return any verifiable news articles specifically about Energetica headquartered at 152 Elizabeth St, Melbourne, VIC 3000, Australia. Available search results referenced other entities in the renewable energy sector (such as government initiatives, large battery projects, and other developers) but none could be confidently matched to this exact company and address. To avoid mixing it up with similarly named firms, no unverified or ambiguous items are included.</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr"/>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/energetica.io/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Energy-Tec (Perth, Western Australia)</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>Energy-Tec expands advanced metering and solar portfolio across WA and eastern states (01/03/2023)
+Perth-based Energy-Tec has broadened its operations from traditional sub‑meter reading and billing into a full technical division delivering Advanced Metering Infrastructure (AMI) and large‑scale solar solutions. The company reports having implemented AMI projects with large solar systems at more than 20 commercial properties across Western Australia and on the eastern seaboard, and now services thousands of properties nationwide. This marks a significant expansion of its renewable and smart‑metering footprint in retail, commercial, industrial, strata, retirement living, airport estates, educational campuses and government buildings.
+Long‑term partnership with Perth Airport underpins Energy-Tec’s growth in embedded network metering (01/06/2022)
+EnergyTec (Energy-Tec) has been a key metering and energy‑management partner to Perth Airport for more than five years, supporting the airport’s transition to advanced and smart meter technology across its 22 kV embedded distribution network. The ongoing role in the Perth Airport Metering Transformation Project highlights the company’s growth in complex embedded‑network projects and reinforces its position as a specialist provider of metering solution management for large infrastructure clients.
+Energy-Tec scales sustainability and renewable solutions offering for commercial property sector (01/09/2021)
+Energy-Tec has expanded its core services beyond sub‑metering into integrated sustainability consulting and renewable energy solutions for commercial property owners. By offering customised ‘energy roadmaps’ designed to prepare assets for the next decade of energy‑market evolution, the company has increased its service scope to include end‑to‑end metering, energy efficiency and renewable project delivery across thousands of properties in Perth, regional Western Australia and nationally.</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 5d] EnergyTec supports the 2026 Property Council WA Awards and commends nominees, indicating company recognition.
+[28/04/2026 - 3w] Our client-facing team is a finalist for Property Council WA Team of the Year, showcasing team excellence.
+[21/04/2026 - 4w] EnergyTec is recognized as a finalist in the SCA Australasia Awards, demonstrating industry acknowledgment and growth.</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/energytecholdings/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Engineering Supplies</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>Engineering Supplies: Online Electrical Supply Store In Welshpool (01/01/2025)
+This company profile highlights Engineering Supplies’ long-standing presence in the Australian electrical market, its broad product range, and its role as a distributor for multiple major brands. While not a traditional news article, it indicates business scale and ongoing market activity rather than a specific growth event.
+Engineering Supplies drawing exceptional interest within the Retail industry (01/01/2025)
+This company overview notes that Engineering Supplies is attracting exceptional interest within its industry, which can be interpreted as a sign of strong market momentum. It suggests increased attention around the business, though the page does not provide a specific growth announcement.</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr"/>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/engineering-supplies-au/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>EpiSoft</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>EpiSoft launches My Health Record upload capability for oncology treatment summaries (01/01/2024)
+EpiSoft announced an Australian-first innovation enabling treatment event summaries covering a full cycle of care to be seamlessly uploaded to My Health Record through its medical oncology management platform, indicating continued product expansion and platform advancement.
+The San partners with EpiSoft for integrated cancer centre (01/01/2019)
+Sydney Adventist Hospital selected EpiSoft’s Cancer CareZone cloud-based clinical information system for its new Integrated Cancer Centre, reflecting a major partnership and deployment in a large hospital redevelopment.
+EpiSoft secures Federal Government grant and private investment to accelerate global expansion (01/01/2014)
+EpiSoft’s co-founders said the company received a $250,000 Federal Government grant and later attracted $1 million in private investment, which was expected to accelerate global expansion of its cloud-based healthcare software platform.</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr"/>
+      <c r="E104" s="16" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Evado (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr"/>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to enhance business networks.
+[24/04/2026 - 3w] Celebration of Fernando Mendoza's appointment.
+[22/04/2026 - 3w] Congratulatory post on new CEO and President appointments, indicating positive leadership changes.</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Everlink (10 Cypress St, Tauranga, Bay of Plenty, 3110, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>Everlink invests in integrated hardware–software platform for fuel‑chain visibility (05/11/2019)
+Everlink has enhanced its core offering by investing in an integrated hardware–software platform designed to ‘connect every link in the fuel supply chain’. The platform provides real‑time visibility and control over fuel usage and inventory, aimed at improving efficiency and compliance for industrial customers. This represents a strategic product‑development initiative that deepens its capabilities in electronic monitoring and control systems manufactured from its Tauranga base.
+Everlink strengthens reputation as a global fuel‑management solutions provider (20/07/2018)
+Everlink, headquartered in Tauranga, has continued to build an international customer base for its purpose‑built hardware and software that manage, monitor, and maintain fuel flows across complex supply chains. The company reports a proven track record of success around the world and positions itself as a trusted name in fuel management, highlighting sustained export growth and increasing adoption of its electronic fuel‑management systems in overseas markets.
+Everlink broadens product range into automated fluid management for heavy industry (10/09/2015)
+Building on its origins as a New Zealand fuel‑management specialist, Everlink has grown its offering to encompass a wider suite of automated fluid management and control products tailored for heavy industries such as rail, civil engineering, mining, and transport. This diversification reflects product‑line expansion from traditional fuel management into broader electronic control and monitoring solutions for industrial fluids, leveraging its in‑house design and manufacturing capabilities in Tauranga.
+Everlink expands Australian presence with dedicated Everlink Australia entity (15/03/2015)
+Everlink, founded in Tauranga in 2001, has expanded its reach by establishing a dedicated Australian operation (Everlink Australia) to design and manufacture fuel and fluid management products for sectors including rail, civil engineering, mining, and transport. The move formalised and scaled up its export activities from New Zealand into Australia, signalling geographic expansion and increased manufacturing capacity beyond its Tauranga base.</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>[10/05/2026 - 1w] Announces a partnership with Mansfield Group to enhance diesel filtration systems at client sites.
+[28/04/2026 - 3w] Acknowledges the distributor's efforts in Papua New Guinea, hinting at market expansion.
+[27/04/2026 - 3w] Mentions a shift towards integrated dispensing solutions as a sign of market adaptation.
+[19/04/2026 - 1mo] Describes the company's participation in an expo and connection with clients through partnerships.</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/everlink-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>Exergenics</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>Exergenics secures Accelerating Commercialisation Grant for 2023/2024 financial year (01/07/2023)
+Exergenics announced it had been awarded an Accelerating Commercialisation Grant for 2023/2024 to support development and scaling of its AI-powered cloud-based chiller plant optimisation platform. The funding was positioned as a boost for product development and market expansion, with claims of enabling up to 35% energy savings.
+How Exergenics' machine learning can help make air conditioning more energy efficient (01/06/2021)
+University of Melbourne coverage highlighted Exergenics as a Melbourne startup using machine learning to optimise large-scale commercial air conditioning and refrigeration systems. The article noted that Exergenics was deploying pilots across multiple sites, had achieved energy savings of 5–15% in most buildings, and was raising capital to accelerate growth and expand internationally.
+Exergenics announced as winner of Start-up Proptech of the Year (01/05/2021)
+Exergenics was recognised with the 'Start-up Proptech of the Year' award from the Proptech Association of Australia, signalling external industry validation and momentum for the Melbourne-based company.</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcement of partnership with Serena Williams and Reckitt to promote networking.
+[27/04/2026 - 3w] LinkedIn recognized as the #1 cited domain for professional queries on AI search engines.
+[22/04/2026 - 3w] Announcement of new CEO and President roles within LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>Expressway Spares Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>Expressway Spares celebrates 60 years of growth, legacy and strategy (15/04/2024)
+In a feature article, Expressway Spares marked its 60th year in business, outlining sustained growth from a small wrecking yard to a major supplier of new, used and reconditioned parts for Caterpillar and Hitachi equipment. The piece highlighted expansion to multiple branches across three states, the scaling of its workforce to more than 380 employees, significant investment in workshops and component rebuild facilities, and a long‑term strategy focused on customer service and international sourcing of machinery and parts.
+Expressway Spares named 2022 Workplace Safety Champions by SafeWork NSW (15/11/2022)
+Expressway Spares was recognised as the 2022 Workplace Safety Champions at the SafeWork NSW Excellence Awards. The award highlighted the company’s strong safety culture, systems and initiatives across its workshops and sites, reinforcing its position as a leading and responsible employer within the heavy equipment parts and machinery sector.
+Expressway Spares grows into one of Australia’s largest independent heavy equipment parts suppliers (01/08/2021)
+A NAB Business profile described how Expressway Spares evolved into a sophisticated aftermarket parts enterprise supplying the mining, construction and logging sectors. The article noted its expansion to five offices across three states, a large headcount at its New South Wales head office, and its position as one of the largest private independent dealers of parts and components suitable for Caterpillar internationally. The company’s model of acquiring, stripping and reconditioning heavy machinery from around the world was highlighted as a key driver of ongoing growth and export activity.
+Perth branch opens as Expressway Spares expands national footprint (01/02/2020)
+Expressway Spares reported the opening of its Perth branch in Western Australia, extending its service coverage to more mining and earthmoving customers across the state. The new location added local inventory, workshop capability and customer support, strengthening the company’s presence in key resource regions and supporting ongoing expansion beyond its New South Wales base.
+Expressway Spares adds AS/NZS 4801 and ISO 14001 certifications to scope (01/06/2019)
+Expressway Spares announced that it had expanded the scope of its management systems to include AS/NZS 4801 (occupational health and safety) and ISO 14001 (environmental management). Achieving these additional certifications formalised the company’s commitment to safety and environmental performance across its operations and supported growth with larger mining and construction customers that require certified suppliers.</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] The company is opening applications for apprenticeships, indicating growth through recruitment and team expansion.</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/expressway-spares-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>Ezihealth</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr"/>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Partnership announcement with Serena Williams and Reckitt to leverage networks for small businesses.
+[27/04/2026 - 3w] Highlighting LinkedIn's dominance as the most-cited domain for AI queries indicates market expansion and relevance.
+[22/04/2026 - 3w] Announcement of new leadership roles at LinkedIn, indicating company leadership changes.</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
+        <is>
+          <t>FRAMECAD</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>FRAMECAD launches ‘Steel Framing Connections’ podcast to showcase global CFS project growth (15/04/2026)
+FRAMECAD has launched a new monthly podcast series, ‘Steel Framing Connections’, focused on real-world applications of cold-formed steel (CFS) framing in global construction markets. Produced from Auckland, the series features industry leaders and project case studies highlighting how steel framing is improving speed, efficiency and performance across residential, commercial and modular construction. The initiative supports FRAMECAD’s market development and brand-building strategy as it promotes its steel framing systems and software to a broader international audience.
+FRAMECAD appoints Aaron Wright as CEO to lead next phase of global growth (02/03/2026)
+FRAMECAD, the Auckland-based steel frame construction technology company, has appointed Aaron Wright as CEO as it enters its next phase of global growth. Wright steps up from his role as Chief Operations Officer, which he has held since April 2024. Founder and long-time CEO Mark Taylor becomes Executive Director of the FRAMECAD Group. The leadership change is positioned as a move to accelerate international expansion of FRAMECAD’s end-to-end cold-formed steel (CFS) construction system, roll-forming technology, and digital design solutions for residential and commercial projects worldwide.
+FRAMECAD launches FRAMECAD Nexa, expanding its steel frame building technology suite (22/10/2024)
+FRAMECAD announced the launch of FRAMECAD Nexa, described as a significant enhancement to its steel frame building innovation platform. As an advanced end-to-end design and build system provider, FRAMECAD is extending its product and software offering to enable faster, more efficient cold-formed steel construction. The launch underscores the company’s ongoing investment in product development to support businesses, governments and communities with rapid, durable, cost-effective buildings worldwide.
+FRAMECAD moves into new Glen Innes premises and begins new R&amp;D contracts (03/11/2011)
+New Zealand Government communications highlighted that steel-frame export company FRAMECAD has relocated into new premises in Glen Innes, Auckland, as it commences work on several new research and development contracts. The move into larger facilities and the securing of multiple R&amp;D projects signal expansion of FRAMECAD’s innovation capability and export-focused operations in cold-formed steel construction technology.</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>[10/05/2026 - 1w] Announcement of Aaron Wright as new CEO to lead growth efforts.
+[08/05/2026 - 1w] Example of how light steel frame technology helped rebuild homes after floods in Brazil.
+[29/04/2026 - 2w] Case study on the rapid adoption of steel framing in a townhouse project.
+[28/04/2026 - 3w] Launch of the Steel Framing Connections podcast focusing on industry insights.
+[28/04/2026 - 3w] Grupo SteelCorp's initiative to rebuild communities with light steel frame homes.</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/framecad-limited/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>FYI (FYI Software Pty Ltd), Adelaide, South Australia</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>FYI emerges as Australia and New Zealand’s fastest‑growing automated document and practice management platform (05/03/2024)
+Trade coverage in outlets such as Accountants Daily and Accounting Times describes FYI as Australia and New Zealand’s fastest‑growing automated document and practice management software, now transforming how more than 30,000 accountants operate. The articles highlight rapid user adoption across accounting firms and emphasise FYI’s automation features, positioning the Adelaide‑headquartered company as a high‑growth player in the accounting technology market.
+FYI scales operations across Australia, New Zealand and the UK from its Adelaide headquarters (15/09/2023)
+In updated company information, FYI reports that it is headquartered in Adelaide’s East End and now has a growing, distributed team across Australia, New Zealand and the United Kingdom. This geographic expansion of staff and operations signals sustained growth in demand for FYI’s cloud‑based document and practice management platform within multiple regions.</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr"/>
+      <c r="E111" s="16" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>Factory Controls Pty Ltd (65 Douro Street, North Geelong, VIC 3215, Australia)</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>Factory Controls strengthens automation offering through new technology partnerships (01/03/2024)
+Factory Controls, a Victorian-based industrial automation and controls specialist headquartered in North Geelong, has expanded its partner network with a series of new and upgraded agreements with leading global vendors in PLCs, drives, industrial networking and safety systems. The company highlighted that its strategic partnerships are aimed at delivering more integrated automation solutions for local manufacturers and infrastructure projects, reinforcing its role in Victoria’s advanced manufacturing and process control supply chains. While financial details were not disclosed, the broadened partner portfolio indicates a growth focus on higher‑value engineering, systems integration and long‑term service contracts.</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr"/>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/factory-controls/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>FeeSynergy</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>FeeSynergy partners with Equifax to integrate business credit scoring for accounting and legal firms (22/05/2023)
+Melbourne-based debtor management fintech FeeSynergy announced a strategic partnership with global data and analytics company Equifax to enhance how accounting and legal firms assess client credit risk. The integration allows FeeSynergy users to access Equifax business credit scores and credit reports directly within their risk assessment workflows, providing greater visibility of clients’ creditworthiness and ability to pay. FeeSynergy’s managing director Malcolm Ebb described the collaboration as ‘ground-breaking’ and noted that the product had been in development for over two years, positioning the company to deliver deeper risk insights and identify new business advisory opportunities for its professional-services customer base.
+FeeSynergy strengthens market position as leading AR automation platform for accounting and legal firms in ANZ (15/03/2022)
+FeeSynergy highlighted continued growth as the leading accounts receivable automation platform tailored to accounting and legal firms across Australia and New Zealand. The company reports widespread adoption of its FeeSynergy Collect platform and Payment Gateway, with client testimonials citing outcomes such as reducing debtor days by around two-thirds within six months of implementation and shifting the majority of client payments to automated channels. This traction underscores FeeSynergy’s expanding customer base and recurring SaaS revenue footprint in the professional-services sector.</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr"/>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/feesynergy-finance-p-l/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="16" t="inlineStr">
+        <is>
+          <t>FilePro</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>Actionstep Acquires Australian Legal Software Company FilePro (31/08/2023)
+Cloud practice management provider Actionstep acquired Perth-based legal software business FilePro, combining two practice management platforms focused on mid-sized law firms. The deal is positioned as a growth step for FilePro’s customers, who are expected to gain access to expanded cloud technologies and increased product development investment, while strengthening Actionstep’s presence in the Australian legal software market.
+FilePro Releases Dashboard and User Interface Enhancements (23/02/2021)
+FilePro announced a set of product updates including the introduction of a new FilePro Dashboard, refreshed screen designs, and upcoming improvements to document assembly. These enhancements are part of ongoing product investment to improve usability and workflow efficiency for law firm customers across Australia.
+FilePro Board Approves Additional $1m Investment in Next-Generation Software (07/08/2017)
+FilePro’s board approved a further AU$1,000,000 investment to accelerate development of its next-generation legal practice management platform. The funding was described as a strategic move to give the company an additional competitive advantage and underpins FilePro’s product roadmap and long-term growth strategy in the legal software sector.
+FilePro Implements Five-Year National Growth Strategy (01/06/2015)
+FilePro outlined a five-year national growth strategy aimed at ensuring its longevity and continued delivery of high service and value to clients. The plan focuses on expanding its footprint with Australian law firms, enhancing its all-in-one practice management offering, and supporting ongoing product development and client support initiatives.</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr"/>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/filepro/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>Fine Orthodontist Sydney</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr"/>
+      <c r="D115" s="17" t="inlineStr"/>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fine-orthosydney/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="16" t="inlineStr">
+        <is>
+          <t>Flash Payments</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>Flash Payments announces 2024 partnership with Eastern Suburbs Rugby (15/03/2024)
+Flash Payments, the Sydney-based fintech headquartered at Level 26, 1 Bligh Street, expanded its brand reach and community presence by becoming a 2024 partner of Eastern Suburbs Rugby. The sponsorship aligns the company with a high-profile Sydney sporting organisation and is positioned as a way to showcase its innovative cross‑border and instant payment capabilities to a broader local audience while deepening ties in its home market.
+Flash Payments strengthens strategic partnership with Ripple to scale blockchain-powered cross‑border payments (10/11/2023)
+Flash Payments highlighted its role as a key Australian strategic partner of Ripple, leveraging RippleNet and On‑Demand Liquidity (ODL) to deliver faster, lower‑cost international money transfers for businesses across 40+ countries and 20+ currencies. The company emphasised scaling of its blockchain-based FX and virtual account offering, signalling operational and product expansion in global B2B and B2E payments out of its Sydney headquarters.
+Flash Payments recognised for innovation in cross‑border payment solutions (05/09/2023)
+Flash Payments reported industry recognition for its innovative cross‑border payment solutions, which use blockchain technology, competitive FX, and AI/ML‑driven fraud detection. The acknowledgment underscores the firm’s growing influence in the Australian fintech ecosystem and validates its technology-led growth strategy in secure international money transfers for businesses.
+Flash Payments joins Australian FinTech as newest member to support scaling businesses (22/08/2023)
+Australian FinTech announced Flash Payments as its newest member, spotlighting the Sydney company’s complete payment solution that spans foreign exchange, international transfers, and digital payment capabilities. Membership enhances Flash Payments’ visibility within the national fintech community and is positioned to support further business development and scaling with enterprise clients.
+Flash Payments underscores regulated status and infrastructure investment to support growth (30/06/2023)
+In an updated corporate overview, Flash Payments detailed its status as a regulated entity holding an ASIC Australian Financial Services Licence (AFSL) and AUSTRAC registration, alongside a management team with over 50 years of banking and financial services experience. The company highlighted investments in AI/ML for fraud detection, virtual accounts, and compliant infrastructure—positioning itself for continued growth in enterprise-grade international payment services from its Sydney headquarters.</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr"/>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/flash-payments/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>Fluid Power Engineering Solutions (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>Fluid Power Engineering Solutions enters Western Australian market with Perth centre of excellence (01/11/2022)
+Fluid Power Engineering Solutions expanded beyond its East Coast base into Perth, Western Australia, establishing a local centre of excellence focused on transformers and high‑voltage assets. The new location offers a full range of turnkey solutions including smart systems and predictive maintenance, rotating equipment consultancy and maintenance, and specialist filtration services, allowing the company to tap into Western Australia’s growing industrial market and serve customers as a one‑source systems integrator.
+Fluid Power Engineering Solutions expands operations with new Wetherill Park headquarters (01/06/2020)
+Fluid Power Engineering Solutions, a privately owned hydraulic and mechanical engineering firm, relocated to a larger, more professional headquarters in Wetherill Park, Western Sydney. The move created a dedicated ‘centre of excellence’ for engineering, hydraulic and filtration solutions, and provided capacity to grow its team and service capabilities for industrial customers in the Sydney region.
+Fluid Power Engineering Solutions scales up offerings through merger of two hydraulic businesses (01/03/2018)
+The formation of Fluid Power Engineering Solutions is described as the result of a powerful combination of two successful hydraulic companies joining forces. This consolidation brought together an extensive suite of capabilities and a larger pool of specialised staff, positioning the business as a premier hydraulic service centre in a key Sydney industrial hub and enhancing its ability to deliver 360° mechanical, hydraulic and electronic solutions.</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Partnership announcement with Serena Williams and Reckitt focusing on network leverage.
+[27/04/2026 - 3w] Announcement of LinkedIn being the top-cited domain for professional queries.
+[22/04/2026 - 3w] Announcement of new leadership roles within LinkedIn indicating team growth.</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>FormTab Ltd (Christchurch, Canterbury Region, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr"/>
+      <c r="D118" s="17" t="inlineStr"/>
+      <c r="E118" s="16" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>FreightSafe (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>FreightSafe Group partners with Ofload to enhance goods protection (05/07/2024)
+Digital freight platform Ofload announced a strategic partnership with the FreightSafe Group, describing FreightSafe as a leading digital‑first freight insurance provider. The collaboration embeds FreightSafe’s technology‑driven, customised transit‑insurance solutions and high‑scale claims management into Ofload’s platform to protect customers’ goods against loss or damage. The deal underscores FreightSafe’s growth via platform integrations, expanded customer reach, and the use of advanced technology and data analytics for real‑time risk assessment.
+FreightInsure, part of FreightSafe Group, launches embedded per‑shipment cover in ANZ (15/03/2024)
+FreightInsure, the embedded insurance solution within the FreightSafe Group, detailed its offering of per‑shipment freight insurance that integrates directly into carriers’ and logistics platforms’ existing workflows. The product activates cover automatically at shipment, with FreightSafe managing claims end‑to‑end and removing liability from distributors. The service is now operating in both Australia and New Zealand, indicating regional expansion and deeper embedding of FreightSafe’s digital insurance and claims capabilities in logistics platforms.
+Lombard backs insurtech FreightInsure, part of FreightSafe Group (19/09/2023)
+Lombard Australia Holdings, parent of Assetinsure, invested capacity and support into FreightInsure, a goods‑in‑transit insurtech that sits within the FreightSafe Group. The partnership launches FreightInsure with many of FreightSafe’s largest transport and logistics clients, embedding per‑shipment insurance into carriers’ booking processes. The product offers pay‑as‑you‑go mini‑policies with cover up to $50,000 per consignment and no excess, indicating product expansion and financial backing for FreightSafe’s insurance and digital offerings in Australia (and later New Zealand).
+Insurtech Australia welcomes FreightSafe as new member (08/06/2022)
+Industry association Insurtech Australia announced that third‑party claims administrator FreightSafe has joined as a member. The move signals FreightSafe’s growing scale—managing tens of thousands of freight and marine claims annually—and its intention to engage more deeply with the Australian insurtech community. The company highlighted its proprietary claims management system, ability to finalise claims in days rather than weeks, and its large and growing team based on Sydney’s Northern Beaches.
+FreightSafe solution offered via Fast Courier to protect goods in transit (10/11/2021)
+Fast Courier promotes FreightSafe as an extended‑warranty / transit‑protection option, allowing every consignment booked through the platform to be covered against loss or damage at varying levels. This reflects an earlier stage of FreightSafe’s growth in embedded protection services, broadening its distribution through online freight marketplaces and increasing its exposure to small and medium‑sized shippers using digital booking channels.</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr"/>
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
+        <is>
+          <t>FundBase Group</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>FundBase to launch platform for retail access to private markets (27/11/2023)
+FundBase Group, the Sydney‑based investment fund infrastructure provider, announced plans to launch a new platform aimed at giving Australian retail investors access to private markets. The initiative expands FundBase Group’s service offering beyond institutional and wholesale managers, positioning the firm to capture growing retail interest in private assets and signalling product expansion and business growth.
+FundBase Group expands into integrated fund infrastructure platform (01/06/2023)
+Originally established to solve internal operational challenges for fund administration and back‑office support, FundBase Group has expanded its model into an integrated fund infrastructure platform supported by proprietary technology. This evolution, highlighted in the firm’s corporate materials, reflects organic growth in client numbers and service breadth, as the company now provides end‑to‑end fund operations and institutional‑grade infrastructure for emerging and established managers across Australia.
+FundBase Group increases national footprint with offices in Sydney, Brisbane and Melbourne (01/03/2023)
+FundBase Group reports a broadened national presence with offices listed in Sydney, Brisbane and Melbourne, demonstrating geographic expansion beyond its original Sydney base. By operating from multiple CBD locations, the firm is strengthening its service coverage for fund managers across Australia, supporting continued client and headcount growth in its fund infrastructure and administration services.</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcement of a collaboration with Serena Williams and Reckitt to leverage networks for opportunities.
+[27/04/2026 - 3w] LinkedIn's achievement as the top-cited domain for professional queries indicating its significant impact and growth in AI context.
+[22/04/2026 - 3w] Announcement of leadership changes at LinkedIn, highlighting the growth potential for the company.</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>FuseWorks (Brisbane, Queensland, Australia)</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>FuseWorks strengthens client support with dedicated Brisbane-based operations (15/11/2023)
+Through its updated contact and company information, FuseWorks confirms a dedicated Brisbane CBD presence at Level 10, 300 Ann Street, along with structured support hours and centralised client assistance. While not a formal press release, the consolidation of office details and support infrastructure reflects an established and growing software provider investing in local operations to better service an expanding client base of accounting firms.
+FuseWorks highlights Brisbane HQ and Australian-based development team (01/06/2023)
+FuseWorks updated its ‘About Us’ and ‘Meet the Team’ pages to emphasise its Brisbane headquarters and locally developed and hosted software. The expanded team profiles and positioning—“made for accountants by accountants” and “all of our products are designed, developed and hosted in Australia in our Brisbane HQ”—indicate a maturing organisation with an in‑house development and support team, supporting continued product expansion and stronger service capability for accounting firms across Australia.
+FuseWorks showcases client growth through automation case studies (10/08/2022)
+FuseWorks published a series of case studies on its website demonstrating how accounting firms have scaled their operations using FuseWorks products such as FuseDocs and FuseSign. The case studies describe firms reducing manual admin work, cutting processing times, and handling higher client volumes without equivalent staff increases. This content signals ongoing adoption of FuseWorks’ products by accounting practices and underlines the company’s role in enabling clients’ operational growth and cost savings.
+Accountants can lean on technology to improve client relationships (15/03/2021)
+In this sponsored feature on AccountantsDaily, FuseWorks is profiled as a key technology partner helping accounting firms improve client relationships and efficiency. The article highlights FuseWorks’ suite of tools (including digital signing and document automation) as examples of how firms are increasingly adopting specialised software to streamline workflows, free up staff time, and expand value‑adding advisory services. The coverage positions FuseWorks as a growing player in the Australian accounting-tech space that supports firm growth and profitability through automation.</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 1d] Celebrating Jackson Brigg's five-year anniversary reflects company growth and employee development.
+[15/05/2026 - 4d] FuseWorks engaged with William Buck at their National Partner Conference to strengthen collaborations.
+[07/05/2026 - 1w] FuseWorks recognized as a Top 5 Best Workplace in Technology 2026, reflecting strong team culture.
+[07/05/2026 - 1w] FuseWorks is hiring a Technical Client Service Specialist to aid in further company growth.
+[05/05/2026 - 2w] The launch of a new FuseSign video highlights positive impacts on client practices due to streamlined signing process.</t>
+        </is>
+      </c>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fuseworksteam/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
+        <is>
+          <t>Fuseco</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr"/>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Launch announcement of the ChargeMaster ShockSafe UPS, highlighting its innovative safety features.
+[27/04/2026 - 3w] Announcement of a $3 million upgrade project supported by Fuseco, showcasing their involvement in renewable energy advancements.
+[21/04/2026 - 4w] Hiring announcement for a new customer service role, indicating team growth and expansion.</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fuseco-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="16" t="inlineStr">
+        <is>
+          <t>GCG Health Safety Hygiene</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>GCG recognised as a leading national WHS and occupational hygiene specialist (10/11/2022)
+In updated corporate materials, GCG Health Safety Hygiene described itself as one of Australia’s leading workplace health and occupational hygiene specialists with over 20 years of operation, reflecting long‑term growth from a small consultancy to a national firm. The company’s expanded geographic footprint and multi‑industry client base, ranging from aerospace to mining to water and energy, illustrate its sustained revenue and capability growth in the management consulting segment of WHS and occupational hygiene.
+GCG strengthens leadership team to support national WHS consulting growth (22/07/2021)
+GCG Health Safety Hygiene publicised additions and promotions within its leadership team, building depth in national management to support a growing portfolio of WHS and occupational hygiene contracts. The refreshed leadership structure was positioned as a key step in scaling delivery across sectors such as mining, water, energy and manufacturing and in supporting continued expansion from its offices including Perth and New South Wales.
+GCG expands capabilities and wins national recognition through growth in occupational hygiene and WHS services (15/03/2019)
+Through a series of internal announcements and case studies, GCG Health Safety Hygiene highlighted expansion in its occupational hygiene and WHS service lines, including larger project engagements in mining, energy and infrastructure. The company reported an increase in senior consultants and project managers across Australia and showcased recognition from major clients for its role in improving workplace exposure monitoring and safety performance, indicating sustained business and headcount growth.
+GCG appoints first Federal Safety Officers to support national WHS growth (28/09/2016)
+GCG Health Safety Hygiene announced the appointment of its first Federal Safety Officers, expanding its capability to support clients working under the Australian Government Building and Construction WHS Accreditation Scheme. The appointments reflect growing national demand for GCG’s specialist WHS and occupational hygiene services and strengthen its position as a key provider to construction and infrastructure projects across Australia.</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>[13/05/2026 - 6d] Celebrating team members' five-year milestones, indicating employee retention and recognition of contributions.
+[22/04/2026 - 3w] GCG is a finalist in the 2026 Hunter Safety Awards for their Exposi Hygiene Management System, highlighting recognition for innovation.</t>
+        </is>
+      </c>
+      <c r="E123" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gcgaust/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>GPC Electronics (138 Blaikie Road, Jamisontown, NSW, 2750, AU)</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>GPC Electronics continues to scale as one of Australasia’s largest contract manufacturers (10/06/2024)
+A company overview on GPC Electronics’ own site and syndicated business directories describes the Jamisontown-based business as one of Australasia’s largest contract manufacturers, with three manufacturing locations in Sydney (NSW), Christchurch (NZ) and Shenzhen (China), and most production exported to more than 40 countries. The profile notes ongoing expansion of production lines and a workforce of roughly 279 employees across the group, along with a revenue base approaching $60 million. These details indicate sustained growth in scale, exports and group-wide employment, with the NSW headquarters as the central hub of operations.
+AUKUS Connect highlights GPC Electronics’ expanded defence-related manufacturing capability (03/08/2023)
+An AUKUS Forum profile on AUKUS Connect features GPC Electronics, founded in 1985 by Christopher Janssen, noting that the NSW-headquartered firm now operates nine state-of-the-art electronics production and testing lines across its network. The piece emphasizes GPC’s role in supplying complex electronics into defence and allied sectors and its focus on sovereign manufacturing capability within the AUKUS framework. This coverage points to the company’s scaling of high‑reliability production capacity and its strategic alignment with growing defence and security-related demand, reflecting both capability and market growth anchored from its Jamisontown headquarters.
+Carbonix and GPC Electronics partner to advance Australian drone sector (09/05/2023)
+Sydney-based Carbonix and GPC Electronics Group announced a partnership to enhance sovereign capability in Australia’s drone and UAV sector. Under the collaboration, GPC Electronics’ Jamisontown-based advanced electronics manufacturing will support Carbonix’s production of sophisticated drone systems, bringing high‑reliability local manufacturing into a segment that often relies on overseas supply chains. The partnership signals GPC’s strategic move into the growing UAV/defence-adjacent market, leveraging its existing export-grade manufacturing capabilities and reinforcing its role as a key domestic electronics manufacturing partner for high-technology Australian companies.
+Penrith manufacturer has global reach (19/01/2022)
+Penrith City Council profiled GPC Electronics as one of Australasia’s largest contract electronics manufacturers, highlighting that it has grown since its 1985 founding to serve global giants such as Toshiba, Nortel, Ericsson, Siemens, Daikin, Johnson Controls, Schneider, Philips and numerous Australian start-ups. The article notes that GPC’s Jamisontown headquarters now employs around 150 people, manufactures products for communications, industrial, agricultural, medical, automotive and defence industries, and exports customers’ products to roughly 40 countries. The company has expanded its footprint with additional facilities in China and New Zealand, underscoring sustained international growth and diversification of its customer base and end markets.
+Thought Leadership: Insights from GPC Electronics’ Managing Director (15/11/2020)
+In a thought-leadership interview hosted by Hawker Richardson, Managing Director Christopher Janssen describes how GPC Electronics, founded in 1985 in New South Wales, has evolved into a global provider of electronics manufacturing services. He outlines the company’s growth from a local contract manufacturer to an exporter serving over 40 countries, supported by facilities in Australia, New Zealand and China. The discussion focuses on scaling advanced manufacturing lines, investing in surface-mount technology and end-to-end EMS capabilities, and positioning the Jamisontown headquarters as the core of a broader regional network—illustrating sustained operational and geographic growth tied directly to its NSW base.</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr"/>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gpc-electronics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="16" t="inlineStr">
+        <is>
+          <t>Genesis Research Services (Broadmeadow, New South Wales, Australia)</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>Genesis Research Services earns NSW Health Clinical Trials Quality Recognition Scheme (QRS) status (13/10/2025)
+Genesis Research Services has been officially recognised by NSW Health under the Clinical Trials Quality Recognition Scheme (QRS), becoming only the second clinical trials site to receive this status. The recognition highlights the organisation’s strength in clinical and medical governance, quality processes, risk management, research team capability, and emergency response readiness, reinforcing its position as a high‑quality independent clinical research site.
+Genesis Research Services reports team expansion with new hires over the past 12 months (01/09/2025)
+Profile information on Genesis Research Services indicates that the organisation is expanding and has recently hired additional staff over the previous 12 months. The added team members support its clinical trial operations and related services, signalling ongoing growth in capability and activity at its Broadmeadow, NSW site.
+Genesis Research Services moves into larger, purpose-designed clinical trials facility in Broadmeadow (15/01/2025)
+Genesis Research Services announced that it has relocated to a newly renovated, purpose-designed clinical trials facility at Ground Floor, 239/245 Denison Street, Broadmeadow NSW 2292, directly across from its previous site. The new space offers a more spacious and modern environment with dedicated participant parking and improved access, supporting expanded clinical trial activity and a better experience for study participants.</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr"/>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/genesis-research-services-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
+        <is>
+          <t>Genomics For Life Pty Ltd (Brisbane, QLD, Australia)</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>Genomics For Life expands clinical and oncology genomic testing menu to over 3,000 genes (01/03/2024)
+Genomics For Life, a NATA‑accredited private pathology laboratory based in Milton, Brisbane, has expanded its clinical and oncology genomic testing range to cover more than 3,000 genes associated with cancer and inherited disease. The broadened menu, highlighted in updated service information for clinicians, positions the lab as having one of the largest genetic testing options of any laboratory in Australia and reflects continued investment in next‑generation sequencing capabilities and assay development.
+Brisbane-based Genomics For Life highlighted as leading private cancer genomics laboratory in Australia (15/11/2023)
+Industry and member communications in the Australian genomics sector reference Genomics For Life Pty Ltd, headquartered in Milton, Brisbane, as a key private pathology provider specialising in cancer genomics and inherited disease testing. The laboratory’s NATA accreditation to ISO 15189 standards and its positioning among Australia’s major oncology genomics services indicate reputational growth and consolidation as a specialist provider in precision oncology and hereditary cancer diagnostics.</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr"/>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/genomics-for-life/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
+        <is>
+          <t>GoodHuman (Sydney, New South Wales, Australia)</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>GoodHuman launches all‑in‑one NDIS service delivery platform for human services providers (15/03/2023)
+GoodHuman, the Sydney‑based human services software company, announced major product updates to its purpose‑built NDIS service delivery platform, integrating workforce, customer and billing management into a single system. The company positions the enhanced platform as the only all‑in‑one solution specifically designed for the human services sector, aiming to help providers scale, streamline operations and deliver greater impact. The breadth of new functionality and repositioning toward larger providers indicate product‑led growth and stronger market traction in Australia’s disability and community services markets.
+GoodHuman strengthens position as a customer success engine for NDIS providers (10/08/2022)
+Startup profiles describe GoodHuman as a fast‑growing Melbourne‑ and Sydney‑linked software startup providing a customer success engine for NDIS service providers. The GoodHuman app enables participants to discover and connect with local support services, while providers use the platform for CRM and case management, rostering and scheduling, mobile workforce management, and instant invoicing and billing. The broadened feature set and emphasis on helping providers grow their business and streamline processes reflect ongoing platform development and an expanding customer base in the NDIS ecosystem.
+GoodHuman highlights growing enterprise focus for human services organisations (01/06/2022)
+Through its ‘GoodHuman for Enterprise’ offering, the company signals a strategic move up‑market toward large, complex human services organisations. The enterprise solution emphasises flexible, scalable features that can evolve with providers as they grow, connecting NDIS participants, rosters, bookings and billing at scale. This enterprise positioning suggests that GoodHuman is targeting larger contracts and more sophisticated providers, indicating a growth strategy beyond smaller organisations and individual support networks.</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr"/>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/goodhuman/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>GreenBe</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr"/>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Discusses a collaboration with Serena Williams and Reckitt, focusing on leveraging networks for business opportunities.
+[27/04/2026 - 3w] Highlights LinkedIn's status as a leading domain in AI search engines, suggesting market expansion and increased visibility.
+[24/04/2026 - 3w] Announces Fernando Mendoza's official role confirmation, indicating a new hire that suggests growth opportunities.
+[22/04/2026 - 3w] Congratulates new leadership appointments at LinkedIn, indicating team growth and strategic positioning for future opportunities.</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>Gullotta Orthodontics (Dr Nino Gullotta), Southport, Gold Coast, QLD, Australia</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>Gullotta Orthodontics Awarded Invisalign Diamond Provider Status (01/07/2023)
+Gullotta Orthodontics, led by Gold Coast orthodontist Dr Nino Gullotta, has been awarded Invisalign Diamond Provider status, reflecting a high volume of successful Invisalign cases and strong clinical expertise. This recognition positions the Southport-based clinic among the top tiers of Invisalign providers and indicates sustained patient growth and treatment demand.
+Gullotta Orthodontics Recognised as One of the Top 3 Orthodontists on the Gold Coast (15/03/2022)
+Review platform ThreeBestRated lists Dr Nino Gullotta and Gullotta Orthodontics as one of the top three orthodontic practices on the Gold Coast. The recognition is based on factors such as reputation, reviews, service quality, and patient satisfaction, highlighting the clinic’s strong market position and ongoing growth in its patient base.
+Gullotta Orthodontics Marks Over 35 Years of Specialist Orthodontic Practice on the Gold Coast (01/06/2021)
+Gullotta Orthodontics celebrates more than 35 years since its establishment in 1987 by founder and director Dr Nino Gullotta. Over this period, the Southport practice has treated thousands of patients and grown into one of the Gold Coast’s most experienced and highly rated orthodontic providers, indicating long-term business stability and sustained demand for its services.</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr"/>
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gullotta-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>Hardcat Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>Hardcat extends global footprint via new Indian partnership with Yotta (01/02/2023)
+The Victorian Government’s Global Victoria program profiled Hardcat as a world leader in asset and evidence management and highlighted its expansion into India through a partnership with Yotta of the Hiranandani Group. The partnership builds on Hardcat’s existing global presence, which already includes wholly owned subsidiaries in the USA, UK and Africa, and a customer base featuring major corporates and public-sector agencies. This signals ongoing international growth for the Melbourne-based software company.
+Yotta partners with Melbourne-based Hardcat to launch Lebosi enterprise asset management platform in India (05/01/2023)
+Yotta Data Services (formerly Yotta Infrastructure) announced an exclusive partnership with Hardcat Pty Ltd of Melbourne to introduce Hardcat’s Lebosi enterprise asset management solution to the Indian market. The collaboration leverages Yotta’s data centre and service delivery capabilities to offer Hardcat’s cloud-based, lifecycle asset management platform to Indian enterprise and government customers, expanding Hardcat’s geographic reach and customer base in a large new market.
+Hardcat positions cloud-based asset and inventory platform for multi-industry growth (01/06/2022)
+Company profile data indicates that Hardcat has evolved into a cloud-based asset, tools and equipment tracking platform serving defence, police, emergency services, aged care, banking, mining and telecom sectors. The suite has expanded with multiple add-on modules such as preventive maintenance, depreciation, stock, procurement and help desk, reflecting product-line growth and broader industry adoption. This positioning underlines Hardcat’s strategy of scaling recurring SaaS revenue across diverse verticals.
+New version of Hardcat software supports strategic customer growth with modern technologies (01/09/2019)
+An industry article described a new version of Hardcat’s asset management software that incorporates evolving technology trends including bar-code scanning and mobile handheld devices. The release demonstrates ongoing product innovation designed to support customers’ strategic growth and operational efficiency, reinforcing Hardcat’s position as a long-standing provider adapting its platform to modern enterprise requirements.
+Hardcat prepares major new release and Next Gen system generator platform (01/01/2009)
+In a Q&amp;A with Managing Director Dan Drum, Hardcat outlined plans for a major software release in January 2009 featuring multilingual web support, user-selectable web templates, and GPS/GIS capabilities, along with a forthcoming ‘Hardcat Next Gen’ product described as a sophisticated system generator four years in development. These releases indicate substantial R&amp;D investment aimed at expanding functionality and supporting future growth.</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>[29/04/2026 - 2w] Announcement of a collaboration between Hardcat and Zebra to enhance asset intelligence solutions.
+[22/04/2026 - 3w] Discussion on the capabilities of Hardcat Lebosi EAM in improving asset management operations for organizations.</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hardcat/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>Hawke's Bay Orthodontics</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>Hawke's Bay Orthodontics highlights expanded treatment range for children and adults (15/03/2024)
+Hawke's Bay Orthodontics in Havelock North has been promoting its broadened suite of orthodontic services, including metal and clear ceramic braces, Invisalign, removable plates and functional appliances. The practice emphasises tailored treatment plans for both children and adults, signalling ongoing investment in modern orthodontic options and service capability for the Hawke's Bay community.
+Regional feature showcases Hawke's Bay Orthodontics as one of three key specialist practices in Hawke's Bay (10/02/2023)
+Orthodontics New Zealand’s directory of Hawke’s Bay specialists lists Hawke's Bay Orthodontics among three main specialist orthodontic practices serving the region. The listing underscores the practice’s established position and continued role in meeting growing demand for specialist orthodontic care across Napier, Hastings, Havelock North and surrounding towns.
+Practice update notes collaboration with specialist orthodontists across Hawke's Bay and Gisborne (20/11/2022)
+Information on partner practice sites indicates that Hawke’s Bay Orthodontics works in collaboration with specialist orthodontists such as Dr Andrew Parton, who splits his time between his Taradale practice and Hawke’s Bay Orthodontics in Havelock North. This shared-specialist model reflects a growth‑oriented approach to increasing specialist availability and service coverage across the wider region.</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr"/>
+      <c r="E131" s="16" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
+        <is>
+          <t>Hearth Support Services (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>Expansion of Support Worker and Allied Health Teams Across Melbourne and Victoria (15/03/2023)
+Hearth Support Services has continued hiring extensively for Support Workers and allied health professionals, signalling ongoing operational expansion in Melbourne and across Victoria. The organisation promotes multiple open roles and clear internal career pathways (including Relationship Manager positions and Allied Health career tracks), indicating both workforce growth and a maturing organisational structure to support more NDIS participants in home and community settings.
+Hearth Support Services Turns Five and Celebrates Rapid Growth Since 2017 (07/04/2022)
+Hearth Support Services marked its fifth anniversary by highlighting “enormous change” and rapid expansion since its inception in 2017. The Melbourne-based NDIS provider reported significant growth in client numbers and service offerings, including support worker services, allied health, and broader NDIS registration groups. The milestone piece emphasises that the organisation has scaled its operations while maintaining a person-centred model and building a larger multidisciplinary team.
+Hearth Support Services Broadens NDIS-Registered Service Categories (10/08/2021)
+Hearth Support Services Pty Ltd is listed by the NDIS Quality and Safeguards Commission as an approved provider across a wide range of registration groups, including Assist Personal Activities High, Daily Tasks/Shared Living, Community Nursing Care, Development-Life Skills, and more. This breadth of approved categories reflects a strategic expansion from basic support worker services into higher-intensity care, community participation, life skills development, and employment-related supports, allowing the company to serve a larger and more diverse participant base.
+Service Offering Expansion: Comprehensive Home and Community Supports for NDIS Participants (01/09/2020)
+Hearth Support Services has expanded its Melbourne-based service offering to cover a comprehensive suite of home and community supports for NDIS participants. These include daily living assistance, high-intensity care and complex medical support, post-hospital discharge support, independent living skills training (meals, household duties, travel skills), manual handling and mobility assistance, behaviour support plan implementation, and specialised training in collaboration with allied health professionals. The diversified service mix positions Hearth to capture broader NDIS demand and indicates sustained service-line growth.</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>[15/05/2026 - 4d] Announcement of a job opening for an experienced Occupational Therapist, indicating team growth in Allied Health practice.
+[12/05/2026 - 1w] Details about growth at Hearth, including job opportunities and the positive impact of their housing solutions in healthcare and disability services.
+[07/05/2026 - 1w] Job opportunity at the head office in Glen Iris that combines administration with passion for healthcare, indicating growth and need for support staff.
+[01/05/2026 - 2w] Mention of increased requirements in the Allied Health practice due to innovative housing solutions, indicating business expansion.</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hearth-personal-care-services/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
+        <is>
+          <t>Hekate (New Zealand, e-commerce retailer)</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr"/>
+      <c r="D133" s="17" t="inlineStr"/>
+      <c r="E133" s="16" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>energyOS</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>Electrifying SaaS growth through full-service support | Case study (01/01/2024)
+A case study featuring energyOS highlights the company as an Australian SaaS platform serving electricity and gas utilities, with CEO Stephen Kubicki discussing support for the company’s growth and expansion as it helps utilities respond to the energy transition.
+Client Story: energyOS (01/01/2024)
+RSM’s client story on energyOS says CEO Stephen Kubicki has ambitious plans to grow the company and expand its presence in the global market, indicating business expansion and scaling activity for the Perth-based software firm.</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr"/>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/energyossolutions/posts/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GOWT_mid_low.xlsx
+++ b/GOWT_mid_low.xlsx
@@ -41354,7 +41354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -45212,6 +45212,2068 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>HSE Global</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>HSE Global acquires HealthForce Group in Western Australia (16/04/2024)
+HSE Global announced the acquisition of HealthForce Group, a Western Australia–based provider of psychosocial risk management, injury management and return-to-work services, initial injury response, injury prevention, and medical and workers’ compensation services. The deal expands HSE Global’s service portfolio and geographic footprint, integrating HealthForce’s advisory support for leaders, individuals and teams into HSE Global’s broader health, safety and environmental risk management offering. Group Managing Director Ben Wilson highlighted the acquisition as part of the firm’s ongoing growth strategy.
+HSE Global highlighted as a key provider for mental health, safety culture and leadership programs through EML (10/10/2023)
+Workers’ compensation specialist EML promotes HSE Global as a delivery partner for mental health, safety culture and leadership initiatives, positioning HSE Global as a go‑to provider of tailored training and consulting in psychosocial risk management, cultural transformation and leadership development. The partnership exposure via EML’s Mutual Benefits program reinforces HSE Global’s market presence and supports growth in its mental health and safety culture consulting services.
+HSE Global recognized as a leading global risk management consultancy with expanded footprint across Australia, New Zealand and the United States (01/09/2023)
+In updated corporate materials, HSE Global describes itself as a leading global risk management consultancy with strategically located offices across Australia, New Zealand and the United States. The firm notes it has assisted hundreds of organisations worldwide over the past decade, is the world’s largest provider of Mental Health First Aid in the private sector, and has created award‑winning digital risk management solutions. These claims signal sustained growth in geographic reach, client base and product innovation.</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Announcement of a partnership with Transit Systems and launch of a new Safety Leadership Pathway, focusing on leadership development.</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hse-global/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>HSR Southern Cross</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>Tailored waste solutions drive HSR Southern Cross’s expansion roadmap (17/04/2024)
+Industry outlet Waste Management Review profiled HSR Southern Cross as it lays out an “ambitious roadmap to expansion.” The article highlights the Western Sydney family-owned manufacturer’s growth in the waste equipment sector, including its Australian-made hook loaders, skip loaders, tarping systems and rear-loader refuse compactors, and notes the company’s national network of distributors and approved service partners stretching from the Pilbara to Launceston. The coverage positions HSR Southern Cross as a benchmark-setter in engineered waste equipment solutions and underscores plans to further scale its operations and market reach.
+Hydreco appoints HSR Southern Cross as authorised installer in Sydney region (06/10/2020)
+Hydraulics specialist Hydreco announced that HSR Southern Cross Pty Ltd has been appointed as the Hydreco Authorised Installer for the Sydney region. HSR Southern Cross will undertake all installations previously performed at Hydreco’s Smeaton Grange site, formalising and deepening the partnership between the two companies. The move expands HSR Southern Cross’s service role in the region, reinforcing its position in hydraulic and waste-equipment installations and supporting its broader growth in machinery and equipment manufacturing services.
+HSR Southern Cross strengthens NSW presence as Hyva rear loader joins Sydney Waste Services fleet (15/03/2019)
+Hyva reported that, in partnership with HSR Southern Cross as its distributor for New South Wales, a Hyva rear-loader compactor successfully completed extensive trials and was added to the Sydney Waste Services fleet. The collaboration demonstrates HSR Southern Cross’s role as a key channel for bringing international waste-handling technology into the NSW market, supporting fleet upgrades and reinforcing the company’s growth as a specialist distributor and integrator of rear-loader refuse compactors in the Sydney region.</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 2d] Celebration of Australian Made Week and recognition as a certified Australian Made manufacturer, promoting local jobs and manufacturing.
+[29/04/2026 - 3w] Recognition of employee achievement in completing a qualification, highlighting team capability and development.
+[27/04/2026 - 3w] Job posting for a Salesperson, indicating team growth and an expansion of the workforce.
+[24/04/2026 - 3w] Announcement of a new contract with SKIPZ Recycling, showcasing client acquisition and operational expansion.</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hsr-southern-cross/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="16" t="inlineStr">
+        <is>
+          <t>Hirotec (97 Tennant Street, Fyshwick, ACT 2609, Australia)</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>Hirotec expands national footprint with ACT headquarters and integrated services hub (15/03/2024)
+Hirotec, a leading Australian facilities maintenance and building services company, has consolidated its ACT operations at its headquarters at 97 Tennant Street, Fyshwick, as part of a broader national expansion strategy. The move supports Hirotec’s evolution from a Sydney-based air-conditioning business into a fully integrated technical services provider across HVAC, electrical, fire, and building services. The ACT hub is positioned as a base for further growth in government, education, and commercial sectors.
+Hirotec secures multi-year building services contracts across Australian institutional portfolio (10/11/2023)
+Hirotec announced that it has secured several multi-year contracts to deliver integrated building services and maintenance across a portfolio of institutional and commercial properties in Australia. The wins include long-term agreements in New South Wales and the ACT, reinforcing the company’s position as a preferred technical services partner and underpinning revenue growth in its construction and asset-services divisions.
+Hirotec strengthens leadership team to support growth in national projects (05/07/2022)
+To support its expanding pipeline of construction and asset-services projects, Hirotec has bolstered its leadership team with experienced executives in operations and finance. The company highlighted the role of senior leaders, including those with chartered accounting backgrounds, in driving disciplined growth, improving project delivery capability, and positioning Hirotec for larger, more complex national contracts.
+Hirotec recognised for excellence in integrated building services delivery (22/09/2021)
+Hirotec received industry recognition for its performance in integrated facilities and building services, reflecting strong project outcomes, client satisfaction, and innovation in technical service delivery. The acknowledgement has supported the company’s reputation in the construction and asset-maintenance sectors and has contributed to new business opportunities across Australia.</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr"/>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hirotec/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>Homestead Pet Retreat</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr"/>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>[22/04/2026 - 4w] The company is hiring an Assistant Site Manager, indicating growth in team size and leadership opportunities.</t>
+        </is>
+      </c>
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kip-happy-stays/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="16" t="inlineStr">
+        <is>
+          <t>HosPortal</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>About HosPortal (01/01/2024)
+HosPortal states that it has grown to support 100+ departments and 11,000+ users across Australia and New Zealand, reflecting strong customer and platform expansion. The company also describes its 15+ years in the market and cloud-based rostering solutions.
+HosPortal (Past Sponsor) - Australian Healthcare Week (01/01/2024)
+HosPortal’s sponsor profile notes that the company has grown to more than 6,000 users across 33 public and private hospitals. This indicates significant adoption and business growth in the healthcare rostering market.
+New health roster customers (2): surgeons (01/02/2012)
+HosPortal announced continued expansion of its rostering software beyond anaesthetic groups, adding surgeons as new customers. The post highlights growth into additional medical craft groups, indicating broader adoption of the platform.</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 2w] Details on how Toowoomba Hospital is utilizing AI-powered rostering to manage workforce complexity and improve operational efficiency.</t>
+        </is>
+      </c>
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hosportal-com/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>Hosico Engineering Group</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>Boeing virtual bid training workshop boosts Hosico Engineering Group’s defence and aerospace capabilities (07/10/2020)
+Hosico Engineering Group, a Melbourne-based manufacturing SME, participated in Boeing’s virtual bid training workshop aimed at building Australian industry capability in defence and aerospace supply chains. CEO Michael Quinn stated that the company gained significant value from the workshop, which focused on improving bidding skills and aligning with global prime contractor requirements. The article describes Hosico as a world‑leading integrated provider of manufacturing solutions for defence, aerospace, medical and technology customers in Australia and internationally, highlighting its established export-facing capabilities and positioning for future contract growth.
+Hosico Group joins local manufacturing consortium to produce 4,000 COVID‑19 ventilators (08/04/2020)
+Hosico Group, described as an injection‑moulding specialist that works with the Australian military and based in Melbourne, was part of a local manufacturing consortium supporting Bosch Australia in producing 4,000 ventilators for federal and state government orders during the COVID‑19 pandemic. The consortium’s work involved rapid scaling of tooling and production capability for critical medical components, demonstrating Hosico’s advanced manufacturing capacity, defence-grade quality standards, and ability to pivot into high‑value medical device supply chains under urgent national demand.</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcing collaboration with Serena Williams and Reckitt to mentor underrepresented founders.
+[27/04/2026 - 3w] LinkedIn becoming the most cited domain for professional queries indicating its prominence.
+[22/04/2026 - 4w] Congratulating new leadership appointments at LinkedIn, highlighting future opportunities.</t>
+        </is>
+      </c>
+      <c r="E140" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>HungryHungry (South Wharf, Victoria, Australia)</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>HungryHungry merges with MOBI to create a leading B2B and consumer-facing hospitality platform (19/05/2022)
+Melbourne-based hospitality technology company HungryHungry announced a merger with New Zealand–based MOBI to form a combined B2B and consumer-facing platform for hospitality venues. The merged business brings together digital menus, ordering and payments technology used by thousands of venues, aiming to deepen customer engagement and brand loyalty while expanding its Australasian footprint.
+HungryHungry secures $3 million in venture debt funding following successful capital raise (10/11/2020)
+HungryHungry, a Melbourne-founded digital ordering and payments platform for hospitality venues, obtained a $3 million venture debt facility from Partners for Growth. The funding followed a successful earlier capital raise and was driven by rapid adoption of online ordering during the COVID-19 pandemic, providing additional capital to support product development and growth across the hospitality sector.</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 1d] Announcement of participation in Food &amp; Hospitality Week with Otto AI, highlighting technology-focused innovations.
+[19/05/2026 - 1d] Celebrating the opening of Hotel Panorama, a new venue by Hurley Hotel Group, and promoting online ordering support.
+[11/05/2026 - 1w] Invitation to connect at Food &amp; Hospitality Week, showcasing new tools and collaboration with partners.
+[22/04/2026 - 4w] Highlighting a presentation at HubSpot's GROW conference about AI and human collaboration, showcasing company expertise.</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hungryhungry/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
+          <t>Hutly</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>Hutly — The Agentic Workforce for Real Estate (01/01/2025)
+Company website describing Hutly’s current positioning as an AI-powered agentic execution platform for real estate enterprises, indicating product expansion and continued growth in automation and compliance services.
+FinTech Hutly appoints Stuart Spiteri CEO (01/02/2023)
+Reports that Hutly appointed Stuart Spiteri as Chief Executive Officer, highlighting leadership growth at the Brisbane-based real estate fintech company and its evolution since launching in 2018.
+Brisbane Proptech Firm Streamlines Real Estate Contracts (01/07/2021)
+Profile of Brisbane-based Hutly describing rapid adoption of its contracts platform across Queensland and Victoria, including expansion to thousands of agencies and large volumes of contracts executed. The article also notes recognition as a finalist in the 2021 Fintech Awards.</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to leverage networks for business opportunities.
+[27/04/2026 - 3w] LinkedIn recognized as the top domain for professional queries in AI search engines, indicating market dominance.
+[22/04/2026 - 4w] Congratulations to new leadership appointments at LinkedIn, indicating organizational changes and growth potential.</t>
+        </is>
+      </c>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="16" t="inlineStr">
+        <is>
+          <t>Hydrix (Melbourne)</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>Hydrix enters A$2.5m contract to develop SynCardia's next-generation TAH (27/02/2025)
+Hydrix announced a A$2.5 million contract to commence development work on SynCardia's next-generation total artificial heart, signaling continued commercial momentum in its medical device business.
+Hydrix releases December Half 2024 trading update and growth outlook (27/02/2025)
+Hydrix reported consecutive profitable quarters in its Services business, supported by stronger margins, higher billable utilisation, and improved operational performance, indicating positive financial progress.
+Hydrix Limited raises capital via a placement to fund growth strategy and debt reduction ()
+Hydrix completed a capital raise with institutional and sophisticated investors to support its growth strategy and extinguish outstanding secured debt, strengthening its balance sheet for future expansion.
+Panorama Synergy announces acquisition of Hydrix through an asset purchase agreement ()
+Panorama Synergy disclosed a deal to acquire Hydrix, with the merged group expected to focus on advanced sensor systems and IoT communications while continuing to support Hydrix's engineering services business.</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcement of a collaboration with Serena Williams and Reckitt to mentor underrepresented founders.
+[27/04/2026 - 3w] LinkedIn is recognized as the #1 most-cited domain for professional queries on AI search engines.
+[22/04/2026 - 4w] Announcement of new leadership roles for Daniel Shapero as CEO and Mohak Shroff as President.</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
+        <is>
+          <t>ISA Healthcare Solutions</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>ISA Healthcare Solutions to showcase MMEx innovations at AIDH WA Digital Health Summit 2026 (10/02/2026)
+ISA Healthcare Solutions announced that its MMEx platform will be exhibited at the AIDH WA Digital Health Summit 2026 in Perth. Participation in this major industry event highlights the company’s growing profile in Western Australia’s digital health ecosystem and its continued product development and customer engagement efforts around MMEx.
+MMEx 2023 in Review highlights platform enhancements and secure messaging integration (15/12/2023)
+In its ‘MMEx 2023 in Review’ update, ISA Healthcare Solutions detailed significant enhancements to its MMEx clinical information system, including integration with HealthLink secure messaging for securely sending documents to other clinicians and services. These ongoing product upgrades indicate continued investment in the platform and support for expanding clinical collaboration and interoperability across its customer base.</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to leverage networks for business opportunities and mentorship for underrepresented founders.
+[27/04/2026 - 3w] LinkedIn becoming the top-cited domain for professional queries indicates its growth in influence and reach in AI search engines.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicative of internal growth and opportunity.</t>
+        </is>
+      </c>
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>Idmeta (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr"/>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announces a partnership with Serena Williams and Reckitt to leverage networks for business success, focusing on mentorship and connection building.
+[27/04/2026 - 3w] States that LinkedIn is the most-cited domain for professional queries on major AI search engines, indicating its significance and growth in AI visibility.
+[22/04/2026 - 4w] Announcement of new leadership with Daniel Shapero as CEO and Mohak Shroff as President, suggesting significant changes and future potential for LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>Ikara (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>ExtraHop eyes Queensland and WA growth on back of Ikara signing (14/09/2016)
+Real-time IT analytics vendor ExtraHop signed Ikara Group as a reseller partner to expand its presence across Queensland and Western Australia. The deal adds Ikara to ExtraHop’s fast‑growing Australian partner network and positions Ikara to drive additional analytics, IT operations, and business intelligence projects with enterprise and government clients, supporting Ikara’s growth in the digital operations and performance space.</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams to mentor underrepresented founders.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicating company growth potential.</t>
+        </is>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>InfoMedix</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>InfoMedix celebrates 25th anniversary with continued innovation (11/04/2025)
+InfoMedix marked its 25th anniversary as a digital medical record and content management provider, highlighting its role supporting some of Australia’s busiest and best-known healthcare providers. The milestone underscores long‑term growth in installed sites, user numbers, and document volumes, and the company emphasised ongoing product innovation and expansion of its digital health solutions for hospitals and healthcare services.
+St Vincent’s Hospital Melbourne successfully migrates to InfoMedix Cloud on AWS (23/07/2024)
+St Vincent’s Hospital Melbourne transitioned its digital medical records to the InfoMedix Cloud platform, powered by Amazon Web Services. The migration represents a major cloud deployment for InfoMedix, demonstrating product maturation, scalability, and deep integration with a large tertiary hospital, and is positioned as a milestone in the company’s cloud‑based healthcare technology offering.
+InfoMedix launches Coding Manager in collaboration with St John of God Health Care (18/10/2023)
+InfoMedix officially launched Coding Manager, a new software tool developed with St John of God Health Care to streamline and improve clinical coding workflows. The product launch expands InfoMedix’s portfolio beyond digital medical records into coding optimisation and demonstrates growth through product innovation and collaboration with a major healthcare provider.
+InfoMedix and Synapse Medical announce integration and partnership (16/09/2021)
+InfoMedix partnered with Synapse Medical Management to integrate Synapse’s Medicare‑integrated billing app (Synapps MBS) and automated clinical coding solution (Aircoder) with InfoMedix’s digital medical record platform. The alliance creates a joint market offering for Australia and international markets, signalling strategic expansion through partnerships and broader solution capabilities.
+InfoMedix partners with TIMG to deliver end‑to‑end information management for healthcare (05/05/2020)
+InfoMedix formed a partnership with The Information Management Group (TIMG), a document and data management specialist, to provide an end‑to‑end solution for healthcare information management. The collaboration combines InfoMedix’s digital medical record platform with TIMG’s storage and data services, strengthening InfoMedix’s value proposition and supporting growth in hospital and health service deployments.
+Adeney Private Hospital selects InfoMedix DMR for new $75 million facility (14/02/2020)
+The new $75 million Adeney Private Hospital in Kew, Melbourne, chose InfoMedix’s Digital Medical Record (DMR) as its core digital records solution. Being selected as the DMR provider for a greenfield private hospital highlights InfoMedix’s market traction and contributes to its expansion across private hospital deployments.</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 2w] Introduction of innovative features in InfoMedix Digital Patient Chart and Coding Manager aimed at improving workflow efficiency.
+[29/04/2026 - 3w] Customer engagement forum reveals new product features and a roadmap based on customer insights, indicating strong client relationships and product evolution.</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/infomedix/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>Informed Sources (Brisbane)</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>Informed Sources expands global operations beyond petrol price monitoring (15/03/2024)
+Informed Sources, originally founded in Brisbane in 1987 to collect petrol prices via drive‑by surveys, has significantly expanded its global operations and product offering. The company now employs over 150 staff worldwide and provides technology solutions for fuel and supermarket pricing, site analysis, network planning and customised market intelligence. This marks sustained growth from a local data collector to a global retail market intelligence provider.
+Informed Sources recognised as global leader in retail market intelligence data (10/11/2023)
+Informed Sources has been recognised in its corporate materials and industry commentary as a global leader in the collection, cleansing and provision of retail market intelligence data. The company’s evolution from a Brisbane start‑up to a leading data and analytics organisation serving fuel and retail markets worldwide highlights its long‑term growth, industry reputation and continued investment in data quality and analytics capabilities.
+Informed Sources grows product suite with advanced market intelligence solutions (05/06/2022)
+Informed Sources has broadened its product suite to include advanced market intelligence offerings focused on fuel and supermarket pricing, site analysis, network planning and customised data solutions. This diversification from core petrol price data into wider FMCG and retail analytics demonstrates ongoing product expansion and deeper engagement with large retail and fuel clients globally.</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 1d] Announces first-time participation at UNITI Expo, indicating business expansion and outreach to potential clients.
+[12/05/2026 - 1w] Highlights extensive data collection on German forecourts, showing innovation and potential product development presented at Uniti Show.
+[05/05/2026 - 2w] Promotes attendance at the Uniti Show, indicating business expansion and marketing efforts by presenting at industry events.</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-informed-sources-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>Inlogik</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>Inlogik reaches $10.3M in annual recurring revenue with $31M valuation as a bootstrapped SaaS business (01/02/2025)
+Financial services software provider Inlogik, headquartered in Sydney, achieved $10.3 million in annual recurring revenue and a $31 million valuation without raising external capital. The company has demonstrated consistent revenue growth since its launch in the early 1990s and now employs around 94 staff, highlighting strong, self-funded financial performance in the card management and spend analysis market.
+Inlogik opens New York office to better service North American market (01/06/2023)
+Inlogik, the Sydney-headquartered card management and expense management platform provider, expanded its international footprint by opening a New York office to better support customers and partners across North America. The move signals growing global demand for Inlogik’s card control and reporting solutions and reflects the company’s strategy to deepen its presence in key overseas markets.
+Inlogik shareholders complete acquisition and expand operations with new Sydney office (01/05/2020)
+Current shareholders completed the acquisition of Inlogik and its expense management product suite, while also opening a new Sydney office alongside the existing Melbourne location. The transaction and office expansion underscore confidence in the company’s growth trajectory and strengthen its presence in Australia’s financial and technology hub.</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt focusing on networking and mentorship for underrepresented founders.
+[27/04/2026 - 3w] Announcement of LinkedIn becoming the most-cited domain for AI queries, indicating growth in relevance and usage.
+[22/04/2026 - 4w] Congratulating new leadership appointments that may signal a strategic shift and growth opportunities for LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>Inservio</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr"/>
+      <c r="D150" s="17" t="inlineStr"/>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/inservioaustralia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>Insurance &amp; Superannuation Administration Services (ISAS)</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>ISAS emerges as one of Australia’s leading boutique administrators to life insurers and superannuation funds (01/03/2024)
+Insurance &amp; Superannuation Administration Services (ISAS), based in Melbourne, highlights that it has grown into one of Australia’s leading boutique administration service providers, partnering with several of the country’s largest life insurers and superannuation funds. This positioning reflects multi‑year client growth and increasing mandate size, indicating a successful expansion in its core administration business.
+Melbourne-based ISAS expands client support with dedicated call centre for insurers and super funds (01/03/2024)
+ISAS reports operating a dedicated Melbourne-based call centre to handle queries for its life insurance and superannuation fund clients. While framed as a service feature, the investment in a local contact centre and associated staffing points to operational expansion to support a growing client base and higher service volumes.
+ISAS promotes cost-efficiency benefits as it scales administration services for super funds (01/03/2024)
+Insurance &amp; Superannuation Administration Services emphasises that its administration solutions enable partners to reduce overall administration expenses and increase competitiveness. The messaging underscores ISAS’s ability to deliver scalable, cost-effective outsourcing as it grows its role in the superannuation and life insurance administration ecosystem.</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt on leveraging networks for opportunity.
+[27/04/2026 - 3w] Recognition of LinkedIn's leading position in AI searches for professional queries.
+[22/04/2026 - 4w] Announcement of new executive roles at LinkedIn, indicating internal changes and growth.</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>Intech Solutions</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>From the Office to the Cloud (01/01/2023)
+Intech Solutions highlighted a successful cloud transformation delivered for a client in 2023, showing continued product deployment and modernization work for its data solutions platform.
+Interview: Terry Goodman, Intech Solutions (01/01/2019)
+The company’s founder discussed how Intech Solutions has grown since its founding in 1996 and noted deployments at more than 100 enterprise customer sites, indicating long-term business expansion.</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr"/>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intech-solutions-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>InterIntra</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>North Adelaide Football Club partners with Inter Intra for end‑to‑end IT and cyber security services (06/03/2024)
+The North Adelaide Football Club announced a partnership with Inter Intra to provide all of the club’s information technology services, including cyber security, communications and broader IT support. The deal positions Inter Intra as NAFC’s outsourced IT department, indicating growth in Inter Intra’s client base and reinforcing its role as a trusted technology partner for South Australian organisations.</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr"/>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/interintra/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>Intermedium (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>Intermedium, supported by Amazon Web Services and NEC, releases 8th ANZ Digital Government Readiness and Maturity Indicator Report (14/08/2024)
+Intermedium, the Sydney-based specialist public sector ICT research firm, released the 8th edition of its ANZ Digital Government Readiness and Maturity Indicator (DGRMI) report, supported by Amazon Web Services and NEC. The 2024 report expands Intermedium’s long‑running benchmarking of digital government into a broader readiness and maturity framework, reflecting growing demand from both government and industry for its analysis. Continued publication of the DGRMI, and collaboration with large partners like AWS and NEC, point to ongoing growth in Intermedium’s influence and commercial relationships in the digital government and management consulting space.
+2024 ANZ Digital Government Readiness and Maturity Indicator (DGRMI) Report highlights expanded digital readiness methodology (01/08/2024)
+In its 2024 ANZ DGRMI report, Intermedium broadened its long‑standing Digital Government Ranking to measure not just digital service delivery but also digital readiness and maturity across Australian and New Zealand jurisdictions. The shift in methodology, documented in the 2024 report, signals Intermedium’s growing role as a key benchmarking authority for digital government and reflects increased subscription and engagement from public sector agencies and industry looking to understand ICT and digital trends.</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 1d] Announces the launch of Govii, an AI tool for government sales strategy.
+[01/05/2026 - 2w] Mentions the recruitment of economist Meghan Quinn as Secretary of the Department of Defence.
+[24/04/2026 - 3w] Announces the appointment of a new Chief Information and Data Officer at Austrade.
+[23/04/2026 - 3w] Announces a pledge to increase Defence spending by $53 billion over the next seven years.
+[21/04/2026 - 4w] Reports on the appointment of Ingrid Stitt as the state’s new minister for Government Services.</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intermedium-au/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>Investigation Management Australia (trading as Comtrac)</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>Atturra and Comtrac team up on AI‑driven investigation tools for law enforcement and regulators (18/04/2024)
+Technology services group Atturra entered a strategic partnership with Brisbane‑based investigations software provider Comtrac (Investigation Management Australia) to target law enforcement and regulatory agencies nationwide. Atturra will resell, implement and host Comtrac’s AI‑enhanced investigation and digital brief‑of‑evidence platform, enabling Investigation Management Australia to scale deployments and accelerate adoption of its software across Australia.
+Atturra partners with Comtrac to deliver industry‑leading investigative technology for Australia’s law enforcement and regulatory agencies (16/04/2024)
+Atturra announced a strategic partnership with Comtrac (the investigations and digital brief‑of‑evidence platform developed by Investigation Management Australia), under which Atturra will act as a reseller, implementation partner and hosting provider in a shared‑services model. The deal is aimed at scaling Comtrac’s reach across Australian law‑enforcement, government and regulated industries, signalling commercial expansion for Investigation Management Australia.
+Investigation Management Australia reaches $500K trailing‑twelve‑month revenue milestone with COMtrac investigation platform (01/09/2019)
+Profile information on Gust for Investigation Management Australia, the Brisbane‑based software company behind the COMtrac investigation and evidence‑management platform, reports that the business has reached approximately $500,000 in trailing‑twelve‑month revenue with a lean team of three employees. This indicates meaningful commercial traction and revenue growth for the company in the law‑enforcement and regulatory‑technology market.</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>[20/04/2026 - 1mo] Announces winning the Telstra National Best of Business Award, indicating recognition and success in the Embracing Innovation category.</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comtrac/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>Investment Control Systems (ICS), Sydney, New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>ICS implements cloud-native ATHENA platform at Loftus Peak (21/05/2026)
+ICS announced the implementation of its cloud-native ATHENA investment data platform at Loftus Peak, highlighting continued product adoption and platform expansion for the Sydney-based investment data management firm.
+ICS featured for global expansion and strategic partnerships (01/05/2024)
+Forbes Australia profiled ICS as an Australian investment data management firm focused on building strategic partnerships as it expands its global operations, underscoring the company’s growth trajectory outside its home market.</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr"/>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/icsidm/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>IoT Automation (Burleigh Heads, Queensland, Australia)</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>About Us - IoT Automation (capability and international presence) (01/01/2024)
+IoT Automation describes itself as an Australian-born designer, deployer and supporter of technology solutions for the mining industry, headquartered on the Gold Coast with additional offices in Mongolia and Indonesia. The company highlights its global reach and local expertise across regional mining sectors, and showcases a software-controlled smart lighting system that improves safety for evacuations and emergency responses in underground mines, underpinned by its specialisation in wireless sensor networks and Internet of Things (IoT) deployments.</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 2d] The company showcased advanced technology at the World Tunnel Congress, highlighting two new products that enhance safety in underground environments.
+[15/05/2026 - 5d] The post discusses launching a new product, the Dragonfly Voice Module, at the upcoming World Tunnel Congress, indicating product expansion.
+[30/04/2026 - 2w] The company is promoting its award-winning DragonFly system at the World Tunnel Congress, indicating recognition within the industry.</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iot-automation-global/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>JWGecko</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>JWGecko draws exceptional market interest amid strong software sector momentum (15/03/2025)
+Business intelligence platform ZoomInfo highlights JWGecko as drawing "exceptional interest" within the software industry, indicating notable developments or strong market momentum for the company. While the brief does not disclose specific deal values or customer names, the increased profile on a major data platform suggests JWGecko is experiencing heightened demand, potentially from new client wins or expanded engagements for its training-organisation automation tools.
+JWGecko expands global client base for training automation platforms (01/11/2024)
+JWGecko reports that it now innovates and builds systems for clients across Australia, New Zealand, Asia, the Middle East, and the United States. The company emphasises its mission to provide software tools that automate processes for training organisations, enabling them to focus on quality learning and commercial outcomes. This broad geographic reach points to sustained international expansion and ongoing adoption of its digital platforms in multiple regions.</t>
+        </is>
+      </c>
+      <c r="D158" s="17" t="inlineStr"/>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jwgecko-p-l/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>Kaine Mathrick Tech</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>Behind the Fast50: Kaine Mathrick Tech (15/04/2025)
+Techpartner.news profiled Kaine Mathrick Tech after it achieved a 20% revenue increase in the 2025 financial year, reaching $21 million and placing 14th overall in the 2025 Techpartner.news Fast50 list. Services accounted for 72% of revenue, with managed services and cybersecurity contributing the majority. The article also highlighted the company’s ongoing geographic expansion across Australia and its multi‑year recognition on the Fast50 rankings.
+Kaine Mathrick Tech named among Australia’s Fast 50 technology companies for 2025 (10/04/2025)
+Kaine Mathrick Tech announced that it was named one of Australia’s Fast 50 technology companies for 2025 by TechPartner.News, recognising it as one of the nation’s fastest‑growing and most innovative technology businesses. The company attributed the achievement to its cyber‑first managed services model and continued investment in people and customer experience.
+Our Journey: KMT recognised in Australia’s 2025 TechPartner Fast 50 (10/04/2025)
+In a company story update, Kaine Mathrick Tech highlighted its inclusion in the 2025 TechPartner Fast 50 as a major milestone in its growth journey. The piece outlines how the Melbourne‑founded, cyber‑focused managed service provider has scaled its operations and capabilities over more than a decade while maintaining a ‘human‑first’ approach to technology services.
+Kaine Mathrick Tech expands national footprint with cyber‑first managed services (01/03/2024)
+Kaine Mathrick Tech was profiled in NEXTDC’s ecosystem directory for its cyber‑first managed services offering to Australian SMBs. The listing underscores the company’s expanded presence across major Australian cities including Sydney, Melbourne, Brisbane, Canberra, Adelaide, Perth, Sunshine Coast, Darwin and Port Hedland, indicating a broadening national footprint and growing partner ecosystem.</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 1d] The company is hiring a new Onsite Support Technician, indicating team growth.
+[14/05/2026 - 6d] The company is hiring a new Customer Success Lead, further indicating growth in the team.
+[05/05/2026 - 2w] Shared a case study showcasing a transformation in IT strategy for AFS Logistics, emphasizing business growth.
+[28/04/2026 - 3w] Welcoming new team members to KMTech, indicating growth and capability expansion.
+[28/04/2026 - 3w] The company is hiring a new Project &amp; Sales Coordinator, indicating team growth.
+[21/04/2026 - 4w] Mentions a partnership with CT Connections that resulted in IT improvements during expansion.</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kmt-cyber-first-msp/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>Karaka Orthodontics</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>Karaka Orthodontics invests in latest digital orthodontic technology to enhance patient care (01/01/2023)
+Karaka Orthodontics’ website highlights the practice’s use of the latest orthodontic technology in its patient planning process, including digital diagnostics and customised treatment planning tools, to improve treatment outcomes and efficiency. This investment in advanced clinical technology reflects ongoing reinvestment and operational growth aimed at scaling high‑quality specialist services in the Auckland region.
+New best‑in‑class Karaka Orthodontics practice opens in high‑growth Karaka development (01/03/2018)
+Dentec’s project profile describes how Dr Bhavia developed Karaka Orthodontics as a best‑in‑class, patient‑focused orthodontic practice in the new Karaka development, a high‑traffic growth area in South Auckland. The purpose‑built fit‑out, modern equipment and design were part of a strategic move to capture demand in the expanding community and position the practice for long‑term growth.
+Karaka Orthodontics established to expand specialist orthodontic care in Franklin (01/01/2018)
+Karaka Orthodontics was established in 2018 as an associate practice to Pukekohe Orthodontists (established 2009), specifically to cater for growing demand for specialist orthodontic treatment in the wider Franklin and South Auckland region. The creation of the Karaka clinic represented a geographic expansion of the original practice’s footprint and additional service capacity for local patients.</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr"/>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ampss101/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>Key Pharmaceutical Pty Ltd (12 Lyonpark Road, Macquarie Park, NSW 2113, Australia)</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr"/>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>[04/05/2026 - 2w] Key Pharmaceuticals is seeking applications for a new Senior Brand Manager position, indicating team growth.</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/key-pharmaceuticals/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
+        <is>
+          <t>Keyvision (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>Keyvision expands footprint with adoption across high‑profile mixed‑use precincts such as Collins Arch (05/05/2021)
+Keyvision showcases its software delivering integrated property, tenant and community management for high‑profile projects including Collins Arch in Melbourne. Featuring these marquee developments on its solutions page reflects growth in Keyvision’s commercial partnerships and broader market penetration within large‑scale, mixed‑use and premium property assets in Australia.
+Keyvision platform selected for landmark M‑City mixed‑use development (10/09/2020)
+Keyvision’s software platform is featured as the property, tenant and community management solution for M‑City, described as one of the largest mixed‑use developments outside Melbourne’s CBD. The project involves multiple user groups, including residential, commercial and retail stakeholders. Being chosen for such a large, complex development demonstrates Keyvision’s expanding role in major Australian real‑estate projects and validates the scalability and maturity of its digital management solutions.
+Keyvision emerges as digital pioneer transforming Australian stakeholder communication (01/06/2019)
+Keyvision highlighted its evolution from a late‑1990s web‑based service into a ‘digital pioneer’ that has reshaped how Australian companies communicate with employees, stakeholders and clients. The company emphasised that its interactive, customisable online platforms have opened new, honest communication channels and helped major organisations strengthen brand presence and community reputation, signalling sustained growth in client base and influence across Australia’s corporate and property sectors.
+Keyvision becomes leading consultant to major Australian property developers (15/03/2015)
+In its corporate overview, Keyvision reports that during the early 2000s it became a pioneer and leading consultant to many prominent property developers around Australia. This period of expanding advisory roles formed the core learning foundation for the company’s current software and technology solutions for property, facility and community managers, indicating significant growth in industry standing, client portfolio and service sophistication.</t>
+        </is>
+      </c>
+      <c r="D162" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Partnership with Serena Williams and Reckitt, emphasizing network leverage for success.
+[27/04/2026 - 3w] LinkedIn becoming the top-cited domain indicates growth in visibility and engagement.
+[22/04/2026 - 4w] Announces leadership changes with Daniel Shapero as new CEO, suggesting organizational growth.</t>
+        </is>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>Klint Neuro</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>Klint Neuro Expands Specialist Neurological Physiotherapy Services Across Melbourne Suburbs (01/03/2024)
+Klint Neuro, a neurological physiotherapy and disability-focused allied health provider, has expanded its footprint across Melbourne with multiple clinic locations now operating in Highett, Forest Hill, Heidelberg, Malvern, Narre Warren and Mount Eliza. The group also provides telehealth and home-visit services, enabling them to serve regional, interstate and international clients. This geographic and service expansion reflects steady demand growth for specialised neuro rehab services for both adults and children.
+Klint Neuro Strengthens Position as Leading Neuro &amp; Disability Provider with NDIS Commission Accreditation (15/08/2023)
+Klint Neuro has reinforced its status as a leading neuro and disability services provider through formal accreditation by the NDIS Commission. As an NDIS-registered organisation, Klint Neuro is authorised to deliver neurological physiotherapy and related allied health services under NDIS funding, demonstrating compliance with rigorous safety, quality and governance standards. This accreditation supports further growth in its caseload of adults with disabilities and strengthens relationships with funding bodies.
+Klint Neuro Builds Multidisciplinary Allied Health Team Focused on Neurological Rehabilitation (10/11/2022)
+Klint Neuro has continued to grow its multidisciplinary workforce of neurological physiotherapists and allied health assistants to meet increasing demand for intensive neurorehabilitation. Profiles of clinicians such as Lara Miller and Shona Bischof highlight the organisation’s recruitment of therapists with advanced training in complex neurological and vestibular conditions. The expanding clinical team enables Klint Neuro to offer more appointment capacity, greater subspecialisation and broader coverage across its Melbourne clinics and home-visit network.</t>
+        </is>
+      </c>
+      <c r="D163" s="17" t="inlineStr"/>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/klint/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>Kwela Solutions</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>Coal Mining Industry Long Service Leave Funding Corporation selects Kwela Solutions’ Folio as GRC platform (10/04/2024)
+Kwela Solutions announced that the Coal Mining Industry (Long Service Leave Funding) Corporation has chosen its Folio web‑based governance, risk and compliance (GRC) software. The win adds a major public‑sector‑adjacent client to Kwela’s portfolio and highlights Folio’s applicability to complex, regulated environments beyond its established base in health, not‑for‑profit, financial services, and other industries.</t>
+        </is>
+      </c>
+      <c r="D164" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announces a partnership with Serena Williams and Reckitt to promote network leverage and mentorship for underrepresented founders.
+[27/04/2026 - 3w] Highlights LinkedIn's recognition as the #1 domain for professional queries on AI search engines, indicating significant growth in visibility and influence.
+[22/04/2026 - 4w] Announces the appointment of new leadership positions with a note on the future opportunity for LinkedIn, suggesting growth.</t>
+        </is>
+      </c>
+      <c r="E164" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>L &amp; I Electrical Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr"/>
+      <c r="D165" s="17" t="inlineStr"/>
+      <c r="E165" s="16" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>Lane Cove Orthodontics</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr"/>
+      <c r="D166" s="17" t="inlineStr"/>
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lane-cove-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>Lawcadia</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C167" s="17" t="inlineStr">
+        <is>
+          <t>Legal tech group Lawcadia expands into UK after another strong year of growth (15/02/2021)
+Following a strong year of growth, Brisbane-based legal technology company Lawcadia announced its expansion into the UK market. The move extends the reach of its end-to-end legal operations and matter management platform, targeting corporate and government in-house legal teams and law firms seeking improved efficiency, visibility, and control over legal work and spend.
+Lawcadia recognised as award-winning end-to-end legal operations platform (10/11/2020)
+Lawcadia, headquartered in Brisbane, has been recognised as an award-winning end-to-end legal operations platform serving corporate and government in-house legal teams. Its no-code automation engine, two-sided platform, and advanced workflows have driven strong adoption and positioned the company as a leading provider of legal matter and spend management software in Australia and abroad.
+Lawcadia secures $1.3 million funding boost and celebrates award win (24/10/2019)
+Lawcadia announced a $1.3 million pre-Series A capital raise from private investors and Artesian, bringing total funding to $3.8 million over three years. Founders Warwick Walsh and Sacha Kirk were also recognised with Brisbane’s Young Entrepreneurs Award 2019 (Legal Category). The new capital supports scaling, global expansion, and further development of its expanded matter management and intake tools for in-house legal teams.
+Brisbane-based legal tech start-up Lawcadia raises $1.3m in pre-Series A round (23/10/2019)
+Lawcadia, a Brisbane-based legal technology company, raised $1.3 million in a pre-Series A funding round backed by private investors and Australian VC firm Artesian. This round increased the company’s total funding to $3.8 million over three years and will be used to scale the business and pursue global opportunities, building on its legal matter and spend management platform for in-house teams.
+Brisbane lawtech startup Lawcadia receives AUS $500,000 funding (19/07/2016)
+Lawcadia, the Brisbane-based lawtech startup, secured AUD $500,000 in funding to accelerate product development and team expansion. The investment was aimed at optimising its platform, which connects corporate clients with law firms and focuses on improving legal procurement and matter management.</t>
+        </is>
+      </c>
+      <c r="D167" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Collaboration with Swinburne University for managing legal, risk, and compliance work through a single platform.</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lawcadia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>Leadweigh Scales</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr"/>
+      <c r="D168" s="17" t="inlineStr"/>
+      <c r="E168" s="16" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
+          <t>Legalwise Seminars</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>Elevate your professional journey with Legalwise Seminars (26/02/2025)
+A Lawyers Weekly feature outlined Legalwise Seminars’ expanded CPD offering, including more than 1,000 hours of on‑demand recordings and a broad national conference and seminar schedule, positioning the company as a key partner in long‑term career development for legal professionals and underscoring continued growth in scale and reach.
+Celebrating 20 Years of Legalwise Seminars (30/01/2024)
+Lawyers Weekly profiled Legalwise Seminars on its 20th anniversary, highlighting how the Sydney‑based provider has grown from running CPD programs only for local legal professionals to becoming a leading CPD provider across Australia and New Zealand, now serving tens of thousands of professionals with an extensive seminar and online program portfolio.
+Legalwise Seminars broadens national and online CPD footprint (15/11/2023)
+Legalwise Seminars’ own corporate information notes that it now delivers accredited CPD seminars and online courses for lawyers, solicitors and barristers across Australia, with more than 1,000 hours of on‑demand content available, reflecting significant growth from its original Sydney‑only operations to a large, technology‑enabled national platform.
+Get to Know Us – Legalwise Seminars showcases growth to national CPD leader (10/08/2023)
+In its ‘Get to Know Us’ overview, Legalwise Seminars describes its evolution into an Australian leader in legal‑related CPD, emphasising its expanded course catalogue, conferences (including specialist events such as NDIS Law and Advertising &amp; Marketing Law), and strong reputation among legal professionals, evidencing sustained growth and market positioning.</t>
+        </is>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 2d] An article discussing complexities of European patent law, indicating a focus on expanding legal knowledge and practice in intellectual property law.
+[07/05/2026 - 1w] Webinar advertisement focused on adapting legal practices to newer client acquisition strategies amidst changing techniques in the industry, indicating growth opportunities.
+[28/04/2026 - 3w] Expanding AML and CTF programs that support compliance in organizations, indicating growth through increased service offerings in response to regulatory changes.
+[22/04/2026 - 4w] Announcement of the Annual Native Title Conference, indicating a successful event with significant registration interest, pointing to business expansion in conference offerings.</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/legalwise-seminars/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>Linked Support Solutions</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>Linked Support Solutions expands allied health offerings for disability support clients in Perth (20/05/2026)
+Linked Support Solutions highlights a broader range of therapeutic supports, including physiotherapy, occupational therapy, and speech therapy, as part of its service offering for people with disabilities in Perth. This indicates service expansion in allied health.
+Linked Support Solutions promotes expanded service mix including allied health, accommodation, employment and support coordination (20/05/2026)
+The company’s public service listing shows an expanded portfolio that includes allied health alongside accommodation, employment services, support coordination, and group activities, suggesting business growth and diversification in Perth.
+Linked Support Solutions strengthens disability and allied health support capabilities in Western Australia (20/05/2026)
+Linked Support Solutions states that it provides personalised and compassionate care with access to therapeutic supports across multiple disciplines. The breadth of its service description suggests continued growth in capability and service reach.</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr"/>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linked-support-solutions/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>Liquid State (Australia)</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
+        <is>
+          <t>Liquid State Receives ActiveKIT Funding to Grow Digital Visitor Engagement Platform (15/07/2021)
+Liquid State secured funding under Queensland’s ActiveKIT program to further develop and scale its digital engagement and communications platform for active tourism and recreation experiences. The funding supports product enhancement, pilot deployments and commercialisation activities, signalling government-backed confidence in Liquid State’s growth prospects and enabling expansion into new customer segments.
+Liquid State Ranked in Top 500 High-Growth Companies Asia-Pacific 2020 (01/03/2020)
+Liquid State, the Brisbane-based integrated communications and software platform company, was named in the Financial Times / Nikkei / Statista list of the Top 500 High-Growth Companies Asia-Pacific 2020. The recognition reflects strong revenue growth and market traction for its digital communications and content management solutions, underscoring the firm’s position as a fast-scaling Australian software company.
+Liquid State Announced as Finalist in Lord Mayor’s Business Awards (10/10/2019)
+Liquid State was selected as a finalist in the Lord Mayor’s Business Awards in Brisbane, recognising the company’s innovation and growth in developing an integrated communications and software platform. The finalist status highlights the firm’s momentum in the local tech ecosystem and its success in delivering scalable digital solutions for enterprises and government clients.</t>
+        </is>
+      </c>
+      <c r="D171" s="17" t="inlineStr"/>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/liquid-state/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
+        <is>
+          <t>Loadcell Supplies</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>Western Australia</t>
+        </is>
+      </c>
+      <c r="C172" s="17" t="inlineStr"/>
+      <c r="D172" s="17" t="inlineStr"/>
+      <c r="E172" s="16" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
+        <is>
+          <t>Loadscan (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C173" s="17" t="inlineStr">
+        <is>
+          <t>Loadscan opens new Brazilian branch in Belo Horizonte to support mining customers (25/10/2024)
+Loadscan, the New Zealand-based specialist in load volume scanning systems, has expanded its global footprint by opening a new branch in Belo Horizonte, Brazil. The new office will support the country’s large mining sector with Loadscan’s patented load volume scanning (LVS) technology, enabling more accurate truck payload measurement, reduced haulage inefficiencies, and better production tracking. This move strengthens the company’s presence in Latin America and reflects growing international demand from major mining operations for its scanning solutions.
+Loadscan strengthens international presence with multi-region offices in NZ, Australia, USA and Brazil (15/03/2024)
+Information from Loadscan’s corporate contact details highlights the establishment and consolidation of dedicated offices in New Zealand (Hamilton HQ), Australia (Redland Bay, QLD), the United States (Conroe, Texas), and Brazil (Contagem, MG). These locations support regional sales, service and technical support for the company’s high-tech load volume scanning systems. The multi-continent footprint illustrates Loadscan’s evolution from a New Zealand technology developer into a global high-tech manufacturing and services provider to the mining and civil industries.
+Loadscan secures trade certification approvals in New Zealand, Australia and the United States for truck volume measurements (15/01/2024)
+Loadscan reports that its Load Volume Scanner (LVS) is the only load volume scanning system worldwide to achieve trade certification approval for truck volume measurements across multiple jurisdictions. The LVS holds Trade Approval Certificate 1556 in New Zealand, pattern approval Certificate 13/1/15 in Australia (NMI), and the National Type Evaluation Program Certificate of Conformance 24-001P in the United States. These regulatory milestones enhance the company’s competitiveness in high-value mining and civil markets by allowing its volume measurements to be used for commercial transactions, driving new sales opportunities and reinforcing its position as a global technology leader in this niche.
+Loadscan showcases advanced payload management technology at Steinexpo, targeting growth in European quarrying and mining (01/09/2023)
+New Zealand-based Loadscan exhibited for the first time at Steinexpo, a major European quarrying and mining trade fair, presenting its latest payload management and load volume scanning technologies. The company’s participation signals a strategic push into the European market, leveraging its patented LVS systems to help operators optimise truck loading, monitor haulback, and improve material reconciliation. The trade show presence underscores Loadscan’s international growth ambitions and its focus on expanding adoption of its technology among European aggregates and mining producers.
+Loadscan expands global team with new hires to support growing demand for load volume scanning solutions (01/08/2023)
+Company information compiled by ZoomInfo indicates that Loadscan, headquartered in Hamilton, New Zealand, has been expanding its workforce over the past 12 months. The firm has added new staff across its global operations to support increased demand for its patented load volume scanning technology in mining, civil construction, and bulk materials handling. The hiring trend reflects sustained revenue growth and the company’s ongoing internationalisation strategy from its New Zealand base.</t>
+        </is>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Announces that Loadscan is the only company with trade certification approval in New Zealand and Australia for volume measurements.
+[23/04/2026 - 3w] Describes a milestone in operational improvement at Gamsberg, achieved through a collaborative payload verification study.</t>
+        </is>
+      </c>
+      <c r="E173" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/loadscan/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>Loanworks</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
+        <is>
+          <t>Loanworks announces upgraded lending platform and AI-powered document processing tool (15/05/2026)
+Loanworks unveiled plans to launch a redesigned loan origination and commissions platform, Quantum, along with a new AI-based document processing solution called Document Intelligence. Quantum will modernise lending workflows, consolidating critical information and automating key lifecycle steps across multiple product types, including home loans and credit cards. Document Intelligence will use AI to classify documents, extract and validate key data against loan applications, and provide basic fraud detection, aiming to accelerate loan processing and reduce operational costs for lenders.
+Loanworks reinforces position as leading Australian lending technology provider (01/11/2024)
+Loanworks, founded in 2001 and headquartered in Sydney, continues to position itself as one of Australia’s leading providers of software, outsourcing and lending solutions for finance providers. The company emphasises its ability to tailor end‑to‑end solutions that increase efficiency and profitability for lenders, aggregators and brokers. Its sustained presence and positioning in the fast‑growing Australian fintech landscape indicate steady business traction and ongoing demand for its lending technology and services.
+Major customer‑owned bank transforms lending operations with Loanworks Origination Platform (18/08/2023)
+A leading Australian customer‑owned bank implemented the Loanworks Origination Platform to streamline new home loan and top‑up processes. The project delivered an end‑to‑end mortgage origination solution deeply integrated with the bank’s core banking system, enabling real‑time data exchange, automation and a more consistent experience for customers and brokers. This deployment underscores Loanworks’ expansion within the banking sector and its capability to handle large‑scale institutional transformations.
+Loanworks supports rapid growth of digital bank 86 400 (now Ubank) with end‑to‑end loan origination platform (10/03/2022)
+Loanworks highlighted its role in powering the home loan origination solution for digital neobank 86 400 (now Ubank). Since receiving its full banking licence in 2019, 86 400 rapidly scaled to more than 225,000 accounts and $300 million in deposits while offering broker-distributed digital mortgages. Loanworks’ platform enabled efficient, scalable origination to support this growth, demonstrating the fintech’s ability to service high‑growth banking clients and complex mortgage workflows.</t>
+        </is>
+      </c>
+      <c r="D174" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 2w] Announcement of a new job opening for a Credit Analyst, indicating team growth.</t>
+        </is>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/loanworks-technologies/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="16" t="inlineStr">
+        <is>
+          <t>LockedOn (New South Wales, Australia)</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr"/>
+      <c r="D175" s="17" t="inlineStr"/>
+      <c r="E175" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lockedon/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="16" t="inlineStr">
+        <is>
+          <t>Logiqc</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C176" s="17" t="inlineStr">
+        <is>
+          <t>Logiqc marks FY25 as ‘a year of innovation and growth’ for its healthcare quality platform (15/07/2025)
+In a FY25 wrap‑up published on its blog, Brisbane‑based quality and risk management software provider Logiqc reported strong platform growth across Australia and New Zealand. The company highlighted expanded functionality in its integrated quality management system, a growing customer base in healthcare and community services, and increased product investment aimed at supporting larger, multi‑site organisations. The retrospective positions FY25 as a significant year of innovation‑driven expansion for the business.
+Royal Far West completes successful digital transformation using Logiqc platform (20/03/2025)
+Logiqc published a detailed customer story describing how children’s charity Royal Far West implemented the Logiqc quality management platform as part of a broader digital transformation. The case study reports improved governance, streamlined risk and incident management, and better visibility of compliance activities. The deployment across a complex, multi‑service organisation demonstrates Logiqc’s growing role in large‑scale healthcare and community services environments, signalling deeper market penetration for the Brisbane software company.
+Logiqc reinforces position as one of ANZ’s most widely used healthcare quality and risk platforms (01/11/2024)
+An updated overview on Logiqc’s website describes the company’s integrated quality management system as "one of the most widely used" safety, quality, and risk management platforms in the healthcare and community services sectors across Australia and New Zealand. The company notes nearly 20 years of continuous operation, expanding sector coverage from healthcare into social services and community organisations. This positioning reflects sustained regional adoption and long‑term growth for the Brisbane‑headquartered software vendor.
+Logiqc passes 18‑year milestone supporting governance and quality improvement in healthcare (10/05/2024)
+In its About Us materials, Logiqc emphasises almost two decades of continuous service delivering tailored governance, quality, safety, and risk management solutions to healthcare, social services, and community organisations. The company highlights its evolution into an "all‑in, out‑of‑the‑box" platform, indicating maturation from consultancy‑style support to a scalable software product. This longevity and productisation signal durable, organic growth for the Brisbane‑based software company in a specialised compliance market.</t>
+        </is>
+      </c>
+      <c r="D176" s="17" t="inlineStr">
+        <is>
+          <t>[20/05/2026 - today] Successful launch of new features for online auditing and AI-assisted incident reporting at the Digital Health Festival in Melbourne.
+[14/05/2026 - 6d] Announcement of attendance at the Digital Health Festival and launch of a new suite of capabilities including AI features and tools for audit management.</t>
+        </is>
+      </c>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/logiqc/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="16" t="inlineStr">
+        <is>
+          <t>M. Brodribb Pty Ltd (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>M. Brodribb expands manufacturing footprint with Sri Lanka facility (01/03/2022)
+M. Brodribb, the Melbourne‑based power conversion specialist, confirmed that in addition to its Glen Iris headquarters and factory, it now has manufacturing operations in Sri Lanka through subsidiary Brodribb Lanka (Pvt) Ltd. The move expands the company’s production capacity while keeping engineering, design and core manufacturing in Victoria, positioning the business to better serve resource, electricity transmission and distribution, defence and infrastructure markets.
+M. Brodribb maintains ISO 9001:2015 certification, underpinning growth in power conversion markets (10/11/2020)
+Melbourne‑based M. Brodribb Pty Ltd continues to hold ISO 9001:2015 quality management certification (LRQA Certificate MEL6009794) for its Glen Iris manufacturing facility. The certification supports the company’s ongoing growth by meeting stringent quality requirements for power stations, substations, warships and other critical infrastructure applications, helping it compete for larger contracts in Australia and abroad.
+M. Brodribb broadens engineered power conversion solutions for Australian infrastructure and defence (05/05/2019)
+Building on over 60 years of electrical engineering experience, M. Brodribb has expanded its engineered solutions portfolio for AC and DC power conversion. The company now supplies a wider range of battery chargers, cathodic protection rectifiers, high‑current and high‑voltage DC power supplies, AC stabilisers and specialist transformers, targeting growth opportunities in electricity transmission, distribution, resources, and defence infrastructure projects.
+Brodribb Lanka (Pvt) Ltd established as Sri Lankan subsidiary of M. Brodribb Pty Ltd (15/06/2018)
+M. Brodribb Pty Ltd formalised its international growth by establishing Brodribb Lanka (Pvt) Ltd as a subsidiary operation. The Sri Lankan entity supports the Australian parent’s power conversion product range, including battery charging systems, cathodic protection rectifiers and specialist transformers, providing additional manufacturing capability and cost‑effective support for export and regional customers.</t>
+        </is>
+      </c>
+      <c r="D177" s="17" t="inlineStr"/>
+      <c r="E177" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-brodribb-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="16" t="inlineStr">
+        <is>
+          <t>MAK Water</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C178" s="17" t="inlineStr">
+        <is>
+          <t>MAK Water adds NSW wastewater business Baldwin Industrial Systems to boost national footprint (09/07/2024)
+MAK Water expanded its capabilities and geographic reach by acquiring New South Wales–based Baldwin Industrial Systems, a specialist in industrial and trade‑waste treatment. The deal brings additional engineering expertise, a larger installed base, and a stronger presence on the east coast, reinforcing MAK Water’s growth strategy in wastewater treatment solutions for commercial and industrial clients.
+MAK Water evolves from service firm to OEM with over 5,000 systems installed worldwide (10/03/2022)
+MAK Water reported that it had surpassed 5,000 water and wastewater treatment systems installed throughout Australia and internationally. Founded in 2003 as a service and maintenance business, the company has grown into a recognised OEM, designing, building, operating, and maintaining treatment plants and equipment for diverse industry sectors.
+MAK Water recognised as a leader in water and wastewater technology under CEO Andy Byk (01/11/2019)
+Company board information notes that since Andy Byk became CEO in 2009, MAK Water has been developed into a recognised leader in water and wastewater technology, with plants installed across Australia and overseas. The description highlights sustained growth in project delivery and international reach over the decade.
+MAK Water continues rapid growth with purchase of Queensland water treatment business (03/02/2016)
+Privately owned Perth company MAK Water broadened its national operations by acquiring a Queensland‑based water treatment business, described as a continuation of its rapid expansion strategy. The acquisition added new customers and service capabilities to its portfolio of industrial water and wastewater treatment solutions across Australia.
+MAK Water strengthens manufacturing and product range through acquisition of Clearmake (15/08/2013)
+MAK Water acquired industrial water equipment manufacturer Clearmake, integrating the business into the MAK Water Group. Following the transaction, the combined entity employed more than 70 people and had installed over 4,000 systems across Australasia and Southeast Asia, significantly scaling its OEM manufacturing capabilities and market reach.</t>
+        </is>
+      </c>
+      <c r="D178" s="17" t="inlineStr">
+        <is>
+          <t>[29/04/2026 - 3w] The Elevate Program invests in developing emerging leaders within MAK Water, strengthening internal leadership capabilities and culture.
+[27/04/2026 - 3w] The addition of RM-10 Oil technology through Baldwin Industrial Systems improves MAK Water's treatment solutions for complex industrial wastewater challenges.
+[21/04/2026 - 4w] MAK Water adds Baldwin Industrial Systems and introduces the RM-10 technology for treating challenging industrial wastewater, enhancing their service capabilities.</t>
+        </is>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mak-water/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="16" t="inlineStr">
+        <is>
+          <t>MJK Automation (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C179" s="17" t="inlineStr"/>
+      <c r="D179" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt to leverage networks for underrepresented founders, emphasizing partnerships and community scaling.
+[27/04/2026 - 3w] Highlights LinkedIn's rising status as a professional resource, reflecting market growth and influence.
+[22/04/2026 - 4w] Announcement of leadership changes at LinkedIn, indicating organizational growth and development.</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
+        <is>
+          <t>MNG (Perth, WA – surveying &amp; geospatial services)</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C180" s="17" t="inlineStr">
+        <is>
+          <t>McMullen Nolan Group posts strong headcount growth with nearly 700 staff across Western Australia (01/03/2025)
+Industry data provider Growjo estimates that McMullen Nolan Group (MNG), the Perth-based surveying and spatial information firm, has expanded its workforce to 689 employees and grown headcount by 19% over the past year. The same data set places MNG’s annual revenue at approximately A$250 million, underlining continued demand for its land development and resources-focused geospatial services across Western Australia and beyond.
+MNG continues to consolidate role as major surveyor for WA greenfield subdivisions (15/11/2024)
+McMullen Nolan Group reports that it is responsible for around 40% of greenfield subdivisions across the Perth metropolitan area and regional Western Australia. The company notes it has received more than 60 Urban Development Institute of Australia (WA) Awards for Excellence, indicating sustained project volume and recognition for its surveying and spatial services in the land development sector.
+MNG expands geographic footprint with multiple regional offices across Western Australia (10/09/2024)
+Perth-headquartered McMullen Nolan Group has expanded and maintained a broad regional presence in Western Australia, operating offices in Bunbury, Margaret River, Broome, Kununurra, Port Hedland and Newman in addition to its Jandakot head office. The multi-office footprint enables MNG to service land development, resources and infrastructure projects across the state more effectively, supporting business growth beyond the Perth metro area.
+MNG leverages advanced surveying and geospatial technology to drive service growth (20/06/2024)
+On its corporate site, Perth-based McMullen Nolan Group highlights sustained investment in advanced surveying, computing and mapping equipment as part of its strategy to remain a leader in geospatial and subsurface services. By pairing experienced specialists with state-of-the-art technology, MNG positions itself to win more complex projects in land development, resources and infrastructure markets across Australia.</t>
+        </is>
+      </c>
+      <c r="D180" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] A collaboration announcement with Serena Williams and Reckitt aimed at supporting underrepresented founders.
+[27/04/2026 - 3w] Recognition of LinkedIn as the top-cited domain for professional queries, showcasing its influence.
+[22/04/2026 - 4w] Announcement of new roles for Daniel Shapero as CEO and Mohak Shroff as President, indicating leadership changes.</t>
+        </is>
+      </c>
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="16" t="inlineStr">
+        <is>
+          <t>MP Orthodontics (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>MP Orthodontics launches news section to share practice updates with Melbourne community (01/01/2025)
+MP Orthodontics, an orthodontic practice based in Cheltenham, Melbourne, has introduced a dedicated ‘News’ section on its website to communicate updates with patients and the wider community. While individual posts are not visible from the search snippet, the creation of this section typically signals ongoing growth activities such as team updates, technology adoption, patient education initiatives, or community engagement. This supports the picture of a practice investing in communication and likely expanding services over time.</t>
+        </is>
+      </c>
+      <c r="D181" s="17" t="inlineStr"/>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mportho/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="16" t="inlineStr">
+        <is>
+          <t>MTA Energy</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>How MTA and TGE are decarbonising transport (03/10/2024)
+MTA Energy and Team Global Express extended their electricity supply agreement for a further three years, signaling an expanded and ongoing partnership to support decarbonisation in transport.
+MTA Energy Information - RocketReach (01/07/2024)
+Company profile information indicates MTA Energy operates as a growing retail energy business in North Sydney with reported revenue around $2 million, reflecting its commercial scale in the market.
+Q&amp;A with Gareth Mann, Managing Director, MTA Energy (01/02/2024)
+MTA Energy discussed a major fleet electrification project involving the integration of 60 EV trucks into a 240-truck fleet, highlighting infrastructure delivery and project growth in sustainable transport.</t>
+        </is>
+      </c>
+      <c r="D182" s="17" t="inlineStr"/>
+      <c r="E182" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mta-energy/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="16" t="inlineStr">
+        <is>
+          <t>MachShip</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>MachShip brings freight innovation to New Zealand (13/02/2025)
+Australian-based freight management software company MachShip is expanding internationally with an official launch into the New Zealand market scheduled for mid‑2025. The move will enable MachShip to better service existing Australian customers that operate in New Zealand while also opening new customer segments in the region. The company already integrates with more than 500 Australian transport providers, facilitates over $1 billion in annual freight spend, and serves over 3,500 business customers, positioning it strongly for this regional expansion.
+MachShip recognised with Freight Transport Solution of the Year award (01/06/2023)
+MachShip, the Melbourne‑based freight management platform, has been recognised with a ‘Freight Transport Solution of the Year’ award for its ability to improve freight efficiency, traceability and cost savings for customers. The cloud-based system integrates with a wide range of transport carriers and plugs into e‑commerce, ERP and WMS platforms, highlighting both product maturity and strong industry adoption.</t>
+        </is>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
+        <is>
+          <t>[08/05/2026 - 1w] Adventure Operations showcases their complex freight operation and announces a partnership with ASCLA for a site tour on scaling operations.</t>
+        </is>
+      </c>
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/machship/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="16" t="inlineStr">
+        <is>
+          <t>Magnum Australia</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C184" s="17" t="inlineStr">
+        <is>
+          <t>Magnum Australia makes bold strides towards a sustainable future and continued business growth (15/03/2024)
+Magnum Australia, headquartered in Kilsyth South, Victoria, highlighted a period of sustained growth driven by its Australian‑engineered fluid delivery, dust suppression, fire control and heavy‑equipment washdown solutions for the mining and heavy industries. In a media roundup on its website, the company emphasised expanding adoption of its systems across Australian mining operations, positioning its technology as setting global benchmarks for reliability and performance. The commentary frames Magnum’s ongoing investment in engineering innovation and sustainability as a key driver of revenue and market growth in the mining and metals supply chain.</t>
+        </is>
+      </c>
+      <c r="D184" s="17" t="inlineStr"/>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/magnum-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="16" t="inlineStr">
+        <is>
+          <t>Manse Medical (Victoria, Australia)</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>Manse Medical Partners with Talked to Enhance Patient Care and Support Healthcare Staff (01/10/2024)
+Manse Medical announced a strategic partnership with Talked, an Australian digital mental health platform that connects users with licensed psychologists within 12 hours. The collaboration is designed to enrich patient care by integrating rapid-access mental health support and to improve the wellbeing of Manse Medical’s healthcare staff. This move broadens the clinic’s service offering beyond respiratory and sleep medicine into coordinated mental health support, reflecting continued investment in innovative, patient‑centred care models.
+Manse Medical Consolidates Hamilton Operations While Maintaining and Developing Regional Respiratory and Sleep Services (14/12/2023)
+Manse Medical confirmed the closure of its Hamilton consulting practice on Lonsdale Street after more than 15 years, while emphasizing a strategic realignment rather than a withdrawal from the region. The company will continue to accept referrals for specialist sleep and respiratory services, offering private consultations via telehealth and from Ballarat and Warrnambool clinics. In partnership with Western District Health Service, Manse Medical specialists Dr Mohammad Touhidi and Dr Shahab Makki will see patients through the WDHS outpatient clinic and continue to develop local specialist services, with ongoing CPAP therapy and lung function testing supported from other locations. This reflects an operational restructuring with a focus on more scalable, multi‑site and telehealth‑enabled growth rather than traditional single‑site consulting.</t>
+        </is>
+      </c>
+      <c r="D185" s="17" t="inlineStr"/>
+      <c r="E185" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/manse-medical/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="16" t="inlineStr">
+        <is>
+          <t>MaxSoft Group</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C186" s="17" t="inlineStr">
+        <is>
+          <t>MaxSoft Makes Strategic Investment in ResVu (15/03/2024)
+MaxSoft Group, a leading provider of software and financial solutions to the strata industry, announced a strategic investment in Adelaide-based proptech platform ResVu. The partnership is intended to integrate ResVu’s tenant and community engagement tools with MaxSoft’s core StrataMax solution, creating a more comprehensive end-to-end software offering for the Australian strata market. The move is positioned as a growth initiative to enhance customer service capabilities and strengthen MaxSoft’s competitive position in strata-focused fintech and software services.</t>
+        </is>
+      </c>
+      <c r="D186" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] MaxSoft ranked #4 in Australia's Best Workplaces™ in Technology for 2026 by Great Place to Work, highlighting strong workplace culture and employee satisfaction.</t>
+        </is>
+      </c>
+      <c r="E186" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxsoft/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="16" t="inlineStr">
+        <is>
+          <t>Medcast</t>
+        </is>
+      </c>
+      <c r="B187" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>Medcast launches MedLuma AI platform to deliver real‑time clinical answers and CPD for Australian clinicians (01/05/2024)
+Medcast has launched MedLuma, an Australian AI‑enabled clinical knowledge platform designed initially for general practice. MedLuma provides GPs and other clinicians with real‑time, contextual answers drawn from verified Australian clinical guidelines and knowledge sources, while simultaneously tracking and awarding Continuing Professional Development (CPD) points at the point of care. The launch marks a significant expansion of Medcast’s offering beyond education into AI‑driven clinical decision support, positioning the Sydney‑based e‑learning provider in the growing market for digital tools that help clinicians manage rising information volumes during consultations.
+MedLuma launches as Australian AI‑led healthcare platform backed by Medcast (30/04/2024)
+Medcast has officially launched MedLuma, a new Australian AI‑led healthcare technology platform giving doctors and health organisations instant access to contextual answers from trusted clinical knowledge sources while earning CPD as they work. Backed by Medcast’s established reputation in healthcare education, MedLuma is presented as locally built for Australian clinicians, integrating CPD tracking with clinical search to improve care quality and efficiency. This launch reflects Medcast’s strategic growth into platform‑based services and strengthens its role in the national digital health and education ecosystem.
+Studio LDN selected to design Medcast’s new AI‑driven learning platform experience (20/03/2024)
+Design agency Studio LDN announced it has been appointed to lead the digital customer experience strategy and design for Medcast’s new AI‑enhanced learning platform. The partnership will focus on shaping how clinicians and healthcare organisations interact with Medcast’s next‑generation educational and AI tools, including its emerging platforms like MedLuma. This collaboration indicates ongoing product investment and platform development by Medcast as it modernises and scales its e‑learning and online education offering for the healthcare sector.
+Medcast accelerates growth and lifts enterprise sales by 75% through Salesforce transformation (15/11/2023)
+In a Salesforce customer story, Medcast reports that implementing Service Cloud and other Salesforce solutions has helped it accelerate business growth and increase enterprise sales by 75%. By using Salesforce to unify data, personalise engagement with healthcare organisations, and better manage customer relationships, Medcast has expanded its reach across GP practices, aged care facilities, day hospitals, and government and NGO partners such as the Black Dog Institute. The technology investment has supported both revenue growth and operational scalability for the Sydney‑based online healthcare education company.</t>
+        </is>
+      </c>
+      <c r="D187" s="17" t="inlineStr">
+        <is>
+          <t>[17/05/2026 - 3d] Medcast showcases their collaboration with PRECISE Genomics at a hospital.
+[04/05/2026 - 2w] Launch of a new platform for end-of-life and palliative care.</t>
+        </is>
+      </c>
+      <c r="E187" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/medcast-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t>Medical Billing Experts</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>Medical Billing Experts reports strong clinic performance gains with Medbill billing services (01/01/2024)
+Medical Billing Experts’ website highlights business growth indicators for its billing services, including an average 27% increase in clinic income, a 32% reduction in billing rejections, and 39% less receivables for clients. While this is a company self-published source rather than independent media coverage, it suggests operational growth and client performance improvements for the Brisbane-based firm.
+Medical Billing Experts’ Medbill Solutions profile cites revenue growth and faster payment processing (01/01/2024)
+The company’s about page states that clients experience an average 10% increase in revenue, a 39% reduction in current receivables, and payments processed 51% faster. This points to measurable business expansion and improved commercial outcomes associated with Medical Billing Experts’ services in Brisbane.</t>
+        </is>
+      </c>
+      <c r="D188" s="17" t="inlineStr"/>
+      <c r="E188" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/medical-billing-experts/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="16" t="inlineStr">
+        <is>
+          <t>Medilogic</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C189" s="17" t="inlineStr">
+        <is>
+          <t>MedSource Labs and Sydney’s Medilogic announce strategic partnership to launch Logiflow Exactus IV catheters in Australia (02/07/2024)
+MedSource Labs and Sydney-based Medilogic entered a strategic partnership to introduce the Logiflow Exactus and Exactus Shield blood-control safety IV catheters to the Australian market, indicating product expansion and a new international supply partnership for Medilogic.
+Medilogic expands its presence across Australia and New Zealand with strategically located offices and distribution centres (01/01/2024)
+Medilogic states that it has built a strong presence across Australia and New Zealand, supported by offices and distribution centres in key cities to improve service and supply efficiency for medical practices, reflecting operational expansion and growth.
+Medilogic highlights growth from its humble beginnings to a trusted medical industry name (01/01/2024)
+The company describes its journey from starting in 2011 to becoming a trusted name in the medical industry, emphasizing growth driven by quality, safety, and innovation.</t>
+        </is>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 2w] Announcing a partnership with Skin Cancer College Australasia to support surgical education programs and offering exclusive services to members.
+[30/04/2026 - 2w] Announcing a partnership with Skin Cancer College Australasia focusing on surgical education and specialized programs.</t>
+        </is>
+      </c>
+      <c r="E189" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/medilogic-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="16" t="inlineStr">
+        <is>
+          <t>Medpro Finance</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C190" s="17" t="inlineStr">
+        <is>
+          <t>Medpro Finance showcases growing demand for rapid, tailored medical finance (12/02/2025)
+In an article discussing ‘five moments when fast, flexible finance makes all the difference’, Medpro Finance illustrates scenarios such as practice expansion, equipment upgrades and managing uneven cash flow where its funding solutions have been used by healthcare professionals. The focus on real‑world use cases and quick turnaround indicates increasing utilisation of its products and supports the company’s narrative of growth as a specialist lender in the medical sector.
+Medpro Finance highlights role as fast, flexible alternative to banks for healthcare sector (10/10/2024)
+Positioning itself as a trusted expert in medical finance, Medpro Finance promotes its ability to provide rapid, customised finance to healthcare professionals for practice expansion, cash‑flow management and investment. The company’s messaging underscores growth in demand for non‑bank medical finance and reinforces its strategy of targeting this specialised market with tailored solutions, suggesting ongoing business development and market penetration within the healthcare finance segment.
+Medpro Finance broadens product suite to support growth of medical practices (20/06/2024)
+Through updates to its product pages, Medpro Finance promotes an expanded portfolio of lending options tailored to medical professionals, including business loans, working‑capital facilities, property finance and equipment rental. The company emphasises quick approvals, flexible structures and solutions designed to help doctors and healthcare businesses expand practices, manage cash flow and invest for the future, indicating continued product development and commercial growth in its specialist lending niche.
+Medpro Finance scales broker and adviser channel to deliver fast, flexible medical finance (15/03/2024)
+Medpro Finance outlines how it is expanding its partnerships with mortgage brokers, financial advisers and accountants across Australia to reach more healthcare professionals. By working alongside these intermediaries, the firm aims to broaden distribution of its specialist lending solutions, including practice, equipment and cash‑flow finance for doctors, dentists and allied health providers. The partnership‑led approach is presented as a key growth lever that enables Medpro Finance to increase deal flow while remaining focused on the healthcare niche.
+ProLending rebrands as Medpro Finance, sharpening focus as specialist medical lender (05/09/2023)
+ProLending has changed its name to Medpro Finance to reflect its evolution from a broker into a specialist non‑bank lender dedicated to medical professionals. The company states that it has refined its value proposition over many years working in the medical sector and is now targeting a niche in the highly specialised medical finance market. Under the new brand, Medpro Finance highlights three core business pillars — borrow, invest and refer — and positions itself as a provider of tailored, innovative and fast financial solutions as an alternative to traditional bank lending.</t>
+        </is>
+      </c>
+      <c r="D190" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt aimed at leveraging networks for opportunity.
+[27/04/2026 - 3w] LinkedIn being recognized as the top domain for professional queries indicates its growing influence in AI and job markets.
+[22/04/2026 - 4w] Announcement of new executive leadership which indicates a shift towards growth for LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E190" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne Institute of Plastic Surgery</t>
+        </is>
+      </c>
+      <c r="B191" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
+        <is>
+          <t>Melbourne Institute of Plastic Surgery expands consulting locations with Malvern clinic (15/03/2024)
+Melbourne Institute of Plastic Surgery, headquartered at 600 Victoria St, Richmond, VIC, has expanded its footprint by operating an additional clinic in Malvern. The organisation now offers consultations and procedures from both its Richmond and Malvern sites, supported by a multidisciplinary team of plastic and reconstructive surgeons, dermal therapists and clinical aesthetic nurses. The expanded locations increase patient access to aesthetic and reconstructive services across Melbourne’s inner suburbs.
+Melbourne Institute of Plastic Surgery broadens service line with dedicated skin and dermal therapy program (20/11/2023)
+The Melbourne Institute of Plastic Surgery has broadened its service offerings by developing a comprehensive skin and dermal therapy program, delivered by qualified dermal therapists and Clinical Aesthetic Nurses. The expanded skin services include non‑surgical rejuvenation and skincare treatments to complement the Institute’s established plastic and reconstructive surgery practice. This diversification represents service-line growth within the allied health and aesthetic care segment at the Richmond‑based institute.</t>
+        </is>
+      </c>
+      <c r="D191" s="17" t="inlineStr"/>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/melbourne-institute-of-plastic-surgery/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="16" t="inlineStr">
+        <is>
+          <t>Menai Orthodontics</t>
+        </is>
+      </c>
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
+        <is>
+          <t>Launch of ‘So Smile’ orthodontic treatment book by Dr Sarah Dan and the Menai Orthodontics team (23/10/2019)
+Dr Sarah Dan, specialist orthodontist at Menai Orthodontics in Menai, NSW, authored and launched the book “So Smile: A guide to straightening out the confusion, concern and catastrophes around orthodontic treatment.” The launch was promoted with events such as a Girls’ Night Out, positioning Dr Dan and the Menai Orthodontics practice as thought‑leaders and educational advocates in orthodontic care. This publication expands the clinic’s reach beyond its local patient base and enhances its professional profile within the allied health and orthodontic community.</t>
+        </is>
+      </c>
+      <c r="D192" s="17" t="inlineStr"/>
+      <c r="E192" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/menai-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>Meshed Group</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C193" s="17" t="inlineStr">
+        <is>
+          <t>Meshed Innovation Day 2025 Brings Together Education Leaders to Explore Future of Student Management Technology (14/10/2025)
+Meshed Group hosted its inaugural Meshed Innovation Day in Sydney, gathering leaders from universities, colleges, and vocational providers to discuss emerging trends in digital student management and compliance. The event highlighted Meshed’s expanding role as a technology partner to education providers and showcased new platform capabilities and integrations, signalling ongoing product investment and market engagement.
+Meshed Group – Student Management System Named ABA100 Winner for Software Innovation (01/08/2020)
+Meshed Group’s Student Management System was recognised as an ABA100 Winner for Software Innovation in The Australian Business Awards 2020. The award acknowledges Meshed’s development of specialised enterprise management and CRM platforms for higher education and VET providers, validating the company’s technology leadership and supporting its reputation-driven growth in the education technology market.</t>
+        </is>
+      </c>
+      <c r="D193" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 6d] Sales Director Simon Jones connected with a client at a forum, discussing partnerships in the international education sector.
+[14/05/2026 - 6d] Insightful discussions at an education conference highlight market needs and innovation opportunities, mentioning the Meshed Admissions Platform.
+[13/05/2026 - 1w] Sales Director Simon Jones represented the company at a forum, engaging with clients and partners, discussing future collaboration opportunities.
+[30/04/2026 - 2w] Astra Institute improved operations using the Meshed Student Management System, indicating effective use of tech solutions and partnership growth.</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meshed-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="16" t="inlineStr">
+        <is>
+          <t>Metromatics</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C194" s="17" t="inlineStr">
+        <is>
+          <t>Metromatics wins Innovation Excellence award for Augmented Hearing Loop System (01/11/2019)
+Metromatics, a Brisbane-based technology and electronics company, was recognised with the Award for Innovation Excellence at the Moreton Bay Business &amp; Innovation Awards for its Augmented Hearing Loop System, a text-to-speech product designed to support people with visual and hearing impairments.</t>
+        </is>
+      </c>
+      <c r="D194" s="17" t="inlineStr">
+        <is>
+          <t>[05/05/2026 - 2w] Dewesoft highlights its scalable solutions for structural health monitoring, indicating global project engagement and market expansion through partnerships with Metromatics in Australia and NZ.
+[04/05/2026 - 2w] Dewesoft launches the new SIRIUS® XR data acquisition system, indicating a new product introduction suited for various engineering applications.
+[29/04/2026 - 3w] WOLF announces its new brochure for embedded GPU and AI acceleration platforms, indicating new product offerings for edge computing in defense and rugged systems.
+[29/04/2026 - 3w] Dewesoft releases the latest version of its DewesoftX software, indicating continuous product improvement and support for engineers in Australia and NZ.</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metromatics-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="16" t="inlineStr">
+        <is>
+          <t>Mettler Toledo</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C195" s="17" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo opens its ANZ head office in Melbourne (01/02/2024)
+Mettler-Toledo officially opened its new ANZ head office in Melbourne, adding upgraded office space, meeting rooms, a cafe and kitchen, two laboratories, and a product inspection demonstration room to showcase its latest solutions.</t>
+        </is>
+      </c>
+      <c r="D195" s="17" t="inlineStr">
+        <is>
+          <t>[20/05/2026 - today] Commemoration of World Metrology Day emphasizing reliable measurements and compliance.
+[14/05/2026 - 6d] Announcement of METTLER TOLEDO Innovator Award winners recognizing innovative research solutions.
+[11/05/2026 - 1w] Launch of the X56 DXD+, a new dual-energy photon counting x-ray system.
+[09/05/2026 - 1w] Introduction of M50 R-Series AdvancedLine, an innovation in metal detection technology.
+[23/04/2026 - 3w] Re-introduction of Eagle product line featuring the advanced MAXIMIZER RMI for poultry manufacturing.</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mettlertoledo/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>Mirus Australia</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
+        <is>
+          <t>Mirus AI and the Careverse: Advancing aged care services through a common data model (12/05/2026)
+Mirus Australia has launched the Careverse, described as the first sector‑wide aggregated clinical dataset for Australian aged care. Developed with leading research institutions and technology partners, the Careverse introduces a unified data model that consolidates fragmented provider data and enables AI‑driven analytics. The platform is positioned to improve care outcomes, operational efficiency, and compliance with ongoing aged care reforms, signalling a significant product and partnership‑led expansion of Mirus Australia’s capabilities.
+Care minutes bounce back as concerning reclassification trend emerges: Mirus reports (18/03/2026)
+Mirus Australia’s latest Mirus Industry Analysis (MIA) report, highlighted by Hello Leaders, shows care minutes have rebounded following a seasonal dip, underscoring the company’s growing role as a key data and analytics provider in the aged care sector. The report’s detailed benchmarking on care minutes and reclassification trends demonstrates strong uptake of Mirus’ analytics and reporting services by providers seeking to manage AN-ACC funding, compliance, and workforce planning, reflecting continued growth in Mirus’ influence and service utilisation across the industry.
+Mirus Industry Analysis (MIA) series strengthens Mirus Australia’s position as a key aged care performance benchmark (15/02/2026)
+Through its recurring Mirus Industry Analysis (MIA) YouTube series, including the February 2026 edition, Mirus Australia continues to publish detailed benchmarks on care minutes, AN‑ACC trends, occupancy, and other performance indicators for residential aged care. The regular production and uptake of these analyses by providers and sector media indicate growing engagement with Mirus’ data services and reinforce the firm’s role as a go‑to source for market intelligence in Australian aged care.
+90% of aged care providers prepared for significant transformation to increase financial sustainability: Mirus Australia (22/11/2025)
+Research and analysis released by Mirus Australia and reported by The Weekly Source show that around 90% of aged care providers are ready to undertake major transformation to improve financial sustainability. The findings position Mirus as a strategic advisor and transformation partner to providers dealing with funding, occupancy, and workforce challenges. The prominence of the research and commentary on sector‑wide change indicates Mirus’ expanding consulting and advisory footprint within Australia’s aged care market.
+MirusPlus platform consolidates aged care software and data for Australian providers (10/09/2025)
+Mirus Australia has expanded its technology offering with MirusPlus, a purpose‑built platform designed to bring together the core operational systems and data used by Australian aged care providers. By integrating funding, workforce, and operational data in a single environment and promoting streamlined workflows, MirusPlus represents a significant product expansion for Mirus Australia and supports its growth from consulting and analytics into an end‑to‑end technology platform provider.</t>
+        </is>
+      </c>
+      <c r="D196" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 6d] Discussion of the Independent Review's findings and the budget response indicating potential growth opportunities.
+[11/05/2026 - 1w] Celebration of International Nurses Day, highlighting the skilled nursing team and their impact.
+[06/05/2026 - 2w] Participation in ITAC 2026, showcasing a new product and engagement with industry leaders.
+[04/05/2026 - 2w] Promotes attendance at ITAC 2026 while showcasing two new products aimed at improving care management.
+[01/05/2026 - 2w] Announcement of a planned webinar about regulatory changes and operational adjustments within the sector.</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mirus-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="16" t="inlineStr">
+        <is>
+          <t>Modelve</t>
+        </is>
+      </c>
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C197" s="17" t="inlineStr"/>
+      <c r="D197" s="17" t="inlineStr">
+        <is>
+          <t>[15/05/2026 - 5d] Post thanks individuals for organizing a collaborative event and emphasizes the innovation in the public sector through new budgeting methods.
+[10/05/2026 - 1w] Announcement of a keynote presentation at a major conference by a co-founder of Modelve, highlighting industry leadership.</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/modelve/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="16" t="inlineStr">
+        <is>
+          <t>Moneycatcha</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
+        <is>
+          <t>Moneycatcha strides forward with high profile board appointments and $1.5 million funds injection (01/05/2024)
+Perth-based fintech Moneycatcha announced two high-profile board appointments and secured a $1.5 million capital raise to accelerate its growth plans and capitalise on renewed momentum in Australia’s Consumer Data Right market.
+Moneycatcha bolsters growth with new appointments (01/05/2024)
+Moneycatcha added Tim Alexander and Lawrie Tremaine as non-executive directors, strengthening its leadership team alongside a $1.5 million funding round that will support further expansion.
+Fintech accelerates growth with $1.5m funding and key hires (01/05/2024)
+The Perth-based open banking fintech Moneycatcha announced a $1.5 million capital raise and two board appointments, signalling expansion and a stronger push to scale its Stryd platform.
+Stryd welcomes new head of product (01/03/2024)
+Moneycatcha’s Stryd brand appointed Cheok Lee as head of product to enhance broker and lender offerings, indicating continued product expansion and investment in growth.</t>
+        </is>
+      </c>
+      <c r="D198" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Announcement of a partnership with Serena Williams and Reckitt, promoting networking and mentorship.
+[24/04/2026 - 3w] Congratulating a new hire, which indicates team growth.
+[22/04/2026 - 4w] Announcing new leadership appointments at LinkedIn, indicating company growth and change.</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="16" t="inlineStr">
+        <is>
+          <t>Mortgage Ezy</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>Mortgage Ezy Group becomes a fully securitised lender after achieving RMBS status (10/04/2025)
+Mortgage Ezy has transitioned into a fully securitised lender after achieving residential mortgage‑backed securities (RMBS) status. Following the launch of its Source Funding platform in 2022 and reaching the required three‑year track record, the group can now obtain a credit rating and tap capital markets directly. It will fund loans via its own Pearl series bond issues, relying on banks only for warehouse facilities. This shift gives Mortgage Ezy greater control over funding costs and lending solutions, supporting future loan book growth and product innovation.
+Mortgage Ezy takes the crown as Mortgage Manager of the Year 2025 (17/02/2025)
+Mortgage Ezy announced it has been awarded “Mortgage Manager of the Year 2025,” recognising the company’s growth, innovation, and service to brokers and borrowers. The award highlights the success of its technology‑driven lending model and specialty products, reinforcing its reputation as a leading non‑bank lender and supporting its strategy to expand market share.
+Mortgage Ezy wins Best Non‑Bank Lender at Australian Lending Awards (second consecutive year) (10/03/2024)
+Mortgage Ezy reported a “flying start” to the year after being named Best Non‑Bank Lender at the Australian Lending Awards for the second year running. The back‑to‑back win reflects strong growth in broker support, product range and service quality, bolstering the lender’s brand and positioning it for further expansion in the non‑bank and fintech‑enabled mortgage segment.
+Mortgage Ezy aims to double business volumes and evolve into a ‘Super Non‑Bank Lender’ (15/08/2023)
+Profile coverage of Mortgage Ezy outlines an ambitious growth strategy to double current business volumes and evolve into a ‘Super Non‑Bank Lender’. The company, which processes over $2 billion in loans annually and focuses on technology‑enabled, specialty residential lending, plans to leverage its niche products and non‑bank funding capabilities to capture more of the Australian mortgage market.
+Mortgage Ezy highlighted among tech‑driven lenders shaking up the finance industry (22/06/2022)
+In a sector overview of technology leaders in finance, Mortgage Ezy is cited as a non‑bank lender leveraging technology and fintech‑style innovation to disrupt traditional mortgage lending. The article notes strong growth in fintech lenders and positions Mortgage Ezy within this trend, supporting its reputation as a technology‑driven, growth‑oriented mortgage provider.</t>
+        </is>
+      </c>
+      <c r="D199" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 2d] Mortgage Ezy is recognized as a finalist for the MFAA Mortgage Manager of the Year Award for the fifth consecutive year.</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mortgage-ezy-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>MotorPlatform</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C200" s="17" t="inlineStr">
+        <is>
+          <t>MotorPlatform launches as a fast-growing automotive software platform for dealerships in Australia and New Zealand (01/01/2024)
+MotorPlatform positions itself as a growing auto-tech company serving dealerships with end-to-end software, streamlined workflows, actionable reporting, and valuation tools. The company highlights rapid growth, expanded capabilities, and a team based in Australia and New Zealand focused on improving wholesale operations.
+MotorPlatform promotes its premier B2B marketplace and efficiency-focused dealership solution (01/01/2024)
+MotorPlatform presents its acquisition, valuation, and disposal ecosystem as a growing business solution for dealerships, emphasizing improved efficiency, pricing accuracy, and streamlined wholesale workflows. This indicates product and market expansion within the automotive software space.
+MotorPlatform expands dealership performance tools for sales teams (01/01/2024)
+MotorPlatform’s sales-team solution highlights expanded wholesale growth opportunities and improved dealership group performance through tablet-based tools and workflow support. The page suggests continued product development and growth-oriented capability expansion.
+MotorPlatform strengthens wholesale operations with team-focused workflow tools (01/01/2024)
+MotorPlatform’s wholesale and teams offering emphasizes improved trade-in and wholesale performance, reflecting business growth through enhanced operational tools for dealership groups. The product messaging indicates ongoing expansion of the company’s platform capabilities.</t>
+        </is>
+      </c>
+      <c r="D200" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 1w] Collaboration with Serena Williams and Reckitt, promoting networking which could lead to growth opportunities.
+[27/04/2026 - 3w] LinkedIn being recognized as the top domain for professional queries indicates market expansion and visibility.
+[24/04/2026 - 3w] Congratulations to Fernando Mendoza on a new role, indicating a new hire.
+[22/04/2026 - 4w] Announcement of new leadership roles at LinkedIn, indicates team growth.</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>Mount Waverley Orthodontics</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>Mount Waverley Orthodontics rebrands and relocates to Glen Waverley (01/01/2012)
+The practice notes that it was renamed and relocated more than 14 years ago, indicating a past expansion/relocation event for the Mount Waverley Orthodontics business in Glen Waverley.</t>
+        </is>
+      </c>
+      <c r="D201" s="17" t="inlineStr"/>
+      <c r="E201" s="16" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>i4T Global</t>
+        </is>
+      </c>
+      <c r="B202" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>i4T Global Shines in 2025: Awards That Recognise Our People and Technology (15/02/2025)
+i4T Global, the Melbourne‑headquartered PropTech and Field Service Management platform, reported a milestone year in 2025 with multiple industry recognitions. The company was named both a finalist and a winner across several prestigious awards, including Real Estate Business Innovator of the Year, the Australian Technologies Competition, the Australian Achiever Awards, and the Australian Small Business Champion Awards. These honours highlight the company’s accelerating growth and its role in transforming the PropTech and FSM sectors through its end‑to‑end digital ecosystem for authorised service agents, field service suppliers, and property occupants.
+i4T Global Targets Rapid Expansion in PropTech and Field Service Management Under New Leadership (10/09/2024)
+i4T Global, formerly known as i4Tradies and based in Melbourne, announced a new leadership structure aimed at accelerating its growth in the PropTech and Field Service Management markets and strengthening its global footprint. The cloud‑based platform, which connects authorised service agents, field service suppliers, and property occupants, outlined plans to scale its product verticals i4T Maintenance, i4T Business, and i4Tradies. The leadership refresh is positioned as a key step to drive international expansion and capitalise on the rapidly growing FSM industry.
+i4T Global Opens Investor Relations Channel to Support Next Phase of Growth in FSM (05/06/2024)
+Melbourne‑headquartered i4T Global launched a dedicated investor relations initiative, inviting strategic investors to participate in the next phase of its expansion in the rapidly growing Field Service Management market. The company emphasised that its connected PropTech and FSM ecosystem is well‑positioned to benefit from global digitisation trends in property management and trades services. The move signals growth ambitions, including scaling its technology platform, increasing market penetration, and strengthening its international presence.</t>
+        </is>
+      </c>
+      <c r="D202" s="17" t="inlineStr"/>
+      <c r="E202" s="16" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="16" t="inlineStr">
+        <is>
+          <t>iWEIGH Solutions</t>
+        </is>
+      </c>
+      <c r="B203" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr"/>
+      <c r="D203" s="17" t="inlineStr"/>
+      <c r="E203" s="16" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>meetpat</t>
+        </is>
+      </c>
+      <c r="B204" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C204" s="17" t="inlineStr">
+        <is>
+          <t>meetpat secures Western Sydney International Airport contract for drinking water stations (03/02/2025)
+meetpat announced that it is supplying its hydration stations for the new Western Sydney International (Nancy-Bird Walton) Airport, providing free, safe drinking water across the terminal. The project positions meetpat as a key environmental services partner in a major public infrastructure development and reflects growing demand for its water quality and sustainability-focused solutions.
+meetpat expands role as contract supplier to Transport for NSW train network (14/11/2024)
+In an update on its public infrastructure work, meetpat highlighted its status as a contract supplier for Transport for NSW across the state’s train network, including recent deployments of its water systems. The ongoing contract demonstrates sustained growth in the company’s footprint in New South Wales transport infrastructure and reinforces its position in environmental and sustainability-focused services for public assets.</t>
+        </is>
+      </c>
+      <c r="D204" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 1d] The company is celebrating the launch of a new product, the advanced auto flush and filtration system, by promoting a giveaway of a water station to local schools. This reflects engagement with the community and highlights a product launch.</t>
+        </is>
+      </c>
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meet-pat/posts/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GOWT_mid_low.xlsx
+++ b/GOWT_mid_low.xlsx
@@ -41354,7 +41354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -47274,6 +47274,2177 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>NQRY</t>
+        </is>
+      </c>
+      <c r="B205" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C205" s="17" t="inlineStr">
+        <is>
+          <t>Broadening the base to find new markets (05/07/2022)
+This article notes that Fay chairs the board of Adelaide-based tech company NQRY Pty Ltd and mentions its involvement in STEMfooty, a program aimed at engaging middle-school-aged children in STEM principles, indicating the company’s ongoing local activity and community-linked growth efforts.</t>
+        </is>
+      </c>
+      <c r="D205" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a collaboration with Serena Williams and Reckitt to leverage networks for success.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicating internal growth.</t>
+        </is>
+      </c>
+      <c r="E205" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>National Property Group</t>
+        </is>
+      </c>
+      <c r="B206" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C206" s="17" t="inlineStr">
+        <is>
+          <t>National Property Group launches as a 60-year-old startup with 12 million property records and new API access (01/01/2021)
+National Property Group was launched in 2020 and reported substantial scale across its property data business, including 12 million property records, 107 million property images, and 250 million sales and lease listing records. The company also highlighted an open and affordable API for proptechs, signaling product expansion and platform growth.
+National Property Group positions itself as an all-in-one property data platform for agents, investors and developers (01/01/2021)
+In the interview transcript, National Property Group described broadening its offering beyond a property platform into a data lake and API-driven product suite for websites and decision support. This indicates product diversification and expansion of its data analytics capabilities.</t>
+        </is>
+      </c>
+      <c r="D206" s="17" t="inlineStr"/>
+      <c r="E206" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/national-property-group-aus/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>Neurocom</t>
+        </is>
+      </c>
+      <c r="B207" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C207" s="17" t="inlineStr">
+        <is>
+          <t>Australian organisations must act on security – or risk AI ambitions falling flat (20/05/2026)
+This article discusses the importance of building a strong cybersecurity foundation for AI and automation adoption. It mentions Spirit as a partner, but does not provide evidence of growth specifically for Neurocom.
+VITG buys Security Centric to boost cyber security (20/05/2026)
+Virtual IT Group acquired Security Centric to expand its security practice across Australia and New Zealand. The story is about VITG, not Neurocom.
+Australian businesses lack confidence in cyber security: RSM research (20/05/2026)
+RSM research reports that Australian businesses are less equipped to respond to cyber attacks than global peers. This is industry commentary and does not indicate growth for Neurocom.
+CPA Australia: SMBs urged to review and update cyber security policies as AI use grows (20/05/2026)
+CPA Australia advises SMBs to strengthen cybersecurity practices as AI adoption rises. The article is about general market guidance, not Neurocom-specific growth news.
+Australian companies behind the global curve on cyber security (20/05/2026)
+This report highlights challenges facing Australian companies in cyber security, including under-reporting and budget constraints. It does not mention Neurocom or any growth event for the company.
+Cybersecurity burnout widespread among Australian businesses (20/05/2026)
+This article covers cybersecurity burnout in Australian organisations based on recent research. It is not specific to Neurocom and does not show company growth.</t>
+        </is>
+      </c>
+      <c r="D207" s="17" t="inlineStr"/>
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neurocom-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>North Sydney Dermatology</t>
+        </is>
+      </c>
+      <c r="B208" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C208" s="17" t="inlineStr"/>
+      <c r="D208" s="17" t="inlineStr"/>
+      <c r="E208" s="16" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="16" t="inlineStr">
+        <is>
+          <t>Nova Biomedical (Gold Coast, Australia)</t>
+        </is>
+      </c>
+      <c r="B209" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C209" s="17" t="inlineStr">
+        <is>
+          <t>Nova Biomedical awarded for pioneering software (04/11/2022)
+Gold Coast–based Nova Biomedical, which provides specialist testing and maintenance services and IT-focused support to the health industry, received a business award recognising its pioneering software development. The award highlights the company’s innovation in developing software that improves efficiency and reliability of medical equipment servicing, reinforcing its reputation as a leading local health IT and support provider.</t>
+        </is>
+      </c>
+      <c r="D209" s="17" t="inlineStr"/>
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nova-biomedical-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>NovoPsych</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C210" s="17" t="inlineStr">
+        <is>
+          <t>NovoPsych launches NovoNote AI Scribe to cut admin time for psychologists (15/08/2023)
+NovoPsych introduced NovoNote, an AI-powered clinical notes tool designed to automatically draft psychotherapy notes and session summaries. The product builds on NovoPsych’s existing psychometric assessment platform and is reported to be in use by thousands of Australian psychologists, signalling a significant expansion of the company’s product suite and user base in the mental health technology market.
+NovoPsych partners with Provisional Psychologist Hub to provide extended complimentary licences (18/05/2022)
+NovoPsych entered into a collaboration with the Provisional Psychologist Hub to offer complimentary 18‑month NovoPsych Pro licences to its members, an offer that was later extended due to demand. The partnership increases platform adoption among early-career psychologists and supports further penetration of NovoPsych’s outcome monitoring software into the Australian mental health sector.
+NovoPsych passes 11,000-user milestone and expands internationally (10/03/2022)
+NovoPsych disclosed that its outcome monitoring and psychometric assessment platform is now used by more than 11,000 users. The company reported operations not only across Australia but also in the UK, Europe, New Zealand and more broadly across the Asia-Pacific region, highlighting sustained user growth and ongoing international expansion from its Melbourne base.
+Domain migration reflects NovoPsych’s period of significant internal growth (05/07/2021)
+Digital agency Spicy Web reported that NovoPsych engaged them during a period of significant internal growth to manage a critical migration from novopsych.com.au to novopsych.com. The shift to a global .com domain and the focus on SEO were positioned as part of NovoPsych’s strategy to support its expanding customer base and international reach in digital mental health services.</t>
+        </is>
+      </c>
+      <c r="D210" s="17" t="inlineStr"/>
+      <c r="E210" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/novopsych/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="16" t="inlineStr">
+        <is>
+          <t>Nueva Solutions</t>
+        </is>
+      </c>
+      <c r="B211" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C211" s="17" t="inlineStr">
+        <is>
+          <t>Nueva Joins Phoenix as a Major Partner (18/11/2024)
+Nueva Solutions announced a major partnership with South East Melbourne Phoenix, signaling brand growth and increased market presence in Australia.</t>
+        </is>
+      </c>
+      <c r="D211" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a collaboration with Serena Williams and Reckitt to leverage networks for business growth.
+[27/04/2026 - 3w] Highlights LinkedIn's status as the #1 domain for professional queries, indicating market leadership and relevance.
+[22/04/2026 - 4w] Announces new leadership appointments at LinkedIn, indicating growth and strategic direction.</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>OHSA Occupational Health Services Australia</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C212" s="17" t="inlineStr">
+        <is>
+          <t>OHSA recognised as one of Australia’s most awarded WHS consulting and training companies (01/06/2023)
+OHSA Occupational Health Services Australia highlighted its growth trajectory and reputation in an updated company profile, noting that it has become “one of the most successful and awarded WHS consulting and training companies in Australia.” The business credits its expansion to a strong client base across high‑risk industries and the development of a wide portfolio of accredited workplace health and safety courses. This positioning as a leading and highly awarded provider indicates sustained brand strength and recognition-based growth within the professional training and coaching sector.
+OHSA expands geographic reach with specialised safety training facilities in Brisbane and Gold Coast and on‑site delivery across Queensland and Western Australia (15/03/2022)
+Building on more than 25 years in operation, OHSA Occupational Health Services Australia operates dedicated safety training centres in Brisbane and on the Gold Coast, while also delivering on‑site training throughout Queensland and Western Australia. This footprint, outlined in the company’s contact and capability information, reflects geographic expansion beyond a single local market and the development of a broader service network, enabling OHSA to service large corporate and resources clients across multiple regions.
+OHSA leverages mining sector demand as industry forecasts need for 21,000 new workers by 2024 (10/08/2021)
+In response to industry projections that Australia’s mining sector will require about 21,000 new onsite operational employees by 2024, OHSA Occupational Health Services Australia promoted its suite of mining inductions and high‑risk work health and safety training. While the article focuses on industry-wide demand, OHSA’s positioning and call to action for enrolments indicate that the company is targeting growth opportunities tied to this labour expansion, aligning its course offerings with projected skills shortages in the resources sector.
+OHSA consolidates status as long‑standing WHS specialist with 25+ years of continuous operation (01/11/2020)
+OHSA Occupational Health Services Australia emphasised that it has been operating for over 25 years, providing safety solutions and WHS training to clients across “almost every industry imaginable worldwide.” The longevity and breadth of service delivery underscore sustained business viability and gradual expansion from local operations into a nationally and internationally active safety training and consulting provider, signalling long-term, organic growth in its professional training and coaching activities.</t>
+        </is>
+      </c>
+      <c r="D212" s="17" t="inlineStr"/>
+      <c r="E212" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ohsa-occupational-health-services-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="16" t="inlineStr">
+        <is>
+          <t>OWNA</t>
+        </is>
+      </c>
+      <c r="B213" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C213" s="17" t="inlineStr">
+        <is>
+          <t>Infocare joins OWNA Group following Juice Technologies acquisition (20/10/2025)
+Following OWNA’s acquisition of Juice Technologies, Infocare Solutions announced that it has officially joined the OWNA family. The move brings Infocare, Kidsoft, SmartCentral and Kangarootime ANZ together under OWNA, creating a comprehensive network of childcare management systems across Australasia and enabling services to operate more efficiently and stay ahead of regulatory requirements.
+BDO advises on OWNA’s acquisition of JUICE Technologies (16/10/2025)
+Professional services firm BDO reported that it advised OWNA on its acquisition of JUICE Technologies, describing OWNA as a leading Australian childcare centre management system (CCMS) software provider. The deal underscores OWNA’s financial and strategic capacity to execute sizeable M&amp;A transactions and further consolidates its leadership position in the childcare software market.
+OWNA acquires Juice Technologies, parent of Kidsoft, Kangarootime Australia, Smart Central &amp; Infocare (15/10/2025)
+OWNA announced the acquisition of Juice Technologies, the parent company of Kidsoft, Kangarootime Australia, Smart Central and Infocare (NZ). This major transaction significantly scales OWNA’s footprint across Australia and New Zealand, broadens its product portfolio, and consolidates multiple leading childcare management platforms under the OWNA group, reinforcing its position as a leading all‑in‑one childcare software provider.
+Aussie tech company OWNA buys Saasu (21/02/2024)
+OWNA, a Sydney-based childcare management software provider, acquired Saasu, an Australian online accounting software business, for an undisclosed sum. The deal expands OWNA’s product capabilities beyond early childhood management into cloud accounting, strengthening its technology stack and enabling deeper integration across finance and operations for its childcare customer base.</t>
+        </is>
+      </c>
+      <c r="D213" s="17" t="inlineStr">
+        <is>
+          <t>[10/05/2026 - 1w] Introduction of 'The Wellness Check', a new tool for staff wellbeing, highlighting innovation in product offerings.</t>
+        </is>
+      </c>
+      <c r="E213" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/owna/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="16" t="inlineStr">
+        <is>
+          <t>OZEDI</t>
+        </is>
+      </c>
+      <c r="B214" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C214" s="17" t="inlineStr">
+        <is>
+          <t>OZEDI reports serving more than 50,000 businesses and working with major government departments and software providers (01/01/2024)
+OZEDI’s company profile states it now supports over 50,000 businesses and has expanded to work with some of the Federal Government’s largest departments and more than 100 software providers, reflecting significant business growth and customer expansion.
+OZEDI partners with Zepto to build one of the first integrations between the New Payments Platform and superannuation workflows (01/11/2023)
+OZEDI highlighted a strategic partnership with Zepto to develop an early integration between real-time payment rails and superannuation processes, signaling product expansion and innovation in its business messaging platform.
+OZEDI strengthens its market position in SuperStream as an early gateway provider (01/03/2019)
+In a Treasury submission, OZEDI stated it was the first company to demonstrate a SuperStream gateway in 2012 and had captured approximately 23% of SuperStream transactions, indicating strong market success and scale in a regulated messaging segment.</t>
+        </is>
+      </c>
+      <c r="D214" s="17" t="inlineStr"/>
+      <c r="E214" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ozedi/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="16" t="inlineStr">
+        <is>
+          <t>Oberix Group</t>
+        </is>
+      </c>
+      <c r="B215" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C215" s="17" t="inlineStr">
+        <is>
+          <t>Oberix Group posts approximately $77.5 million in revenue as it scales building automation operations (10/02/2025)
+According to IBISWorld’s company profile, Oberix Group Pty Ltd, headquartered in Melbourne and trading as Oberix, generated about $77.5 million in revenue in 2025. The report describes Oberix as deriving most of its income from generator, motor and other electrical equipment manufacturing, alongside security system installation and monitoring, with building automation services delivered through divisions including Alerton Australia, Optergy, Leading Edge Automation, Abakus Analytics, Operational Intelligence and Conservia. The revenue figure and diversified business lines indicate sustained financial scale and ongoing growth in its automation and energy‑management activities.
+Oberix Group expands global footprint with new New Zealand office and delivery of three smart city projects (15/03/2024)
+Business View Oceania profiled Oberix Group’s growth as a global provider of building automation and smart infrastructure solutions. The article highlighted that since its founding in Melbourne in 1992, Oberix has expanded to a network of more than 300 specialists across six businesses (Operational Intelligence, Conservia, Abakus Analytics, Alerton Australia, Leading Edge Automation and Optergy) and now operates offices in Australia, Singapore, Malaysia, the UK, the US and, most recently, New Zealand. The feature also noted that Oberix has enabled three smart cities, over 70 high‑rated NABERS facilities and more than 3,700 smart solutions worldwide, underscoring strong project‑driven growth and international expansion from its Melbourne headquarters.
+Qantec Automation, part of Oberix Group, forms strategic IoT partnership with Milesight to drive smart infrastructure growth (08/11/2023)
+Milesight announced a strategic partnership with Qantec Automation, a member of the Melbourne‑headquartered Oberix Group. Qantec is described as a visionary smart‑infrastructure partner specialising in cutting‑edge Internet of Things solutions, operating in Australia, the United States, Singapore, Malaysia and the United Kingdom. The collaboration aims to expand both companies’ IoT presence and meet growing demand for smart infrastructure and smart agriculture solutions, signalling partnership‑led growth and a broader international market reach for Oberix Group’s IoT capabilities.
+Oberix Group capabilities overview highlights integrated smart‑building and energy‑efficiency growth platform (15/01/2021)
+Oberix Group’s published capabilities overview details its evolution into an international provider of smart‑building, energy‑efficiency and digital‑workplace solutions headquartered in Burwood, Melbourne. The document outlines how the group’s businesses—Operational Intelligence, Conservia, Abakus Analytics, Alerton Australia, Leading Edge Automation and Optergy—collectively deliver end‑to‑end services across thousands of sites, leveraging building analytics, IoT and automation technologies. While not a news article in the traditional sense, the overview evidences sustained growth in service breadth, technology offerings and an expanding client base across commercial buildings, precincts and cities.</t>
+        </is>
+      </c>
+      <c r="D215" s="17" t="inlineStr"/>
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oberix-group-/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="16" t="inlineStr">
+        <is>
+          <t>Obesity Surgery WA</t>
+        </is>
+      </c>
+      <c r="B216" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C216" s="17" t="inlineStr"/>
+      <c r="D216" s="17" t="inlineStr"/>
+      <c r="E216" s="16" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="16" t="inlineStr">
+        <is>
+          <t>Octossure</t>
+        </is>
+      </c>
+      <c r="B217" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C217" s="17" t="inlineStr">
+        <is>
+          <t>Directors &amp; Boards | Automate RTO Compliance Management &amp; Audits (01/01/2026)
+This page describes Octossure as a platform designed to work seamlessly alongside existing LMS and SMS systems, highlighting product capability and business positioning in compliance automation. It suggests ongoing product development and market expansion across training and compliance workflows.</t>
+        </is>
+      </c>
+      <c r="D217" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 2d] Octossure announced as a Bronze Sponsor for the ITECA Higher Education Conference, indicating involvement and recognition in the education sector.</t>
+        </is>
+      </c>
+      <c r="E217" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shiro-corp/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
+          <t>Olinqua</t>
+        </is>
+      </c>
+      <c r="B218" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C218" s="17" t="inlineStr">
+        <is>
+          <t>Olinqua and FiveP announce strategic partnership at HIMSS23 (20/04/2023)
+Olinqua, a Melbourne-based provider of hospital communication and workflow solutions, formed a strategic partnership with FiveP, developers of the role-based messaging solution Baret, announced at the HIMSS23 global health IT conference in Chicago. Both firms, with growing hospital client bases across APAC, will invest in integration pathways between Olinqua’s Ignite interoperability platform and FiveP’s Baret for Microsoft Teams. The collaboration aims to deliver next‑generation role-based messaging and alarm management capabilities to hospitals, strengthening Olinqua’s product ecosystem and market reach.
+Olinqua’s Ignite platform reaches approximately 90 hospital deployments (20/04/2023)
+In company information released alongside its HIMSS23 partnership announcement, Olinqua reported that its Ignite interoperability platform is operating in approximately 90 hospitals. The platform connects clinical, operational, and facility systems to enable seamless communication and workflow automation. This deployment figure highlights Olinqua’s substantial customer growth and adoption across hospitals in Australia and the broader APAC region.
+New Footscray Hospital to deploy Hills’ nurse call platform integrated with Olinqua technology (14/09/2022)
+The new Footscray Hospital in Melbourne’s west selected Hills Health Solutions’ nurse call platform, which is offered in conjunction with Olinqua’s critical messaging technology, for more than 500 beds. While Hills is the prime contractor, the project extends Olinqua’s technology footprint into a large, next-generation public hospital, reinforcing its role in critical communications and workflow automation within major healthcare infrastructure developments.
+Olinqua and Hills Health Solutions announce strategic digital health partnership (21/12/2021)
+Olinqua entered a strategic digital health partnership with Hills Health Solutions, Australia’s largest supplier of nurse call and patient management systems, to deliver a converged IP-based platform for hospitals and aged care facilities. The joint offering connects disparate clinical and operational systems and workflows, combining Hills’ nurse call capabilities with Olinqua’s automation, integration, and critical messaging technology. This agreement expands Olinqua’s distribution and embeds its platform into large-scale healthcare infrastructure projects, supporting commercial and geographic growth.
+Hills teams up with Olinqua for integrated nurse call and critical messaging (21/12/2021)
+Hills Health Solutions and Olinqua launched an integrated, converged IP-based solution that unifies Hills’ nurse call with Olinqua’s critical messaging platform for hospitals and aged care providers. The solution, designed to improve response to medical emergencies and streamline communication, has already been deployed at Melbourne’s Austin Hospital and Canberra Hospital. These deployments demonstrate Olinqua’s successful expansion into major hospital sites and validate market demand for its interoperability and workflow technology.</t>
+        </is>
+      </c>
+      <c r="D218" s="17" t="inlineStr"/>
+      <c r="E218" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/olinqua/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="16" t="inlineStr">
+        <is>
+          <t>OneLaw (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B219" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C219" s="17" t="inlineStr">
+        <is>
+          <t>OneLaw and VXT launch integrated phone and practice management solution for NZ law firms (19/06/2025)
+OneLaw, a New Zealand-based legal practice management platform, announced a new integration with VXT, a cloud-based VoIP phone system built for law firms. The partnership connects OneLaw’s trust accounting, compliance, and productivity tools with VXT’s communication platform to streamline call handling, matter management, and time recording for New Zealand law firms. This integration broadens OneLaw’s product ecosystem and enhances its value proposition to existing and prospective firms, supporting continued growth in its core market.
+New shareholder and $1m+ investment boost legal software firm OneLaw (04/03/2020)
+Legal practice management provider OneLaw secured a strategic investment of more than NZ$1 million from Stratos Technology Partners, which acquired a 14% stake in the company. As part of the deal, Stratos CEO David Carter became OneLaw’s CEO and Tony Rogers joined as CTO, with product owner Bex Craig also added to the team. The funding is earmarked to accelerate product development, expand headcount, and grow OneLaw’s footprint in the New Zealand legal market, with plans for multiple strategic initiatives to position the company as a leading innovator in legal tech.</t>
+        </is>
+      </c>
+      <c r="D219" s="17" t="inlineStr"/>
+      <c r="E219" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/data-doctors-nz-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="16" t="inlineStr">
+        <is>
+          <t>OneWiFi (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B220" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C220" s="17" t="inlineStr">
+        <is>
+          <t>Superloop to deliver Bradfield digital network using OneWiFi smart pole technology (18/04/2024)
+Superloop was appointed as the sole statutory digital infrastructure provider for the new city of Bradfield in Western Sydney, responsible for the FTTP network and pit‑and‑pipe assets. As part of this role, Superloop will manage deployment of multi‑function smart poles supported by technology partner OneWiFi. The project highlights OneWiFi’s growth in 5G neutral host and smart city infrastructure, positioning the Sydney-based company at the core of a large greenfield digital city build.
+Superloop selects OneWiFi to support smart poles, public Wi‑Fi and mobile coverage in Bradfield City Centre (17/04/2024)
+Superloop was appointed sole statutory infrastructure provider for Bradfield City Centre in the Western Sydney Aerotropolis and chose OneWiFi as the smart city services partner. OneWiFi will support multi‑function ‘smart poles’ delivering public Wi‑Fi, CCTV and mobile coverage. This engagement expands OneWiFi’s portfolio in next‑generation urban infrastructure and underscores its growth as a leading smart city technology partner.
+NSW Government digital deal taps Superloop and OneWiFi for Bradfield innovation ecosystem (16/04/2024)
+The NSW Government announced a digital infrastructure partnership with Superloop and partner OneWiFi to ensure Bradfield will be a fully digital city from day one. OneWiFi will help deliver critical infrastructure services to support high‑tech industries, institutions and residents, reinforcing the company’s position as a key smart city solutions provider and expanding its role in large‑scale, government-backed urban developments.
+Digital infrastructure deal secures Bradfield’s connectivity with Superloop and OneWiFi (15/04/2024)
+A commercial infrastructure deal between Superloop, OneWiFi and the NSW Government secured the digital backbone for Bradfield, a new city in South Western Sydney. Under the arrangement, Superloop assumes operational ownership of 18km of pit‑and‑pipe infrastructure, while OneWiFi participates as a smart city and connectivity partner. The deal represents a major win and long-term growth opportunity for OneWiFi in delivering integrated telecommunications and smart city services for Australia’s first new city in more than a century.
+OneWiFi positions as Australia’s leading 5G neutral host and smart city provider with over 1,200 live locations (10/02/2024)
+In an updated corporate profile, OneWiFi &amp; Infrastructure described itself as Australia’s leading 5G Neutral Host, Small Cells, IBC/DAS and Smart City solutions provider. Established in 2012, the company reported delivering solutions across more than 1,200 locations nationwide, including retail precincts, shopping centres, hospitality venues, commercial buildings and regional communities. The scale of active deployments indicates sustained growth in customer base and infrastructure footprint. The profile also references ongoing strategic relationships with mobile operators, councils and property owners, and mentions recent advocacy and industry activity such as questioning proposed mobile coverage maps and urging that smart city funding be tied to council savings.
+OneWiFi grows neutral host footprint with mobile active solutions for First Nations communities (15/11/2023)
+In documentation submitted for the Woollahra Council Wi‑Fi proposal, OneWiFi highlighted its ongoing delivery of Mobile Active Neutral Host solutions for First Nations communities under the Australian Government’s Mobile Black Spot Program Round 7 (RCP3/MBSP R7). Participation in federally funded programs and regional connectivity initiatives demonstrates geographic expansion and supports revenue and capability growth in remote and regional telecommunications infrastructure.
+OneWiFi urges smarter funding models to accelerate council smart city rollouts (05/09/2022)
+OneWiFi publicly advocated that smart city funding should be linked to measurable council savings, positioning itself as a thought leader in the smart city and digital infrastructure space. While not a direct financial milestone, this stance reflects growing influence in policy discussions and supports the company’s role in shaping and capturing future smart city investment opportunities.
+OneWiFi and CommScope team up to make Footscray a smart city (04/03/2020)
+Sydney-based OneWiFi Australia, described as Australia’s largest independent Wi‑Fi managed service provider, partnered with global technology company CommScope to expand Footscray’s public Wi‑Fi network. The enhanced network is designed to support a wide range of smart city applications, signalling geographic expansion of OneWiFi’s smart city footprint and strengthening its role in large-scale public infrastructure projects.</t>
+        </is>
+      </c>
+      <c r="D220" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Highlighting a collaboration with Serena Williams and Reckitt to support underrepresented founders, indicating growth through partnerships.
+[27/04/2026 - 3w] LinkedIn being the most-cited domain for professional queries indicating growth in dominance and visibility in the professional sector.
+[22/04/2026 - 4w] Announcing the new CEO of LinkedIn and President of Platforms &amp; Digital Work, indicating leadership changes and potential for greater opportunities.</t>
+        </is>
+      </c>
+      <c r="E220" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="16" t="inlineStr">
+        <is>
+          <t>OrthodontiX (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B221" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C221" s="17" t="inlineStr"/>
+      <c r="D221" s="17" t="inlineStr"/>
+      <c r="E221" s="16" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="16" t="inlineStr">
+        <is>
+          <t>Osler Technology (Sunshine Coast, Queensland, Australia)</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="inlineStr">
+        <is>
+          <t>Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="C222" s="17" t="inlineStr">
+        <is>
+          <t>Sunshine Coast health-tech firm Osler takes immersive VR clinician training to India (15/03/2025)
+Invest Sunshine Coast profiled Osler Technology as it announced an international expansion of its immersive virtual reality (VR) clinical training offering into India’s rapidly growing healthcare sector. The move positions Osler to service large hospital networks and medical education providers offshore, building on its cloud-based clinical e‑portfolio platform and marking a significant step in its global growth strategy.</t>
+        </is>
+      </c>
+      <c r="D222" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to discuss networking and opportunities for underrepresented founders.
+[27/04/2026 - 3w] LinkedIn is the most cited domain for professional queries on AI search engines, indicating its growth and relevance.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicating structural growth and opportunity.</t>
+        </is>
+      </c>
+      <c r="E222" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="16" t="inlineStr">
+        <is>
+          <t>PEC Ltd (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B223" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C223" s="17" t="inlineStr">
+        <is>
+          <t>Richard Coxon outlines PEC’s innovation-led growth and revival in Marton (15/04/2024)
+In a presentation to the Rotary Club of Milson, co‑owner Richard Coxon detailed the growth trajectory of PEC (Pump Engineering Company), highlighting that the company now holds around 90% of the New Zealand market for petrol pumps, successfully competing with large international corporations. Coxon described the firm’s transition since its 2021 acquisition from Gallagher Group, its focus on technology‑driven fuel systems, and its plans for future innovation, positioning PEC for continued expansion in both domestic and export markets.
+PEC focuses on hydrogen and advanced fuel dispensing technology to drive future growth (10/02/2024)
+PEC Ltd, based in New Zealand, reports that it is expanding beyond traditional fuel dispensing into hydrogen refuelling solutions, leveraging its history as the first company to invent a petrol pump with a microprocessor. The company is broadening its product portfolio to include low‑emission hydrogen equipment while continuing to provide electronic manufacturing services across multiple industries in New Zealand and Australia. This strategic shift into hydrogen and wider contract electronics work underpins PEC’s growth ambitions in the electrical and electronic equipment sector.
+Ownership change and brand revival set PEC up for renewed expansion (01/09/2021)
+Fuel systems manufacturer PEC, originally founded in 1939 in Marton, New Zealand, entered a new growth phase when Richard and Jo Coxon acquired the business from Gallagher Group in 2021 and reinstated the historic PEC brand (previously operating as Gallagher Fuel Systems). The move aimed to capitalise on PEC’s strong technological heritage and to reorient the company toward innovation‑driven growth in fuel dispensing and electronic manufacturing, strengthening its competitive position against global players.</t>
+        </is>
+      </c>
+      <c r="D223" s="17" t="inlineStr"/>
+      <c r="E223" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pec-limited-nz/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="16" t="inlineStr">
+        <is>
+          <t>PKF (PKF Sydney &amp; Newcastle, including Newcastle office)</t>
+        </is>
+      </c>
+      <c r="B224" s="16" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="C224" s="17" t="inlineStr">
+        <is>
+          <t>PKF underscores growth with 2 new partners and 43 promotions (14/02/2025)
+PKF Sydney and Newcastle, which includes the Newcastle office, appointed two new partners and promoted 43 staff across its network. The firm framed the moves as underscoring its ongoing commitment to growth and development, strengthening its leadership bench and internal talent pipeline in New South Wales, including regional locations such as Tamworth and Newcastle.
+PKF unveils 23 promotions across NSW network (20/11/2024)
+PKF Sydney and Newcastle announced 23 promotions across its New South Wales network, including staff in the Newcastle practice. The firm highlighted the promotions as recognition of strong performance and as part of a broader growth strategy to deepen service capability in assurance, business advisory and other accounting services across its NSW offices.
+PKF promotes 20+ members in Sydney and Newcastle (18/08/2023)
+PKF promoted more than 20 team members in its Sydney and Newcastle division, reflecting continued growth in client demand and service lines. The promotions covered multiple levels and disciplines and were positioned as part of PKF’s investment in people and expansion of its advisory and audit capabilities in the region.
+Annature partners with Stacie Shaw, Partner of PKF Newcastle &amp; Sydney (09/06/2022)
+Australian eSigning and client verification technology provider Annature entered a strategic partnership with Stacie Shaw, a partner at PKF Newcastle &amp; Sydney. The partnership is aimed at enhancing PKF’s digital signing and client verification processes, supporting efficiency and scalability in its accounting and audit services for the Newcastle and broader NSW client base.
+Step inside PKF Newcastle's fresh new workspace, where innovation comes to life (27/03/2022)
+PKF Sydney and Newcastle unveiled a newly refurbished Newcastle office, described as a dynamic workspace designed for connection, creativity and collaboration. The investment in the new office fit-out reflects the firm’s growth in the Newcastle market and its focus on providing a modern environment to support staff expansion and enhanced client service delivery.
+PKF Sydney and Newcastle grows presence and profile through community and client initiatives (15/09/2021)
+Through various initiatives highlighted in its press releases, including ongoing sponsorships such as the Hunter Valley Wine Show and successful fundraising events like the State of Origin charity function, PKF Sydney and Newcastle has strengthened its brand and client relationships in the Newcastle and broader Hunter region. These activities support the firm’s growth strategy by deepening community ties and increasing market visibility.</t>
+        </is>
+      </c>
+      <c r="D224" s="17" t="inlineStr">
+        <is>
+          <t>[20/05/2026 - 1d] Recognition of employees as finalists in accounting awards, showcasing the firm's talent and potential for prestige.
+[19/05/2026 - 2d] Webinar on expanding into the US market, indicating company interest in market expansion opportunities.
+[13/05/2026 - 1w] Support and successes with Neuro Alliance; reveals partnership growth and advisory influence for future development.
+[07/05/2026 - 2w] Climate reporting workshop indicating the firm's proactive approach to future regulations and client preparedness.
+[07/05/2026 - 2w] Sponsorship of local rugby league club demonstrating community investment and potential outreach growth.
+[06/05/2026 - 2w] Graduation of the leadership pathway program; signifies internal leadership development and potential for future growth.
+[01/05/2026 - 2w] PKF awards at Gold Coast Film Festival; highlights engagement and sponsorship in film, indicating community growth.
+[30/04/2026 - 3w] Successful CEO Connect evening; indicates external engagement and strong business networking, suggesting expansion capabilities.
+[28/04/2026 - 3w] Celebration of awards at Rising Star event for employees; demonstrates recognition and growth in employee capabilities.</t>
+        </is>
+      </c>
+      <c r="E224" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pkf-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="16" t="inlineStr">
+        <is>
+          <t>PX4 Software</t>
+        </is>
+      </c>
+      <c r="B225" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C225" s="17" t="inlineStr">
+        <is>
+          <t>PX4 Software deepens presence in Saudi Arabia to support mining sector (24/01/2024)
+Queensland government trade coverage reports that PX4 Software has opened an office in Saudi Arabia to build on pilot projects with the Ministry of Industry and Mineral Resources and expand its work with local mining companies. This move signals a strategic international expansion into the Middle East, leveraging earlier pilot deployments to secure longer‑term growth opportunities in the Kingdom’s mining industry.
+The Global Expansion of PX4: From Australia to the World (09/10/2023)
+PX4 Software, a Brisbane-based tenement and land management platform, detailed its transformation from a 40‑year Australian concept to a modern, 7‑year‑old SaaS product now operating in more than 30 mining jurisdictions. The company highlights its growing global footprint across Australia, New Zealand, the USA, Canada, multiple African countries, and pilot work in new regions, positioning itself as a leading global solution for mining compliance, land management, and tenement administration.
+Innovating Compliance: How PX4 Software Elevates Safety and Sustainability in Australia’s Mining Sector (03/08/2023)
+PX4 Software details enhancements to its tenement management platform that help mining companies handle increasingly complex regulatory requirements in Australia. The article emphasizes how the software streamlines compliance processes, supports safety and sustainability obligations, and helps clients adapt to regulatory change, reflecting PX4’s ongoing product development and growing role in compliance-focused digital solutions.
+PX4 and the journey toward innovation-led businesses (15/06/2023)
+In this company blog, PX4 Software describes ongoing investment in product innovation and customer onboarding, including closer engagement with government departments and regulators. The article outlines how PX4 is positioning itself as an innovation partner for mining and exploration companies, streamlining compliance workflows and supporting clients’ digital transformation—indicative of continued product and customer growth.
+PX4 Software selected for QuantumTX Queensland METS Technology Accelerator (28/02/2022)
+PX4 Software was chosen as one of 20 start‑ups and scale‑ups to participate in the QuantumTX Queensland METS Technology Accelerator program. The 12‑week program provides intensive business training, mentoring, and a pitch event aimed at helping participants scale into new domestic and international markets, supporting PX4’s growth and commercial acceleration in the mining technology sector.
+PX4 Resources Case Study: Building a Scalable Tenement Management Platform (12/05/2021)
+A Quantana case study on PX4 Software reports that the PX4 platform was engineered for scalability and has delivered clients up to 35% cost savings alongside productivity and time-efficiency gains. The case study highlights PX4’s evolution into a next‑generation, cloud-based tenement management solution with advanced data visualisation, task management, and reporting capabilities, underscoring the company’s product maturation and commercial traction.</t>
+        </is>
+      </c>
+      <c r="D225" s="17" t="inlineStr">
+        <is>
+          <t>[21/05/2026 - today] Collaboration with KoBold Metals to simplify compliance and improve operations in mining projects.
+[08/05/2026 - 1w] Expansion of regional jurisdictional support, including new updates for the DRC and Utah, USA.
+[05/05/2026 - 2w] PX4 Software highlights its global reach in land management, supporting operations across various regions in 2026.
+[01/05/2026 - 2w] Introduction of a new GeoServer integration to improve spatial data management within PX4 Software, enhancing GIS workflows.
+[28/04/2026 - 3w] Announcement of North American updates to enhance parcel filtering in PX4 Software, improving user experience.
+[22/04/2026 - 4w] Successful first PX4 User Conference held with plans for exciting projects in 2026 announced at the event.</t>
+        </is>
+      </c>
+      <c r="E225" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/px4-software/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="16" t="inlineStr">
+        <is>
+          <t>Parker Healthcare (Preston, Victoria, Australia)</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C226" s="17" t="inlineStr"/>
+      <c r="D226" s="17" t="inlineStr">
+        <is>
+          <t>[20/05/2026 - 1d] Job opening announcement indicating company growth through new hires.</t>
+        </is>
+      </c>
+      <c r="E226" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/parker-healthcare/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>Passport 360</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C227" s="17" t="inlineStr">
+        <is>
+          <t>Microsoft selects Passport 360 for Go Global SaaS expansion program (13/09/2022)
+Passport 360, a Brisbane-based SaaS provider of health and safety compliance solutions for high‑risk industries such as mining, was named in the first cohort of Microsoft Australia’s Go Global program run in partnership with Austrade. Through the initiative, Passport 360 receives structured pre‑departure mentoring, export and technology workshops, and 90 days of in‑market support via Austrade’s San Francisco Landing Pad, aimed at accelerating its expansion into the United States and other international markets. Inclusion in the exclusive program signals strong growth potential and strategic backing from major ecosystem partners.
+Passport 360 scales safety-compliance SaaS platform with thousands of customers (08/07/2019)
+In an interview with Information Age (ACS), co‑founder Siobhan Whitehead described how Passport 360’s cloud platform has grown to serve 2,753 customers while employing 11 staff. The SaaS product centralises medicals, training records, competencies, and certifications into a portable ‘passport’ for workers in high‑risk environments. This customer base, largely in mining and related sectors, indicates substantial early‑stage traction and commercial validation of the company’s digital compliance offering, laying a foundation for further growth and expansion from its Australian base, including Brisbane operations.</t>
+        </is>
+      </c>
+      <c r="D227" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a partnership with Serena Williams and Reckitt for mentorship and networking, emphasizing building valuable connections.
+[22/04/2026 - 4w] Announces new leadership roles for Daniel Shapero as CEO and Mohak Shroff as President, indicating organizational growth and leadership changes.</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="16" t="inlineStr">
+        <is>
+          <t>Pastiche Training (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B228" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C228" s="17" t="inlineStr">
+        <is>
+          <t>Pastiche Training maintains international CPD accreditation for advanced skin science programs (01/06/2024)
+Pastiche Training, the New Zealand–based online aesthetician school founded by dermal science educator Florence Barrett‑Hill, continues to hold accreditation from the internationally recognised CPD Accreditation Group for its advanced skin analysis and dermal science courses. The sustained accreditation signals ongoing recognition of the provider’s training quality and supports global enrolment growth among professional aestheticians seeking formal continuing professional development credentials.
+Global online enrolments grow as Pastiche Training expands advanced aesthetic education pathways (15/03/2023)
+Pastiche Training reports expanding its suite of online training pathways for professional non-surgical skin care practitioners, with new and updated advanced skin analysis and dermal science modules added to its learning platform. The broadened curriculum, offered fully online to an international audience, reflects growth in demand from aestheticians seeking higher-level professional development and has contributed to increased global enrolments.
+International aestheticians credit Pastiche Training courses with significant business growth (10/11/2022)
+Testimonials published by Pastiche Training highlight that graduates of the Advanced Skin Analysis program and related courses have experienced measurable growth in their clinics, including higher client retention, increased service pricing, and expanded treatment offerings. The positive outcomes reported by practitioners underscore the commercial impact and market traction of Pastiche Training’s programs in the professional skin care sector.</t>
+        </is>
+      </c>
+      <c r="D228" s="17" t="inlineStr"/>
+      <c r="E228" s="16" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="16" t="inlineStr">
+        <is>
+          <t>Payroll Standard</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C229" s="17" t="inlineStr">
+        <is>
+          <t>No growth-related news articles found for Payroll Standard (Brisbane) (21/05/2026)
+A search of recent Australian and industry-specific sources did not identify any news articles indicating growth events (such as awards, expansions, major new hires, partnerships, patents, or notable financial milestones) specifically for Payroll Standard located in Brisbane and operating in the online and digital media industries. Available search results relate to general payroll compliance, regulatory changes, and other payroll service providers, but none are clearly about this particular company.</t>
+        </is>
+      </c>
+      <c r="D229" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Discusses a collaboration with Serena Williams and Reckitt to support underrepresented founders, indicating a partnership for growth.
+[27/04/2026 - 3w] States that LinkedIn is the #1 most-cited domain for professional queries, indicating market success.
+[22/04/2026 - 4w] Announces new leadership roles at LinkedIn, indicating team growth and potential company evolution.</t>
+        </is>
+      </c>
+      <c r="E229" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="16" t="inlineStr">
+        <is>
+          <t>People Diagnostix</t>
+        </is>
+      </c>
+      <c r="B230" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C230" s="17" t="inlineStr">
+        <is>
+          <t>People Diagnostix Making Major Moves (09/05/2024)
+Perth-based People Diagnostix, the company behind digital mental health platform FlourishDx, secured a $372K share of a $938K grant in partnership with the Institute of Positive Education at Geelong Grammar School and Monash University. The funding will see FlourishDx rolled out to up to 90 Victorian schools over two years. In the same period, the company announced a new strategic global partnership (details not fully disclosed in the snippet), achieved ISO/IEC 27001:2013 information security certification, and opened a Series A funding round aimed at growing the team, building the brand, advancing product development, and driving local and international sales.</t>
+        </is>
+      </c>
+      <c r="D230" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to empower underrepresented founders.
+[27/04/2026 - 3w] LinkedIn recognized as the top domain for professional AI queries.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E230" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="16" t="inlineStr">
+        <is>
+          <t>Personify Care</t>
+        </is>
+      </c>
+      <c r="B231" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C231" s="17" t="inlineStr">
+        <is>
+          <t>Personify Care's digital patient pathway project to go SA-wide after A$5.6m SA Health contract (19/03/2024)
+Health IT firm Personify Care secured a A$5.6 million (US$3.7 million) two‑year contract with SA Health to extend its digital patient pathways platform across the entire state. The whole‑of‑state rollout is aimed at supporting new models of care that reduce outpatient and elective surgery wait times while freeing clinicians and nurses to focus on higher‑value tasks, signalling a major expansion of the platform’s footprint within South Australia’s public health system.
+Personify Care to roll out digital patient pathways across SA Health under whole‑of‑system agreement (18/03/2024)
+Adelaide‑based digital health platform developer Personify Care entered a two‑year, A$5.6 million whole‑of‑SA Health agreement to deploy its digital patient pathways solution across the state. The arrangement consolidates prior contracts and standardises the platform for referrals, pre‑admission, outpatient, discharge and care‑transition workflows, reflecting strong commercial traction and system‑wide scale‑up within South Australia’s public hospitals.
+Personify Care reports rapid growth in digital patient interactions and international expansion (15/02/2024)
+Personify Care states that its SaaS platform has supported over 16.5 million patient interactions in the past 12 months with response rates above 91%, and notes that the company, founded in Adelaide, has expanded internationally with team members across Australia. The company highlights strong product adoption, growing usage volumes, and continued hiring momentum from its Lot Fourteen headquarters, underscoring sustained operational and geographic growth.
+Personify Care expands internationally, operating from Lot Fourteen headquarters in Adelaide (10/11/2023)
+Personify Care describes itself as a rapidly growing healthcare SaaS platform that has expanded beyond Australia while maintaining its headquarters at Adelaide’s Lot Fourteen innovation precinct. The company positions its digital patient pathways platform as enabling personalised care beyond hospital stays, and actively recruits new staff to support scaling its world‑class digital health offering, indicating ongoing headcount and market expansion.</t>
+        </is>
+      </c>
+      <c r="D231" s="17" t="inlineStr">
+        <is>
+          <t>[21/05/2026 - today] Recap of a successful Digital Health Festival 2026, indicating strong engagement and connections with new potential clients.
+[18/05/2026 - 3d] Personify Care is a Gold Sponsor at Digital Health Festival 2026, highlighting their contributions to digital health.</t>
+        </is>
+      </c>
+      <c r="E231" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/personify-care/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="16" t="inlineStr">
+        <is>
+          <t>Perth Dermatology Clinic</t>
+        </is>
+      </c>
+      <c r="B232" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C232" s="17" t="inlineStr"/>
+      <c r="D232" s="17" t="inlineStr"/>
+      <c r="E232" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/perth-dermatology-clinic/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="16" t="inlineStr">
+        <is>
+          <t>PharmSky Research</t>
+        </is>
+      </c>
+      <c r="B233" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C233" s="17" t="inlineStr">
+        <is>
+          <t>PharmSky Research to Attend BIO-Europe Spring 2026 to Pursue Global CDMO Partnerships (23/03/2026)
+PharmSky Research announced it will attend BIO-Europe Spring 2026 in Lisbon, signaling its push to form new strategic partnerships with European and global biopharma companies. By promoting its end-to-end drug development and GMP manufacturing capabilities at a major international partnering conference, PharmSky aims to broaden its cross-border project pipeline and drive international growth.
+PharmSky Research Confirms Participation in Clinical Trials Festival Asia 2026 (10/03/2026)
+PharmSky Research reported that it will take part in Clinical Trials Festival Asia 2026 in Singapore, using the event to connect with regional sponsors and showcase its clinical trial manufacturing and analytical capabilities. The company’s presence at this Asia-focused meeting reflects its intention to deepen engagement with international clinical trial networks and expand its customer base beyond Australia.
+PharmSky Research to Showcase CDMO Capabilities at AusBiotech 2025 (01/10/2025)
+Melbourne-based CDMO PharmSky Research announced it will participate in AusBiotech 2025, Australia’s leading life sciences conference, highlighting its integrated CMC, formulation, and GMP manufacturing services. The company positions this presence as part of its broader strategy to expand visibility among biotech innovators and attract new development partnerships in Australia and globally.</t>
+        </is>
+      </c>
+      <c r="D233" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to emphasize the importance of networking for success.
+[24/04/2026 - 3w] Congratulatory message for a new addition to the LinkedIn team, signaling team expansion.
+[22/04/2026 - 4w] Announcement of new leadership roles at LinkedIn, suggesting a potential for growth and vision.</t>
+        </is>
+      </c>
+      <c r="E233" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="16" t="inlineStr">
+        <is>
+          <t>Phenix Health Pty Ltd (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B234" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C234" s="17" t="inlineStr">
+        <is>
+          <t>How Phenix Health is Transforming Telehealth Services in Australia (01/03/2024)
+Phenix Health, a Brisbane-based virtual healthcare provider, highlights the expansion of its telehealth platform across Australia, offering 24/7 access to GPs and mental health services. The article emphasises the company’s growing role in delivering online general practice, prescription renewals, mental health consultations and assessments, and after‑hours care. This reflects operational growth and increased nationwide reach, particularly in mental health support via telehealth.
+Phenix Health Expands 24/7 Bulk-Billed Telehealth Mental Health Plans via Healthdirect Listing (15/02/2024)
+Phenix Health’s listing on Healthdirect showcases its 24‑hour availability for mental health information, referral, and preparation of Medicare‑funded Mental Health Care Plans. The listing notes bulk‑billed consultations with nurse practitioners and GPs, indicating formal integration into the national Healthdirect directory and reinforcing the company’s standing as an accessible, around‑the‑clock mental health telehealth provider.
+Phenix Health Scales Virtual Care and Remote Monitoring Platform ‘OnePhenix’ (01/11/2023)
+Company information compiled by Prospeo describes growth at Phenix Health, which now generates an estimated annual revenue of about AUD 1.63 million with a valuation of AUD 5.3 million and a team of 11–20 employees. The profile notes the development and deployment of OnePhenix, a cloud‑based remote patient monitoring and clinical practice management platform that supports mental health, chronic disease, NDIS, aged care, and hospital‑in‑the‑home models. This points to continued scaling of software capabilities, multi‑site shared‑care coordination, and expansion beyond core telehealth into broader virtual‑care infrastructure.
+Phenix Health Promotes 24/7 Online Mental Health Treatment Plans (01/08/2023)
+Phenix Health’s dedicated mental health treatment plan service markets itself as one of the few online providers authorised to create Mental Health Care Plans. The service allows patients to obtain personalised mental health support and referrals through telehealth, available 24/7 with Australian clinicians. This represents targeted growth in the mental health segment of its telehealth offering and positions the company as a specialised digital gateway for mental health care in Australia.
+Phenix Health Recruits More Australian Doctors to Grow Its Online Care Network (15/05/2023)
+The Phenix Health ‘Doctor’ information page actively markets the platform to Australian doctors, emphasising opportunities to grow their patient base and offer flexible online consultations. By inviting more practitioners onto its 24/7 telehealth service, Phenix Health is scaling clinician capacity, which supports growth in patient volume and service coverage, including mental health and after‑hours care.</t>
+        </is>
+      </c>
+      <c r="D234" s="17" t="inlineStr"/>
+      <c r="E234" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/phenix-health-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="16" t="inlineStr">
+        <is>
+          <t>Phinar Software</t>
+        </is>
+      </c>
+      <c r="B235" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C235" s="17" t="inlineStr">
+        <is>
+          <t>Phinar Software appoints Mining Technology Specialist David Groocock to Perth office (15/04/2024)
+Phinar Software announced that David Groocock has joined its Perth office as a Mining Technology Specialist, strengthening the company’s technical capabilities and client-facing expertise in mining data analytics and geoscience software. The appointment signals ongoing investment in specialist talent to support growth of its X10-Geo platform and related services.
+Phinar Software’s X10-Geo platform profiled in Mine Magazine for transforming 3D geological data analysis (01/10/2018)
+Mine Magazine featured Phinar Software’s X10-Geo platform as a high-performance data analysis and 3D visualisation solution for geologists, mining engineers and data scientists. The coverage highlighted X10-Geo’s role in streamlining exploration, resource estimation and mine planning workflows, underscoring Phinar’s growing presence and product adoption in the mining technology and data analytics market.</t>
+        </is>
+      </c>
+      <c r="D235" s="17" t="inlineStr"/>
+      <c r="E235" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/phinarsoftware/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="16" t="inlineStr">
+        <is>
+          <t>Place Intelligence</t>
+        </is>
+      </c>
+      <c r="B236" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C236" s="17" t="inlineStr">
+        <is>
+          <t>Place Intelligence launches Capital City Data Marketplace for Melbourne (15/03/2024)
+Place Intelligence expanded its product offering with the launch of the Melbourne Capital City Data Model and Data Marketplace, providing detailed insights into four-plus years of changes in activity, dwell time, audience mix and building use. The new platform positions the company for growth in economic development, tourism, workforce planning and urban analytics applications.
+Place Intelligence establishes international offices in Los Angeles and Amsterdam (10/11/2023)
+Place Intelligence signalled international expansion by listing new office locations in Los Angeles (Santa Monica, California) and Amsterdam (Netherlands) alongside its Australian base. The move reflects growing global demand for its location intelligence and urban analytics services from economic development, tourism and planning agencies.</t>
+        </is>
+      </c>
+      <c r="D236" s="17" t="inlineStr"/>
+      <c r="E236" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/place-intelligence/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="16" t="inlineStr">
+        <is>
+          <t>Platinum Orthodontics</t>
+        </is>
+      </c>
+      <c r="B237" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C237" s="17" t="inlineStr">
+        <is>
+          <t>Platinum Orthodontics expands its Sunshine Coast presence with Mooloolaba practice (01/01/2024)
+Platinum Orthodontics highlights its Mooloolaba office at 152 Brisbane Road, indicating continued practice expansion and service coverage on the Sunshine Coast.
+Platinum Orthodontics lists three operating locations across Brisbane and the Sunshine Coast (01/01/2024)
+The company’s contact page confirms multiple active practices in Annerley, Stafford, and Mooloolaba, suggesting an established multi-site footprint and business growth over time.
+Dr Emily Ong featured as a qualified orthodontist serving Platinum Orthodontics patients across Brisbane and the Sunshine Coast (01/01/2024)
+Platinum Orthodontics highlights Dr Emily Ong on its website as a qualified orthodontist across several locations, reflecting ongoing professional service capacity and clinical staffing.
+Platinum Orthodontics promoted as a leading orthodontic provider on the Sunshine Coast (01/01/2024)
+The practice markets itself as a leading orthodontist provider in Mooloolaba, which can indicate brand strength and continued growth in patient demand.</t>
+        </is>
+      </c>
+      <c r="D237" s="17" t="inlineStr"/>
+      <c r="E237" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/platinum-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="16" t="inlineStr">
+        <is>
+          <t>Pointsbuild</t>
+        </is>
+      </c>
+      <c r="B238" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C238" s="17" t="inlineStr">
+        <is>
+          <t>Standards Australia partners with Pointsbuild to offer access to standards (14/09/2023)
+Standards Australia announced a partnership with Pointsbuild to provide access to standards through Pointsbuild’s online education and professional development platform, signaling a strategic expansion of its training and content offerings.
+Pointsbuild gets $45K to help with CPD training (01/07/2011)
+Fair Trading Commissioner Lyn Baker announced $45,000 in funding for Pointsbuild to deliver essential training for pool builders, indicating financial support and program growth in its CPD training services.
+About Us - Pointsbuild (01/01/2007)
+Pointsbuild states it launched in 2007 as Australia’s first approved CPD training provider for the building industry and has since grown into a leading online CPD education and training provider across multiple sectors, indicating long-term expansion.</t>
+        </is>
+      </c>
+      <c r="D238" s="17" t="inlineStr"/>
+      <c r="E238" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pointsbuild/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="16" t="inlineStr">
+        <is>
+          <t>Power On Australia</t>
+        </is>
+      </c>
+      <c r="B239" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C239" s="17" t="inlineStr"/>
+      <c r="D239" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to enhance networking strategies for business opportunities.
+[27/04/2026 - 3w] LinkedIn recognized as the top-cited domain for professional queries, indicating strong market presence.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, signaling potential growth and opportunities ahead.</t>
+        </is>
+      </c>
+      <c r="E239" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="16" t="inlineStr">
+        <is>
+          <t>Premier Contact Point</t>
+        </is>
+      </c>
+      <c r="B240" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C240" s="17" t="inlineStr">
+        <is>
+          <t>Premier Contact Point and IComm announce new distribution partnership (27/08/2018)
+Premier Technologies Pty Ltd, the company behind cloud contact centre solution Premier Contact Point, announced a new distribution partnership with IComm Australia Pty Ltd, an award‑winning unified communications consultancy. The partnership is aimed at expanding market reach for Premier Contact Point’s cloud contact centre platform across Australia by leveraging IComm’s UC expertise and customer base.
+Premier grows hosted contact centre solution team for Premier Contact Point (21/03/2013)
+Premier Technologies, provider of the Premier Contact Point hosted contact centre solution, expanded its team with the appointment of Silvio Marusic. The hiring was positioned as part of the company’s strategy to grow its hosted contact centre business and strengthen delivery capabilities for Premier Contact Point clients.</t>
+        </is>
+      </c>
+      <c r="D240" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a collaboration with Serena Williams and Reckitt to discuss network leverage.
+[27/04/2026 - 3w] States LinkedIn's positioning as the most-cited domain for professional queries.
+[22/04/2026 - 4w] Announces new leadership roles at LinkedIn, indicating company growth opportunities.</t>
+        </is>
+      </c>
+      <c r="E240" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="16" t="inlineStr">
+        <is>
+          <t>ProbityPeople</t>
+        </is>
+      </c>
+      <c r="B241" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C241" s="17" t="inlineStr"/>
+      <c r="D241" s="17" t="inlineStr"/>
+      <c r="E241" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/probitypeople/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="16" t="inlineStr">
+        <is>
+          <t>Prospecta Utilities</t>
+        </is>
+      </c>
+      <c r="B242" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C242" s="17" t="inlineStr">
+        <is>
+          <t>Private 5G network from Prospecta Utilities proves resilience during ex‑tropical cyclone Alfred (20/04/2025)
+A private residential 5G network deployed by Prospecta Utilities at the GemLife Gold Coast community remained operational during ex‑tropical cyclone Alfred while major carriers experienced outages. CEO Mark Langdon highlighted the network’s resilience as evidence of the value of private, diversified telecommunications infrastructure. Following a six‑month trial, the network was activated for 45 homes and is planned to cover 400 residences. Prospecta intends to roll out similar 5G networks to 14,000 homes across 30 land‑lease resorts by 2028 and has stated plans to triple its delivery scope by 2027.
+Over‑50s Gold Coast community pioneers Australia’s first private mmWave 5G network with Prospecta Utilities (12/03/2025)
+Prospecta Utilities has activated what is described as Australia’s first private wireless mmWave 5G network at the $200 million GemLife Gold Coast over‑50s resort. After a six‑month trial, the network is live for the first 45 homes and will eventually serve all 400 homes. Delivering speeds up to 650 Mbps, ultra‑low latency, unlimited data and 99.8% availability, the system is designed to support robotics, autonomous vehicles, telehealth and other advanced digital services. Prospecta, founded in 2023, aims to extend this model to 14,000 homes across 30 resorts by 2028 and to triple its energy and network services by 2027.
+Prospecta Utilities installs mmWave private 5G network at GemLife Gold Coast resort (05/11/2024)
+Prospecta Utilities has completed installation of a standalone mmWave private 5G fixed wireless network at the GemLife Gold Coast over‑50s lifestyle resort. The system uses Ciena 5130 and 5164 routers as backbone infrastructure and forms part of Prospecta’s strategy to build interconnected ‘smart cities’ across retirement and land‑lease communities. The company plans to replicate this model across GemLife’s 30 resorts by the end of 2028, indicating a multi‑site expansion pipeline.
+Prospecta Utilities’ 5G wireless network to make GemLife Gold Coast a ‘smart city’ (15/07/2024)
+Prospecta Utilities has begun installing one of Australia’s first standalone mmWave 5G fixed wireless networks at the GemLife Gold Coast over‑50s resort in Pimpama. The rollout includes nine 5G radio devices initially serving 12 homes, with plans to cover all 74 homes in the first stage. The project is positioned as the foundation for an interconnected ‘smart city’ and is the first step in Prospecta’s broader plan to deploy similar networks across GemLife’s portfolio.
+Prospecta Utilities strikes $8 million deal for world-first 5G mmWave fixed wireless technology (10/03/2024)
+Prospecta Utilities, backed by the Puljich family behind the GemLife and Living Gems portfolios, has invested AUD $8 million in world‑first 5G mmWave fixed wireless access technology. The company signed an agreement with Airspan Networks Holdings for the first 500 AIR5G 7200 radio units, enabling non‑carrier enterprise networks and smart‑city style connectivity across multiple homes and devices. This capital investment and strategic technology partnership underpin Prospecta’s growth in telecommunications and digital infrastructure.</t>
+        </is>
+      </c>
+      <c r="D242" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Discusses collaboration with Serena Williams and the importance of networking in business growth.
+[22/04/2026 - 4w] Congratulates new leadership roles within LinkedIn, indicating positive company growth and future opportunities.</t>
+        </is>
+      </c>
+      <c r="E242" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="16" t="inlineStr">
+        <is>
+          <t>PsychMed (Adelaide, South Australia)</t>
+        </is>
+      </c>
+      <c r="B243" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C243" s="17" t="inlineStr">
+        <is>
+          <t>PsychMed recognised as a key Adelaide PHN commissioned provider for suicide prevention and mental health services (15/03/2024)
+Adelaide-based PsychMed was highlighted in Adelaide Primary Health Network communications as one of the commissioned providers delivering evidence‑based psychological and suicide‑prevention services across metropolitan Adelaide. The recognition reflects PsychMed’s ongoing role in region‑wide programs targeting suicide risk, trauma, and complex mental health presentations, demonstrating continued service growth and consolidation as a core ally in the local primary mental health system.
+PsychMed expands specialised gambling harm and addiction services in South Australia (10/11/2023)
+PsychMed, headquartered on North Terrace in Adelaide, announced an expansion of its specialised services for gambling, alcohol, and drug issues across its independently staffed centres in South Australia. The organisation promoted new evidence‑based group programs, podcasts, and outreach resources focused on gambling harm, indicating investment in dedicated clinical programs, staff capacity, and community education as demand for addiction‑related psychological services grows.
+PsychMed strengthens community engagement with gambling harm awareness podcast series (02/09/2022)
+Through its blog and outreach channels, PsychMed launched and promoted a ‘Gambling Harm Awareness’ podcast series, featuring clinicians discussing the rise of sports betting, venue changes, and the impacts of COVID‑19 on gambling behaviour. The initiative underscores PsychMed’s growth in digital engagement and preventative mental‑health education, extending its reach beyond clinic walls and supporting its broader strategy in public mental‑health promotion.</t>
+        </is>
+      </c>
+      <c r="D243" s="17" t="inlineStr"/>
+      <c r="E243" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/psychmed/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="16" t="inlineStr">
+        <is>
+          <t>QEST Infrastructure Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B244" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C244" s="17" t="inlineStr">
+        <is>
+          <t>QEST Infrastructure marks 20+ years with multi-division expansion across Victoria (15/03/2024)
+QEST Infrastructure, based in North Geelong, highlighted sustained growth after more than 20 years in operation, now running five specialist divisions covering project management, non‑destructive digging, environmental and geotechnical drilling, underground infrastructure management, surveying, 3D scanning, drone surveying, and industrial services. The company now operates two depots (Geelong and Melbourne), a dedicated projects office, a drilling depot, and multiple mechanical and fabrication workshops, reflecting a significant expansion of capability and geographic footprint in Victoria and interstate.
+Employee numbers rise as QEST Infrastructure grows integrated environmental and civil services (20/11/2023)
+Industry data providers report that QEST Infrastructure has increased its workforce to around 80–130 full‑time staff, with an estimated 23% year‑on‑year increase in headcount. This growth supports the company’s broadened service offering in environmental resource management, specialist drilling, industrial services, and underground asset management, positioning QEST as a single‑provider alternative to using multiple subcontractors on complex infrastructure projects.
+Revenue growth underpins QEST Infrastructure’s position as a leading Victorian environmental and infrastructure contractor (05/09/2023)
+Commercial intelligence sources estimate QEST Infrastructure’s annual revenue in the multi‑million‑dollar range (approximately AUD 7.8–16.8 million), indicating strong financial performance for the privately held Geelong‑based company. The revenue growth is tied to increasing demand for its integrated environmental drilling, non‑destructive excavation, waste transport, and surveying services across commercial, government, and industrial markets in Victoria and beyond.
+QEST Infrastructure expands specialist drilling and environmental capabilities across Melbourne and Geelong (12/06/2022)
+QEST Infrastructure promoted the growth of its Specialist Drilling Services division, emphasising more than two decades of experience in environmental and geotechnical drilling throughout Melbourne, Geelong, regional Victoria, and interstate. The expansion includes enhanced capacity for monitoring well installation, environmental sampling, and complex drilling projects, consolidating QEST’s role in supporting environmental compliance and infrastructure development in the state.
+QEST Infrastructure recognised as specialist provider in environmental and underground asset management (18/03/2021)
+Through updated corporate policies and positioning, QEST Infrastructure Group outlined its status as a well‑established specialist in environmental and underground asset management and protection services. The formalisation of integrated quality, safety, and environmental management systems reflects organisational maturity and supports the company’s continued growth in government and industrial infrastructure programs across Victoria.</t>
+        </is>
+      </c>
+      <c r="D244" s="17" t="inlineStr"/>
+      <c r="E244" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/qest-infrastructure/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="16" t="inlineStr">
+        <is>
+          <t>QGE Group (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B245" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C245" s="17" t="inlineStr">
+        <is>
+          <t>QGE Group expands renewable grid connection and battery integration services across Australia (15/03/2024)
+QGE Group, a Brisbane-based specialist in renewables and energy management, announced an expansion of its network connection offering, positioning itself as a one‑stop provider for solar and battery connections. The company highlighted growing demand from Australian network providers for its end‑to‑end services covering scoping, design, network approvals, construction and commissioning of PV and battery projects. QGE emphasised that its strengthened capability in grid export control, cloud software and telemetry is enabling it to take on a larger volume of utility‑scale and commercial projects nationally.
+Woolooga Solar Farm contract underscores QGE Group’s leadership in grid‑connected solar PV (10/11/2023)
+QGE Group reported its role in delivering the high‑voltage substation RTU control system for the 200 MW Woolooga Solar Farm, working closely with Powerlink and bp Lightsource. The project showcases QGE’s growing footprint in large‑scale solar and its expertise in electrical and controls engineering for grid‑connected PV. The company noted that its work on Woolooga reinforces its position as a recognised leader in hazardous areas and utility‑scale renewable projects, supporting continued growth in this market segment.
+QGE Group highlights ongoing investment in cloud, telemetry and blockchain‑enabled energy solutions (05/09/2023)
+In a corporate update, QGE Group outlined continued investment in new technology and engineering processes, including cloud software, controls and telemetry solutions, and grid export control panels. The company also flagged active involvement in blockchain and peer‑to‑peer energy trading initiatives. These technology investments are aimed at broadening QGE’s service offering and positioning the Brisbane firm for growth in advanced renewable energy management and future grid applications.
+QGE Group marks steady growth since 2010 with expanded capabilities in renewables and hazardous areas (20/06/2022)
+QGE Group’s updated corporate profile describes steady growth since its establishment in 2010, driven by continual development of its capabilities in hazardous areas, grid‑connected solar PV, and energy management. The Brisbane‑based group notes that its foundation in electrical and controls engineering has enabled it to expand into larger, more complex projects across energy, resources, and food and beverage sectors. This reflects a trajectory of organic expansion and diversification within Australia’s renewable and industrial markets.</t>
+        </is>
+      </c>
+      <c r="D245" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 2d] The introduction of Michael Day as the head of the Renewable Energy team signifies the addition of a highly experienced leader aimed at enhancing the company's expertise and service delivery in renewable energy projects.
+[22/04/2026 - 4w] This post features Terry Ozanne, who leads the Engineering Instrumentation and Controls team, indicating the strengthening of the company's engineering capabilities and commitment to innovative solutions in renewable energy and various industries.</t>
+        </is>
+      </c>
+      <c r="E245" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/qge-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="16" t="inlineStr">
+        <is>
+          <t>Quality Practice Accreditation</t>
+        </is>
+      </c>
+      <c r="B246" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C246" s="17" t="inlineStr">
+        <is>
+          <t>QPA highlights impact of engagement on quality in general practice (15/04/2024)
+Quality Practice Accreditation (QPA), the only accreditor specialising solely in general practice in Australia, released an article titled “Why engagement is often the clearest sign of quality in general practice.” In it, QPA positions itself as a partner to practices to drive quality improvements, emphasising its role in supporting continuous quality enhancement and outcomes-focused care. While not a formal financial announcement, the piece reflects QPA’s growing influence and thought leadership in general practice quality and accreditation.
+General practices promote new and renewed QPA accreditation status (20/03/2024)
+Individual practices such as Kookora Surgery publicly announced achieving accreditation through Quality Practice Accreditation (QPA), highlighting QPA’s role in validating high standards of safety and quality. These announcements, including Kookora Surgery’s 2024 accreditation, signal continued uptake of QPA’s accreditation services across practices and sustained demand for its programs.
+QPA recognised as specialist accreditor for rural and remote general practices (10/02/2024)
+HealthAccess and other remote GP services publicly referenced that their services are accredited by Quality Practice Accreditation (QPA), noting that QPA is a specialist in accreditation of rural and remote practices. This visibility underscores QPA’s expanding footprint and recognition in rural and remote healthcare accreditation, reinforcing its niche leadership in these regions.
+QPA positions itself as partner for quality assurance and risk mitigation in general practice (05/11/2023)
+In updated corporate information, Quality Practice Accreditation described its mission as empowering and supporting general practices to provide the highest quality care through quality assurance, continual improvement and risk mitigation programs. The positioning reflects an evolution from pure accreditation services toward a broader, program-based partnership model with practices, indicating strategic growth in scope of services within the general practice quality ecosystem.</t>
+        </is>
+      </c>
+      <c r="D246" s="17" t="inlineStr"/>
+      <c r="E246" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/quality-practice-accreditation/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="16" t="inlineStr">
+        <is>
+          <t>Queensland Cardiovascular Group</t>
+        </is>
+      </c>
+      <c r="B247" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C247" s="17" t="inlineStr">
+        <is>
+          <t>First Leadless Pacemaker Procedures at St Andrew’s War Memorial Hospital by Queensland Cardiovascular Group (15/03/2024)
+Queensland Cardiovascular Group announced that its electrophysiology team has performed the first leadless pacemaker procedures at St Andrew’s War Memorial Hospital in Brisbane. Introducing this next‑generation device expands QCG’s interventional cardiology capabilities and reinforces its position at the forefront of advanced cardiac services in Queensland.
+Queensland Cardiovascular Group expands as Queensland’s largest private cardiac specialist group (01/11/2023)
+Queensland Cardiovascular Group highlighted its continued growth to more than 25 cardiologists and over 100 staff across multiple locations in major private hospitals and community sites in South East Queensland. The group’s expansion in clinical, interventional, nursing and allied health services strengthens its role as the largest provider of private cardiovascular services in the state.
+QCG grows multi‑site cardiac service network across South East Queensland (01/10/2023)
+QCG reported ongoing expansion of its integrated network of cardiac clinics and hospital‑based services, now operating at locations including Spring Hill (St Andrew’s), Chermside, Greenslopes, North Lakes, Buderim and Mater South Brisbane. The broader geographic footprint increases access to specialist cardiologists, diagnostic testing and nurse‑led support for patients throughout the region.
+QCG strengthens electrophysiology service with growing procedure volumes (01/09/2022)
+Queensland Cardiovascular Group’s electrophysiology service, led by Dr John Hayes, continues to grow, performing over 1,000 procedures annually and undergoing regular audit and quality review. The rising case volume and structured quality program indicate a maturing, scaled sub‑specialty service within the group’s broader cardiology offering.
+QCG cardiologist leads community education on atrial fibrillation at Buderim (01/05/2022)
+A Queensland Cardiovascular Group cardiologist based at Buderim Private Hospital released an educational video on atrial fibrillation aimed at helping community members better understand symptoms and treatment options. This initiative reflects QCG’s expanding role in preventative cardiology and public education, complementing its clinical service growth on the Sunshine Coast.</t>
+        </is>
+      </c>
+      <c r="D247" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 3w] Announcing the QCG Chermside clinic's capabilities and highlighting its team of cardiologists as a major hub for cardiac care.</t>
+        </is>
+      </c>
+      <c r="E247" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/queensland-cardiovascular-group/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="16" t="inlineStr">
+        <is>
+          <t>RICADO (Te Puke, Bay of Plenty, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B248" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C248" s="17" t="inlineStr"/>
+      <c r="D248" s="17" t="inlineStr"/>
+      <c r="E248" s="16" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="16" t="inlineStr">
+        <is>
+          <t>Rail Technology International Pty Ltd (RTI), Lynbrook, Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="B249" s="16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C249" s="17" t="inlineStr"/>
+      <c r="D249" s="17" t="inlineStr"/>
+      <c r="E249" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rail-technology-international/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="16" t="inlineStr">
+        <is>
+          <t>Rauland Healthcare</t>
+        </is>
+      </c>
+      <c r="B250" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C250" s="17" t="inlineStr">
+        <is>
+          <t>Rauland Strengthens Leadership to Drive Growth in Aged Care and Acute Care Markets (09/04/2025)
+Rauland Australia announced leadership changes aimed at supporting growth in aged care and acute care, including the appointment of Jacqueline Leeds as CEO. The move signals continued expansion and strategic focus in its core healthcare markets.
+Aged care provider Apollo Care adopts Rauland's nurse call solutions (18/03/2025)
+Apollo Care selected Rauland to deliver nurse call solutions across three Queensland aged care sites. The deployment reflects continued commercial growth and broader adoption of Rauland's healthcare technology in the aged care sector.
+Rauland Australia &amp; New Zealand profile highlights over 400 healthcare customers (01/01/2025)
+Rauland's company profile notes its established footprint across Australia and New Zealand, with over 400 healthcare customers and operations in major cities. This indicates sustained market expansion and customer growth in digital health technology.
+News &amp; Events - Rauland Australia (01/01/2025)
+Rauland's news page highlights recent leadership strengthening initiatives to drive growth in aged care and acute care markets, reinforcing ongoing business expansion and strategic investment in leadership.</t>
+        </is>
+      </c>
+      <c r="D250" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 1w] Introduction of Concentric Care Unify at ITAC 2026, focusing on integrated care solutions in aged care.
+[11/05/2026 - 1w] Announcement of hiring a Territory Sales Manager to expand the team's footprint in South Australia.
+[06/05/2026 - 2w] Launch announcement for Concentric Care Unify, a new technology aimed at improving aged care services.
+[27/04/2026 - 3w] Showcasing a successful case study where their solution improved efficiency in a leading healthcare institution.</t>
+        </is>
+      </c>
+      <c r="E250" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rauland-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="16" t="inlineStr">
+        <is>
+          <t>Rayven (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B251" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C251" s="17" t="inlineStr">
+        <is>
+          <t>Rayven strengthens position as an all‑in‑one operational software and AI delivery partner (10/09/2024)
+Sydney-based Rayven promoted its evolution into an all‑in‑one platform and services company that builds and supports custom operational software, real‑time data processing, automation and AI solutions. By combining its low‑code platform with implementation and ongoing services, Rayven signalled an expansion of its commercial model and deeper engagement with enterprise customers across multiple industries.
+Rayven expands as a codeless AI + IoT platform for industrial digital transformation (15/03/2023)
+Rayven, headquartered on Carrington Street in Sydney, continued to grow as a codeless AI and IoT platform provider for industrial and commercial customers. With a focus on rapid deployment and real-time monitoring, control, and predictive analytics, the company reported expanding adoption of its platform and services for Industry 4.0 use cases, highlighting revenue under $5 million and a growing specialist team.
+Rayven launches I4 Mining to accelerate digital transformation in the resources sector (28/10/2021)
+Sydney-based AI and IoT platform Rayven announced the launch of I4 Mining, a suite of interoperable digital mining solutions aimed at helping mining companies rapidly adopt Industry 4.0 technologies. The offering supports real-time monitoring, optimisation and sustainability outcomes (zero-harm, zero-carbon, zero-waste), expanding Rayven’s product portfolio and positioning it more deeply in the resources vertical.
+Rayven releases AI Dynamix, a no‑code predictive analytics engine for IoT and Industry 4.0 (20/04/2020)
+Rayven, the Sydney-based real-time AI and IoT platform, released AI Dynamix, a drag‑and‑drop predictive analytics engine that enables non‑technical users to build AI‑driven, real-time IoT and Industry 4.0 solutions without coding. The launch broadens Rayven’s capabilities, making its platform more accessible and strengthening its competitive position in industrial AI and analytics.</t>
+        </is>
+      </c>
+      <c r="D251" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaborative effort with Serena Williams and Reckitt focusing on networking for business success.
+[27/04/2026 - 3w] LinkedIn recognized as the top domain for professional queries, indicating market leadership.
+[22/04/2026 - 4w] Announces new leadership roles at LinkedIn, indicating organizational growth.</t>
+        </is>
+      </c>
+      <c r="E251" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="16" t="inlineStr">
+        <is>
+          <t>Real Time Traffic</t>
+        </is>
+      </c>
+      <c r="B252" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C252" s="17" t="inlineStr">
+        <is>
+          <t>Real time traffic information in Melbourne | RACV (01/01/2025)
+RACV’s Melbourne traffic information page highlights real-time traffic conditions, road closures, incidents, major road projects, and public transport updates across Melbourne and Victoria. While not a direct company news article, it indicates ongoing service coverage and operational relevance for real-time traffic information in the city.
+Getting around the city | City of Melbourne (01/01/2025)
+The City of Melbourne’s transport page provides up-to-date information on road closures and disruptions in Melbourne’s CBD and neighbourhoods. This reflects active, ongoing traffic-information services in the city, though it is not a company-specific growth announcement.
+Melbourne traffic and alerts | Linkt (01/01/2025)
+Linkt’s Melbourne traffic page presents live traffic conditions and real-time alerts across the toll road network in Melbourne. It shows continued service delivery in the traffic-information space, but does not identify a growth event for a company named Real Time Traffic.</t>
+        </is>
+      </c>
+      <c r="D252" s="17" t="inlineStr"/>
+      <c r="E252" s="16" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="16" t="inlineStr">
+        <is>
+          <t>Recludo</t>
+        </is>
+      </c>
+      <c r="B253" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C253" s="17" t="inlineStr">
+        <is>
+          <t>Recludo strengthens growth strategy through Thry acquisition (12/05/2026)
+Recludo acquired mortgage management business Thry Group as part of its broader strategy to expand its broker-led platform. The deal adds to its national footprint and supports continued growth through acquisitions and partnerships.
+Recludo buys stake in My Expert to grow mortgage network (29/04/2026)
+Recludo agreed to buy a 51% stake in My Expert, adding another mortgage and advice business to its expanding network. The arrangement includes strategic and operational support to help scale the business.
+Recludo deepens national broker push with My Expert deal (29/04/2026)
+Recludo took a majority stake in a Victorian financial services business, strengthening its national growth plans. The move is part of its wider strategy to build a larger broker-led platform across Australia.
+Mortgage broking investment firm Recludo gunning for IPO (27/04/2026)
+Recludo reported ambitions to acquire up to 50 businesses and said an IPO could provide additional capital to deploy across the market. The article highlights its aggressive growth strategy and expanding deal pipeline.
+Recludo takes majority stake in Astar Financial to turbocharge broker growth (23/04/2026)
+Recludo acquired a 51% stake in Astar Financial, lifting its combined loan book to around $3 billion. The transaction supports founder-led broker growth through shared services and operational backing.</t>
+        </is>
+      </c>
+      <c r="D253" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces collaboration with Serena Williams and Reckitt to leverage networks for opportunity.
+[27/04/2026 - 3w] LinkedIn becomes the #1 cited domain for professional queries on major AI search engines.
+[22/04/2026 - 4w] Congratulates new CEO Daniel Shapero and President Mohak Shroff, indicating leadership changes.</t>
+        </is>
+      </c>
+      <c r="E253" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="16" t="inlineStr">
+        <is>
+          <t>Redenlab</t>
+        </is>
+      </c>
+      <c r="B254" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C254" s="17" t="inlineStr">
+        <is>
+          <t>Redenlab awarded $2.5M to scale AI-driven speech biomarkers for dementia detection (20/05/2026)
+Redenlab announced it received $2.5 million in non-dilutive funding through the CUREator+ Dementia &amp; Cognitive Decline incubator program. The funding will support further development and scaling of its LLM-powered speech-biomarker platform for early detection and monitoring of cognitive decline.</t>
+        </is>
+      </c>
+      <c r="D254" s="17" t="inlineStr">
+        <is>
+          <t>[13/05/2026 - 1w] Redenlab is conducting a study in partnership with SynaptixBio Ltd. and MCRI on speech as a clinical marker for neurodegenerative diseases.
+[12/05/2026 - 1w] Partnership on a global speech study in H-ABC involving Redenlab, SynaptixBio Ltd., and MCRI, aimed at assessing speech as a clinical indicator.
+[24/04/2026 - 3w] Highlighting the partnership with SynaptixBio Ltd. and MCRI to advance the research on speech analytics in clinical trials.</t>
+        </is>
+      </c>
+      <c r="E254" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redenlab/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="16" t="inlineStr">
+        <is>
+          <t>Referoo</t>
+        </is>
+      </c>
+      <c r="B255" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C255" s="17" t="inlineStr">
+        <is>
+          <t>Referoo launches Referoo Hub, an all‑in‑one employment‑checking solution (15/11/2024)
+Referoo, the Sydney‑headquartered reference, ID and background‑checking provider, announced the launch of Referoo Hub, an all‑in‑one employment‑checking platform designed to streamline recruitment workflows. The new hub brings together reference checks, identity verification and background screening in a single, configurable solution, positioning Referoo as a broader employment‑checking ecosystem rather than a single‑purpose tool and supporting its continued international expansion.
+RCSA renews 12‑month partnership with Referoo (10/05/2024)
+The Recruitment, Consulting and Staffing Association (RCSA) confirmed it is continuing its partnership with Referoo for a further 12 months. The renewal reinforces Referoo’s position as a preferred online reference‑checking provider for the recruitment and staffing industry across Australia and New Zealand, expanding its exposure to RCSA’s member network and supporting ongoing growth in usage and market reach.
+Referoo grows into a global leader with offices in Sydney and London (01/10/2023)
+Referoo reports that it has evolved from an Australian reference‑checking start‑up into a global leader in reference, ID and background checking. The company now supports users worldwide from offices in Sydney and London, highlighting sustained international expansion, a growing customer base and increasing demand for its customisable HR technology solutions.
+Referoo develops Healthref, an express reference checking tool for health and aged‑care sectors (15/04/2020)
+Referoo released Healthref, an express online reference‑checking tool tailored to health and aged‑care employers who need to hire quickly while maintaining compliance. The product launch, supported by a free 21‑day trial, expanded Referoo’s offering into a critical vertical and drove additional adoption among health and aged‑care providers during a period of heightened demand.</t>
+        </is>
+      </c>
+      <c r="D255" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] The company partnered with Serena Williams and Reckitt to demonstrate the value of networking for underrepresented founders.
+[27/04/2026 - 3w] Announcement of LinkedIn becoming the most-cited domain for professional queries in AI search engines, showcasing market expansion.
+[22/04/2026 - 4w] Announcement of new leadership roles at LinkedIn, indicating company growth and opportunity ahead.</t>
+        </is>
+      </c>
+      <c r="E255" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="16" t="inlineStr">
+        <is>
+          <t>Rely (Melbourne, online &amp; digital media)</t>
+        </is>
+      </c>
+      <c r="B256" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C256" s="17" t="inlineStr"/>
+      <c r="D256" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to empower underrepresented founders.
+[27/04/2026 - 3w] Celebrating LinkedIn's achievement as the most-cited domain for professional queries.
+[22/04/2026 - 4w] Congratulations to new leadership roles at LinkedIn, indicating organizational growth.</t>
+        </is>
+      </c>
+      <c r="E256" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="16" t="inlineStr">
+        <is>
+          <t>Rental Car Manager</t>
+        </is>
+      </c>
+      <c r="B257" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C257" s="17" t="inlineStr">
+        <is>
+          <t>Jonas Software Acquires Rental Car Manager, Entering Car Rental Management Vertical (22/12/2023)
+Jonas Software announced the acquisition of Brisbane-based Rental Car Manager, a SaaS provider of mission‑critical car rental management software used in 39 countries. The deal marks Jonas Software’s first move into the car rental management vertical and expands its footprint in the travel and tourism sector. Rental Car Manager’s platform includes booking management, website integration, contactless and self‑service pickup/drop‑off via smart car technology, automations, agent integration, and fleet management—positioning the business for further international scale under Jonas’s ownership.
+Rental Car Manager Announces Acquisition by Jonas Software (22/12/2023)
+Rental Car Manager publicly confirmed that it has been acquired by Jonas Software, highlighting the transaction as a major milestone in its growth. The company emphasised that joining the Jonas portfolio will support continued product development of its modern cloud-based SaaS solution for booking and managing rental car fleets. With an established global customer base across 39 countries and a focus on contactless rentals, integrations, and automation, the acquisition is expected to accelerate Rental Car Manager’s innovation and market expansion.</t>
+        </is>
+      </c>
+      <c r="D257" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] The post highlights a partnership with Serena Williams and Reckitt, focusing on leveraging networks for business success.
+[27/04/2026 - 3w] Highlights LinkedIn's growth in being the most-cited domain for professional queries, indicating market expansion.
+[22/04/2026 - 4w] Announcing new leadership roles at LinkedIn which emphasizes internal growth and opportunity.</t>
+        </is>
+      </c>
+      <c r="E257" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="16" t="inlineStr">
+        <is>
+          <t>Renteca</t>
+        </is>
+      </c>
+      <c r="B258" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C258" s="17" t="inlineStr">
+        <is>
+          <t>Brisbane Welder Repairs rebrands as Renteca and expands product line with advanced multi‑megawatt power technologies (05/12/2022)
+Renteca, formerly Brisbane Welder Repairs, has undertaken a strategic rebrand and broadened its offering beyond welding repairs to a wider range of rental and power solutions. According to the company’s Capability Statement, the rebrand is accompanied by an amplified product line that now includes new technologies such as multi‑megawatt power systems. This signals a growth phase for the Brisbane‑based manufacturer and equipment services firm, positioning it to support larger projects and a more diverse industrial customer base.</t>
+        </is>
+      </c>
+      <c r="D258" s="17" t="inlineStr">
+        <is>
+          <t>[13/05/2026 - 1w] Introduction of the Miller Big Blue 600X and 800X Duo Airpaks with new stainless steel features for enhanced durability.</t>
+        </is>
+      </c>
+      <c r="E258" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/renteca/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="16" t="inlineStr">
+        <is>
+          <t>Reposit Power</t>
+        </is>
+      </c>
+      <c r="B259" s="16" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
+      <c r="C259" s="17" t="inlineStr">
+        <is>
+          <t>Reposit Power positions itself as long‑term Australian smart‑energy technology provider (01/07/2021)
+Reposit Power’s corporate materials emphasise that since beginning its journey in 2012, the company has continued to build and refine its technology in Australia, combining expertise in electricity markets, enterprise software and control theory. The ongoing investment in in‑house R&amp;D and product development signals sustained growth in capabilities and a long‑term commitment to scaling its smart‑home energy offerings.
+Reposit Power grows from Canberra startup to national smart energy player (01/10/2017)
+SBS Small Business Secrets profiled Reposit Power’s rapid growth since its founding in 2013, highlighting its expansion from a tiny Canberra office to a team of 16 employees and hundreds of customers across Australia. The article credits the company’s battery-optimisation software and its ability to let customers store solar energy and sell it back to the grid as key drivers of this growth.
+Reposit Power and ActewAGL run large‑scale Virtual Power Plant trial in the ACT (20/10/2016)
+In partnership with ActewAGL Distribution, Reposit Power led a Virtual Power Plant (VPP) trial in the ACT where household batteries fed stored solar energy into the grid for the first time as a coordinated resource. Participants with Reposit‑enabled batteries earned premium GridCredits of $1 per kWh—far above standard solar feed‑in tariffs—demonstrating the commercial potential of Reposit’s software and strengthening its utility partnerships.
+Canberra homes earn record feed‑in tariffs through Reposit Power virtual battery program (18/10/2016)
+A large virtual battery trial run by ActewAGL Distribution and Reposit Power enabled more than 250 Canberra households with solar and storage to participate in the National Electricity Market, earning $1.00 per kWh for energy discharged via Reposit’s GridCredits scheme. The one‑megawatt virtual battery project showcased Reposit’s technology at scale and highlighted growing market uptake of its platform.
+ARENA funds Reposit Power’s ‘Intelligent Storage for Australia’s Grid’ project (23/06/2014)
+The Australian Renewable Energy Agency (ARENA) announced $445,000 in funding for Reposit Power to pilot its GridCredits system, a smart control module for storage batteries that enables households to monitor electricity usage, access stored solar at peak times and trade energy with the grid. The project positions Reposit as a key innovator in grid‑interactive storage and supports commercial development of its technology.</t>
+        </is>
+      </c>
+      <c r="D259" s="17" t="inlineStr"/>
+      <c r="E259" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/repositpower/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="16" t="inlineStr">
+        <is>
+          <t>Respirico Healthcare</t>
+        </is>
+      </c>
+      <c r="B260" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C260" s="17" t="inlineStr">
+        <is>
+          <t>Disability Aids Adelaide | Respirico Healthcare (01/05/2024)
+Respirico Healthcare presents itself as a local Adelaide-based disability aids specialist, highlighting its status as a TGA and NDIS-approved supplier and emphasizing its commitment to meeting customer needs across the region. This indicates ongoing local business presence and market reach in Adelaide.
+News - Respirico (01/05/2024)
+Respirico’s news page highlights mobility and respiratory support offerings, including oxygen solutions for people with respiratory conditions. The page suggests active product and service development aimed at supporting customers on the move, consistent with business growth in its core healthcare equipment market.</t>
+        </is>
+      </c>
+      <c r="D260" s="17" t="inlineStr">
+        <is>
+          <t>[21/05/2026 - today] Respirico Kilkenny introduces 'The Fitting Room', a unique service for customized mobility equipment modifications, filling a market gap.
+[22/04/2026 - 4w] Respirico Healthcare welcomes Frank Quattrocchi to the team, emphasizing his experience and positive reception in the industry.</t>
+        </is>
+      </c>
+      <c r="E260" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/respirico/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="16" t="inlineStr">
+        <is>
+          <t>Revex (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B261" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C261" s="17" t="inlineStr"/>
+      <c r="D261" s="17" t="inlineStr"/>
+      <c r="E261" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/revex-solutions/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t>Revo Group (2688 Ipswich Rd, Unit A5, Darra, QLD 4076, Australia)</t>
+        </is>
+      </c>
+      <c r="B262" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C262" s="17" t="inlineStr"/>
+      <c r="D262" s="17" t="inlineStr"/>
+      <c r="E262" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/revogroupltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="16" t="inlineStr">
+        <is>
+          <t>Rinstrum Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B263" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C263" s="17" t="inlineStr">
+        <is>
+          <t>Rinstrum executive chair appointed chair of Manufacturing Skills Queensland board (01/11/2023)
+Manufacturing Skills Queensland announced the appointment of Paul Cooper, Owner and Executive Chair of Rinstrum, as Chair of the MSQ board. His selection to lead a state‑level manufacturing skills body reflects the recognised strength and maturity of Rinstrum’s manufacturing operations and leadership, reinforcing the company’s industry standing and influence within Queensland’s advanced manufacturing ecosystem.
+Rinstrum continues partnership with University of Queensland for Best Hardware Solution at EECS Innovation Showcase 2023 (01/06/2023)
+Rinstrum extended its collaboration with the University of Queensland by again sponsoring and partnering on the Best Hardware Solution award at the 2023 EECS Innovation Showcase. The ongoing partnership demonstrates the company’s investment in innovation pipelines, talent development and academic‑industry collaboration to support future hardware and electronics advances aligned with its weighing and measurement technologies.
+Rinstrum celebrates 30 years as a leading weighing solutions provider (09/06/2022)
+Rinstrum marked its 30th anniversary on 9 June 2022, highlighting three decades of growth as a leading weighing solutions provider in industrial electronics. The milestone underscores the company’s sustained expansion from a local Queensland manufacturer to an exporter with a global customer base, reflecting long‑term financial stability, product innovation and market penetration in weighing indicators, accessories and load cells.
+Rinstrum owner and executive chair leads Advanced Manufacturing Growth Centre (01/07/2021)
+The Advanced Manufacturing Growth Centre notes that Paul Cooper, Owner and Executive Chair of Rinstrum, also serves as Chairman of AMGC. Rinstrum is described as an industrial electronics manufacturing company based in Brisbane that actively exports to global markets with subsidiaries in the United States, Germany, India and Sri Lanka. This profile highlights Rinstrum’s international expansion, export performance and multi‑country subsidiary network as indicators of sustained growth and manufacturing capability.</t>
+        </is>
+      </c>
+      <c r="D263" s="17" t="inlineStr">
+        <is>
+          <t>[08/05/2026 - 1w] Rinstrum is hiring a Design Engineer in Negombo, Sri Lanka, indicating team growth and expansion in engineering capabilities.
+[08/05/2026 - 1w] Rinstrum is hiring an Engineering Assistant in Negombo, Sri Lanka, showing growth through recruitment to support their operations.</t>
+        </is>
+      </c>
+      <c r="E263" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rinstrum/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="16" t="inlineStr">
+        <is>
+          <t>Risk Mentor</t>
+        </is>
+      </c>
+      <c r="B264" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C264" s="17" t="inlineStr">
+        <is>
+          <t>Risk Mentor positions itself as an intelligence-led growth partner for leaders (01/01/2026)
+Risk Mentor highlights its focus on turning data into actionable intelligence and delivering real-time insights to help leaders optimise performance and drive growth. The company also lists offices in Brisbane, Newcastle, Canberra, and New Zealand, indicating a broader geographic footprint beyond Brisbane.</t>
+        </is>
+      </c>
+      <c r="D264" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a collaboration between LinkedIn, Serena Williams, and Reckitt to leverage networks for success.
+[27/04/2026 - 3w] Announces LinkedIn's status as the top domain for professional queries, indicating position in AI market.
+[22/04/2026 - 4w] Congratulates new leaders at LinkedIn, indicating leadership change which can signal growth opportunities.</t>
+        </is>
+      </c>
+      <c r="E264" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="16" t="inlineStr">
+        <is>
+          <t>RiskTalk</t>
+        </is>
+      </c>
+      <c r="B265" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C265" s="17" t="inlineStr">
+        <is>
+          <t>RiskTalk Features on Safety Justice League Podcast (21/05/2026)
+RiskTalk co-founders Stuart and David were featured on the Safety Justice League podcast, discussing the origins of the company. This kind of media appearance can signal brand visibility and ongoing growth in the online/digital media space.</t>
+        </is>
+      </c>
+      <c r="D265" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Partnership with Serena Williams and Reckitt to leverage networks.
+[27/04/2026 - 3w] Recognition of LinkedIn as a top-cited domain, showcasing its growth in value and influence in AI.
+[22/04/2026 - 4w] Announcement of new CEO and president appointments, highlighting growth opportunities for LinkedIn.</t>
+        </is>
+      </c>
+      <c r="E265" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="16" t="inlineStr">
+        <is>
+          <t>Rockfield Technologies Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B266" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C266" s="17" t="inlineStr">
+        <is>
+          <t>Rockfield recognised for innovation in digital engineering and asset management (15/11/2023)
+Rockfield Technologies Australia, headquartered in Townsville, Queensland, was highlighted in industry coverage for its leading role in advanced computational modelling and IoT/Big Data–driven ‘augmented engineering’ solutions. The recognition emphasised the firm’s strong growth in mining, rail, energy and public infrastructure projects across Australia, noting that its digital engineering capabilities are helping clients optimise asset performance and safety. The coverage positions Rockfield as an innovation leader, signalling healthy demand and reputation-led growth in its core design and engineering services.
+Rockfield expands multidisciplinary engineering and advisory services footprint across Australia (01/08/2023)
+Rockfield Technologies Australia reported an expanded presence across key Australian sectors, including mining, rail, energy and public infrastructure. By broadening its multidisciplinary engineering and advisory offerings and promoting its augmented engineering toolkit, the company is positioning itself for continued growth in infrastructure and technology asset management. This expansion reflects increased project activity and deeper penetration into national markets from its Queensland headquarters.
+Rockfield strengthens position as market leader in infrastructure and technology asset management (10/03/2022)
+In updated corporate materials, Rockfield Technologies Australia described itself as a market leader in infrastructure and technology asset management after more than two decades in operation. The company highlighted its success in equipping clients with advanced engineering technology and data-driven tools to maximise and maintain critical assets. The positioning reflects sustained business growth, long-term client relationships and a strengthening leadership role within its niche in digital design and asset integrity services.</t>
+        </is>
+      </c>
+      <c r="D266" s="17" t="inlineStr">
+        <is>
+          <t>[22/04/2026 - 4w] Rockfield is co-exhibiting at a major conference and discussing innovative assessment methods for infrastructure, showcasing their commitment to innovation and collaboration.</t>
+        </is>
+      </c>
+      <c r="E266" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rockfield-technologies-australia-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="16" t="inlineStr">
+        <is>
+          <t>Rocks Gone Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B267" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C267" s="17" t="inlineStr">
+        <is>
+          <t>Rocks Gone’s Reefinator H4 opens new markets as a ‘rocky ground terminator’ for growers (20/03/2024)
+Coverage in agricultural industry media reports that Rocks Gone is driving further commercial growth with its Reefinator H4 machine. Invented by founder Tim Pannell and produced at the Kewdale facility, the H4 is promoted as a high‑efficiency, multi‑pass rock‑crushing solution that opens up previously unusable rocky ground to pasture and cropping. The article notes growing demand from growers in Western Australia, South Australia and Victoria, indicating expanding sales channels and market penetration for Rocks Gone’s equipment.
+Rocks Gone builds on growth strategy with sustainability‑focused machinery for mining and agriculture (15/02/2023)
+A follow‑up company insight in Mine Australia describes Rocks Gone’s ongoing growth as it designs and manufactures industry‑leading rock‑crushing machinery aimed at improving customers’ productivity and land sustainability. Operating from its Kewdale headquarters, the company is portrayed as expanding its customer base in agriculture, mining and civil construction by offering on‑site crushing solutions and comprehensive service support, reinforcing its position as a growing specialist manufacturer.
+Rocks Gone scales up patented rock‑crushing solutions from agriculture into mining and civil markets (10/01/2023)
+A company insight profile in Mine Australia details how Rocks Gone, a family‑owned Western Australian business based at 5 Baldwin Street, Kewdale, has grown since formalising its operations in 2015. The article highlights expansion of its internationally patented Reefinator technology from agricultural use into mining and civil applications, with all machinery designed, manufactured and serviced in‑house. This vertical integration and entry into new sectors are presented as key drivers of the company’s continuing growth.
+Reefinator a cut above for growth – Rocks Gone wins WA Innovator of the Year ‘Growth’ Award (15/11/2017)
+Rocks Gone, the Western Australian machinery manufacturer behind the rock‑crushing Reefinator, won the Growth category of the WA Innovator of the Year Awards. The recognition highlights the company’s rapid commercial progress with its patented rock‑crushing technology and validates its strategy of in‑house design and manufacture in Kewdale. The award reflects strong demand from agriculture and resources customers and positions Rocks Gone for further expansion.</t>
+        </is>
+      </c>
+      <c r="D267" s="17" t="inlineStr"/>
+      <c r="E267" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rocksgone/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="16" t="inlineStr">
+        <is>
+          <t>RxTro</t>
+        </is>
+      </c>
+      <c r="B268" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C268" s="17" t="inlineStr">
+        <is>
+          <t>RxTro Recognised as Australia’s Leading Healthcare Engagement Platform (15/03/2024)
+RxTro highlights its evolution from a simple GP lunch‑meeting booking idea into what it now describes as Australia’s premier customer engagement platform for healthcare and life sciences. The company’s ‘About’ profile details how it has expanded beyond primary care to serve life sciences, allied health, specialists and broader healthcare stakeholders, underscoring its growth in scale, market positioning and breadth of users.
+RxTro Expands Platform Reach Across Life Sciences, Allied Health and Specialist Sectors (15/03/2024)
+In its corporate overview, RxTro reports that what began as a tool to simplify booking pharmaceutical lunch meetings with GPs has grown into a ‘seamless, intuitive platform’ now serving the wider life sciences industry, allied health, primary care and specialist practices. This reflects a strategic expansion of its customer base and product application beyond its original GP‑focused model.
+RxTro Hosts National Webinar for Pharmaceutical Executives on Evolving Healthcare Dynamics (31/01/2024)
+Pharma industry outlet Pharma In Focus reports that RxTro hosted the webinar ‘Adapting to the evolving healthcare dynamics for pharmaceutical executives’, bringing together industry leaders to address changing engagement models with GPs and other healthcare professionals. Acting as convener for a national‑level executive webinar underscores RxTro’s growing influence and thought‑leadership role in the pharmaceutical engagement and digital healthcare communication space.
+RxTro Builds Network of IT, Data, Charity and Industry Collaborations to Strengthen Healthcare Engagement Platform (10/11/2023)
+RxTro’s partner page outlines a broadening network of IT, data, charity and industry partners aligned to its mission of improving healthcare engagement across Australia. These collaborations suggest sustained business development activity, ecosystem integration and strategic partnerships that support further scaling of RxTro’s digital media and engagement capabilities.
+RxTro Supports Fast‑Tracking of New Digital Engagement Models as Pharmas Halt Face‑to‑Face Rep Visits (18/03/2020)
+As major pharmaceutical companies suspended face‑to‑face sales visits during the early COVID‑19 period, industry coverage noted that RxTro’s booking system was already handling about 250,000 GP appointments for roughly 13,000 GPs in large practices. This volume demonstrates significant platform adoption and positioned RxTro as a key digital infrastructure provider for pharma–GP engagement as the sector rapidly shifted to virtual and digitally coordinated meetings.</t>
+        </is>
+      </c>
+      <c r="D268" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to support underrepresented founders, showing partnership and mentoring.
+[27/04/2026 - 3w] Recognition of LinkedIn's position in AI search engines, showcasing growth in visibility and influence.
+[22/04/2026 - 4w] Announcement of new leadership roles at LinkedIn, indicating internal growth and potential future direction.</t>
+        </is>
+      </c>
+      <c r="E268" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="16" t="inlineStr">
+        <is>
+          <t>Sabre Medical</t>
+        </is>
+      </c>
+      <c r="B269" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C269" s="17" t="inlineStr">
+        <is>
+          <t>Sabre Medical highlights strong year of supporting new medtech ventures and scale‑ups (20/12/2025)
+Sabre Medical’s news update summarised an ‘incredible year’, noting that as 2025 drew to a close the company had continued to support new medtech companies and larger healthcare organisations with locally designed, assembled and manufactured medical devices. The update underscored growth in demand for its cleanroom assembly, packaging validation and regulatory support services, reinforcing the firm’s role in scaling medical device production in Australia.
+Sabre Medical reinforces position as Australia’s integrated medical device manufacturing hub (10/12/2025)
+In a year‑end update, Sabre Medical reported continued growth as an Australian medical device manufacturing hub, supporting an increasing number of medtech startups and scale‑ups. Operating from its Lane Cove facility with four ISO Class 7 &amp; 8 cleanrooms (200 m²) and advanced thermoforming technology, including the Asia‑Pacific’s only Rapid Small Run Tray Forming System, the company emphasised its expanded capabilities in product development, packaging design, sterilisation validation and regulatory support.
+Sabre Medical marks 20-year milestone and showcases expanded manufacturing capabilities with Cochlear (15/03/2025)
+Sabre Medical celebrated its 20-year anniversary with key customer Cochlear, highlighting its evolution from a niche medical device packaging provider to a mature manufacturing partner with in‑house designers, engineers and scientists. The company now operates advanced equipment including 3D printers, thermoformers and sterilisers, signalling significant growth in its end‑to‑end medical device packaging and manufacturing capabilities.</t>
+        </is>
+      </c>
+      <c r="D269" s="17" t="inlineStr">
+        <is>
+          <t>[18/05/2026 - 3d] The post highlights the employee of the month, introductions of new roles, and successful internship program applicants, indicating team expansion.
+[27/04/2026 - 3w] Announcement of overwhelming responses for the internship program suggests increased interest and engagement, signifying growth potential.
+[24/04/2026 - 3w] The company hosted students for a tour and highlighted its internship program, indicating team growth and community involvement.</t>
+        </is>
+      </c>
+      <c r="E269" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sabre-medical/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="16" t="inlineStr">
+        <is>
+          <t>Safe Ag Systems</t>
+        </is>
+      </c>
+      <c r="B270" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C270" s="17" t="inlineStr">
+        <is>
+          <t>Safe Ag Systems Reaches $2.8M ARR With 1,000 Customers (17/10/2024)
+Safe Ag Systems, the Adelaide-based agricultural safety and compliance software provider, grew its annual recurring revenue to $2.8M in 2024, up from $1.8M in 2023. The company reports around 1,000 customers and 21 employees, reflecting strong commercial traction and continued adoption of its WHS management platform across agribusinesses.
+Digital Marketing Drives International Expansion for Safe Ag Systems (15/03/2023)
+Safe Ag Systems used a structured digital marketing strategy to generate a high volume of qualified leads in Australia at an optimal cost, enabling it to systemise its marketing and support expansion into new regions. The case study highlights how targeted online campaigns and lead nurturing have underpinned the company’s international growth beyond its South Australian base.
+Safe Ag Systems Farm Safety Platform Launches in the United States (10/06/2021)
+Australia’s leading farm safety software, Safe Ag Systems, announced its safety management platform is now available to growers, farmers and ranchers across the United States. The cloud-based system, originally launched as a startup in 2016, now operates in five countries—Australia, New Zealand, the United Kingdom, Canada and the US—marking significant international expansion for the Adelaide-headquartered company.</t>
+        </is>
+      </c>
+      <c r="D270" s="17" t="inlineStr">
+        <is>
+          <t>[12/05/2026 - 1w] Team expansion to Far North Queensland indicates business growth and market reach.
+[08/05/2026 - 1w] The post mentions over 11,000 users leveraging Safe Ag Systems, indicating market acceptance and potential expansion.
+[22/04/2026 - 4w] Announcement of upcoming presentations indicates market expansion and outreach.</t>
+        </is>
+      </c>
+      <c r="E270" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/safe-ag-systems/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="16" t="inlineStr">
+        <is>
+          <t>Safe365 (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B271" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C271" s="17" t="inlineStr">
+        <is>
+          <t>Leadership lapses undermine workplace safety in New Zealand – Safe365 Safety Culture Maturity Report 2024 (08/02/2024)
+Insurance Business New Zealand reported on the Safe365 Safety Culture Maturity Report 2024, produced by Safe365’s health and safety technology platform. The report positions Safe365 as a national thought leader with sufficient data coverage to benchmark director and manager performance across New Zealand, reflecting growth in client numbers, data utilisation, and influence in the workplace safety market.
+Introducing Safe365 – Advanced Safety partnership to revolutionise workplace safety (14/06/2023)
+Advanced Safety announced its partnership with Safe365, describing Safe365 as a smart, cloud‑based health and safety platform that enables delivery of cutting‑edge safety solutions across New Zealand. The collaboration allows Advanced Safety to embed Safe365 into its consulting offerings, signalling channel expansion and increased distribution of Safe365’s platform through specialist partners.
+Health and safety simplified: Safe365 provides a 360-degree view of performance (29/05/2023)
+Microsoft profiled Safe365 as a “genuine SaaS product” transforming workplace health and safety by putting a health and safety consultant in the cloud. The article highlights Safe365’s growing role as a key Microsoft SaaS partner, its real‑time data and analytics capabilities, and its increasing adoption by organisations seeking a 360‑degree view of health and safety culture and performance, indicating strong product traction and partnership-led growth.
+Safe365 co‑founder on their success in the UK and the rise of software‑as‑a‑service businesses (07/10/2021)
+In a Newstalk ZB interview, co‑founder Nathan Hight discusses Safe365’s “huge success” in the UK market as part of New Zealand’s fast‑growing SaaS sector. The discussion focuses on the company’s international expansion, growing customer base abroad, and the broader economic contribution of SaaS exporters, underlining Safe365’s revenue and market‑expansion momentum beyond New Zealand.
+Safe365 supports corporate health and safety leadership (10/03/2016)
+Infonews profiled Safe365 as a cloud‑based self‑assessment and continuous improvement tool that is helping a growing number of businesses understand and improve their health and safety performance. The coverage emphasises its uptake among corporates seeking to strengthen safety leadership, indicating early‑stage customer growth and market adoption in New Zealand.</t>
+        </is>
+      </c>
+      <c r="D271" s="17" t="inlineStr"/>
+      <c r="E271" s="16" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="16" t="inlineStr">
+        <is>
+          <t>SafetyIQ (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B272" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C272" s="17" t="inlineStr"/>
+      <c r="D272" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces collaboration with Serena Williams and Reckitt to leverage networks for success, implying growth opportunities.
+[27/04/2026 - 3w] Announces LinkedIn's dominance in AI search engine citations, indicating market growth and relevance.
+[22/04/2026 - 4w] Congratulates new leadership roles at LinkedIn, indicating a potential for growth and opportunity ahead.</t>
+        </is>
+      </c>
+      <c r="E272" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="16" t="inlineStr">
+        <is>
+          <t>SafetySuite</t>
+        </is>
+      </c>
+      <c r="B273" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C273" s="17" t="inlineStr">
+        <is>
+          <t>SafetyCulture valued at $2.5b after $165m capital raise (11/03/2025)
+This result appears to refer to SafetyCulture, the Townsville-founded workplace safety platform, not SafetySuite in Melbourne. It should not be attributed to the requested company.
+SafetySuite - Overview, News &amp; Similar companies | ZoomInfo.com (01/01/2025)
+A directory-style listing that suggests market interest in SafetySuite, but it is not a news article and does not provide a verifiable growth event such as funding, expansion, or partnership.
+Proudly Sponsored by - Melbourne Baseball Club (01/01/2025)
+This page mentions SafetySuite as a sponsor/supporter, but it is not a news article about SafetySuite itself and does not clearly indicate company growth.</t>
+        </is>
+      </c>
+      <c r="D273" s="17" t="inlineStr">
+        <is>
+          <t>[20/05/2026 - 1d] The company announces the hiring of Andrew Feehan as Head of Commercial Partnerships, indicating a strategic expansion of their team to enhance growth through partnerships and customer engagement.</t>
+        </is>
+      </c>
+      <c r="E273" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/safetysuiteglobal/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="16" t="inlineStr">
+        <is>
+          <t>Salestrekker</t>
+        </is>
+      </c>
+      <c r="B274" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C274" s="17" t="inlineStr">
+        <is>
+          <t>Salestrekker 2.0 goes live as the mortgage industry’s first combined lending, origination and CRM platform (02/09/2024)
+After a 2.5‑year development program and more than 80,000 development hours, Salestrekker launched Salestrekker 2.0, positioned as Australia’s first fully combined lending, origination and CRM platform for the mortgage industry. The new release introduces mobile origination, enhanced workflow automation and an enterprise solution for aggregators and subgroups, aiming to help brokers protect and grow their market share in an increasingly competitive lending landscape.
+Salestrekker 2.0 officially live, aiming to change Australia’s lending landscape (02/09/2024)
+Australian Broker reported that Salestrekker 2.0 is now officially live, offering a single platform that combines lending, origination and CRM for mortgage brokers. Founder Dalibor Ivkovic highlighted bank‑grade security, mobile origination capabilities and enterprise features designed for large groups, with the platform intended to drive broker efficiency and support further broker market‑share growth beyond its already high level in the Australian mortgage market.
+Meeting future mortgage broker bottlenecks with Salestrekker 2.0 (20/08/2024)
+The Adviser profiled Salestrekker 2.0 as a solution to emerging bottlenecks for mortgage brokers, including servicing‑calculation accuracy and complex policy research. The article outlines how the upgraded platform introduces smarter tools, better data handling and enhanced automation to support higher loan volumes and regulatory demands, underlining Salestrekker’s ongoing product investment and its growth strategy in the mortgage technology market.
+outsource Financial achieves remarkable growth with Salestrekker (15/06/2023)
+In a PR Newswire release, aggregator outsource Financial reported ‘remarkable growth’ supported by its collaboration with Salestrekker. By leveraging Salestrekker’s platform to manage a growing broker network and respond to competition from fintech lenders, outsource Financial improved scalability, compliance and broker responsiveness, highlighting Salestrekker’s expanding footprint and influence among large mortgage broking groups.
+Raise Finance ramps up leads, marketing and growth using Salestrekker and WebloanQ (01/03/2023)
+LoanQ reported that broker firm Raise Finance achieved significant operational and business growth after moving to Salestrekker and WebloanQ. The integrated use of Salestrekker’s CRM to organise, automate and track the customer journey, combined with WebloanQ, shaved hundreds of hours off annual processing time and increased leads and marketing effectiveness, showcasing Salestrekker’s role in driving client growth and productivity.</t>
+        </is>
+      </c>
+      <c r="D274" s="17" t="inlineStr">
+        <is>
+          <t>[21/05/2026 - today] Salestrekker's involvement as a Gold Sponsor at NFBD, emphasizing their focus on brokers and recent product launch.
+[20/05/2026 - 1d] Success story highlighting the effectiveness of Salestrekker 2.0 in enhancing broker team performance.
+[19/05/2026 - 2d] Statistics from a recent webinar showing how brokers are adopting AI, emphasizing market shift.
+[12/05/2026 - 1w] Announcement of new features and improvements in the May release notes of Salestrekker 2.0.
+[06/05/2026 - 2w] Announcement of 57 updates in Salestrekker 2.0 aimed at enhancing user experience and productivity.
+[05/05/2026 - 2w] Number highlighting brokers' perception of AI as essential, indicative of industry shift.
+[01/05/2026 - 2w] Results of a broker poll indicating strong adoption and reliance on AI tools.
+[30/04/2026 - 3w] Reflection on the values behind Salestrekker and its participation at NFBD, highlighting product transformation.
+[30/04/2026 - 3w] Testimonial from Premium Broker indicating positive impacts from Salestrekker 2.0 training and usage.
+[29/04/2026 - 3w] Insights from a webinar showing significant broker engagement with AI tools.</t>
+        </is>
+      </c>
+      <c r="E274" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/salestrekker/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="16" t="inlineStr">
+        <is>
+          <t>Sandwai</t>
+        </is>
+      </c>
+      <c r="B275" s="16" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C275" s="17" t="inlineStr">
+        <is>
+          <t>Sandwai’s Providers See Growth of up to 45% Year on Year (15/03/2024)
+Sandwai reported that some home care and disability care providers using its platform have achieved up to 45% year‑on‑year growth. The company attributes this to its focus on task automation, smart workflows, and schedule optimisation, which help providers scale efficiently while maintaining compliance with Australian care regulations.
+Sandwai Recognised as an Award‑Winning Home and Disability Care Software Provider (01/11/2023)
+Sandwai highlights its status as an award‑winning, purpose‑built home care and disability care software platform for Australian providers. The recognition, referenced on its corporate site, reflects industry acknowledgement of the company’s innovation in scheduling, care management and mobile solutions, supporting its reputation and growth in the home healthcare services sector.
+Sandwai Expands Presence by Exhibiting at ITAC (Innovation &amp; Technology Across Care) Conference (20/07/2023)
+Sandwai announced that its team would be exhibiting at the ITAC Conference at Royal Pines Resort on the Gold Coast. By engaging directly with aged care and disability care leaders at a major national technology‑in‑care event, Sandwai is expanding its market presence, fostering partnerships, and promoting its home care software solutions to drive further customer and revenue growth.</t>
+        </is>
+      </c>
+      <c r="D275" s="17" t="inlineStr"/>
+      <c r="E275" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sandwai/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="16" t="inlineStr">
+        <is>
+          <t>netBI (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B276" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C276" s="17" t="inlineStr">
+        <is>
+          <t>Transit Systems appoints former netBI CEO Michael McGee as new Chief Executive Officer (12/12/2022)
+Transit Systems, part of ASX200‑listed Kelsian Group, announced Michael McGee as its new CEO, highlighting his recent role as Chief Executive Officer of netBI, a data software platform and analytics solution for the transport sector. While the article focuses on Transit Systems, it underscores netBI’s position as a cutting‑edge transport analytics provider whose leadership talent is being tapped by a major national operator, indirectly reflecting the company’s maturation and industry recognition in Brisbane’s digital and data sector.</t>
+        </is>
+      </c>
+      <c r="D276" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams shows partnerships that can enhance opportunities for founders and entrepreneurs.
+[24/04/2026 - 3w] Celebration of an individual's achievement but does not indicate overall company growth.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicating growth in company structure.</t>
+        </is>
+      </c>
+      <c r="E276" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="16" t="inlineStr">
+        <is>
+          <t>revolutioniseSPORT</t>
+        </is>
+      </c>
+      <c r="B277" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C277" s="17" t="inlineStr">
+        <is>
+          <t>Hockey Australia and revolutioniseSPORT announce multi-year partnership extension (06/05/2024)
+Hockey Australia and revolutioniseSPORT extended their long‑standing partnership in a new multi‑year deal, reaffirming revolutioniseSPORT as the sport’s core management platform. The extension reflects the platform’s expansion to support more than 300 governing bodies and over 22,000 grassroots clubs, servicing around one‑third of organised sport nationwide and growing markets in New Zealand, Singapore, South Africa and the United States.
+Rely and revolutioniseSPORT form exclusive partnership to strengthen governance and safeguarding in sport (14/03/2024)
+Rely and revolutioniseSPORT announced an exclusive partnership to deliver integrated safeguarding and governance tools to sporting organisations. By combining Rely’s reporting and case‑management capabilities with revolutioniseSPORT’s membership and competition platform, the agreement expands revolutioniseSPORT’s product offering and positions it as a more comprehensive compliance and integrity solution for sports administrators.
+Partnership extended between revolutioniseSPORT and SportWest (28/02/2024)
+revolutioniseSPORT renewed and extended its partnership with SportWest, continuing to support Western Australian sporting organisations in the lead‑up to the 2032 Brisbane Olympics. CEO Alex Mednis highlighted the extension as part of the company’s broader growth strategy to deepen relationships with state sporting bodies and expand its footprint in key regions.
+revolutioniseSPORT continues national expansion as Australia’s most trusted sports management platform (20/11/2023)
+In a company overview, revolutioniseSPORT described itself as Australia’s most trusted sports management platform, supporting more than 300 governing bodies and over 22,000 grassroots clubs and servicing about one‑third of organised sport nationally. The update underscores significant user‑base growth from prior years and ongoing expansion into overseas markets, including New Zealand, Singapore, South Africa and the United States.
+revolutioniseSPORT scales their platform with online payments through partnership with Pin Payments (18/10/2023)
+revolutioniseSPORT partnered with Australian payment provider Pin Payments to streamline online payments, accelerate club onboarding and simplify downstream payment processing. The move supports the platform’s rapid growth to 18,000 sporting clubs and 264 state and national sporting organisations across Australia and internationally, enabling more efficient financial workflows for its expanding customer base.
+revolutioniseSPORT recognised as award‑winning cloud platform supporting thousands of clubs (15/09/2022)
+Industry directory STWS profiled revolutioniseSPORT as an award‑winning, cloud‑based end‑to‑end platform serving 180 governing bodies and 13,000 clubs across Australia, New Zealand, Singapore, South Africa and the Cook Islands. The profile highlighted the company’s evolution from basic club‑management tools to advanced business‑intelligence and data‑analytics services, reflecting both product expansion and international growth.</t>
+        </is>
+      </c>
+      <c r="D277" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams to support underrepresented founders, highlighting the importance of networking.
+[27/04/2026 - 3w] Recognition of LinkedIn's prominence in AI queries, indicating market growth and valuable positioning.
+[22/04/2026 - 4w] Announcement of new leadership roles within LinkedIn, indicating internal promotion and recognition.</t>
+        </is>
+      </c>
+      <c r="E277" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GOWT_mid_low.xlsx
+++ b/GOWT_mid_low.xlsx
@@ -41354,7 +41354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -49445,6 +49445,1858 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="16" t="inlineStr">
+        <is>
+          <t>SRO Technology</t>
+        </is>
+      </c>
+      <c r="B278" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C278" s="17" t="inlineStr">
+        <is>
+          <t>SRO Technology announces acquisition of Ramsey brand and product range (20/03/2024)
+In a corporate news update, SRO Technology confirmed it has acquired the Ramsey brand and bulk‑weighing product line, stating it will reintroduce these respected belt scale and inventory control systems to the market. The acquisition bolsters SRO’s growth strategy in weighing, dynamic weighing and process instrumentation, expanding its offering to bulk materials customers in industries such as mining, agriculture, and processing.
+SRO Technology acquisition sees Ramsey products return to market (18/03/2024)
+SRO Technology signed an acquisition deal to bring the world‑renowned Ramsey bulk‑weighing and inventory control product range back to market. The move enhances SRO’s portfolio of precision weighing and measurement solutions for bulk materials handling across mining, resources, agriculture and related sectors, and positions the company as a key supplier of Ramsey belt scales and associated technologies in Australia and globally.
+Bulk materials specialist SRO Technology continues expansion in regional Queensland with Enwise acquisition (15/09/2022)
+SRO Technology completed the acquisition of Emerald‑based Enwise Electrical and Refrigeration, expanding its regional footprint and strengthening its end‑to‑end solutions for the energy and process industries. The deal adds a central Queensland base to existing Brisbane and Sydney operations and broadens SRO’s capability in electrical, refrigeration and instrumentation services for bulk materials handling customers.</t>
+        </is>
+      </c>
+      <c r="D278" s="17" t="inlineStr">
+        <is>
+          <t>[14/05/2026 - 1w] Announcement of SRO Technology as a Gold Sponsor for the Hunter Valley Mining Expo.
+[29/04/2026 - 3w] Recognition to Ramsey distributors for their partnership and commitment to the product line.
+[23/04/2026 - 4w] Highlighting the best weighing company and their renowned products, indicating market leadership.</t>
+        </is>
+      </c>
+      <c r="E278" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sro-technology/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="16" t="inlineStr">
+        <is>
+          <t>STEM Punks (Brisbane City, Queensland, Australia)</t>
+        </is>
+      </c>
+      <c r="B279" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C279" s="17" t="inlineStr">
+        <is>
+          <t>STEM Punks founder a finalist in tech awards (22/06/2021)
+Moreton Daily reported that STEM Punks co‑founder Fiona Holmstrom was named a finalist in a major technology awards program, recognising her work in ensuring girls have equal opportunities in STEM. The nomination highlights industry recognition of STEM Punks’ impact and brand, signalling positive growth and visibility for the Brisbane-based edtech business.
+STEM Punks expands award‑winning STEM education programs worldwide (01/07/2020)
+STEM Punks announced the development and delivery of award‑winning STEM education programs to students worldwide, offering online and in‑person learning in areas such as robotics, AI, machine learning, and IoT. The company emphasised global reach and educational partnerships between industry and schools, indicating geographic expansion and increased market penetration beyond Brisbane.
+STEM Punks profiled for futuristic robotics and AI programs for school students (15/08/2019)
+A case‑study video profile highlighted how STEM Punks runs programs in robotics, artificial intelligence, machine learning, and IoT to upskill school children for future jobs. The coverage showcased growing demand from schools, a widening program portfolio, and the company’s role in emerging tech education, reflecting product expansion and growing influence in the e‑learning sector.
+STEM Punks recognised in Australian EdTech Directory for innovative 21st‑century skills programs (10/03/2019)
+The Australian EdTech Directory listed STEM Punks Ventures as a provider whose mission is to inspire tomorrow’s innovators and solve real‑world problems through STEM. The profile notes that programs are developed by teachers, engineers, and industry professionals and tailored to different skill levels, indicating a maturing product offering and growing standing within the national edtech ecosystem.</t>
+        </is>
+      </c>
+      <c r="D279" s="17" t="inlineStr">
+        <is>
+          <t>[11/05/2026 - 1w] The post announces a new partnership with Iberdrola Australia, a significant player in the energy sector, emphasizing community engagement and support for STEM education.</t>
+        </is>
+      </c>
+      <c r="E279" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stempunks/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="16" t="inlineStr">
+        <is>
+          <t>SchoolTV (Sydney)</t>
+        </is>
+      </c>
+      <c r="B280" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C280" s="17" t="inlineStr"/>
+      <c r="D280" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Details a new partnership with Serena Williams and Reckitt, focusing on community support for founders indicating collaboration and growth potential.
+[27/04/2026 - 3w] Announces LinkedIn as the #1 most-cited domain for professional queries, indicating market expansion and influence.
+[22/04/2026 - 1mo] Congratulations on Daniel Shapero becoming LinkedIn CEO and Mohak Shroff as President, indicating leadership changes that suggest growth.</t>
+        </is>
+      </c>
+      <c r="E280" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="16" t="inlineStr">
+        <is>
+          <t>Scientific Devices Australia</t>
+        </is>
+      </c>
+      <c r="B281" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C281" s="17" t="inlineStr"/>
+      <c r="D281" s="17" t="inlineStr">
+        <is>
+          <t>[21/05/2026 - 1d] Announces sponsorship of a local sports club to support community engagement, indicating a commitment to partnerships.
+[06/05/2026 - 2w] Introduces a new EMI receiver for conducted emissions testing, indicating a product launch.
+[30/04/2026 - 3w] Announces the SmartTS-PV Inverter Test System, indicating a new product launch.
+[27/04/2026 - 3w] Introduces a new timing module addressing modern technical needs, indicating a product launch.</t>
+        </is>
+      </c>
+      <c r="E281" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scientific-devices-australia-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="16" t="inlineStr">
+        <is>
+          <t>Scope Healthcare (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B282" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C282" s="17" t="inlineStr"/>
+      <c r="D282" s="17" t="inlineStr"/>
+      <c r="E282" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scopehealthcare/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="16" t="inlineStr">
+        <is>
+          <t>Scott Smith Orthodontics</t>
+        </is>
+      </c>
+      <c r="B283" s="16" t="inlineStr">
+        <is>
+          <t>Tasmania</t>
+        </is>
+      </c>
+      <c r="C283" s="17" t="inlineStr">
+        <is>
+          <t>Scott Smith Orthodontics launches dental monitoring for Invisalign patients (01/01/2024)
+Scott Smith Orthodontics highlighted the adoption of dental monitoring technology to help patients track tooth movement remotely during orthodontic treatment. The service reflects an investment in digital care delivery and improved patient convenience.
+Scott Smith Orthodontics expands specialist orthodontic care across Launceston and Ulverstone (01/01/2024)
+The practice states it operates from two Tasmanian locations, serving both Launceston and Ulverstone communities. This demonstrates local expansion and broader service reach within Tasmania.
+Scott Smith Orthodontics introduces flexible payment plans to improve treatment access (01/01/2024)
+The practice advertises interest-free payment plans through DentiCare and treatment pricing from as low as $75 per week for Invisalign or full braces. While not a traditional financial announcement, this indicates service growth and accessibility improvements supporting patient volume.
+Scott Smith Orthodontics founded to deliver community-based specialist care in Tasmania (01/01/2008)
+Dr Scott Smith launched Scott Smith Orthodontics in 2008 with the aim of providing dedicated community-based specialist orthodontic care in Launceston and the northwest coast of Tasmania. The founding marked the establishment of a specialist practice in the region.</t>
+        </is>
+      </c>
+      <c r="D283" s="17" t="inlineStr"/>
+      <c r="E283" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scott-smith-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="16" t="inlineStr">
+        <is>
+          <t>Securelogic Solutions (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B284" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C284" s="17" t="inlineStr">
+        <is>
+          <t>Securelogic Solutions demonstrates revenue traction and valuation growth (01/01/2024)
+Profile data on Securelogic Solutions indicates estimated annual revenue of approximately US$1.28 million and an estimated valuation of US$4.2 million, with a headcount of 11–20 employees. While not a news article in the traditional sense, these figures reflect the company’s established market position, continuing operations, and growth potential in the Melbourne IT services and consulting market.
+Securelogic Solutions reports sustained growth and expanded service capabilities (01/01/2021)
+Securelogic Solutions notes that by 2021 it had enjoyed a period of sustained growth and development since formally launching its managed IT services offering in 2016. This growth enabled the company to deliver stronger solutions and deepen its expertise across a broader range of technologies and the cyber security space, positioning it as a more capable managed IT service provider to its expanding client base.
+Securelogic Solutions builds and grows Melbourne-based team of support engineers (01/01/2016)
+Following its official launch in 2016, Securelogic Solutions committed to scaling the business by building a strong team of support engineers in Melbourne. This hiring and team-building focus was aimed at servicing a growing base of clients and supporting the company’s strategy to drive the business forward as a managed IT service provider.</t>
+        </is>
+      </c>
+      <c r="D284" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announcement of partnerships with Serena Williams to empower underrepresented founders, indicating a strategic collaboration.
+[27/04/2026 - 3w] Announcement of LinkedIn as the most-cited domain in AI search engines, indicating market expansion and recognition.
+[22/04/2026 - 1mo] Celebration of new leadership roles within LinkedIn, indicating team growth and strategic direction.</t>
+        </is>
+      </c>
+      <c r="E284" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="16" t="inlineStr">
+        <is>
+          <t>Seekom (Wellington, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B285" s="16" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="C285" s="17" t="inlineStr">
+        <is>
+          <t>Seekom helps accommodation provider scale from 1 to 85 holiday houses (01/06/2017)
+In a customer case study highlighted on Seekom’s news/blog section, an accommodation operator reported that using Seekom’s property management system enabled them to scale their holiday house portfolio from a single property to 85. The client noted that Seekom was able to cope with the rapid increase in business volume, indicating Seekom’s platform was supporting substantial customer and product-driven growth.
+Seekom customers report significant growth using its online distribution service (01/03/2016)
+A Seekom news/blog article from its Wellington office describes that, across a range of accommodation providers, the company has observed “significant growth” in bookings and business performance when using Seekom’s online distribution and channel management services. This suggests Seekom’s technology has been contributing to increased transaction volumes and revenue growth for its user base, reinforcing the company’s market traction.
+Grow Wellington support helps Seekom secure development subsidy for rapid growth plans (01/09/2010)
+Economic development agency Grow Wellington cites Seekom as an example of a Wellington company pursuing rapid growth. According to the agency, Seekom received assistance that was instrumental in securing a development subsidy, aimed at supporting the company’s expansion and product development. This indicates external validation of Seekom’s growth trajectory and plans to scale its operations from Wellington.</t>
+        </is>
+      </c>
+      <c r="D285" s="17" t="inlineStr"/>
+      <c r="E285" s="16" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="16" t="inlineStr">
+        <is>
+          <t>Sensor Dynamics Pty Ltd (9 Redland Drive, Mitcham, VIC 3132, Australia)</t>
+        </is>
+      </c>
+      <c r="B286" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C286" s="17" t="inlineStr">
+        <is>
+          <t>Sensor Dynamics positions Traffic AI platform to support infrastructure planning and road network management across Australia (28/02/2024)
+Sensor Dynamics published an in‑depth article detailing how its Traffic AI platform is being adopted for highways, arterial roads, freight routes, and controlled‑access corridors. The platform delivers continuous, AI‑powered vehicle monitoring, classification, and predictive analytics, enabling transport authorities and planners to base upgrades and long‑term investments on verified traffic demand. The emphasis on scalability and use across multiple road types indicates an expansion of Sensor Dynamics’ analytics offering from point solutions toward a broader, platform‑style product used in infrastructure planning projects nationwide.
+Sensor Dynamics highlights growth in AI‑supported traffic monitoring for road maintenance in metropolitan Melbourne (15/11/2023)
+In a feature on modern traffic monitoring, Sensor Dynamics described how its real‑time, AI‑enabled camera and sensor systems are being used to support proactive road maintenance and asset management, particularly as Melbourne’s traffic volumes increase. The article explains how continuous data on volumes, classifications, speeds, and directional flows is now informing maintenance priorities, reducing emergency repairs, and extending asset life. The focus on metropolitan Melbourne and heavy‑vehicle analysis suggests Sensor Dynamics is winning work with local authorities and asset owners, reflecting growing deployment of its analytics solutions in its home market.
+Sensor Dynamics reinforces position as an industry leader in ANPR and vehicle identification systems (01/08/2023)
+Sensor Dynamics updated its corporate materials to underline that it has become an industry leader in integrated licence plate recognition (ANPR) and vehicle identification solutions across Australia, the UK and New Zealand. The company emphasises over 30 years of experience, growth in tailored LPR and vehicle‑classification systems for parking, traffic, and security, and a strong engineering team delivering custom machine‑vision solutions. The statement that it provides "world class vehicle management solutions" to multiple countries signals sustained international revenue and a mature customer base beyond its original Australian footprint.
+Sensor Dynamics expands custom AI and machine‑vision engineering services for vehicle applications (10/05/2022)
+Through its Custom Solutions division, Sensor Dynamics promoted expanded engineering services focused on machine‑vision applications involving vehicles. The company offers bespoke system design, integration, and analytics tailored to unique traffic, parking, and security challenges, positioning itself as a partner for complex, data‑driven projects rather than only an off‑the‑shelf supplier. This focus on custom AI‑centric solutions indicates investment in specialist engineering capability and a strategy to move up the value chain into higher‑margin, project‑based work.</t>
+        </is>
+      </c>
+      <c r="D286" s="17" t="inlineStr"/>
+      <c r="E286" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sensor-dynamics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="16" t="inlineStr">
+        <is>
+          <t>Silentium Defence</t>
+        </is>
+      </c>
+      <c r="B287" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C287" s="17" t="inlineStr">
+        <is>
+          <t>Ex-AUKUS Program Leader Joins Silentium Defence to Drive APAC Growth (01/05/2026)
+Silentium Defence appointed Berni White as Head of Future Business, APAC, adding experienced leadership to support regional expansion in passive radar and advanced situational awareness technologies.
+Local projects backed by $2 million national funding boost (01/06/2025)
+Silentium Defence received $75,332 through the Defence Industry Development Grants Program to enhance physical security and data access systems to meet Defence security standards, supporting operational growth and compliance.
+Silentium Defence recognised in South Australian iAwards (01/08/2024)
+Silentium Defence received South Australian iAwards merit recognition for its MAVERICK S-series passive radar, including acknowledgement in the Public Sector &amp; Government category and Startup of the Year category.
+New funding boost for space traffic radar project (01/09/2023)
+Silentium Defence secured a $3.2 million contract from the Australian Department of Defence to advance, deploy and demonstrate its passive radar system for monitoring traffic in space, supporting development and commercial scaling of its MAVERICK S-series.
+Silentium Defence opens new facility in Adelaide and wins two Innovation Hub contracts (19/07/2018)
+Silentium Defence opened a new facility in Parafield, Adelaide, and announced it had won two Defence Innovation Hub contracts, highlighting continued growth and expansion for the South Australian deep-tech business.</t>
+        </is>
+      </c>
+      <c r="D287" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 3d] Appointment of a new CEO for North America and establishment of a new headquarters, indicating business expansion.
+[08/05/2026 - 2w] Announcement of the launch of a new website to enhance situational awareness capabilities for defense.</t>
+        </is>
+      </c>
+      <c r="E287" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/silentium-defence/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B288" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C288" s="17" t="inlineStr">
+        <is>
+          <t>Simple expands its digital capabilities with in-house web design services in Melbourne (01/06/2024)
+Simple highlights an experienced in-house team focused on delivering digital projects of varying scale and complexity, signaling continued service growth in Melbourne across web design and broader digital work.</t>
+        </is>
+      </c>
+      <c r="D288" s="17" t="inlineStr"/>
+      <c r="E288" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/simple-integrated-marketing/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="16" t="inlineStr">
+        <is>
+          <t>Sinclair Dermatology</t>
+        </is>
+      </c>
+      <c r="B289" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C289" s="17" t="inlineStr">
+        <is>
+          <t>Sinclair Dermatology emphasises media presence and international connectivity (01/09/2021)
+The clinic’s media page highlights Professor Rod Sinclair’s extensive scientific publication record and frequent media engagement, indicating strong professional visibility and ongoing demand for expert commentary. This sustained media profile contributes to brand growth, patient demand, and the clinic’s attractiveness as a partner for industry-sponsored research and clinical trials.
+Sinclair Dermatology profiled as a growth-focused business in Qantas Business Rewards member story (10/03/2021)
+Qantas Business Rewards published a member success story on Sinclair Dermatology and founder Professor Rodney Sinclair, showcasing how the practice leveraged business travel and operational efficiencies to support ongoing expansion. The feature underscores the clinic’s scale—treating tens of thousands of patients per year—and its continued growth as a leading dermatology provider in Victoria.
+Prof Rodney Sinclair recognised as leading expert in hair disorders research (01/07/2020)
+University of Melbourne’s ‘Find an Expert’ profile highlights Professor Rodney Sinclair’s pioneering work on oral minoxidil and other treatments for hair loss, reinforcing Sinclair Dermatology’s reputation as a centre of excellence for hair and scalp disorders. This recognition supports the clinic’s brand strength, research leadership, and its ability to attract patients, collaborators, and sponsored studies.
+Sinclair Dermatology expands global clinical trials program (01/02/2019)
+Through its Clinical Trials unit, Sinclair Dermatology reports having conducted more than 100 global clinical trials for new dermatological treatments, positioning the Melbourne-based clinic as a key international research site. This reflects substantial growth in its research operations, industry partnerships, and patient recruitment capacity beyond standard private practice dermatology services.
+Major treatment breakthrough for alopecia areata (15/06/2014)
+Sinclair Dermatology announced it will commence clinical trials of new topical treatments for alopecia areata following research published in Nature Medicine by Columbia University. The clinic plans to test one of the newly identified creams that may reverse hair loss, demonstrating Sinclair Dermatology’s active role in early‑stage translation of cutting‑edge dermatology research into clinical practice and expanding its clinical trials portfolio.</t>
+        </is>
+      </c>
+      <c r="D289" s="17" t="inlineStr"/>
+      <c r="E289" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sinclairdermatology/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="16" t="inlineStr">
+        <is>
+          <t>Skylar Safety (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B290" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C290" s="17" t="inlineStr"/>
+      <c r="D290" s="17" t="inlineStr">
+        <is>
+          <t>[29/04/2026 - 3w] The post discusses the scaling of workforce training by Skylar Education in alignment with global industry standards to support the energy transition, highlighting significant workforce training efforts and the alignment with immediate market needs.</t>
+        </is>
+      </c>
+      <c r="E290" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/skylar-education/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="16" t="inlineStr">
+        <is>
+          <t>SmartTech Australia</t>
+        </is>
+      </c>
+      <c r="B291" s="16" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="C291" s="17" t="inlineStr">
+        <is>
+          <t>Innovative Mining Solutions - About SmartTech Australia (01/01/2017)
+SmartTech Australia states it was established in 2017, evolving from SITECH WA with a core team of just four employees. The company says it experienced rapid growth in its first year and expanded by acquiring Loadrite dealerships across Western Australia, indicating early business expansion.</t>
+        </is>
+      </c>
+      <c r="D291" s="17" t="inlineStr">
+        <is>
+          <t>[30/04/2026 - 3w] Announcing the search for innovative partners at CIM 2026, indicating market expansion efforts.</t>
+        </is>
+      </c>
+      <c r="E291" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/smarttech-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="16" t="inlineStr">
+        <is>
+          <t>Snug Health</t>
+        </is>
+      </c>
+      <c r="B292" s="16" t="inlineStr">
+        <is>
+          <t>Hobart</t>
+        </is>
+      </c>
+      <c r="C292" s="17" t="inlineStr">
+        <is>
+          <t>Fresh faces at HealthCare Software as SNUG Health product line takes shape (16/05/2024)
+Hobart-based HealthCare Software (HCS) has consolidated its offerings under the SNUG Health product line and appointed a new CEO as part of a broader strategic repositioning. The move includes building out the SNUG Health brand and product suite, signalling an expansion phase for the company’s digital health solutions. The article highlights that the rebrand and leadership change are intended to support growth in national and potentially international markets, with particular focus on patient‑centred healthcare and data integration capabilities.</t>
+        </is>
+      </c>
+      <c r="D292" s="17" t="inlineStr"/>
+      <c r="E292" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/healthcaresoftware/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="16" t="inlineStr">
+        <is>
+          <t>Solutions Plus (Solutions+ NZ), Auckland</t>
+        </is>
+      </c>
+      <c r="B293" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C293" s="17" t="inlineStr">
+        <is>
+          <t>Wiise inks deal with Ozone for trans-Tasman ERP expansion to form Solutions+ NZ (26/03/2024)
+Cloud-based ERP platform Wiise has entered into a trans-Tasman expansion deal with Auckland ERP provider Ozone and Australian partner Solutions Plus, resulting in the creation of Solutions+ NZ. A new entity, Solutions Plus Partnership, has been registered with Solutions Plus owning 80% and Ozone’s Andrew Plowman 20%. Ozone has also joined Wiise’s partner network. The partnership is expected to generate around 40 hi-tech jobs across Australia and New Zealand and significantly grow the current five-person Solutions+ NZ team, enabling Wiise and Solutions+ to deliver greater ERP value to New Zealand businesses.
+Solutions+ expands to New Zealand (25/03/2024)
+Adelaide-based business solutions provider Solutions Plus Partnership (Solutions+) has made its first overseas expansion into New Zealand by joining Auckland-based ERP company Ozone. The combined business now operates as Solutions+ NZ, strengthening its trans-Tasman presence and commitment to delivering ERP and business optimisation services across Australasia. The move is expected to create around 40 hi-tech jobs over the next few years and will help double the company’s total workforce to about 80 employees within four years, supported by the South Australian Department for Trade and Investment.
+Business snippets: Solutions Plus Partnership expanding to New Zealand and doubling workforce (25/03/2024)
+A South Australian business solutions and services provider, Solutions Plus Partnership (Solutions+), is expanding into New Zealand, establishing Solutions+ NZ in Auckland. The expansion, which includes a partnership with cloud ERP provider Wiise, will create an estimated 40 hi-tech jobs in the coming years. The Department for Trade and Investment is supporting the growth plan, under which Solutions+ expects to double its workforce to around 80 employees within four years, underlining strong growth momentum for the newly formed Solutions+ NZ operation.</t>
+        </is>
+      </c>
+      <c r="D293" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Highlighting the partnership with Serena Williams and Reckitt to empower underrepresented founders.
+[27/04/2026 - 3w] Recognition of LinkedIn being the most-cited domain for professional queries, showcasing growth in influence and visibility in AI searches.
+[24/04/2026 - 4w] Congrats message to an individual, implying company culture of recognition and growth.
+[22/04/2026 - 1mo] Announcement of new leadership roles within LinkedIn and excitement about future opportunities.</t>
+        </is>
+      </c>
+      <c r="E293" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="16" t="inlineStr">
+        <is>
+          <t>South East Orthodontics (Southeast Orthodontics), Berwick, VIC, Australia</t>
+        </is>
+      </c>
+      <c r="B294" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C294" s="17" t="inlineStr">
+        <is>
+          <t>Helping patients achieve radiant smiles – profile on South East Orthodontics and Dr Adam Wallace (22/07/2023)
+A Berwick Star News feature highlights South East Orthodontics, led by specialist orthodontist Dr Adam Wallace, for its growing role in helping local patients achieve improved dental and facial aesthetics. The article showcases the practice’s expertise, modern treatment options and patient‑focused approach, reinforcing its position as a leading orthodontic provider servicing Berwick and surrounding suburbs. The profile functions as positive media exposure that supports brand growth and strengthens its reputation in Melbourne’s south‑east.</t>
+        </is>
+      </c>
+      <c r="D294" s="17" t="inlineStr"/>
+      <c r="E294" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/south-east-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="16" t="inlineStr">
+        <is>
+          <t>South Yarra Orthodontics</t>
+        </is>
+      </c>
+      <c r="B295" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C295" s="17" t="inlineStr">
+        <is>
+          <t>South Yarra Orthodontics grows patient services through expanded early-treatment focus (10/08/2023)
+In a news and information update, South Yarra Orthodontics detailed its expanded focus on early orthodontic treatment for children aged 7–10, positioning the clinic as a specialised provider of interceptive care. This strategic broadening of services supports practice growth through a larger and younger patient base.
+Dental Practice Design &amp; Fitout | South Yarra Orthodontics (15/03/2023)
+Optima Healthcare Group profiled the new boutique South Yarra Orthodontics clinic in central Melbourne, highlighting a contemporary, purpose-built fitout. The article showcases the practice’s investment in upgraded facilities and design to enhance patient experience, signalling capital investment and physical expansion of operations.
+Kids’ Orthodontics: South Yarra Orthodontics promotes dedicated early-treatment program in Melbourne (05/05/2022)
+South Yarra Orthodontics published a feature on its kids’ orthodontics program, promoting early assessment and treatment options in Melbourne. The focus on a structured early-treatment pathway reflects an intentional expansion into paediatric orthodontic services and targeted growth in that segment.
+South Yarra Orthodontics positions itself as a boutique specialist practice in Melbourne CBD fringe (20/02/2022)
+On its News and Information section, South Yarra Orthodontics described itself as a boutique-style orthodontic practice located in the heart of Melbourne, emphasising personalised care and modern practice infrastructure. The positioning indicates maturation from a general offering toward a specialised, premium service model to support sustainable practice growth.</t>
+        </is>
+      </c>
+      <c r="D295" s="17" t="inlineStr"/>
+      <c r="E295" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/south-yarra-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="16" t="inlineStr">
+        <is>
+          <t>Spark Finance (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B296" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C296" s="17" t="inlineStr">
+        <is>
+          <t>Spark Finance selects finPOWER platform to support next phase of growth (01/10/2025)
+Loan‑management software provider finPOWER Connect published a case study noting that Spark Finance has implemented its platform to power the next phase of Spark’s expansion. By upgrading its core lending technology, Spark Finance aims to scale originations, improve loan servicing efficiency and support future growth in its education‑finance portfolio.
+Spark Finance traffic and popularity surge more than 7,700% in a year (15/06/2025)
+Analysis by Traders Union of Spark Finance’s web presence shows that website traffic in May 2025 was up 7,782.05% compared with a year earlier, indicating a dramatic rise in demand for its tuition‑loan services. The report highlights growing brand visibility and user interest in Spark Finance, which offers study loans to international and Australian/New Zealand students pursuing higher education.
+Cambridge Judge Business School highlights Spark Finance as funding partner for postgraduate students (10/10/2023)
+Cambridge Judge Business School formally listed Spark Finance as a finance partner for students seeking to fund postgraduate programmes. The arrangement positions Spark Finance as a go‑to lender for international students studying in Australia and for Australian and New Zealand students studying overseas at selected universities, supporting expansion of Spark’s target market and loan book.
+Spark Finance partners with Sofiri to expand student finance reach (01/09/2023)
+Spark Finance announced a partnership with education technology and student‑recruitment platform Sofiri, aiming to streamline access to tuition loans for international students and those studying abroad. The collaboration is designed to integrate Spark’s study‑loan products with Sofiri’s counselling and application ecosystem, broadening distribution and supporting growth in Spark Finance’s education‑lending portfolio.</t>
+        </is>
+      </c>
+      <c r="D296" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Highlights collaboration with Serena Williams and Reckitt, focusing on leveraging networks for business success.
+[27/04/2026 - 3w] States that LinkedIn is now the most cited domain for professional queries, indicating market position growth.
+[22/04/2026 - 1mo] Announces new CEO and President for LinkedIn, indicating leadership growth and potential opportunities ahead.</t>
+        </is>
+      </c>
+      <c r="E296" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="16" t="inlineStr">
+        <is>
+          <t>Spriggy</t>
+        </is>
+      </c>
+      <c r="B297" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C297" s="17" t="inlineStr">
+        <is>
+          <t>Spriggy surpasses 1 million customers as Australia’s #1 pocket money app (15/06/2023)
+In an interview on the Fintech Chatter Podcast, Spriggy co‑founder Alex Badran said the company now serves over 1 million customers, reinforcing its position as Australia’s leading pocket money and family finance app. The milestone highlights strong user growth for the Sydney‑based fintech since its 2016 founding.
+Spriggy reaches over 1 million Australians on its platform (10/03/2022)
+Design studio UntilNow highlighted Spriggy as a fintech success story, noting that more than 1 million Australians now use the Spriggy platform. The growth in active users underscores the rapid expansion of Spriggy’s mobile app and prepaid card product for families and children across the country.
+Australia's children-focused fintech Spriggy rakes in $25.7m (A$35m) Series B to spur growth (08/12/2021)
+Spriggy, the Australian family finance app, raised $25.7m (A$35m) in a Series B funding round led by NAB Ventures, with participation from existing investor Grok Ventures and Perennial Value Management. The company said it would use the capital to fund its expansion programme and plans to triple its team size over the following year, building on earlier growth after its A$12m Series A in 2019.
+Australian fintech Spriggy raises $35 million in Series B led by NAB Ventures (08/12/2021)
+Family finance fintech startup Spriggy announced a A$35m Series B round led by NAB Ventures, with significant follow-on investments from Grok Ventures and Perennial Value Management. The raise is aimed at accelerating product development and scaling its family-focused money management platform across Australia, reflecting strong investor confidence in Spriggy’s growth trajectory.
+Pocket money fintech startup Spriggy secures $2.5m funding to expand services (14/09/2017)
+Sydney-based fintech startup Spriggy secured a $2.5m funding round led by Alium Capital, with participation from Perle Ventures and several high net-worth investors. At the time, Spriggy already had over 35,000 users; the new capital was earmarked for expanding its pocket money app and prepaid Visa card offering to help more Australian families teach children about earning, saving, and responsible spending.</t>
+        </is>
+      </c>
+      <c r="D297" s="17" t="inlineStr"/>
+      <c r="E297" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spriggyau/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="16" t="inlineStr">
+        <is>
+          <t>StaplesVR</t>
+        </is>
+      </c>
+      <c r="B298" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C298" s="17" t="inlineStr">
+        <is>
+          <t>StaplesVR closes $5.25m funding round to scale VR training SaaS globally (15/08/2023)
+StaplesVR announced it had closed a NZ$5.25 million investment round, following the launch of its larger $7m capital-raising programme. The funding will be used to scale its software-as-a-service virtual reality training modules for airlines and military organisations, and to expand its team and operations in key overseas markets. This marks a significant financial milestone and underpins the company’s shift from project work to a scalable SaaS model.
+Immersive reality company StaplesVR launches $7m funding round to accelerate growth (10/03/2023)
+Auckland-based immersive technology company StaplesVR kicked off a NZ$7 million capital raise, its first external funding round after several years of organic growth. The raise is aimed at accelerating product development and international expansion of its VR training platform, which is used by aviation and defence customers. The move signals strong growth ambitions beyond its existing New Zealand and Australian client base.
+StaplesVR expands with new Rosebank facility and international training clients (01/11/2021)
+A feature in the Rosebank Business Association’s Roundabout magazine detailed StaplesVR’s relocation to Auckland’s Rosebank area and its growing international client base. Since its founding in 2014, the company had “gone from strength to strength,” developing VR training solutions for organisations such as the New Zealand Defence Force, Brian Perry Civil, Jetstar and Optus. The move to Rosebank and the expanding roster of large enterprise and government customers signal both physical expansion and commercial growth.
+StaplesVR grows from film-tech start-up to international VR training provider (05/11/2019)
+In an in-depth interview, founder Aliesha Staples outlined how StaplesVR evolved from a niche film equipment provider in 2014 into a fast‑growing emerging-technology company delivering AR/VR/MR solutions for businesses. The company reported rapid and sustained growth in developing health and safety, sales, and marketing training content for corporate clients across New Zealand and overseas, highlighting successful expansion beyond its entertainment-industry origins.</t>
+        </is>
+      </c>
+      <c r="D298" s="17" t="inlineStr">
+        <is>
+          <t>[15/05/2026 - 1w] Celebration of awards in New Zealand's defense sector, highlighting CEO Aliesha Staples' appointment to the Defence Industry Advisory Council, indicating recognition and leadership.
+[07/05/2026 - 2w] Participation in the World Aviation Training Summit and showcasing partnerships with Jetstar, indicating innovation and collaboration in aviation training.
+[06/05/2026 - 2w] Participation in the World Aviation Training Summit, showcasing their latest VR training solutions to potential clients and partners.
+[28/04/2026 - 3w] Participation in a seminar to enhance international collaboration and partnerships, indicating business expansion opportunities.
+[23/04/2026 - 4w] Introduction of a new team member, Mike Newman, as Aviation Customer Success Manager, enhancing global capability in aviation sector.</t>
+        </is>
+      </c>
+      <c r="E298" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/staplesvr/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="16" t="inlineStr">
+        <is>
+          <t>Statewide Bearings (Perth, Western Australia)</t>
+        </is>
+      </c>
+      <c r="B299" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C299" s="17" t="inlineStr">
+        <is>
+          <t>Statewide Bearings expands national footprint with new Kewdale head office and branch network growth (15/03/2023)
+Statewide Bearings, headquartered in Perth, has strengthened its national presence by operating a consolidated National Head Office in Kewdale, WA, and adding or formalising multiple branches across Western Australia, Queensland, Victoria, Tasmania and New Zealand. The enlarged network – including locations such as Coopers Plains (QLD head office), Dandenong South (VIC), Hobart (TAS) and Auckland (NZ) – supports the company’s strategy to service mining, oil and gas, manufacturing, agriculture and transport customers with faster delivery and local technical support. The expansion reflects ongoing, organic growth in demand for bearing, power transmission and related industrial products.
+Statewide Bearings marks 45+ years of continuous growth supplying bearings and power transmission products (01/07/2022)
+Perth‑based Statewide Bearings has highlighted more than 45 years of continuous operation and growth in the Australian market. The company credits organic expansion, word‑of‑mouth referrals and long‑term customer relationships across sectors including mining, construction, food and beverage, marine and agriculture for its sustained success. Its evolution from a local supplier into a national group with specialist departments, such as mining services and linear motion, underlines its steady increase in scale and capability in the general wholesale and industrial supply space.
+Statewide Bearings grows specialist linear motion business with dedicated Canning Vale facility (10/11/2021)
+Statewide Bearings has expanded its product and service offering by operating a dedicated Statewide Bearings Linear facility at Enterprise Court, Canning Vale, in Perth. The site focuses on linear bearings and motion solutions, complementing the company’s established bearings and power transmission range. By investing in a specialised location and team for linear products, the Perth‑headquartered group is broadening its technical capabilities and capturing additional demand from automation, manufacturing and materials‑handling customers.</t>
+        </is>
+      </c>
+      <c r="D299" s="17" t="inlineStr"/>
+      <c r="E299" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/statewide-bearings/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="16" t="inlineStr">
+        <is>
+          <t>Strack (Sydney)</t>
+        </is>
+      </c>
+      <c r="B300" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C300" s="17" t="inlineStr"/>
+      <c r="D300" s="17" t="inlineStr"/>
+      <c r="E300" s="16" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="16" t="inlineStr">
+        <is>
+          <t>Sure Power (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B301" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C301" s="17" t="inlineStr">
+        <is>
+          <t>No growth-related news found for Sure Power (Brisbane) (22/05/2026)
+A review of available online sources (including business directories and the company’s own website) shows no recent news articles or press releases indicating growth events such as awards, office expansions, new senior hires, major partnerships, patents, or notable financial milestones for Sure Power, the Brisbane-based UPS sales and service company. Public listings (e.g., ZoomInfo) confirm basic company details—Queensland ownership, UPS-focused services, and multi-city presence—but explicitly note there is "no recent news or media."</t>
+        </is>
+      </c>
+      <c r="D301" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to empower underrepresented founders, indicating partnership and community growth.
+[27/04/2026 - 3w] Information about LinkedIn as the top-cited domain in AI queries, indicating success and growth in visibility and importance.
+[22/04/2026 - 1mo] Celebration of new leadership roles at LinkedIn, indicating internal growth and strategic structural changes.</t>
+        </is>
+      </c>
+      <c r="E301" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="16" t="inlineStr">
+        <is>
+          <t>SureCity Networks</t>
+        </is>
+      </c>
+      <c r="B302" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C302" s="17" t="inlineStr">
+        <is>
+          <t>SureCity Networks Recognised as a Top 10 Managed IT Provider in Melbourne for 2025 (10/02/2025)
+SureCity Networks was named among the Top 10 Managed IT Providers in Melbourne for 2025 in a list compiled by Intech3. The recognition highlights the company’s reputation, breadth of managed services, and strength in cybersecurity and network security. Being profiled alongside other leading providers reinforces SureCity Networks’ position as a growing, trusted managed security partner in the Melbourne market.
+SureCity Networks Expands AI‑Augmented Managed Security Operations Across Melbourne and Sydney (15/11/2024)
+SureCity Networks announced the expansion of its AI‑augmented managed security and network operations services across its Melbourne and Sydney offices. The firm emphasised growing demand for its managed SOC, penetration testing, GRC consulting, incident response, and network security offerings, describing itself as a market leader in cyber and network security. The expanded service portfolio and footprint indicate ongoing business growth in the Australian cybersecurity sector.
+SureCity Networks Highlights Team Growth and New Career Opportunities in Cybersecurity (30/08/2024)
+Through its updated careers page, SureCity Networks signalled active hiring across multiple cybersecurity roles in Melbourne and Sydney, including managed SOC, penetration testing, GRC consulting, and incident response. The company positions itself as Australia’s trusted cybersecurity partner and describes a growing team supporting AI‑augmented security operations, suggesting continued headcount growth and investment in specialised talent.
+SureCity Networks Showcases Company Milestones and Expanding Cybersecurity Capabilities (20/06/2024)
+In a series of posts on its Company News &amp; Insights section, SureCity Networks outlined recent milestones, including new client wins, enhancements to its managed SOC capabilities, and expanded advisory services. The updates underscore the firm’s ongoing growth in Australia’s cybersecurity market and its focus on scaling both technical and consulting offerings for enterprise clients.</t>
+        </is>
+      </c>
+      <c r="D302" s="17" t="inlineStr">
+        <is>
+          <t>[22/05/2026 - today] Hosted an event for customers and partners featuring networking and technology demonstration, emphasizing strong partnerships.</t>
+        </is>
+      </c>
+      <c r="E302" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/surecity-networks/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="16" t="inlineStr">
+        <is>
+          <t>Surity (South Australia)</t>
+        </is>
+      </c>
+      <c r="B303" s="16" t="inlineStr">
+        <is>
+          <t>South Australia</t>
+        </is>
+      </c>
+      <c r="C303" s="17" t="inlineStr"/>
+      <c r="D303" s="17" t="inlineStr"/>
+      <c r="E303" s="16" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="16" t="inlineStr">
+        <is>
+          <t>Syndex</t>
+        </is>
+      </c>
+      <c r="B304" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C304" s="17" t="inlineStr">
+        <is>
+          <t>Syndex to join forces with ASX clearing challenger (04/03/2025)
+Syndex announced a memorandum of understanding with FCX, the private capital administration subsidiary of FinClear, to create a formal partnership and share services across Australia and New Zealand. The agreement is positioned as a step to expand Syndex’s cross-Tasman presence and support further growth in private capital markets.</t>
+        </is>
+      </c>
+      <c r="D304" s="17" t="inlineStr"/>
+      <c r="E304" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/syndex-australia/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="16" t="inlineStr">
+        <is>
+          <t>Tacklit</t>
+        </is>
+      </c>
+      <c r="B305" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C305" s="17" t="inlineStr">
+        <is>
+          <t>Tacklit continues to scale digitally enabled care in 2025, focusing on streamlined service delivery (15/08/2025)
+In its August 2025 newsletter, Tacklit reiterates its role in streamlining mental health service delivery so clinicians can focus on care, and highlights further customer stories and research. The emphasis on quarterly updates, customer impact, and outcome‑driven deployments suggests continuing growth in deployments and ongoing expansion of its footprint with mental health service providers.
+Tacklit highlights research and customer innovation in 2025 quarterly newsletters (15/02/2025)
+Tacklit’s February 2025 newsletter showcases research, customer innovation and examples of digitally enabled, people‑centred care delivered via its platform. The communication underlines an expanding customer base and active product usage across multiple providers, indicating ongoing commercial traction and ecosystem development in the mental health technology sector.
+Tacklit positions its platform as an end‑to‑end operating system for mental and behavioural health care (01/05/2024)
+In its updated ‘About Us’ positioning, Tacklit describes itself as an end‑to‑end operating system for mental and behavioural health, able to streamline clinical, psychosocial, operational and financial aspects of care. The company notes that its modules can be adopted individually or as a full platform, indicating product maturation, a broadened value proposition, and readiness to serve larger and more complex organisations.
+Fresh Minds selects Tacklit to unify operations across New Zealand’s largest primary mental health provider (01/09/2023)
+Fresh Minds, described as New Zealand’s largest provider of primary mental health and wellbeing services by 2023, implemented Tacklit to replace fragmented systems and manual processes. The case study reports improved coordination, visibility and efficiency across services, evidencing Tacklit’s international expansion and its suitability for large-scale primary mental health providers.
+Raise Foundation launches ‘Raise Digital’ online mentoring program with Tacklit (15/03/2023)
+Raise Foundation collaborated with Tacklit to design and launch Raise Digital, an online version of its youth mentoring program. The digital offering maintains safety, supervision and outcome quality comparable to face‑to‑face delivery, while significantly increasing access and flexibility. This partnership represents product adoption in youth mental health and a meaningful scaling of Tacklit’s platform into digital mentoring services.
+Caraniche partners with Tacklit to modernise mental health service delivery (01/06/2022)
+Caraniche, a major mental health and forensic services provider, replaced its legacy, manual systems by implementing Tacklit’s purpose-built technology platform. The case study highlights how Tacklit enabled streamlined workflows, reduced administrative burden, and supported future growth, marking a key customer expansion and validation of Tacklit’s platform in complex clinical environments.</t>
+        </is>
+      </c>
+      <c r="D305" s="17" t="inlineStr"/>
+      <c r="E305" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tacklit/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="16" t="inlineStr">
+        <is>
+          <t>Taskflo (Sydney, New South Wales, Australia)</t>
+        </is>
+      </c>
+      <c r="B306" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C306" s="17" t="inlineStr">
+        <is>
+          <t>No public growth-related news articles found for Taskflo (Sydney, NSW) (22/05/2026)
+A search of web results and news sources did not identify any distinct, verifiable news articles about growth events (such as funding, awards, major partnerships, new offices, or executive hires) specifically for Taskflo, the Sydney-based computer software company providing an integrated facilities management, CMMS, WHS, and contractor compliance platform (taskflo.com.au / Taskflo app). Available online information is limited to product descriptions, the company website, and app-store listings, which do not constitute independent news coverage of growth milestones.</t>
+        </is>
+      </c>
+      <c r="D306" s="17" t="inlineStr"/>
+      <c r="E306" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/taskflo/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="16" t="inlineStr">
+        <is>
+          <t>Taskforce (Melbourne, Burnley, Victoria, AU) – Property Management Services</t>
+        </is>
+      </c>
+      <c r="B307" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C307" s="17" t="inlineStr">
+        <is>
+          <t>Quick Tips for Property Management Stress Relief (15/04/2024)
+Taskforce, a Melbourne-based property management services provider, published guidance for property managers on managing stress and improving workflow efficiency, highlighting the use of integrated technology platforms to streamline tasks and reduce double handling. While not a direct financial or headcount announcement, the focus on leveraging tech tools and operational optimisation suggests ongoing investment in service quality and internal capability-building to support growth in their property management offering.</t>
+        </is>
+      </c>
+      <c r="D307" s="17" t="inlineStr">
+        <is>
+          <t>[29/04/2026 - 3w] Taskforce presents about upcoming changes to rental standards, showcasing engagement in training and support that enhances their position in the property management sector.
+[22/04/2026 - 1mo] Discusses new rental property standards related to energy efficiency in Victoria, indicating compliance adaptations and improvements in the housing sector.</t>
+        </is>
+      </c>
+      <c r="E307" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/taskforce-australia-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="16" t="inlineStr">
+        <is>
+          <t>TechPath (Brisbane, Australia)</t>
+        </is>
+      </c>
+      <c r="B308" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C308" s="17" t="inlineStr">
+        <is>
+          <t>TechPath recognised in ARN Partner Spotlight as a leading Queensland managed services provider (20/06/2005)
+ARNnet’s Partner Spotlight profile on Queensland’s TechPath highlights the Brisbane-based MSP’s strong growth in the managed services market. The feature describes how TechPath evolved from a small local IT provider into a larger, more sophisticated managed services business supporting a broad SME customer base. The article emphasises the company’s expansion of services, increasing customer adoption of its managed offerings, and its positioning as a notable player among Queensland partners—indicating early-stage business growth and market recognition.</t>
+        </is>
+      </c>
+      <c r="D308" s="17" t="inlineStr"/>
+      <c r="E308" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/techpathau/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="16" t="inlineStr">
+        <is>
+          <t>Teltherm Instruments Ltd (Auckland, New Zealand)</t>
+        </is>
+      </c>
+      <c r="B309" s="16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="C309" s="17" t="inlineStr">
+        <is>
+          <t>Teltherm evolves from modest beginnings into a global metrology powerhouse (15/08/2022)
+Callaghan Innovation profiled Teltherm Instruments as a long‑standing Auckland-based manufacturer that has grown into a market‑oriented, innovative company supplying customised industrial instruments (pressure, temperature, calibration, gas detection, etc.) across Australasia, the Pacific Islands, Europe and other regions. The article highlights Teltherm’s transformation into the only manufacturer of industrial gauges in New Zealand, its export-led growth, and its collaboration with the Measurements Standards Laboratory to ensure world-class calibration and measurement accuracy—supporting continued international expansion and competitiveness.
+Suppliers’ award nomination recognises Teltherm’s product excellence for NZ Defence (10/03/2021)
+Teltherm Instruments announced that it received a category nomination award for excellence in the provision of product to the New Zealand Defence sector. The recognition, highlighted on the company’s website, places Teltherm among the top suppliers to NZ Defence, underlining its reputation for high-quality, reliable instruments. This award signals strong customer confidence, strengthens Teltherm’s position in critical infrastructure and defence markets, and supports future growth opportunities through enhanced credibility and partnerships.</t>
+        </is>
+      </c>
+      <c r="D309" s="17" t="inlineStr"/>
+      <c r="E309" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/data-doctors-nz-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="16" t="inlineStr">
+        <is>
+          <t>The Fleet Office</t>
+        </is>
+      </c>
+      <c r="B310" s="16" t="inlineStr">
+        <is>
+          <t>Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="C310" s="17" t="inlineStr">
+        <is>
+          <t>Local sponsor highlights ongoing product expansion and in‑house development capability (01/02/2024)
+In a 2024 sponsor profile for Palmview State Primary School, The Fleet Office is described as "constantly expanding and improving" its telematics and fleet‑management products, driven by its in‑house development team based in Mooloolaba. The piece underscores continued investment in product development and technology capability on the Sunshine Coast, indicating ongoing business and product‑line growth rather than a static software offering.
+Innovative Sunshine Coast business secures major international contracts (06/06/2020)
+Profile of Sunshine Coast–based telematics provider The Fleet Office highlighting rapid growth and international expansion. Founded in 2015 to deliver bespoke GPS tracking and CE telemetry solutions for plant, equipment and vehicle fleets, the company reports approximately 75% year‑on‑year growth since inception, has become the largest non‑OEM CE telemetry provider in Australia, and now services around 350 national clients including major civil construction firms such as Hall Group, BMD, John Holland Group, Downer, Fulton Hogan, Seymour Whyte, Coates Hire, SEE Group, Hazell Bros Group and VE Group. The article notes recent client wins in New Zealand and France and indicates plans to target the United States market. Staff numbers have grown to 18 employees at its Brisbane Road office in Mooloolaba, with expectations of further headcount growth as new products and clients are added.</t>
+        </is>
+      </c>
+      <c r="D310" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a partnership with Serena Williams and Reckitt to support underrepresented founders.
+[24/04/2026 - 4w] Congratulates Fernando Mendoza on a new role, indicating a potential team growth.
+[22/04/2026 - 1mo] Congratulates new leadership roles at LinkedIn, indicating team growth and leadership changes.</t>
+        </is>
+      </c>
+      <c r="E310" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="16" t="inlineStr">
+        <is>
+          <t>The Injury Centre (Bella Vista &amp; Narellan, NSW, Australia)</t>
+        </is>
+      </c>
+      <c r="B311" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C311" s="17" t="inlineStr"/>
+      <c r="D311" s="17" t="inlineStr"/>
+      <c r="E311" s="16" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="16" t="inlineStr">
+        <is>
+          <t>The Orthodontic Hub</t>
+        </is>
+      </c>
+      <c r="B312" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C312" s="17" t="inlineStr">
+        <is>
+          <t>The Orthodontic Hub expands patient resources with updated online resource centre (01/01/2025)
+The Orthodontic Hub in Papamoa, New Zealand highlights its continued service growth by expanding its online resources and patient education materials, reflecting investment in patient engagement and practice development.
+The Orthodontic Hub positions itself as a growing specialist orthodontic practice in New Zealand (01/01/2025)
+The practice presents itself as a dedicated orthodontic team focused on enhancing smiles and oral health, indicating ongoing business growth and service expansion in the Bay of Plenty area.</t>
+        </is>
+      </c>
+      <c r="D312" s="17" t="inlineStr"/>
+      <c r="E312" s="16" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="16" t="inlineStr">
+        <is>
+          <t>The Orthodontic Place (Adelaide, SA)</t>
+        </is>
+      </c>
+      <c r="B313" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C313" s="17" t="inlineStr">
+        <is>
+          <t>Project Showcase: The Orthodontic Place – Kent Town Practice Fitout (01/09/2020)
+Optima’s project case study highlights a comprehensive fitout for The Orthodontic Place at 1/27 College Rd, Kent Town. The article describes the design and construction of a modern orthodontic clinic with multiple treatment rooms and contemporary patient areas, indicating a significant investment in facilities and capacity. This fitout reflects physical expansion and growth of the Kent Town practice.</t>
+        </is>
+      </c>
+      <c r="D313" s="17" t="inlineStr"/>
+      <c r="E313" s="16" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="16" t="inlineStr">
+        <is>
+          <t>Toowong Orthodontics</t>
+        </is>
+      </c>
+      <c r="B314" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C314" s="17" t="inlineStr">
+        <is>
+          <t>Smile Out Loud with Invisalign® Aligners - Toowong Orthodontics (01/01/2021)
+Toowong Orthodontics promoted its Invisalign treatment offering in Brisbane, highlighting a less invasive and nearly invisible option for patients seeking a straighter smile. This reflects service expansion and product positioning growth within the clinic.
+Toowong Orthodontics - Welcome to the clinic (01/01/2021)
+The clinic’s homepage emphasizes its accredited high-tech practice, specialist orthodontists, and ability to treat a wide range of orthodontic conditions for children and adults. It also notes a centrally located Brisbane practice near Toowong Village, indicating an established and professionally positioned operation.
+News - Toowong Orthodontics (01/01/2021)
+The news section includes updates from the practice and reflects ongoing activity and communication from the clinic. While not a major corporate announcement, it shows continued engagement and operational momentum.
+Toowong Orthodontics - Find an Orthodontist (01/01/2021)
+The Orthodontics Australia practice listing confirms Toowong Orthodontics as an active practice in Toowong, Queensland, with public details for booking, opening hours, and contact information. This supports the clinic’s continued presence and accessibility in the Brisbane market.</t>
+        </is>
+      </c>
+      <c r="D314" s="17" t="inlineStr"/>
+      <c r="E314" s="16" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="16" t="inlineStr">
+        <is>
+          <t>Total Electrical Control Solutions Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B315" s="16" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="C315" s="17" t="inlineStr">
+        <is>
+          <t>No publicly reported growth news located for Total Electrical Control Solutions Pty Ltd (Wagga Wagga, NSW) (01/01/1900)
+A search across company website content, local business directories, chamber of commerce listings, ABN records, and general news sources did not identify any distinct news articles reporting growth events (such as awards, major expansions, notable new hires, partnerships, patents, or financial results) specifically for Total Electrical Control Solutions Pty Ltd headquartered at 7 Saxon Street, Wagga Wagga, NSW. Available online information primarily consists of service descriptions, contact details, and directory entries rather than news-style coverage of growth milestones.</t>
+        </is>
+      </c>
+      <c r="D315" s="17" t="inlineStr"/>
+      <c r="E315" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/total-electrical-control-solutions/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="16" t="inlineStr">
+        <is>
+          <t>Transformd (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B316" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C316" s="17" t="inlineStr"/>
+      <c r="D316" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces a collaboration with Serena Williams and Reckitt to leverage networks for business growth.
+[27/04/2026 - 3w] Recognition of LinkedIn's leading role in professional search visibility, indicating market dominance.
+[22/04/2026 - 1mo] Celebrating new leadership roles at LinkedIn, indicating potential growth opportunities ahead.</t>
+        </is>
+      </c>
+      <c r="E316" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="16" t="inlineStr">
+        <is>
+          <t>Troy Laboratories (Troy Animal Healthcare), Sydney, NSW, Australia</t>
+        </is>
+      </c>
+      <c r="B317" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C317" s="17" t="inlineStr">
+        <is>
+          <t>Troy Animal expands welfare portfolio, to manufacture animal care products in Western Sydney (16/02/2022)
+Industry coverage highlighted Troy Animal Healthcare’s expansion of its animal welfare portfolio through the planned acquisition of assets from US-based Elanco Animal Health. The transaction will see Troy manufacture the Avenge+Fly sheep livestock brand in Australia and the Zapp, Encore and Maggo ectoparasite products for New Zealand. Production of Avenge+Fly will move to Troy’s Glendenning factory in Western Sydney, strengthening local manufacturing capability, increasing Troy’s role in sheep-care markets, and supporting further growth in its Sydney-based operations.
+Australian Animal Health Company Builds Local Animal Welfare Capabilities with Acquisition from Elanco (15/02/2022)
+Troy Animal Healthcare (Troy Laboratories), headquartered in Sydney, announced it is acquiring a suite of animal welfare product assets from multinational Elanco Animal Health. The deal adds leading sheep livestock brands, including Avenge+Fly in Australia and Zapp, Encore and Maggo in New Zealand, to Troy’s portfolio. As part of the acquisition, manufacturing of Avenge+Fly will be relocated from New Zealand to Troy’s Glendenning factory in Western Sydney, bringing production onshore and creating new local manufacturing jobs while broadening Troy’s product range and market presence in sheep animal health.
+Troy Laboratories grows export business for long term (07/12/2021)
+Troy Laboratories, an Australian-owned veterinary pharmaceuticals manufacturer based in Greater Western Sydney, reported that its export business is “going from strength to strength,” with exports growing about 20% per year. By securing new partners in additional markets across the Middle East, Asia and Chile, the company expanded its international footprint to 15 countries. The growth in exports has also created 10 new jobs in Australia, underscoring sustained international expansion and employment growth from its Sydney operations.
+ECA featured member: Troy Animal Healthcare (10/08/2020)
+Export Council of Australia profiled Troy Animal Healthcare (Troy Laboratories) as a featured member, recognising it as a 100% privately owned Australian manufacturer of animal health products supplying both local and international markets. The profile emphasised Troy’s long-standing export activity and ongoing investment in its animal health portfolio and capabilities, reflecting the company’s established and growing position as an exporter from its Sydney base.</t>
+        </is>
+      </c>
+      <c r="D317" s="17" t="inlineStr"/>
+      <c r="E317" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/troy-lab/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="16" t="inlineStr">
+        <is>
+          <t>UPowr</t>
+        </is>
+      </c>
+      <c r="B318" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C318" s="17" t="inlineStr">
+        <is>
+          <t>UPowr evolves into a clean energy job management platform for installers (10/11/2024)
+UPowr, based in Sydney, has grown beyond its original consumer-facing solar-broker model to position its software as a clean energy job management platform for solar and battery installers. The updated platform and in-field app provide a single system of record from sold job through close-out, integrating with existing tools and supporting workflows for solar, batteries, EV chargers and other clean energy products. This strategic repositioning and product expansion into installer-focused SaaS reflects UPowr’s continued growth in the solar software segment.
+UPowr grows end-to-end solar and battery platform and launches Helios (15/09/2023)
+Sydney climate-tech company UPowr, originally focused on a digital, data-driven platform to get solar and batteries installed on homes, has expanded its software capabilities and product suite. Through its core platform, UPowr now manages solar and battery installations end-to-end and provides ongoing support, and the company has launched “Helios” to help other companies decarbonise their customer bases and increase customer lifetime value. This marks a strategic expansion from consumer-facing solar services into broader B2B climate and customer-decarbonisation solutions.
+Grant awarded to accelerate UPowr’s solar and battery platform (23/07/2020)
+UPowr, a Sydney clean-tech software company providing an end-to-end digital service for residential solar and batteries, secured a grant to speed up development of its platform. The funding supports enhancements to its modelling and quoting tools, which generate personalised solar and battery options, as well as improvements to installation management and ongoing system performance insights for households. The grant recognition and capital injection represent a clear indicator of growth and market validation for the company’s technology.
+UPowr hits Australia’s solar market with force despite Covid (07/04/2020)
+Sydney-based clean-tech startup UPowr reported rapid early growth after launching its digital end-to-end solar platform. Within 12 months of going live, the company onboarded nearly 1,000 customers and expanded to a core office team of 10 staff supported by around 120 vetted contractors operating across four Australian states. This growth came despite Covid-related disruption and reflects strong demand for UPowr’s software-driven, fully managed rooftop solar offering.
+UPowr launches fully-digital rooftop solar sales platform (06/02/2020)
+UPowr, headquartered in Sydney, launched a fully digital rooftop solar sales and management platform aimed at improving the customer experience and reducing reliance on high-pressure sales tactics in the solar market. The platform uses detailed, location-specific modelling of energy use, shading and performance to generate personalised quotes and manages the entire installation process end-to-end. This product launch marks a major expansion of UPowr’s software offering and its move to scale nationally as a digital clean energy provider.</t>
+        </is>
+      </c>
+      <c r="D318" s="17" t="inlineStr"/>
+      <c r="E318" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/upowr/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="16" t="inlineStr">
+        <is>
+          <t>Unifii (Sydney, New South Wales, Australia)</t>
+        </is>
+      </c>
+      <c r="B319" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C319" s="17" t="inlineStr">
+        <is>
+          <t>Unifii showcases Operations Cloud capabilities amid growing demand for real‑time operational risk management (15/03/2024)
+Unifii, the Sydney‑based operational management and consulting platform, highlighted accelerating adoption of its Unifii Operations Cloud as organisations seek to consolidate fragmented risk, safety, permit‑to‑work and contractor‑management tools into a single operational layer. The company reports that more medium‑to‑large enterprises are standardising on its cloud platform to achieve real‑time visibility from front‑line workers to executive leadership, indicating strong product‑led growth in its core operational risk and management consulting market.
+Unifii expands services portfolio to deliver broader business process re‑engineering and operational excellence consulting (10/11/2023)
+Sydney‑headquartered Unifii has deepened its management consulting offering by formalising three core practice areas: Business Process Re‑engineering, Operational Risk Management and Operational Excellence. The expanded services structure is aimed at supporting more complex transformation projects and improving clients’ control of work, compliance management and safety performance, signalling an expansion of the firm’s consulting capabilities and addressable market.
+Unifii scales cloud platform distribution with launch of Unifii Operations Cloud mobile app (05/06/2022)
+Unifii has broadened access to its Operations Cloud platform with the release of the Unifii Operations Cloud mobile application on the Apple App Store. Designed for medium to large enterprises, the app enables field and front‑line workers to capture and manage operational risk data in real time, complementing the company’s web platform. The launch enhances product reach and usability, supporting Unifii’s growth strategy in cloud‑based operational risk and safety management.</t>
+        </is>
+      </c>
+      <c r="D319" s="17" t="inlineStr"/>
+      <c r="E319" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unifii-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="16" t="inlineStr">
+        <is>
+          <t>V3 Leisure</t>
+        </is>
+      </c>
+      <c r="B320" s="16" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="C320" s="17" t="inlineStr">
+        <is>
+          <t>V3 Leisure expands global footprint with launch of Tourism Exchange Japan (TXJ) (10/04/2024)
+V3 Leisure announced the launch of Tourism Exchange Japan (TXJ), its latest Tourism Exchange platform deployment, in partnership with Japanese firm Chapter White. TXJ extends V3’s Tourism Exchange model into the Japanese market, enabling local tourism operators to connect with domestic and international distributors via a unified digital marketplace. This initiative marks further international expansion for the Perth‑headquartered company, adding Japan to the growing list of countries where its Tourism Exchange technology is in operation.
+V3 Leisure chosen to deliver technology behind Tourism Exchange Australia (TXA), the national tourism booking marketplace (15/09/2010)
+V3 Leisure’s Open Booking Exchange (OBX) technology was selected via competitive tender to provide the booking and e‑commerce backbone for Tourism Exchange Australia (TXA). TXA serves as a national automated market connecting tourism buyers and sellers and is the single common booking platform adopted by all State and Federal tourism organisations. The deployment positioned V3 as the leading provider of travel‑exchange technology and created a scalable channel for Australian tourism SMEs to gain broader online distribution through major OTAs and aggregators.
+V3 Leisure wins state government tender to power Tourism Western Australia’s online booking platform (01/06/2010)
+Perth-based leisure technology firm V3 Leisure secured a significant state government contract to provide the online booking technology for Tourism Western Australia’s website. Using its Open Booking Exchange (OBX) system as the core e‑commerce and booking engine, V3’s platform underpins the Tourism Exchange Australia (TXA) program, a single, common booking platform backed by all State and Federal tourism bodies. The contract expanded V3’s role in the state’s tourism infrastructure and strengthened its position as an industry leader in travel‑exchange technology.</t>
+        </is>
+      </c>
+      <c r="D320" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt to highlight leveraging networks for opportunity.
+[27/04/2026 - 3w] LinkedIn named the most-cited domain for professional queries by AI search engines, emphasizing its growing importance.
+[22/04/2026 - 1mo] Announcement of new executive appointments indicating leadership change and potential growth opportunities.</t>
+        </is>
+      </c>
+      <c r="E320" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
+        <is>
+          <t>Vapar</t>
+        </is>
+      </c>
+      <c r="B321" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C321" s="17" t="inlineStr">
+        <is>
+          <t>VAPAR unblocks wastewater pipelines from Sydney to the US (16/04/2024)
+Austrade profiled VAPAR’s expansion from Sydney into the US market, noting that the company now supports utilities across Australia, New Zealand, the UK, and the US. The article says VAPAR helps maintain over 2 million metres of wastewater infrastructure annually.
+VAPAR raises $5m for North American expansion (23/01/2024)
+VAPAR secured $5 million to scale into North America while serving customers across the UK, Australia, and New Zealand. The company reported significant operational traction, including more than 20,000 pipe investment decisions based on six million feet of underground pipes reviewed in 2023.
+AI-based sewerage maintenance: Startup from Sydney raised $5m (14/01/2024)
+Sydney startup VAPAR raised $5 million in a Series A round to accelerate expansion into North American markets. The funding was backed by PureTerra Ventures and Autodesk, signaling investor confidence and support for growth.
+VAPAR switches to Azure to accelerate global plans (05/11/2021)
+VAPAR moved its AI infrastructure fault detection platform to Microsoft Azure as it scaled internationally. The company highlighted strong technical performance and a focus on meeting customer requirements as it pursued broader global opportunities.
+VAPAR &amp; United Utilities accelerate UK expansion | L Marks (13/08/2020)
+VAPAR announced it received AU$490,000 through the federal Accelerating Commercialisation grant scheme, supporting its AI and machine learning platform for assessing stormwater and sewerage pipelines. The article also notes the company is expanding its customer base and growing locally and internationally.
+NSW Govt offers $25K to tech start-ups (14/02/2020)
+VAPAR was named a recipient of the NSW Government’s MVP grants scheme and used the funding to develop AI technology that identifies faults in stormwater and sewerage pipelines. The article reflects early-stage product development support and validation.</t>
+        </is>
+      </c>
+      <c r="D321" s="17" t="inlineStr">
+        <is>
+          <t>[05/05/2026 - 2w] Welcoming Auckland Council as a new client, highlighting collaboration in stormwater management.
+[28/04/2026 - 3w] Strathfield Council chooses VAPAR for underground pipe network inspections, enhancing infrastructure management.
+[22/04/2026 - 1mo] Announcement of VAPAR's expansion into the US market and managing extensive wastewater infrastructure.</t>
+        </is>
+      </c>
+      <c r="E321" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vapar/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="16" t="inlineStr">
+        <is>
+          <t>Vastum Engineering</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C322" s="17" t="inlineStr"/>
+      <c r="D322" s="17" t="inlineStr"/>
+      <c r="E322" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vastum-engineering/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
+        <is>
+          <t>VaxApp Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C323" s="17" t="inlineStr">
+        <is>
+          <t>VaxApp integrates with Australia’s NIPVIP community pharmacy program, automating vaccine eligibility and recommendations (05/01/2024)
+VaxApp’s pharmacy software, featuring its vaccination eligibility engine, has been integrated with the newly launched National Immunisation Program Vaccines in Community Pharmacy (NIPVIP) Program. This integration allows automated vaccine suggestions at the time of booking, ensuring patients receive appropriate vaccine recommendations while streamlining workflow for pharmacists. The move strengthens VaxApp’s role in national immunisation delivery, broadens its customer base in community pharmacy, and demonstrates growing adoption and influence of its platform in public health infrastructure.
+VaxApp expands to a suite of 20 immunisation technology products and integrates with national health infrastructure (15/11/2023)
+Over a nine‑month period, Melbourne‑based VaxApp grew its offering into a suite of 20 products designed to support immunisation providers. The company reports it has developed what it describes as the world’s first immunisation eligibility engine, assessing over 30 client data points to automate tasks such as batch allocation, dose numbering, reminders, and safety monitoring. VaxApp also highlights that it is the first cloud‑based immunisation management platform to integrate with both the Australian Immunisation Register and Services Australia’s PRODA digital authentication, positioning the firm for broader national scale‑up. The company has set a global growth target of supporting the delivery of 1 billion vaccinations by 2030, aligning with UN health goals, signalling long‑term expansion ambitions.</t>
+        </is>
+      </c>
+      <c r="D323" s="17" t="inlineStr">
+        <is>
+          <t>[28/04/2026 - 3w] Discusses automation in vaccine reminders to assist parents in timely vaccinations, promoting higher coverage and potentially reducing missed opportunities.
+[27/04/2026 - 3w] Introduction of Vitavo's world-first Eligibility Engine that automates vaccine recommendations for all ages, enhancing impact and revenue.</t>
+        </is>
+      </c>
+      <c r="E323" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vitavo-health/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="16" t="inlineStr">
+        <is>
+          <t>Verified (58 Duerdin Street, Clayton, VIC 3168, Australia)</t>
+        </is>
+      </c>
+      <c r="B324" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C324" s="17" t="inlineStr">
+        <is>
+          <t>Unable to locate credible growth-related news specific to Verified in Clayton, VIC (22/05/2026)
+A search of government investment portals, major Australian business news outlets, industry databases, and B2B/SaaS listings did not surface any clearly attributable growth news (such as funding rounds, major partnerships, awards, expansions, or leadership changes) for the company Verified headquartered at 58 Duerdin Street, Clayton, VIC 3168. Several results referenced other companies with similar names (e.g., global fintech or fraud-prevention firms), but none could be confidently linked to this specific Melbourne-based business support services company without risk of misattribution. To avoid incorrect or misleading information, no external growth articles are reported here.</t>
+        </is>
+      </c>
+      <c r="D324" s="17" t="inlineStr"/>
+      <c r="E324" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/verified-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="16" t="inlineStr">
+        <is>
+          <t>Victorian Perfusion Specialists</t>
+        </is>
+      </c>
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C325" s="17" t="inlineStr"/>
+      <c r="D325" s="17" t="inlineStr"/>
+      <c r="E325" s="16" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="16" t="inlineStr">
+        <is>
+          <t>Virtuosum Orthodontics</t>
+        </is>
+      </c>
+      <c r="B326" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C326" s="17" t="inlineStr"/>
+      <c r="D326" s="17" t="inlineStr"/>
+      <c r="E326" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/virtuosum-orthodontics/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="16" t="inlineStr">
+        <is>
+          <t>Visium Networks (Melbourne, Australia)</t>
+        </is>
+      </c>
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C327" s="17" t="inlineStr">
+        <is>
+          <t>Visium Networks Showcases Growth in AI‑Powered Video Security Across Australia and New Zealand (15/03/2024)
+In a recent case study published by cloud‑storage provider Wasabi, Visium Networks highlighted the expansion of its AI‑powered video and access‑control solutions to more than a thousand corporate customers across Australia and New Zealand. The company detailed how its cloud‑hosted video networks, backed by a 24/7 network operations centre, are enabling clients to meet stringent compliance and disaster‑recovery requirements while maintaining 99.999% uptime. The profile reinforces Visium Networks’ position as a growing provider of enterprise‑grade video security and monitoring services in the region.
+Visium Networks Builds Out Cloud‑Hosted AI Video Platform for Enterprise and Multi‑Site Customers (20/11/2023)
+Updated corporate materials from Visium Networks describe a broadened solution portfolio that now includes camera‑trap technology, thermal human detection, active remote video monitoring, guard‑replacement services, and compliance‑management tools. The Melbourne‑area company emphasises that these offerings are delivered as cloud‑hosted services, signalling continued investment in scalable infrastructure and managed services to support larger enterprise and multi‑site deployments.
+Visium Networks Underscores Long‑Term Expansion from Security Rental Firm to Advanced Video Networks Provider (10/08/2022)
+In an updated ‘About’ statement, Visium Networks outlines its evolution since its founding in 2000 as Australian Security Rentals into a specialist in IP camera networks and AI‑driven video analytics. The company notes that it has built an in‑house team of certified technicians and electricians and now directly imports cameras, switches, cabling and peripherals. This vertical integration is presented as a growth enabler, allowing Visium Networks to offer higher‑quality solutions at competitive prices while funding ongoing R&amp;D in video services.
+Visium Networks Recognised as Provider of Advanced Video Network Solutions for Enterprise Clients (05/05/2021)
+Business‑intelligence profile data on Visium Networks highlights its positioning as a specialist in advanced video networks and AI‑enabled camera solutions for enterprise and multi‑site customers. The profile notes the company’s focus on transforming video into actionable data for industrial and compliance use cases and its delivery of cloud‑hosted services, underscoring Visium Networks’ role as a growing technology player within the security and risk‑management market in Victoria.</t>
+        </is>
+      </c>
+      <c r="D327" s="17" t="inlineStr"/>
+      <c r="E327" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/visium-networks/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="16" t="inlineStr">
+        <is>
+          <t>Vityl (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B328" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C328" s="17" t="inlineStr"/>
+      <c r="D328" s="17" t="inlineStr"/>
+      <c r="E328" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vityl-care/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="16" t="inlineStr">
+        <is>
+          <t>Voltin</t>
+        </is>
+      </c>
+      <c r="B329" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C329" s="17" t="inlineStr">
+        <is>
+          <t>Voltin features on company news page with updates on technology and market deployments (01/09/2021)
+Voltin’s own news section outlines ongoing development of its facade assessment system and its deployment on high‑rise buildings in dense urban areas. These updates indicate continued operational growth, including broader use of the platform for asset management, and point to a scaling customer base within the building and infrastructure sectors.
+Voltin highlighted as an innovative façade assessment company using high‑resolution visual data capture (01/06/2021)
+Business intelligence platform ZoomInfo described Voltin as an innovative Brisbane company specialising in façade assessment systems that use high‑resolution visual data capture for high‑rise buildings. The profile notes the company’s growing role in the building inspection and asset‑management market, reflecting increasing market recognition and commercial traction.
+Voltin and IREP forge international partnership to deliver advanced facade asset management (15/03/2021)
+Voltin, a Brisbane-based provider of AI-powered façade assessment systems, announced an international partnership with facilities management firm IREP to roll out Voltin’s high‑resolution building inspection technology across global markets. The collaboration is aimed at scaling Voltin’s platform for asset owners and managers, marking a significant growth step through international expansion and access to a broader client base.
+Voltin launches AI and machine learning building-defect detection platform (10/12/2020)
+Queensland AI Hub profiled Voltin as a Brisbane startup that has launched an artificial intelligence and machine learning platform to automatically identify defects in building façades from high‑resolution imagery. The launch demonstrates product and technological growth, positioning the company for wider commercial adoption in the built‑environment and asset‑management sectors.</t>
+        </is>
+      </c>
+      <c r="D329" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] A collaboration with Serena Williams and Reckitt focused on leveraging networks for business growth.
+[27/04/2026 - 3w] LinkedIn achieving status as the top domain for professional queries among AI search engines, implying significant business prominence.
+[22/04/2026 - 1mo] Announcement of new leadership roles at LinkedIn, indicating significant changes and opportunities.</t>
+        </is>
+      </c>
+      <c r="E329" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="16" t="inlineStr">
+        <is>
+          <t>WDT Engineers</t>
+        </is>
+      </c>
+      <c r="B330" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C330" s="17" t="inlineStr">
+        <is>
+          <t>WDT Engineers expands capability across Brisbane and Mackay workshops (01/01/2024)
+WDT Engineers highlights its ongoing operational scale and project capability across its Brisbane and Mackay facilities, including full-scope design, manufacturing, and construction services for major industrial projects. This indicates business expansion and sustained growth in capacity.
+WDT Engineers continues to invest in full turnkey engineering services (01/01/2024)
+The company’s engineering page states that WDT supports projects from concept to completion with over 40 years of mechanical and materials handling experience. The emphasis on turnkey delivery and broad capability suggests service-line growth and strengthened market position.
+WDT Engineers reports long-term growth since incorporation in 1970 (01/01/2024)
+WDT describes itself as having grown steadily in knowledge and expertise since being incorporated in 1970, building a reputation as a reliable supplier to industry. This reflects sustained organic growth and long-term business success.</t>
+        </is>
+      </c>
+      <c r="D330" s="17" t="inlineStr"/>
+      <c r="E330" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wdtengineers/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="16" t="inlineStr">
+        <is>
+          <t>WHS Systems (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C331" s="17" t="inlineStr"/>
+      <c r="D331" s="17" t="inlineStr"/>
+      <c r="E331" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whssystems/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="16" t="inlineStr">
+        <is>
+          <t>Wageloch</t>
+        </is>
+      </c>
+      <c r="B332" s="16" t="inlineStr">
+        <is>
+          <t>Adelaide</t>
+        </is>
+      </c>
+      <c r="C332" s="17" t="inlineStr">
+        <is>
+          <t>Wageloch reinforces long‑term growth strategy with Australian and New Zealand expansion focus (01/07/2024)
+Wageloch highlights continuing business growth after more than 14 years in operation, with founder Phillip van Mourik and a long‑standing leadership team reaffirming their commitment to scaling the business. The company emphasises its expansion from an Adelaide base to serving clients across Australia and into New Zealand, positioning its all‑in‑one rostering and payroll platform as a key driver of that growth. The focus on a dedicated Australian support team and clear company values is presented as central to attracting and retaining a growing client base in the business support services sector.
+Wageloch builds profile as an industry resource with expanded newsroom and compliance coverage (15/03/2024)
+Through its online newsroom and industry news category, Wageloch has increased its visibility and influence in the workforce management space by regularly publishing articles on award changes, Fair Work Commission decisions, and payroll compliance updates. This ongoing content investment suggests a growth strategy focused on strengthening brand authority, supporting an expanding customer base that relies on Wageloch for up‑to‑date guidance on rostering, wage, and payroll issues.</t>
+        </is>
+      </c>
+      <c r="D332" s="17" t="inlineStr">
+        <is>
+          <t>[24/04/2026 - 4w] Highlights participation in the AUR Conference and showcases the company's platform, emphasizing connections and support for independent retailers.</t>
+        </is>
+      </c>
+      <c r="E332" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wageloch/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="16" t="inlineStr">
+        <is>
+          <t>Webstercare</t>
+        </is>
+      </c>
+      <c r="B333" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C333" s="17" t="inlineStr">
+        <is>
+          <t>Webstercare expands medication management portfolio to more than 600 products and services (01/06/2022)
+Webstercare reports having developed more than 600 products and services focused on medication management, spanning pharmacy, aged care, community and health sectors, and including innovations supporting Aboriginal and Torres Strait Islander communities. This expanded portfolio, built around solutions such as Webster‑pak and associated software, indicates sustained product development and market broadening within aged care and medication adherence services.
+Webstercare grows as a leading Australian medication management specialist with Webster‑pak and electronic compliance solutions (15/03/2021)
+Webstercare, headquartered in Leichhardt, NSW, continues to position itself as a leading medication management specialist in Australia, with its flagship Webster‑pak systems widely used in aged care and community settings. The company has also rolled out electronic medication compliance solutions that connect the care team in real time via a centralised profile, reflecting ongoing investment in digital tools and reinforcing its role in the aged care medication management market.
+Australian Digital Health Agency and Webstercare launch Pharmacist Shared Medicines List in My Health Record (11/10/2019)
+The Australian Digital Health Agency partnered with Webstercare to launch the Pharmacist Shared Medicines List (PSML) within My Health Record. The PSML is a consolidated medicines list prepared and uploaded by pharmacists, covering prescription, over‑the‑counter, and complementary medicines with usage instructions. This collaboration embeds Webstercare’s medication-management capability directly into the national digital health infrastructure and is being integrated into pharmacy systems across Australia, extending Webstercare’s reach and influence in aged care and community care medication safety.
+Webstercare founder Gerard Stevens appointed a Member of the Order of Australia for pharmaceutical industry contributions (26/01/2019)
+Webstercare founder Gerard Stevens was appointed a Member (AM) of the Order of Australia for his service to the pharmaceutical industry and medication management. The honour recognises decades of innovation, including the Webster‑pak and related systems that are widely used in aged care, community, and pharmacy settings. This national honour reinforced Webstercare’s profile and credibility as a leading Australian provider of medication management solutions, supporting continued growth and uptake of its products.
+Webstercare ranked 6th in BRW 50 Most Innovative Companies list for MedsPro System (15/08/2013)
+Webstercare was named Australia’s sixth most innovative company in the Business Review Weekly (BRW) 50 Most Innovative Companies survey. The recognition focused on its MedsPro System, which uses virtual pill count technology and barcode scanning to identify patients, check medication packing, and automate ordering and restocking for pharmacies and aged care facilities. This national innovation award highlighted Webstercare’s leadership in medication management technology and supported further commercial adoption of its systems.</t>
+        </is>
+      </c>
+      <c r="D333" s="17" t="inlineStr"/>
+      <c r="E333" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/webstercare/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="16" t="inlineStr">
+        <is>
+          <t>Wilhelm Integrated Solutions (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B334" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C334" s="17" t="inlineStr">
+        <is>
+          <t>Wilhelm Integrated Solutions and Hilti Australia announce strategic collaboration in modular hospital construction (03/12/2025)
+Wilhelm Integrated Solutions, a Sydney‑based, family‑owned healthcare construction and technology company, entered a strategic collaboration with Hilti Australia to deliver modular ceiling support systems for hospital projects nationwide. The partnership leverages Wilhelm’s expertise in modular operating rooms, critical care spaces, and infection‑control solutions together with Hilti’s structural systems, aiming to accelerate project delivery and improve sustainability and clinical outcomes in Australian hospitals. This marks a significant partnership‑driven growth step for Wilhelm as it scales its modular healthcare infrastructure offering across Australia.
+Wilhelm Integrated Solutions expands into Western Australia, recruiting healthcare service engineer (15/04/2025)
+Wilhelm Integrated Solutions announced its expansion into Western Australia, signalling geographic growth beyond its established east‑coast hospital projects. As part of this move, the company is hiring a Healthcare Service Engineer to support a growing portfolio of hospital technology and infrastructure solutions. The role will provide on‑the‑ground technical support for Wilhelm’s modular operating theatres, bedheads, clean air delivery systems, and other integrated clinical technologies, reflecting increasing demand for its solutions from hospitals in the WA market.
+Wilhelm Integrated Solutions ramps up hiring amid rapid growth in modular operating room and critical care projects (10/02/2025)
+Wilhelm Integrated Solutions highlighted rapid business growth and an expanding customer base among major Australian and New Zealand hospitals as it opened recruitment for multiple roles, including product marketing positions. The company, a leader in modular design and construction for operating rooms and critical care units, is increasing headcount to support demand for its integrated digital ORs, modular bedheads, and infection‑control infrastructure. The hiring drive underscores Wilhelm’s sustained growth trajectory in the hospital technology and construction sector.</t>
+        </is>
+      </c>
+      <c r="D334" s="17" t="inlineStr">
+        <is>
+          <t>[19/05/2026 - 3d] Hospitals are increasingly trusting Wilhelm, suggesting potential business expansion.
+[12/05/2026 - 1w] Focus on hospital efficiencies and improvements through digital solutions, suggesting innovation and potential growth.
+[06/05/2026 - 2w] Promotion of radiation safety solutions indicating innovation and market positioning in healthcare.
+[06/05/2026 - 2w] Successful partnership with a hospital for complex installations indicates business growth and client acquisition.</t>
+        </is>
+      </c>
+      <c r="E334" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wilhelm-integrated-solutions-pty-ltd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="16" t="inlineStr">
+        <is>
+          <t>Williams Logistics (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B335" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C335" s="17" t="inlineStr">
+        <is>
+          <t>Williams Logistics becomes Australia’s first B Corp-certified 3PL, positioning for sustainable growth (15/03/2024)
+Williams Logistics, a Sydney-based third‑party logistics provider, has been certified as Australia’s first B Corp 3PL. The company highlights this milestone as part of a broader growth strategy focused on sustainable, tech‑driven fulfilment for retail and eCommerce brands. In an advertorial feature, Williams notes that its infrastructure has scaled alongside clients that expanded from four to more than 90 stores, and it continues to invest in systems and processes to support omnichannel growth for brands such as MJ Bale, Faithfull the Brand and Napoleon Perdis.
+Williams Logistics outlines growth focus and expanded retail/eCommerce fulfilment offering (20/02/2024)
+On its corporate site, Williams Logistics presents itself as one of Australia’s leading specialist 3PL providers, with over 40 years of experience in warehousing, distribution, e‑commerce fulfilment, inventory management and related services. The company emphasises that its service suite is designed to support client growth, streamline operations and enhance customer experience, and invites brands to engage for tailored solutions — signalling an ongoing expansion focus around eCommerce, omnichannel fulfilment and value‑added logistics services from its Sydney base.
+Williams Logistics shares updates on B Corp journey and sustainability‑driven growth (11/04/2023)
+Through its ‘Latest News’ section, Williams Logistics reports on its B Corp journey and related sustainability initiatives, framing them as integral to its long‑term growth strategy. The company discusses investing in more responsible fulfilment practices and industry innovation to attract and retain leading Australian retail brands, thereby strengthening its position in the competitive 3PL and eCommerce fulfilment market.</t>
+        </is>
+      </c>
+      <c r="D335" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Collaboration with Serena Williams and Reckitt aimed at supporting underrepresented founders.
+[27/04/2026 - 3w] LinkedIn being the most cited domain for professional queries indicates business strength and visibility.
+[22/04/2026 - 1mo] Promoting new leadership roles at LinkedIn, indicating potential future growth and opportunity.</t>
+        </is>
+      </c>
+      <c r="E335" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="16" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="B336" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C336" s="17" t="inlineStr">
+        <is>
+          <t>WorkBuddy: Job Management and Field Service Management Software for Trades (01/01/2026)
+WorkBuddy is presented as a cloud-based job management and field service management platform for trade and field service businesses, with messaging focused on helping customers streamline operations and reach new heights. This indicates ongoing business development and product growth for the Sydney-based software company.</t>
+        </is>
+      </c>
+      <c r="D336" s="17" t="inlineStr"/>
+      <c r="E336" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/workbuddyapp/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="16" t="inlineStr">
+        <is>
+          <t>Xylo Systems</t>
+        </is>
+      </c>
+      <c r="B337" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C337" s="17" t="inlineStr">
+        <is>
+          <t>Xylo Systems and EnviroDNA team up to make biodiversity tracking as easy as carbon reporting (14/02/2025)
+Sydney-based Xylo Systems formed a first-of-its-kind collaboration with Melbourne-based EnviroDNA, integrating Xylo’s AI-driven biodiversity assessment platform with EnviroDNA’s environmental DNA (eDNA) field monitoring. The partnership aims to make biodiversity measurement and reporting as streamlined and data-driven as carbon reporting, and will use EnviroDNA’s real-world data to ‘ground truth’ Xylo’s models. This represents a significant strategic expansion of Xylo’s product capability and market offering across biodiversity measurement and reporting services.
+Xylo Systems expands AI-powered biodiversity intelligence platform usage across multiple countries (01/02/2025)
+According to company materials, Xylo Systems has expanded its cloud-based biodiversity intelligence platform to operate across six countries and has completed more than 57 biodiversity assessments covering 122 square kilometres of land. The platform streamlines biodiversity impact data collection, analysis and reporting for sectors such as property development and energy, indicating both geographic expansion and increased adoption of its software-as-a-service offering.
+Xylo Systems secures pre-seed funding to scale biodiversity management software (01/06/2023)
+Xylo Systems, a Sydney-based biodiversity intelligence software company serving property development and energy industries, has raised a total of US$200,000 in pre-seed funding, including a latest round of approximately US$50,000. Investors include Investible, Startmate and Taronga Conservation Society Australia. The funding supports the company’s early-stage growth, product development and go-to-market activities in environmental consulting and biodiversity management.</t>
+        </is>
+      </c>
+      <c r="D337" s="17" t="inlineStr"/>
+      <c r="E337" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/xylo-systems/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="16" t="inlineStr">
+        <is>
+          <t>Yaktrak</t>
+        </is>
+      </c>
+      <c r="B338" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C338" s="17" t="inlineStr"/>
+      <c r="D338" s="17" t="inlineStr"/>
+      <c r="E338" s="16" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="16" t="inlineStr">
+        <is>
+          <t>Yarris Technologies</t>
+        </is>
+      </c>
+      <c r="B339" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C339" s="17" t="inlineStr">
+        <is>
+          <t>Yarris Technologies draws exceptional interest in software industry, signalling strong growth momentum (15/03/2026)
+Business‑intelligence platform ZoomInfo reports that Yarris Technologies is attracting "exceptional interest" within the software industry, suggesting notable developments and strong market momentum for the Melbourne‑based workflow‑management provider. While the listing does not disclose financials, the spike in engagement and profile activity is flagged as consistent with companies experiencing growth in customer acquisition, partnerships or product rollout.
+Steven Leong appointed Chief Financial Officer and Head of Strategy at Yarris Technologies (10/11/2023)
+The Australian Malaysian Business Council (Victoria) profiles Steven Leong as Chief Financial Officer and Head of Strategy at Yarris Technologies, confirming his senior leadership role at the Melbourne software company. The combined CFO and strategy appointment indicates Yarris is strengthening its executive team to support scaling activities, capital management and long‑term growth planning for its digital workflow platforms.
+Yarris Technologies highlighted by Technology Council of Australia for complex workflow solutions (01/09/2021)
+In its national "Roadmap to Deliver One Million Tech Jobs" report, the Technology Council of Australia cites Yarris Technologies as a provider of a suite of products designed to manage complex business workflow processes. Inclusion in this industry roadmap positions the Melbourne‑based company as a notable contributor to Australia’s tech ecosystem, supporting future employment growth and signalling recognition of its expanding role in enterprise and government digital transformation projects.</t>
+        </is>
+      </c>
+      <c r="D339" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Mentions a partnership with Serena Williams and Reckitt to leverage networks for business opportunities.
+[27/04/2026 - 3w] Recognizes LinkedIn's top citation status in AI queries, indicating market growth.
+[22/04/2026 - 1mo] Announces new leadership roles within LinkedIn, suggesting organizational growth.</t>
+        </is>
+      </c>
+      <c r="E339" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="16" t="inlineStr">
+        <is>
+          <t>Zanda Health</t>
+        </is>
+      </c>
+      <c r="B340" s="16" t="inlineStr">
+        <is>
+          <t>Ballarat</t>
+        </is>
+      </c>
+      <c r="C340" s="17" t="inlineStr">
+        <is>
+          <t>Zanda Health Revenue 2025: $6.5M ARR, $19.5M Valuation (01/01/2025)
+Latka reports that Zanda Health reached $6.5M in revenue in 2025, highlighting consistent growth since its 2010 launch and describing the business as bootstrapped with no outside funding.
+About Us | Practice Management Software - Zanda Health (01/01/2024)
+Zanda states that its practice management system is used by health practices in 23+ countries, indicating international expansion and broader market adoption.
+Zanda Health Company Overview, Contact Details &amp; Competitors (01/01/2024)
+LeadIQ notes recent major launches such as the Practice Dashboard and BizzyAI, suggesting active product expansion and continued development at Zanda Health.</t>
+        </is>
+      </c>
+      <c r="D340" s="17" t="inlineStr">
+        <is>
+          <t>[13/05/2026 - 1w] Damien Adler nominated for Allied Health Awards, showcasing recognition of Zanda Health's contributions.
+[25/04/2026 - 3w] Interview featuring Damien Adler discussing Zanda's growth and insights.
+[24/04/2026 - 4w] In-depth interview with co-founder Damien Adler discussing the origins and growth of Zanda, addressing challenges faced.</t>
+        </is>
+      </c>
+      <c r="E340" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/zandahealth/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="16" t="inlineStr">
+        <is>
+          <t>Zap (Zap Fitness, Melbourne, VIC, Australia)</t>
+        </is>
+      </c>
+      <c r="B341" s="16" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C341" s="17" t="inlineStr">
+        <is>
+          <t>Val Morgan Outdoor renews multi‑year media partnership with Fitness &amp; Lifestyle Group covering 87 Zap Fitness gyms (12/03/2024)
+Val Morgan Outdoor (VMO) renewed its partnership with Fitness &amp; Lifestyle Group, securing a multi‑year agreement to remain the exclusive outdoor media partner across 97 Goodlife Health Clubs, 50 Fitness First locations and 87 Zap Fitness gyms nationally. For Zap Fitness in Melbourne, this signals continued investment in its gym network and in‑club digital media, supporting revenue growth and reinforcing Zap’s position as part of a large, commercially attractive fitness portfolio.
+Zap Fitness expands Melbourne footprint to more than a dozen 24/7 gyms across inner‑city, northern, south‑east and south‑west suburbs (15/09/2023)
+Zap Fitness, now part of Fitness &amp; Lifestyle Group, has grown its Melbourne presence to a broad network of 24/7 clubs spanning inner‑city locations such as Carlton, Elsternwick, Flemington, Hawthorn and St Kilda, as well as northern, south‑east and south‑west suburbs including Reservoir, Northcote, Carnegie, Clyde North, Tarneit and Williams Landing. The expanded list of clubs on Zap’s Melbourne locations page highlights sustained site roll‑out and network density, improving convenience for members and signalling ongoing investment in the Victorian market.
+Fitness &amp; Lifestyle Group acquisition of Zap Fitness underpins continued expansion of Zap gyms in Melbourne and Tasmania (08/02/2017)
+Fitness &amp; Lifestyle Group announced the acquisition of Tasmanian‑based Zap Fitness, adding 37 24/7 gyms to its portfolio, including 13 in Melbourne and one in Adelaide (at the time of the deal). The acquisition placed Zap within one of the largest health club groups in the Asia‑Pacific region, providing capital, brand support and operational scale that have since enabled ongoing expansion of Zap’s Melbourne footprint across inner‑city, northern, south‑east and south‑west suburbs.</t>
+        </is>
+      </c>
+      <c r="D341" s="17" t="inlineStr"/>
+      <c r="E341" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/zapfitness/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="16" t="inlineStr">
+        <is>
+          <t>Zzoota</t>
+        </is>
+      </c>
+      <c r="B342" s="16" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="C342" s="17" t="inlineStr"/>
+      <c r="D342" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announces collaboration with Serena Williams and Reckitt, emphasizing network improvement for founders.
+[27/04/2026 - 3w] Reports LinkedIn is the most-cited domain for professional queries, indicating market leadership.
+[22/04/2026 - 1mo] Congratulates new CEO and President roles at LinkedIn, indicating strong leadership and positive prospects.</t>
+        </is>
+      </c>
+      <c r="E342" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="16" t="inlineStr">
+        <is>
+          <t>x-RD</t>
+        </is>
+      </c>
+      <c r="B343" s="16" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
+      <c r="C343" s="17" t="inlineStr">
+        <is>
+          <t>x-RD grows to support defence, national security, government and private sector clients (01/06/2025)
+x-RD reported that after six years it had grown into an award-winning managed IT services company serving defence, national security, government, and private sector customers, indicating business expansion and sustained growth.
+x-RD named a finalist in the 2024 Defence &amp; National Security Innovation Awards (14/11/2024)
+x-RD was recognised as a finalist in a major defence and national security awards program, highlighting the company’s continued growth and credibility in secure software, AI, and cyber security delivery for high-compliance sectors.
+x-RD launches secd3v SaaS platform for government, defence and high-compliance customers (01/10/2024)
+The company expanded its product offering by launching its secd3v SaaS platform, which supports enterprise GitLab Platform services, GitLab Duo services, and an AI assistant for government, defence industry, and other high-compliance customers.
+x-RD recognised by Canberra Cyber Hub as a leader in DevSecOps and AI-enabled software development (01/09/2024)
+Canberra Cyber Hub profiled x-RD as a growing cyber business and described it as a leader in DevSecOps and AI-enabled software development in secure environments, noting partnerships with GitLab Select and Chainguard.
+Canberra Cyber Hub highlights x-RD as a cyber startup building leading-edge security solutions (01/09/2024)
+A Canberra Cyber Hub feature described x-RD as a specialist in cyber security solutions using AI and automation, supporting visibility and growth for the Canberra-based company in the local cyber ecosystem.</t>
+        </is>
+      </c>
+      <c r="D343" s="17" t="inlineStr"/>
+      <c r="E343" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/x-rd/posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="16" t="inlineStr">
+        <is>
+          <t>youX (Sydney, Australia)</t>
+        </is>
+      </c>
+      <c r="B344" s="16" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C344" s="17" t="inlineStr">
+        <is>
+          <t>youX appoints Matt Perry as Chief Commercial Officer to drive commercial expansion (18/02/2026)
+Sydney-based asset finance fintech youX, which provides digital finance technology to lenders, brokers and dealers, has re-appointed Matt Perry—formerly Pepper Money’s head of asset finance product—as its Chief Commercial Officer. The move is aimed at strengthening youX’s commercial strategy and growth across its network of OEM-branded lenders and finance partners.</t>
+        </is>
+      </c>
+      <c r="D344" s="17" t="inlineStr">
+        <is>
+          <t>[07/05/2026 - 2w] Announcement of a partnership with Serena Williams and Reckitt emphasizing network leverage for business growth.
+[27/04/2026 - 3w] LinkedIn being recognized as the top domain for professional queries, indicating market success.
+[24/04/2026 - 4w] Congratulations to Fernando Mendoza, suggesting a significant achievement or new role.
+[22/04/2026 - 1mo] Congratulations to new leadership roles within LinkedIn, indicating internal growth and future opportunities.</t>
+        </is>
+      </c>
+      <c r="E344" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/linkedin/posts/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
